--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="579" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0354CB33-FBFD-5346-8C20-368C96E91644}"/>
+  <xr:revisionPtr revIDLastSave="593" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEDFFF89-2C16-464A-9512-D8854BC6F4E1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5599" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5633" uniqueCount="1168">
   <si>
     <t>Id</t>
   </si>
@@ -3522,13 +3522,31 @@
   </si>
   <si>
     <t>Sierra Club magazine story on Port Everglades dredging, with interview from me</t>
+  </si>
+  <si>
+    <t>Career chat for After School Matters</t>
+  </si>
+  <si>
+    <t>AQSCI teachers conference - lecture on migratory fishes program request from L&amp;C</t>
+  </si>
+  <si>
+    <t>Barraza, J. E., Melara, V., Quintana, Y., Knapp, C. R., &amp; Inoue, K. (2026). New records of freshwater mussels (Unionida, Mycetopodidae and Unionidae) from rivers, lakes, and lagoons in El Salvador, with notes on the expansion of invasive mollusc species. Check List, 22(4), 618–629. https://doi.org/10.15560/22.4.618</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.15560/22.4.618</t>
+  </si>
+  <si>
+    <t>Conducted field sampling for freshwater mussels in southeastern Missouri with Lauren Western, a master's student at Central Michigan University.</t>
+  </si>
+  <si>
+    <t>Presentation on Central American freshwater mussels (title: Facilitating freshwater mussel conservation through partnership and collaboration).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3644,8 +3662,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W795" totalsRowShown="0">
-  <autoFilter ref="A1:W795" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W800" totalsRowShown="0">
+  <autoFilter ref="A1:W800" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W744">
     <sortCondition ref="B1:B744"/>
   </sortState>
@@ -3815,7 +3833,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="801" latestEventMarker="839">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="806" latestEventMarker="844">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4142,21 +4160,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W795"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W800"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
     <col min="12" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="52.6640625" customWidth="1"/>
-    <col min="16" max="16" width="48.5" customWidth="1"/>
-    <col min="17" max="17" width="46.83203125" customWidth="1"/>
-    <col min="18" max="18" width="50.33203125" customWidth="1"/>
+    <col min="15" max="15" width="52.7109375" customWidth="1"/>
+    <col min="16" max="16" width="48.42578125" customWidth="1"/>
+    <col min="17" max="17" width="46.85546875" customWidth="1"/>
+    <col min="18" max="18" width="50.28515625" customWidth="1"/>
     <col min="21" max="21" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4227,7 +4245,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4265,7 +4283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4300,7 +4318,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4335,7 +4353,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4370,7 +4388,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4405,7 +4423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4440,7 +4458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4475,7 +4493,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4510,7 +4528,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4545,7 +4563,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4580,7 +4598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4618,7 +4636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4656,7 +4674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4694,7 +4712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4732,7 +4750,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4770,7 +4788,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4808,7 +4826,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4843,7 +4861,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4878,7 +4896,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4916,7 +4934,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4951,7 +4969,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4989,7 +5007,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5024,7 +5042,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5065,7 +5083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5100,7 +5118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5135,7 +5153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5167,7 +5185,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5202,7 +5220,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5234,7 +5252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5272,7 +5290,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5313,7 +5331,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5351,7 +5369,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5392,7 +5410,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5433,7 +5451,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5474,7 +5492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5515,7 +5533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5556,7 +5574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5597,7 +5615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5632,7 +5650,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5667,7 +5685,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5702,7 +5720,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5737,7 +5755,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5775,7 +5793,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5813,7 +5831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5848,7 +5866,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5883,7 +5901,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5918,7 +5936,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5956,7 +5974,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5988,7 +6006,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6026,7 +6044,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6061,7 +6079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6093,7 +6111,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6131,7 +6149,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6166,7 +6184,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6201,7 +6219,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6239,7 +6257,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6277,7 +6295,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6315,7 +6333,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6353,7 +6371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6391,7 +6409,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6429,7 +6447,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23">
       <c r="A62">
         <v>67</v>
       </c>
@@ -6461,7 +6479,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6496,7 +6514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6534,7 +6552,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6572,7 +6590,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6607,7 +6625,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6642,7 +6660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23">
       <c r="A68">
         <v>66</v>
       </c>
@@ -6683,7 +6701,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6715,7 +6733,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6750,7 +6768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6785,7 +6803,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6823,7 +6841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6861,7 +6879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6902,7 +6920,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6943,7 +6961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6978,7 +6996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7016,7 +7034,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7057,7 +7075,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7092,7 +7110,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7133,7 +7151,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7171,7 +7189,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7209,7 +7227,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7247,7 +7265,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7288,7 +7306,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7326,7 +7344,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7367,7 +7385,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7399,7 +7417,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7431,7 +7449,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23">
       <c r="A89">
         <v>95</v>
       </c>
@@ -7469,7 +7487,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23">
       <c r="A90">
         <v>88</v>
       </c>
@@ -7510,7 +7528,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23">
       <c r="A91">
         <v>89</v>
       </c>
@@ -7545,7 +7563,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23">
       <c r="A92">
         <v>90</v>
       </c>
@@ -7580,7 +7598,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23">
       <c r="A93">
         <v>91</v>
       </c>
@@ -7615,7 +7633,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23">
       <c r="A94">
         <v>92</v>
       </c>
@@ -7656,7 +7674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23">
       <c r="A95">
         <v>93</v>
       </c>
@@ -7694,7 +7712,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23">
       <c r="A96">
         <v>94</v>
       </c>
@@ -7729,7 +7747,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7767,7 +7785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7802,7 +7820,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7840,7 +7858,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7875,7 +7893,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7910,7 +7928,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7950,7 +7968,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7990,7 +8008,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8030,7 +8048,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8104,7 +8122,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8141,7 +8159,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8178,7 +8196,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8215,7 +8233,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8250,7 +8268,7 @@
       </c>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8293,7 +8311,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8336,7 +8354,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8373,7 +8391,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:23">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8416,7 +8434,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8455,7 +8473,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8492,7 +8510,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8529,7 +8547,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8568,7 +8586,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8603,7 +8621,7 @@
       </c>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8641,7 +8659,7 @@
       </c>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8681,7 +8699,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8721,7 +8739,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8761,7 +8779,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8801,7 +8819,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8841,7 +8859,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8884,7 +8902,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8927,7 +8945,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8968,7 +8986,7 @@
       </c>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9009,7 +9027,7 @@
       </c>
       <c r="W129" s="3"/>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23">
       <c r="A130">
         <v>129</v>
       </c>
@@ -9052,7 +9070,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23">
       <c r="A131">
         <v>130</v>
       </c>
@@ -9089,7 +9107,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23">
       <c r="A132">
         <v>131</v>
       </c>
@@ -9126,7 +9144,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9163,7 +9181,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9206,7 +9224,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9246,7 +9264,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9286,7 +9304,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9325,7 +9343,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9364,7 +9382,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9407,7 +9425,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9447,7 +9465,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9486,7 +9504,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9525,7 +9543,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9564,7 +9582,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9604,7 +9622,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9647,7 +9665,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9686,7 +9704,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9723,7 +9741,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9760,7 +9778,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9797,7 +9815,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:23">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9840,7 +9858,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9883,7 +9901,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9922,7 +9940,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9961,7 +9979,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9998,7 +10016,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23">
       <c r="A155">
         <v>154</v>
       </c>
@@ -10037,7 +10055,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23">
       <c r="A156">
         <v>155</v>
       </c>
@@ -10077,7 +10095,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23">
       <c r="A157">
         <v>156</v>
       </c>
@@ -10117,7 +10135,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:23">
       <c r="A158">
         <v>157</v>
       </c>
@@ -10157,7 +10175,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23">
       <c r="A159">
         <v>158</v>
       </c>
@@ -10197,7 +10215,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23">
       <c r="A160">
         <v>159</v>
       </c>
@@ -10240,7 +10258,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23">
       <c r="A161">
         <v>160</v>
       </c>
@@ -10283,7 +10301,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23">
       <c r="A162">
         <v>161</v>
       </c>
@@ -10320,7 +10338,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23">
       <c r="A163">
         <v>162</v>
       </c>
@@ -10359,7 +10377,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23">
       <c r="A164">
         <v>163</v>
       </c>
@@ -10396,7 +10414,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23">
       <c r="A165">
         <v>164</v>
       </c>
@@ -10433,7 +10451,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23">
       <c r="A166">
         <v>165</v>
       </c>
@@ -10468,7 +10486,7 @@
       </c>
       <c r="W166" s="3"/>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23">
       <c r="A167">
         <v>166</v>
       </c>
@@ -10507,7 +10525,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23">
       <c r="A168">
         <v>167</v>
       </c>
@@ -10546,7 +10564,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23">
       <c r="A169">
         <v>168</v>
       </c>
@@ -10586,7 +10604,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:23">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10629,7 +10647,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:23">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10672,7 +10690,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:23">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10709,7 +10727,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:23">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10746,7 +10764,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:23">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10785,7 +10803,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:23">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10825,7 +10843,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:23">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10865,7 +10883,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10905,7 +10923,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10948,7 +10966,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10991,7 +11009,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11034,7 +11052,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11073,7 +11091,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23">
       <c r="A182">
         <v>182</v>
       </c>
@@ -11112,7 +11130,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23">
       <c r="A183">
         <v>183</v>
       </c>
@@ -11155,7 +11173,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:23">
       <c r="A184">
         <v>184</v>
       </c>
@@ -11192,7 +11210,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:23">
       <c r="A185">
         <v>185</v>
       </c>
@@ -11235,7 +11253,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23">
       <c r="A186">
         <v>186</v>
       </c>
@@ -11278,7 +11296,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:23">
       <c r="A187">
         <v>187</v>
       </c>
@@ -11315,7 +11333,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:23">
       <c r="A188">
         <v>188</v>
       </c>
@@ -11358,7 +11376,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:23">
       <c r="A189">
         <v>189</v>
       </c>
@@ -11401,7 +11419,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:23">
       <c r="A190">
         <v>190</v>
       </c>
@@ -11438,7 +11456,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:23">
       <c r="A191">
         <v>191</v>
       </c>
@@ -11481,7 +11499,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:23">
       <c r="A192">
         <v>192</v>
       </c>
@@ -11518,7 +11536,7 @@
       </c>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:23">
       <c r="A193">
         <v>193</v>
       </c>
@@ -11557,7 +11575,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:23">
       <c r="A194">
         <v>194</v>
       </c>
@@ -11596,7 +11614,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:23">
       <c r="A195">
         <v>195</v>
       </c>
@@ -11637,7 +11655,7 @@
       </c>
       <c r="W195" s="3"/>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:23">
       <c r="A196">
         <v>196</v>
       </c>
@@ -11676,7 +11694,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:23">
       <c r="A197">
         <v>197</v>
       </c>
@@ -11717,7 +11735,7 @@
       </c>
       <c r="W197" s="3"/>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:23">
       <c r="A198">
         <v>198</v>
       </c>
@@ -11758,7 +11776,7 @@
       </c>
       <c r="W198" s="3"/>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:23">
       <c r="A199">
         <v>199</v>
       </c>
@@ -11798,7 +11816,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:23">
       <c r="A200">
         <v>200</v>
       </c>
@@ -11835,7 +11853,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:23">
       <c r="A201">
         <v>201</v>
       </c>
@@ -11872,7 +11890,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:23">
       <c r="A202">
         <v>202</v>
       </c>
@@ -11909,7 +11927,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:23">
       <c r="A203">
         <v>223</v>
       </c>
@@ -11946,7 +11964,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:23">
       <c r="A204">
         <v>203</v>
       </c>
@@ -11983,7 +12001,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:23">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12023,7 +12041,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:23">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12058,7 +12076,7 @@
       </c>
       <c r="W206" s="3"/>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:23">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12097,7 +12115,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:23">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12136,7 +12154,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:23">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12176,7 +12194,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:23">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12211,7 +12229,7 @@
       </c>
       <c r="W210" s="3"/>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:23">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12249,7 +12267,7 @@
       </c>
       <c r="W211" s="3"/>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:23">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12287,7 +12305,7 @@
       </c>
       <c r="W212" s="3"/>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:23">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12325,7 +12343,7 @@
       </c>
       <c r="W213" s="3"/>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:23">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12362,7 +12380,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:23">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12397,7 +12415,7 @@
       </c>
       <c r="W215" s="3"/>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:23">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12432,7 +12450,7 @@
       </c>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:23">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12469,7 +12487,7 @@
       </c>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:23">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12506,7 +12524,7 @@
       </c>
       <c r="W218" s="3"/>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:23">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12545,7 +12563,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:23">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12582,7 +12600,7 @@
       </c>
       <c r="W220" s="3"/>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:23">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12621,7 +12639,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:23">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12662,7 +12680,7 @@
       </c>
       <c r="W222" s="3"/>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:23">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12702,7 +12720,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:23">
       <c r="A224">
         <v>224</v>
       </c>
@@ -12742,7 +12760,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:23">
       <c r="A225">
         <v>225</v>
       </c>
@@ -12785,7 +12803,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:23">
       <c r="A226">
         <v>226</v>
       </c>
@@ -12825,7 +12843,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:23">
       <c r="A227">
         <v>227</v>
       </c>
@@ -12865,7 +12883,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:23">
       <c r="A228">
         <v>228</v>
       </c>
@@ -12902,7 +12920,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:23">
       <c r="A229">
         <v>229</v>
       </c>
@@ -12945,7 +12963,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:23">
       <c r="A230">
         <v>230</v>
       </c>
@@ -12985,7 +13003,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:23">
       <c r="A231">
         <v>231</v>
       </c>
@@ -13025,7 +13043,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:23">
       <c r="A232">
         <v>232</v>
       </c>
@@ -13062,7 +13080,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:23">
       <c r="A233">
         <v>233</v>
       </c>
@@ -13105,7 +13123,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:23">
       <c r="A234">
         <v>234</v>
       </c>
@@ -13144,7 +13162,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:23">
       <c r="A235">
         <v>235</v>
       </c>
@@ -13183,7 +13201,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:23">
       <c r="A236">
         <v>236</v>
       </c>
@@ -13224,7 +13242,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:23">
       <c r="A237">
         <v>237</v>
       </c>
@@ -13261,7 +13279,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:23">
       <c r="A238">
         <v>238</v>
       </c>
@@ -13301,7 +13319,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:23">
       <c r="A239">
         <v>239</v>
       </c>
@@ -13341,7 +13359,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:23">
       <c r="A240">
         <v>240</v>
       </c>
@@ -13376,7 +13394,7 @@
       </c>
       <c r="W240" s="3"/>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:23">
       <c r="A241">
         <v>241</v>
       </c>
@@ -13411,7 +13429,7 @@
       </c>
       <c r="W241" s="3"/>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:23">
       <c r="A242">
         <v>242</v>
       </c>
@@ -13451,7 +13469,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:23">
       <c r="A243">
         <v>243</v>
       </c>
@@ -13486,7 +13504,7 @@
       </c>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:23">
       <c r="A244">
         <v>244</v>
       </c>
@@ -13525,7 +13543,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:23">
       <c r="A245">
         <v>246</v>
       </c>
@@ -13562,7 +13580,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:23">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13602,7 +13620,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:23">
       <c r="A247">
         <v>247</v>
       </c>
@@ -13642,7 +13660,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:23">
       <c r="A248">
         <v>248</v>
       </c>
@@ -13679,7 +13697,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:23">
       <c r="A249">
         <v>249</v>
       </c>
@@ -13718,7 +13736,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:23">
       <c r="A250">
         <v>251</v>
       </c>
@@ -13761,7 +13779,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:23">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13796,7 +13814,7 @@
       </c>
       <c r="W251" s="3"/>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:23">
       <c r="A252">
         <v>252</v>
       </c>
@@ -13837,7 +13855,7 @@
       </c>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:23">
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="3"/>
@@ -13851,7 +13869,7 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:23">
       <c r="A254">
         <v>256</v>
       </c>
@@ -13891,7 +13909,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:23">
       <c r="A255">
         <v>253</v>
       </c>
@@ -13928,7 +13946,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:23">
       <c r="A256">
         <v>255</v>
       </c>
@@ -13965,7 +13983,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:23">
       <c r="A257">
         <v>254</v>
       </c>
@@ -14002,7 +14020,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:23">
       <c r="A258">
         <v>257</v>
       </c>
@@ -14045,7 +14063,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:23">
       <c r="A259">
         <v>258</v>
       </c>
@@ -14082,7 +14100,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:23">
       <c r="A260">
         <v>259</v>
       </c>
@@ -14122,7 +14140,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:23">
       <c r="A261">
         <v>260</v>
       </c>
@@ -14162,7 +14180,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:23">
       <c r="A262">
         <v>261</v>
       </c>
@@ -14199,7 +14217,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:23">
       <c r="A263">
         <v>262</v>
       </c>
@@ -14239,7 +14257,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:23">
       <c r="A264">
         <v>263</v>
       </c>
@@ -14279,7 +14297,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:23">
       <c r="A265">
         <v>264</v>
       </c>
@@ -14319,7 +14337,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:23">
       <c r="A266">
         <v>265</v>
       </c>
@@ -14356,7 +14374,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:23">
       <c r="A267">
         <v>266</v>
       </c>
@@ -14396,7 +14414,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:23">
       <c r="A268">
         <v>267</v>
       </c>
@@ -14433,7 +14451,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:23">
       <c r="A269">
         <v>268</v>
       </c>
@@ -14470,7 +14488,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:23">
       <c r="A270">
         <v>269</v>
       </c>
@@ -14513,7 +14531,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:23">
       <c r="A271">
         <v>270</v>
       </c>
@@ -14552,7 +14570,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:23">
       <c r="A272">
         <v>271</v>
       </c>
@@ -14593,7 +14611,7 @@
       </c>
       <c r="W272" s="3"/>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:23">
       <c r="A273">
         <v>272</v>
       </c>
@@ -14636,7 +14654,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:23">
       <c r="A274">
         <v>276</v>
       </c>
@@ -14677,7 +14695,7 @@
       </c>
       <c r="W274" s="3"/>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:23">
       <c r="A275">
         <v>273</v>
       </c>
@@ -14720,7 +14738,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:23">
       <c r="A276">
         <v>274</v>
       </c>
@@ -14760,7 +14778,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:23">
       <c r="A277">
         <v>275</v>
       </c>
@@ -14800,7 +14818,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:23">
       <c r="A278">
         <v>277</v>
       </c>
@@ -14841,7 +14859,7 @@
       </c>
       <c r="W278" s="3"/>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:23">
       <c r="A279">
         <v>278</v>
       </c>
@@ -14876,7 +14894,7 @@
       </c>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:23">
       <c r="A280">
         <v>279</v>
       </c>
@@ -14914,7 +14932,7 @@
       </c>
       <c r="W280" s="3"/>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:23">
       <c r="A281">
         <v>280</v>
       </c>
@@ -14957,7 +14975,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:23">
       <c r="A282">
         <v>281</v>
       </c>
@@ -14997,7 +15015,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:23">
       <c r="A283">
         <v>282</v>
       </c>
@@ -15037,7 +15055,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:23">
       <c r="A284">
         <v>283</v>
       </c>
@@ -15077,7 +15095,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:23">
       <c r="A285">
         <v>284</v>
       </c>
@@ -15117,7 +15135,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:23">
       <c r="A286">
         <v>285</v>
       </c>
@@ -15154,7 +15172,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:23">
       <c r="A287">
         <v>286</v>
       </c>
@@ -15197,7 +15215,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:23">
       <c r="A288">
         <v>287</v>
       </c>
@@ -15234,7 +15252,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:23">
       <c r="A289">
         <v>288</v>
       </c>
@@ -15277,7 +15295,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:23">
       <c r="A290">
         <v>289</v>
       </c>
@@ -15317,7 +15335,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:23">
       <c r="A291">
         <v>290</v>
       </c>
@@ -15354,7 +15372,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:23">
       <c r="A292">
         <v>291</v>
       </c>
@@ -15397,7 +15415,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:23">
       <c r="A293">
         <v>292</v>
       </c>
@@ -15440,7 +15458,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:23">
       <c r="A294">
         <v>294</v>
       </c>
@@ -15479,7 +15497,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:23">
       <c r="A295">
         <v>293</v>
       </c>
@@ -15522,7 +15540,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:23">
       <c r="A296">
         <v>295</v>
       </c>
@@ -15559,7 +15577,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:23">
       <c r="A297">
         <v>296</v>
       </c>
@@ -15598,7 +15616,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:23">
       <c r="A298">
         <v>297</v>
       </c>
@@ -15637,7 +15655,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:23">
       <c r="A299">
         <v>298</v>
       </c>
@@ -15676,7 +15694,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:23">
       <c r="A300">
         <v>299</v>
       </c>
@@ -15715,7 +15733,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:23">
       <c r="A301">
         <v>300</v>
       </c>
@@ -15754,7 +15772,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:23">
       <c r="A302">
         <v>301</v>
       </c>
@@ -15793,7 +15811,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:23">
       <c r="A303">
         <v>302</v>
       </c>
@@ -15832,7 +15850,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:23">
       <c r="A304">
         <v>303</v>
       </c>
@@ -15871,7 +15889,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:23">
       <c r="A305">
         <v>304</v>
       </c>
@@ -15910,7 +15928,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:23">
       <c r="A306">
         <v>305</v>
       </c>
@@ -15949,7 +15967,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:23">
       <c r="A307">
         <v>306</v>
       </c>
@@ -15987,7 +16005,7 @@
       </c>
       <c r="W307" s="3"/>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:23">
       <c r="A308">
         <v>307</v>
       </c>
@@ -16026,7 +16044,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:23">
       <c r="A309">
         <v>308</v>
       </c>
@@ -16065,7 +16083,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23">
       <c r="A310">
         <v>309</v>
       </c>
@@ -16102,7 +16120,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23">
       <c r="A311">
         <v>310</v>
       </c>
@@ -16139,7 +16157,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:23">
       <c r="A312">
         <v>311</v>
       </c>
@@ -16176,7 +16194,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:23">
       <c r="A313">
         <v>312</v>
       </c>
@@ -16216,7 +16234,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:23">
       <c r="A314">
         <v>313</v>
       </c>
@@ -16253,7 +16271,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:23">
       <c r="A315">
         <v>314</v>
       </c>
@@ -16288,7 +16306,7 @@
       </c>
       <c r="W315" s="3"/>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:23">
       <c r="A316">
         <v>315</v>
       </c>
@@ -16325,7 +16343,7 @@
       </c>
       <c r="W316" s="3"/>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:23">
       <c r="A317">
         <v>316</v>
       </c>
@@ -16360,7 +16378,7 @@
       </c>
       <c r="W317" s="3"/>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:23">
       <c r="A318">
         <v>317</v>
       </c>
@@ -16397,7 +16415,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:23">
       <c r="A319">
         <v>318</v>
       </c>
@@ -16432,7 +16450,7 @@
       </c>
       <c r="W319" s="3"/>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:23">
       <c r="A320">
         <v>319</v>
       </c>
@@ -16471,7 +16489,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23">
       <c r="A321">
         <v>320</v>
       </c>
@@ -16506,7 +16524,7 @@
       </c>
       <c r="W321" s="3"/>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23">
       <c r="A322">
         <v>321</v>
       </c>
@@ -16543,7 +16561,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23">
       <c r="A323">
         <v>322</v>
       </c>
@@ -16580,7 +16598,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23">
       <c r="A324">
         <v>323</v>
       </c>
@@ -16617,7 +16635,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23">
       <c r="A325">
         <v>324</v>
       </c>
@@ -16656,7 +16674,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23">
       <c r="A326">
         <v>325</v>
       </c>
@@ -16693,7 +16711,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23">
       <c r="A327">
         <v>326</v>
       </c>
@@ -16732,7 +16750,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23">
       <c r="A328">
         <v>327</v>
       </c>
@@ -16767,7 +16785,7 @@
       </c>
       <c r="W328" s="3"/>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23">
       <c r="A329">
         <v>328</v>
       </c>
@@ -16802,7 +16820,7 @@
       </c>
       <c r="W329" s="3"/>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23">
       <c r="A330">
         <v>329</v>
       </c>
@@ -16837,7 +16855,7 @@
       </c>
       <c r="W330" s="3"/>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23">
       <c r="A331">
         <v>330</v>
       </c>
@@ -16872,7 +16890,7 @@
       </c>
       <c r="W331" s="3"/>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23">
       <c r="A332">
         <v>331</v>
       </c>
@@ -16907,7 +16925,7 @@
       </c>
       <c r="W332" s="3"/>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23">
       <c r="A333">
         <v>332</v>
       </c>
@@ -16946,7 +16964,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23">
       <c r="A334">
         <v>333</v>
       </c>
@@ -16983,7 +17001,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23">
       <c r="A335">
         <v>334</v>
       </c>
@@ -17023,7 +17041,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23">
       <c r="A336">
         <v>335</v>
       </c>
@@ -17062,7 +17080,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:23">
       <c r="A337">
         <v>336</v>
       </c>
@@ -17099,7 +17117,7 @@
       </c>
       <c r="W337" s="3"/>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:23">
       <c r="A338">
         <v>337</v>
       </c>
@@ -17136,7 +17154,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:23">
       <c r="A339">
         <v>338</v>
       </c>
@@ -17173,7 +17191,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:23">
       <c r="A340">
         <v>339</v>
       </c>
@@ -17210,7 +17228,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:23">
       <c r="A341">
         <v>340</v>
       </c>
@@ -17247,7 +17265,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:23">
       <c r="A342">
         <v>341</v>
       </c>
@@ -17290,7 +17308,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:23">
       <c r="A343">
         <v>342</v>
       </c>
@@ -17327,7 +17345,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:23">
       <c r="A344">
         <v>343</v>
       </c>
@@ -17362,7 +17380,7 @@
       </c>
       <c r="W344" s="3"/>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:23">
       <c r="A345">
         <v>344</v>
       </c>
@@ -17403,7 +17421,7 @@
       </c>
       <c r="W345" s="3"/>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:23">
       <c r="A346">
         <v>345</v>
       </c>
@@ -17446,7 +17464,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:23">
       <c r="A347">
         <v>346</v>
       </c>
@@ -17489,7 +17507,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:23">
       <c r="A348">
         <v>347</v>
       </c>
@@ -17528,7 +17546,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:23">
       <c r="A349">
         <v>348</v>
       </c>
@@ -17571,7 +17589,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:23">
       <c r="A350">
         <v>349</v>
       </c>
@@ -17608,7 +17626,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:23">
       <c r="A351">
         <v>350</v>
       </c>
@@ -17648,7 +17666,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:23">
       <c r="A352">
         <v>351</v>
       </c>
@@ -17683,7 +17701,7 @@
       </c>
       <c r="W352" s="3"/>
     </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:23">
       <c r="A353">
         <v>352</v>
       </c>
@@ -17726,7 +17744,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:23">
       <c r="A354">
         <v>353</v>
       </c>
@@ -17763,7 +17781,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:23">
       <c r="A355">
         <v>354</v>
       </c>
@@ -17802,7 +17820,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:23">
       <c r="A356">
         <v>355</v>
       </c>
@@ -17839,7 +17857,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:23">
       <c r="A357">
         <v>356</v>
       </c>
@@ -17876,7 +17894,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="358" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:23">
       <c r="A358">
         <v>357</v>
       </c>
@@ -17915,7 +17933,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:23">
       <c r="A359">
         <v>358</v>
       </c>
@@ -17954,7 +17972,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:23">
       <c r="A360">
         <v>359</v>
       </c>
@@ -17994,7 +18012,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:23">
       <c r="A361">
         <v>360</v>
       </c>
@@ -18037,7 +18055,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:23">
       <c r="A362">
         <v>361</v>
       </c>
@@ -18074,7 +18092,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:23">
       <c r="A363">
         <v>362</v>
       </c>
@@ -18113,7 +18131,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:23">
       <c r="A364">
         <v>363</v>
       </c>
@@ -18152,7 +18170,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:23">
       <c r="A365">
         <v>364</v>
       </c>
@@ -18189,7 +18207,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:23">
       <c r="A366">
         <v>365</v>
       </c>
@@ -18228,7 +18246,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:23">
       <c r="A367">
         <v>366</v>
       </c>
@@ -18267,7 +18285,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:23">
       <c r="A368">
         <v>367</v>
       </c>
@@ -18304,7 +18322,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:23">
       <c r="A369">
         <v>368</v>
       </c>
@@ -18341,7 +18359,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:23">
       <c r="A370">
         <v>369</v>
       </c>
@@ -18378,7 +18396,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:23">
       <c r="A371">
         <v>370</v>
       </c>
@@ -18421,7 +18439,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:23">
       <c r="A372">
         <v>371</v>
       </c>
@@ -18458,7 +18476,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:23">
       <c r="A373">
         <v>372</v>
       </c>
@@ -18495,7 +18513,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:23">
       <c r="A374">
         <v>373</v>
       </c>
@@ -18538,7 +18556,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="375" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:23">
       <c r="A375">
         <v>374</v>
       </c>
@@ -18575,7 +18593,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="376" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:23">
       <c r="A376">
         <v>375</v>
       </c>
@@ -18618,7 +18636,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:23">
       <c r="A377">
         <v>376</v>
       </c>
@@ -18658,7 +18676,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:23">
       <c r="A378">
         <v>377</v>
       </c>
@@ -18695,7 +18713,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:23">
       <c r="A379">
         <v>378</v>
       </c>
@@ -18732,7 +18750,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:23">
       <c r="A380">
         <v>379</v>
       </c>
@@ -18769,7 +18787,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:23">
       <c r="A381">
         <v>380</v>
       </c>
@@ -18809,7 +18827,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:23">
       <c r="A382">
         <v>381</v>
       </c>
@@ -18849,7 +18867,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="383" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:23">
       <c r="A383">
         <v>382</v>
       </c>
@@ -18886,7 +18904,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="384" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:23">
       <c r="A384">
         <v>383</v>
       </c>
@@ -18925,7 +18943,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:23">
       <c r="A385">
         <v>384</v>
       </c>
@@ -18964,7 +18982,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:23">
       <c r="A386">
         <v>385</v>
       </c>
@@ -19003,7 +19021,7 @@
       </c>
       <c r="W386" s="3"/>
     </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:23">
       <c r="A387">
         <v>386</v>
       </c>
@@ -19042,7 +19060,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:23">
       <c r="A388">
         <v>387</v>
       </c>
@@ -19082,7 +19100,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:23">
       <c r="A389">
         <v>388</v>
       </c>
@@ -19122,7 +19140,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:23">
       <c r="A390">
         <v>389</v>
       </c>
@@ -19163,7 +19181,7 @@
       </c>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:23">
       <c r="A391">
         <v>390</v>
       </c>
@@ -19204,7 +19222,7 @@
       </c>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:23">
       <c r="A392">
         <v>391</v>
       </c>
@@ -19245,7 +19263,7 @@
       </c>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:23">
       <c r="A393">
         <v>392</v>
       </c>
@@ -19286,7 +19304,7 @@
       </c>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:23">
       <c r="A394">
         <v>393</v>
       </c>
@@ -19323,7 +19341,7 @@
       </c>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:23">
       <c r="A395">
         <v>394</v>
       </c>
@@ -19358,7 +19376,7 @@
       </c>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:23">
       <c r="A396">
         <v>395</v>
       </c>
@@ -19395,7 +19413,7 @@
       </c>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:23">
       <c r="A397">
         <v>396</v>
       </c>
@@ -19430,7 +19448,7 @@
       </c>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:23">
       <c r="A398">
         <v>397</v>
       </c>
@@ -19465,7 +19483,7 @@
       </c>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:23">
       <c r="A399">
         <v>398</v>
       </c>
@@ -19500,7 +19518,7 @@
       </c>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:23">
       <c r="A400">
         <v>399</v>
       </c>
@@ -19535,7 +19553,7 @@
       </c>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:23">
       <c r="A401">
         <v>400</v>
       </c>
@@ -19576,7 +19594,7 @@
       </c>
       <c r="W401" s="3"/>
     </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:23">
       <c r="A402">
         <v>401</v>
       </c>
@@ -19615,7 +19633,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:23">
       <c r="A403">
         <v>402</v>
       </c>
@@ -19654,7 +19672,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:23">
       <c r="A404">
         <v>403</v>
       </c>
@@ -19697,7 +19715,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:23">
       <c r="A405">
         <v>404</v>
       </c>
@@ -19740,7 +19758,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:23">
       <c r="A406">
         <v>405</v>
       </c>
@@ -19783,7 +19801,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="407" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:23">
       <c r="A407">
         <v>406</v>
       </c>
@@ -19820,7 +19838,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="408" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:23">
       <c r="A408">
         <v>407</v>
       </c>
@@ -19863,7 +19881,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="409" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:23">
       <c r="A409">
         <v>408</v>
       </c>
@@ -19906,7 +19924,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="410" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:23">
       <c r="A410">
         <v>409</v>
       </c>
@@ -19949,7 +19967,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="411" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:23">
       <c r="A411">
         <v>410</v>
       </c>
@@ -19988,7 +20006,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:23">
       <c r="A412">
         <v>411</v>
       </c>
@@ -20027,7 +20045,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:23">
       <c r="A413">
         <v>412</v>
       </c>
@@ -20062,7 +20080,7 @@
       </c>
       <c r="W413" s="3"/>
     </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:23">
       <c r="A414">
         <v>413</v>
       </c>
@@ -20101,7 +20119,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:23">
       <c r="A415">
         <v>414</v>
       </c>
@@ -20144,7 +20162,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="416" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:23">
       <c r="A416">
         <v>415</v>
       </c>
@@ -20183,7 +20201,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="417" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:23">
       <c r="A417">
         <v>416</v>
       </c>
@@ -20226,7 +20244,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="418" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:23">
       <c r="A418">
         <v>417</v>
       </c>
@@ -20265,7 +20283,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="419" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:23">
       <c r="A419">
         <v>418</v>
       </c>
@@ -20302,7 +20320,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="420" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:23">
       <c r="A420">
         <v>419</v>
       </c>
@@ -20345,7 +20363,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="421" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:23">
       <c r="A421">
         <v>420</v>
       </c>
@@ -20385,7 +20403,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="422" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:23">
       <c r="A422">
         <v>421</v>
       </c>
@@ -20422,7 +20440,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="423" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:23">
       <c r="A423">
         <v>422</v>
       </c>
@@ -20465,7 +20483,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="424" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:23">
       <c r="A424">
         <v>423</v>
       </c>
@@ -20508,7 +20526,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="425" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:23">
       <c r="A425">
         <v>424</v>
       </c>
@@ -20551,7 +20569,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="426" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:23">
       <c r="A426">
         <v>425</v>
       </c>
@@ -20592,7 +20610,7 @@
       </c>
       <c r="W426" s="3"/>
     </row>
-    <row r="427" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:23">
       <c r="A427">
         <v>426</v>
       </c>
@@ -20635,7 +20653,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="428" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:23">
       <c r="A428">
         <v>427</v>
       </c>
@@ -20678,7 +20696,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="429" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:23">
       <c r="A429">
         <v>428</v>
       </c>
@@ -20721,7 +20739,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="430" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:23">
       <c r="A430">
         <v>429</v>
       </c>
@@ -20758,7 +20776,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="431" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:23">
       <c r="A431">
         <v>430</v>
       </c>
@@ -20797,7 +20815,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="432" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:23">
       <c r="A432">
         <v>431</v>
       </c>
@@ -20836,7 +20854,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="433" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:23">
       <c r="A433">
         <v>432</v>
       </c>
@@ -20874,7 +20892,7 @@
       </c>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:23">
       <c r="A434">
         <v>433</v>
       </c>
@@ -20912,7 +20930,7 @@
       </c>
       <c r="W434" s="3"/>
     </row>
-    <row r="435" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:23">
       <c r="A435">
         <v>434</v>
       </c>
@@ -20950,7 +20968,7 @@
       </c>
       <c r="W435" s="3"/>
     </row>
-    <row r="436" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:23">
       <c r="A436">
         <v>435</v>
       </c>
@@ -20988,7 +21006,7 @@
       </c>
       <c r="W436" s="3"/>
     </row>
-    <row r="437" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:23">
       <c r="A437">
         <v>436</v>
       </c>
@@ -21026,7 +21044,7 @@
       </c>
       <c r="W437" s="3"/>
     </row>
-    <row r="438" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:23">
       <c r="A438">
         <v>437</v>
       </c>
@@ -21061,7 +21079,7 @@
       </c>
       <c r="W438" s="3"/>
     </row>
-    <row r="439" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:23">
       <c r="A439">
         <v>438</v>
       </c>
@@ -21098,7 +21116,7 @@
       </c>
       <c r="W439" s="3"/>
     </row>
-    <row r="440" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:23">
       <c r="A440">
         <v>439</v>
       </c>
@@ -21135,7 +21153,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="441" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:23">
       <c r="A441">
         <v>440</v>
       </c>
@@ -21172,7 +21190,7 @@
       </c>
       <c r="W441" s="3"/>
     </row>
-    <row r="442" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:23">
       <c r="A442">
         <v>441</v>
       </c>
@@ -21209,7 +21227,7 @@
       </c>
       <c r="W442" s="3"/>
     </row>
-    <row r="443" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:23">
       <c r="A443">
         <v>442</v>
       </c>
@@ -21250,7 +21268,7 @@
       </c>
       <c r="W443" s="3"/>
     </row>
-    <row r="444" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:23">
       <c r="A444">
         <v>443</v>
       </c>
@@ -21289,7 +21307,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="445" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:23">
       <c r="A445">
         <v>444</v>
       </c>
@@ -21330,7 +21348,7 @@
       </c>
       <c r="W445" s="3"/>
     </row>
-    <row r="446" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:23">
       <c r="A446">
         <v>445</v>
       </c>
@@ -21370,7 +21388,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="447" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:23">
       <c r="A447">
         <v>446</v>
       </c>
@@ -21410,7 +21428,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="448" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:23">
       <c r="A448">
         <v>447</v>
       </c>
@@ -21447,7 +21465,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="449" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:23">
       <c r="A449">
         <v>448</v>
       </c>
@@ -21486,7 +21504,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="450" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:23">
       <c r="A450">
         <v>449</v>
       </c>
@@ -21525,7 +21543,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="451" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:23">
       <c r="A451">
         <v>450</v>
       </c>
@@ -21564,7 +21582,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="452" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:23">
       <c r="A452">
         <v>451</v>
       </c>
@@ -21604,7 +21622,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="453" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:23">
       <c r="A453">
         <v>452</v>
       </c>
@@ -21641,7 +21659,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="454" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:23">
       <c r="A454">
         <v>453</v>
       </c>
@@ -21676,7 +21694,7 @@
       </c>
       <c r="W454" s="3"/>
     </row>
-    <row r="455" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:23">
       <c r="A455">
         <v>454</v>
       </c>
@@ -21715,7 +21733,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="456" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:23">
       <c r="A456">
         <v>455</v>
       </c>
@@ -21754,7 +21772,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="457" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:23">
       <c r="A457">
         <v>456</v>
       </c>
@@ -21793,7 +21811,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="458" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:23">
       <c r="A458">
         <v>457</v>
       </c>
@@ -21832,7 +21850,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="459" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:23">
       <c r="A459">
         <v>458</v>
       </c>
@@ -21871,7 +21889,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="460" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:23">
       <c r="A460">
         <v>459</v>
       </c>
@@ -21910,7 +21928,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="461" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:23">
       <c r="A461">
         <v>460</v>
       </c>
@@ -21949,7 +21967,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="462" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:23">
       <c r="A462">
         <v>461</v>
       </c>
@@ -21988,7 +22006,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="463" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:23">
       <c r="A463">
         <v>462</v>
       </c>
@@ -22027,7 +22045,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="464" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:23">
       <c r="A464">
         <v>463</v>
       </c>
@@ -22066,7 +22084,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="465" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:23">
       <c r="A465">
         <v>464</v>
       </c>
@@ -22105,7 +22123,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="466" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:23">
       <c r="A466">
         <v>465</v>
       </c>
@@ -22144,7 +22162,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="467" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:23">
       <c r="A467">
         <v>466</v>
       </c>
@@ -22183,7 +22201,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="468" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:23">
       <c r="A468">
         <v>467</v>
       </c>
@@ -22222,7 +22240,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="469" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:23">
       <c r="A469">
         <v>468</v>
       </c>
@@ -22261,7 +22279,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="470" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:23">
       <c r="A470">
         <v>469</v>
       </c>
@@ -22300,7 +22318,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="471" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:23">
       <c r="A471">
         <v>470</v>
       </c>
@@ -22337,7 +22355,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="472" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:23">
       <c r="A472">
         <v>471</v>
       </c>
@@ -22377,7 +22395,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="473" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:23">
       <c r="A473">
         <v>472</v>
       </c>
@@ -22414,7 +22432,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="474" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:23">
       <c r="A474">
         <v>473</v>
       </c>
@@ -22453,7 +22471,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="475" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:23">
       <c r="A475">
         <v>474</v>
       </c>
@@ -22492,7 +22510,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="476" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:23">
       <c r="A476">
         <v>475</v>
       </c>
@@ -22529,7 +22547,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="477" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:23">
       <c r="A477">
         <v>476</v>
       </c>
@@ -22566,7 +22584,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="478" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:23">
       <c r="A478">
         <v>477</v>
       </c>
@@ -22609,7 +22627,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="479" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:23">
       <c r="A479">
         <v>478</v>
       </c>
@@ -22648,7 +22666,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="480" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:23">
       <c r="A480">
         <v>479</v>
       </c>
@@ -22687,7 +22705,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="481" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:23">
       <c r="A481">
         <v>480</v>
       </c>
@@ -22724,7 +22742,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="482" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:23">
       <c r="A482">
         <v>481</v>
       </c>
@@ -22761,7 +22779,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="483" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:23">
       <c r="A483">
         <v>482</v>
       </c>
@@ -22798,7 +22816,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="484" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:23">
       <c r="A484">
         <v>483</v>
       </c>
@@ -22837,7 +22855,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="485" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:23">
       <c r="A485">
         <v>484</v>
       </c>
@@ -22876,7 +22894,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="486" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:23">
       <c r="A486">
         <v>485</v>
       </c>
@@ -22913,7 +22931,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="487" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:23">
       <c r="A487">
         <v>486</v>
       </c>
@@ -22950,7 +22968,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="488" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:23">
       <c r="A488">
         <v>487</v>
       </c>
@@ -22987,7 +23005,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="489" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:23">
       <c r="A489">
         <v>488</v>
       </c>
@@ -23025,7 +23043,7 @@
       </c>
       <c r="W489" s="3"/>
     </row>
-    <row r="490" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:23">
       <c r="A490">
         <v>489</v>
       </c>
@@ -23064,7 +23082,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="491" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:23">
       <c r="A491">
         <v>490</v>
       </c>
@@ -23103,7 +23121,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="492" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:23">
       <c r="A492">
         <v>491</v>
       </c>
@@ -23140,7 +23158,7 @@
       </c>
       <c r="W492" s="3"/>
     </row>
-    <row r="493" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:23">
       <c r="A493">
         <v>492</v>
       </c>
@@ -23177,7 +23195,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="494" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:23">
       <c r="A494">
         <v>493</v>
       </c>
@@ -23215,7 +23233,7 @@
       </c>
       <c r="W494" s="3"/>
     </row>
-    <row r="495" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:23">
       <c r="A495">
         <v>494</v>
       </c>
@@ -23252,7 +23270,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="496" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:23">
       <c r="A496">
         <v>495</v>
       </c>
@@ -23289,7 +23307,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="497" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:23">
       <c r="A497">
         <v>496</v>
       </c>
@@ -23332,7 +23350,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="498" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:23">
       <c r="A498">
         <v>497</v>
       </c>
@@ -23369,7 +23387,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="499" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:23">
       <c r="A499">
         <v>498</v>
       </c>
@@ -23408,7 +23426,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="500" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:23">
       <c r="A500">
         <v>499</v>
       </c>
@@ -23451,7 +23469,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="501" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:23">
       <c r="A501">
         <v>500</v>
       </c>
@@ -23494,7 +23512,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="502" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:23">
       <c r="A502">
         <v>501</v>
       </c>
@@ -23531,7 +23549,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="503" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:23">
       <c r="A503">
         <v>502</v>
       </c>
@@ -23570,7 +23588,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="504" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:23">
       <c r="A504">
         <v>503</v>
       </c>
@@ -23607,7 +23625,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="505" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:23">
       <c r="A505">
         <v>504</v>
       </c>
@@ -23650,7 +23668,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="506" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:23">
       <c r="A506">
         <v>505</v>
       </c>
@@ -23689,7 +23707,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="507" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:23">
       <c r="A507">
         <v>506</v>
       </c>
@@ -23728,7 +23746,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="508" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:23">
       <c r="A508">
         <v>507</v>
       </c>
@@ -23767,7 +23785,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="509" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:23">
       <c r="A509">
         <v>508</v>
       </c>
@@ -23810,7 +23828,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="510" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:23">
       <c r="A510">
         <v>509</v>
       </c>
@@ -23847,7 +23865,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="511" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:23">
       <c r="A511">
         <v>510</v>
       </c>
@@ -23886,7 +23904,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="512" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:23">
       <c r="A512">
         <v>511</v>
       </c>
@@ -23925,7 +23943,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="513" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:23">
       <c r="A513">
         <v>512</v>
       </c>
@@ -23964,7 +23982,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="514" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:23">
       <c r="A514">
         <v>513</v>
       </c>
@@ -24003,7 +24021,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="515" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:23">
       <c r="A515">
         <v>514</v>
       </c>
@@ -24042,7 +24060,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="516" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:23">
       <c r="A516">
         <v>515</v>
       </c>
@@ -24085,7 +24103,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="517" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:23">
       <c r="A517">
         <v>516</v>
       </c>
@@ -24124,7 +24142,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="518" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:23">
       <c r="A518">
         <v>517</v>
       </c>
@@ -24163,7 +24181,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="519" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:23">
       <c r="A519">
         <v>518</v>
       </c>
@@ -24200,7 +24218,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="520" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:23">
       <c r="A520">
         <v>519</v>
       </c>
@@ -24240,7 +24258,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="521" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:23">
       <c r="A521">
         <v>520</v>
       </c>
@@ -24277,7 +24295,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="522" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:23">
       <c r="A522">
         <v>521</v>
       </c>
@@ -24320,7 +24338,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="523" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:23">
       <c r="A523">
         <v>522</v>
       </c>
@@ -24359,7 +24377,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="524" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:23">
       <c r="A524">
         <v>523</v>
       </c>
@@ -24398,7 +24416,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="525" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:23">
       <c r="A525">
         <v>524</v>
       </c>
@@ -24435,7 +24453,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="526" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:23">
       <c r="A526">
         <v>525</v>
       </c>
@@ -24472,7 +24490,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="527" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:23">
       <c r="A527">
         <v>526</v>
       </c>
@@ -24515,7 +24533,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="528" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:23">
       <c r="A528">
         <v>527</v>
       </c>
@@ -24558,7 +24576,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="529" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:23">
       <c r="A529">
         <v>528</v>
       </c>
@@ -24601,7 +24619,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="530" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:23">
       <c r="A530">
         <v>529</v>
       </c>
@@ -24642,7 +24660,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="531" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:23">
       <c r="A531">
         <v>530</v>
       </c>
@@ -24681,7 +24699,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="532" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:23">
       <c r="A532">
         <v>531</v>
       </c>
@@ -24720,7 +24738,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="533" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:23">
       <c r="A533">
         <v>532</v>
       </c>
@@ -24755,7 +24773,7 @@
       </c>
       <c r="W533" s="3"/>
     </row>
-    <row r="534" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:23">
       <c r="A534">
         <v>533</v>
       </c>
@@ -24796,7 +24814,7 @@
       </c>
       <c r="W534" s="3"/>
     </row>
-    <row r="535" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:23">
       <c r="A535">
         <v>534</v>
       </c>
@@ -24834,7 +24852,7 @@
       </c>
       <c r="W535" s="3"/>
     </row>
-    <row r="536" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:23">
       <c r="A536">
         <v>535</v>
       </c>
@@ -24872,7 +24890,7 @@
       </c>
       <c r="W536" s="3"/>
     </row>
-    <row r="537" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:23">
       <c r="A537">
         <v>536</v>
       </c>
@@ -24910,7 +24928,7 @@
       </c>
       <c r="W537" s="3"/>
     </row>
-    <row r="538" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:23">
       <c r="A538">
         <v>537</v>
       </c>
@@ -24948,7 +24966,7 @@
       </c>
       <c r="W538" s="3"/>
     </row>
-    <row r="539" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:23">
       <c r="A539">
         <v>538</v>
       </c>
@@ -24986,7 +25004,7 @@
       </c>
       <c r="W539" s="3"/>
     </row>
-    <row r="540" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:23">
       <c r="A540">
         <v>539</v>
       </c>
@@ -25024,7 +25042,7 @@
       </c>
       <c r="W540" s="3"/>
     </row>
-    <row r="541" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:23">
       <c r="A541">
         <v>540</v>
       </c>
@@ -25065,7 +25083,7 @@
       </c>
       <c r="W541" s="3"/>
     </row>
-    <row r="542" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:23">
       <c r="A542">
         <v>541</v>
       </c>
@@ -25106,7 +25124,7 @@
       </c>
       <c r="W542" s="3"/>
     </row>
-    <row r="543" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:23">
       <c r="A543">
         <v>542</v>
       </c>
@@ -25143,7 +25161,7 @@
       </c>
       <c r="W543" s="3"/>
     </row>
-    <row r="544" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:23">
       <c r="A544">
         <v>543</v>
       </c>
@@ -25182,7 +25200,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="545" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:23">
       <c r="A545">
         <v>544</v>
       </c>
@@ -25219,7 +25237,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="546" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:23">
       <c r="A546">
         <v>545</v>
       </c>
@@ -25256,7 +25274,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="547" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:23">
       <c r="A547">
         <v>546</v>
       </c>
@@ -25296,7 +25314,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="548" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:23">
       <c r="A548">
         <v>547</v>
       </c>
@@ -25333,7 +25351,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="549" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:23">
       <c r="A549">
         <v>548</v>
       </c>
@@ -25370,7 +25388,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="550" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:23">
       <c r="A550">
         <v>549</v>
       </c>
@@ -25407,7 +25425,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="551" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:23">
       <c r="A551">
         <v>550</v>
       </c>
@@ -25444,7 +25462,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="552" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:23">
       <c r="A552">
         <v>551</v>
       </c>
@@ -25481,7 +25499,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="553" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:23">
       <c r="A553">
         <v>552</v>
       </c>
@@ -25518,7 +25536,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="554" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:23">
       <c r="A554">
         <v>553</v>
       </c>
@@ -25555,7 +25573,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="555" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:23">
       <c r="A555">
         <v>554</v>
       </c>
@@ -25592,7 +25610,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="556" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:23">
       <c r="A556">
         <v>555</v>
       </c>
@@ -25629,7 +25647,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="557" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:23">
       <c r="A557">
         <v>556</v>
       </c>
@@ -25666,7 +25684,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="558" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:23">
       <c r="A558">
         <v>557</v>
       </c>
@@ -25703,7 +25721,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="559" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:23">
       <c r="A559">
         <v>558</v>
       </c>
@@ -25740,7 +25758,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="560" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:23">
       <c r="A560">
         <v>559</v>
       </c>
@@ -25779,7 +25797,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="561" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:23">
       <c r="A561">
         <v>560</v>
       </c>
@@ -25816,7 +25834,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="562" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:23">
       <c r="A562">
         <v>561</v>
       </c>
@@ -25851,7 +25869,7 @@
       </c>
       <c r="W562" s="3"/>
     </row>
-    <row r="563" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:23">
       <c r="A563">
         <v>562</v>
       </c>
@@ -25886,7 +25904,7 @@
       </c>
       <c r="W563" s="3"/>
     </row>
-    <row r="564" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:23">
       <c r="A564">
         <v>563</v>
       </c>
@@ -25921,7 +25939,7 @@
       </c>
       <c r="W564" s="3"/>
     </row>
-    <row r="565" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:23">
       <c r="A565">
         <v>564</v>
       </c>
@@ -25956,7 +25974,7 @@
       </c>
       <c r="W565" s="3"/>
     </row>
-    <row r="566" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:23">
       <c r="A566">
         <v>565</v>
       </c>
@@ -25991,7 +26009,7 @@
       </c>
       <c r="W566" s="3"/>
     </row>
-    <row r="567" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:23">
       <c r="A567">
         <v>566</v>
       </c>
@@ -26030,7 +26048,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="568" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:23">
       <c r="A568">
         <v>567</v>
       </c>
@@ -26069,7 +26087,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="569" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:23">
       <c r="A569">
         <v>568</v>
       </c>
@@ -26108,7 +26126,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="570" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:23">
       <c r="A570">
         <v>569</v>
       </c>
@@ -26143,7 +26161,7 @@
       </c>
       <c r="W570" s="3"/>
     </row>
-    <row r="571" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:23">
       <c r="A571">
         <v>570</v>
       </c>
@@ -26182,7 +26200,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="572" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:23">
       <c r="A572">
         <v>571</v>
       </c>
@@ -26223,7 +26241,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="573" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:23">
       <c r="A573">
         <v>572</v>
       </c>
@@ -26262,7 +26280,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="574" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:23">
       <c r="A574">
         <v>573</v>
       </c>
@@ -26299,7 +26317,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="575" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:23">
       <c r="A575">
         <v>574</v>
       </c>
@@ -26338,7 +26356,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="576" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:23">
       <c r="A576">
         <v>575</v>
       </c>
@@ -26377,7 +26395,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="577" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:23">
       <c r="A577">
         <v>576</v>
       </c>
@@ -26414,7 +26432,7 @@
       </c>
       <c r="W577" s="3"/>
     </row>
-    <row r="578" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:23">
       <c r="A578">
         <v>577</v>
       </c>
@@ -26451,7 +26469,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="579" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:23">
       <c r="A579">
         <v>578</v>
       </c>
@@ -26490,7 +26508,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="580" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:23">
       <c r="A580">
         <v>579</v>
       </c>
@@ -26527,7 +26545,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="581" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:23">
       <c r="A581">
         <v>580</v>
       </c>
@@ -26562,7 +26580,7 @@
       </c>
       <c r="W581" s="3"/>
     </row>
-    <row r="582" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:23">
       <c r="A582">
         <v>581</v>
       </c>
@@ -26601,7 +26619,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="583" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:23">
       <c r="A583">
         <v>582</v>
       </c>
@@ -26639,7 +26657,7 @@
       </c>
       <c r="W583" s="3"/>
     </row>
-    <row r="584" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:23">
       <c r="A584">
         <v>583</v>
       </c>
@@ -26677,7 +26695,7 @@
       </c>
       <c r="W584" s="3"/>
     </row>
-    <row r="585" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:23">
       <c r="A585">
         <v>584</v>
       </c>
@@ -26712,7 +26730,7 @@
       </c>
       <c r="W585" s="3"/>
     </row>
-    <row r="586" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:23">
       <c r="A586">
         <v>585</v>
       </c>
@@ -26747,7 +26765,7 @@
       </c>
       <c r="W586" s="3"/>
     </row>
-    <row r="587" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:23">
       <c r="A587">
         <v>586</v>
       </c>
@@ -26782,7 +26800,7 @@
       </c>
       <c r="W587" s="3"/>
     </row>
-    <row r="588" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:23">
       <c r="A588">
         <v>587</v>
       </c>
@@ -26817,7 +26835,7 @@
       </c>
       <c r="W588" s="3"/>
     </row>
-    <row r="589" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:23">
       <c r="A589">
         <v>588</v>
       </c>
@@ -26852,7 +26870,7 @@
       </c>
       <c r="W589" s="3"/>
     </row>
-    <row r="590" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:23">
       <c r="A590">
         <v>589</v>
       </c>
@@ -26887,7 +26905,7 @@
       </c>
       <c r="W590" s="3"/>
     </row>
-    <row r="591" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:23">
       <c r="A591">
         <v>590</v>
       </c>
@@ -26922,7 +26940,7 @@
       </c>
       <c r="W591" s="3"/>
     </row>
-    <row r="592" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:23">
       <c r="A592">
         <v>591</v>
       </c>
@@ -26957,7 +26975,7 @@
       </c>
       <c r="W592" s="3"/>
     </row>
-    <row r="593" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:23">
       <c r="A593">
         <v>592</v>
       </c>
@@ -26994,7 +27012,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="594" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:23">
       <c r="A594">
         <v>593</v>
       </c>
@@ -27031,7 +27049,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="595" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:23">
       <c r="A595">
         <v>594</v>
       </c>
@@ -27074,7 +27092,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="596" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:23">
       <c r="A596">
         <v>595</v>
       </c>
@@ -27117,7 +27135,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="597" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:23">
       <c r="A597">
         <v>596</v>
       </c>
@@ -27160,7 +27178,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="598" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:23">
       <c r="A598">
         <v>597</v>
       </c>
@@ -27203,7 +27221,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="599" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:23">
       <c r="A599">
         <v>598</v>
       </c>
@@ -27246,7 +27264,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="600" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:23">
       <c r="A600">
         <v>599</v>
       </c>
@@ -27289,7 +27307,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="601" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:23">
       <c r="A601">
         <v>600</v>
       </c>
@@ -27329,7 +27347,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="602" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:23">
       <c r="A602">
         <v>601</v>
       </c>
@@ -27372,7 +27390,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="603" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:23">
       <c r="A603">
         <v>602</v>
       </c>
@@ -27415,7 +27433,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="604" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:23">
       <c r="A604">
         <v>605</v>
       </c>
@@ -27453,7 +27471,7 @@
       </c>
       <c r="W604" s="3"/>
     </row>
-    <row r="605" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:23">
       <c r="A605">
         <v>607</v>
       </c>
@@ -27494,7 +27512,7 @@
       </c>
       <c r="W605" s="3"/>
     </row>
-    <row r="606" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:23">
       <c r="A606">
         <v>608</v>
       </c>
@@ -27535,7 +27553,7 @@
       </c>
       <c r="W606" s="3"/>
     </row>
-    <row r="607" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:23">
       <c r="A607">
         <v>611</v>
       </c>
@@ -27573,7 +27591,7 @@
       </c>
       <c r="W607" s="3"/>
     </row>
-    <row r="608" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:23">
       <c r="A608">
         <v>612</v>
       </c>
@@ -27611,7 +27629,7 @@
       </c>
       <c r="W608" s="3"/>
     </row>
-    <row r="609" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:23">
       <c r="A609">
         <v>613</v>
       </c>
@@ -27649,7 +27667,7 @@
       </c>
       <c r="W609" s="3"/>
     </row>
-    <row r="610" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:23">
       <c r="A610">
         <v>614</v>
       </c>
@@ -27687,7 +27705,7 @@
       </c>
       <c r="W610" s="3"/>
     </row>
-    <row r="611" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:23">
       <c r="A611">
         <v>615</v>
       </c>
@@ -27725,7 +27743,7 @@
       </c>
       <c r="W611" s="3"/>
     </row>
-    <row r="612" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:23">
       <c r="A612">
         <v>616</v>
       </c>
@@ -27763,7 +27781,7 @@
       </c>
       <c r="W612" s="3"/>
     </row>
-    <row r="613" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:23">
       <c r="A613">
         <v>617</v>
       </c>
@@ -27804,7 +27822,7 @@
       </c>
       <c r="W613" s="3"/>
     </row>
-    <row r="614" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:23">
       <c r="A614">
         <v>618</v>
       </c>
@@ -27845,7 +27863,7 @@
       </c>
       <c r="W614" s="3"/>
     </row>
-    <row r="615" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:23">
       <c r="A615">
         <v>619</v>
       </c>
@@ -27886,7 +27904,7 @@
       </c>
       <c r="W615" s="3"/>
     </row>
-    <row r="616" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:23">
       <c r="A616">
         <v>620</v>
       </c>
@@ -27927,7 +27945,7 @@
       </c>
       <c r="W616" s="3"/>
     </row>
-    <row r="617" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:23">
       <c r="A617">
         <v>621</v>
       </c>
@@ -27968,7 +27986,7 @@
       </c>
       <c r="W617" s="3"/>
     </row>
-    <row r="618" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:23">
       <c r="A618">
         <v>622</v>
       </c>
@@ -28009,7 +28027,7 @@
       </c>
       <c r="W618" s="3"/>
     </row>
-    <row r="619" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:23">
       <c r="A619">
         <v>623</v>
       </c>
@@ -28050,7 +28068,7 @@
       </c>
       <c r="W619" s="3"/>
     </row>
-    <row r="620" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:23">
       <c r="A620">
         <v>624</v>
       </c>
@@ -28091,7 +28109,7 @@
       </c>
       <c r="W620" s="3"/>
     </row>
-    <row r="621" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:23">
       <c r="A621">
         <v>625</v>
       </c>
@@ -28132,7 +28150,7 @@
       </c>
       <c r="W621" s="3"/>
     </row>
-    <row r="622" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:23">
       <c r="A622">
         <v>626</v>
       </c>
@@ -28173,7 +28191,7 @@
       </c>
       <c r="W622" s="3"/>
     </row>
-    <row r="623" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:23">
       <c r="A623">
         <v>627</v>
       </c>
@@ -28214,7 +28232,7 @@
       </c>
       <c r="W623" s="3"/>
     </row>
-    <row r="624" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:23">
       <c r="A624">
         <v>628</v>
       </c>
@@ -28252,7 +28270,7 @@
       </c>
       <c r="W624" s="3"/>
     </row>
-    <row r="625" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:23">
       <c r="A625">
         <v>629</v>
       </c>
@@ -28290,7 +28308,7 @@
       </c>
       <c r="W625" s="3"/>
     </row>
-    <row r="626" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:23">
       <c r="A626">
         <v>630</v>
       </c>
@@ -28331,7 +28349,7 @@
       </c>
       <c r="W626" s="3"/>
     </row>
-    <row r="627" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:23">
       <c r="A627">
         <v>631</v>
       </c>
@@ -28369,7 +28387,7 @@
       </c>
       <c r="W627" s="3"/>
     </row>
-    <row r="628" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:23">
       <c r="A628">
         <v>632</v>
       </c>
@@ -28407,7 +28425,7 @@
       </c>
       <c r="W628" s="3"/>
     </row>
-    <row r="629" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:23">
       <c r="A629">
         <v>633</v>
       </c>
@@ -28448,7 +28466,7 @@
       </c>
       <c r="W629" s="3"/>
     </row>
-    <row r="630" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:23">
       <c r="A630">
         <v>634</v>
       </c>
@@ -28489,7 +28507,7 @@
       </c>
       <c r="W630" s="3"/>
     </row>
-    <row r="631" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:23">
       <c r="A631">
         <v>635</v>
       </c>
@@ -28528,7 +28546,7 @@
       </c>
       <c r="W631" s="3"/>
     </row>
-    <row r="632" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:23">
       <c r="A632">
         <v>636</v>
       </c>
@@ -28565,7 +28583,7 @@
       </c>
       <c r="W632" s="3"/>
     </row>
-    <row r="633" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:23">
       <c r="A633">
         <v>637</v>
       </c>
@@ -28606,7 +28624,7 @@
       </c>
       <c r="W633" s="3"/>
     </row>
-    <row r="634" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:23">
       <c r="A634">
         <v>638</v>
       </c>
@@ -28647,7 +28665,7 @@
       </c>
       <c r="W634" s="3"/>
     </row>
-    <row r="635" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:23">
       <c r="A635">
         <v>639</v>
       </c>
@@ -28688,7 +28706,7 @@
       </c>
       <c r="W635" s="3"/>
     </row>
-    <row r="636" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:23">
       <c r="A636">
         <v>640</v>
       </c>
@@ -28728,7 +28746,7 @@
       </c>
       <c r="W636" s="3"/>
     </row>
-    <row r="637" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:23">
       <c r="A637">
         <v>641</v>
       </c>
@@ -28769,7 +28787,7 @@
       </c>
       <c r="W637" s="3"/>
     </row>
-    <row r="638" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:23">
       <c r="A638">
         <v>642</v>
       </c>
@@ -28810,7 +28828,7 @@
       </c>
       <c r="W638" s="3"/>
     </row>
-    <row r="639" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:23">
       <c r="A639">
         <v>643</v>
       </c>
@@ -28851,7 +28869,7 @@
       </c>
       <c r="W639" s="3"/>
     </row>
-    <row r="640" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:23">
       <c r="A640">
         <v>644</v>
       </c>
@@ -28888,7 +28906,7 @@
       </c>
       <c r="W640" s="3"/>
     </row>
-    <row r="641" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:23">
       <c r="A641">
         <v>650</v>
       </c>
@@ -28929,7 +28947,7 @@
       </c>
       <c r="W641" s="3"/>
     </row>
-    <row r="642" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:23">
       <c r="A642">
         <v>645</v>
       </c>
@@ -28970,7 +28988,7 @@
       </c>
       <c r="W642" s="3"/>
     </row>
-    <row r="643" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:23">
       <c r="A643">
         <v>646</v>
       </c>
@@ -29006,7 +29024,7 @@
       </c>
       <c r="W643" s="3"/>
     </row>
-    <row r="644" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:23">
       <c r="A644">
         <v>647</v>
       </c>
@@ -29047,7 +29065,7 @@
       </c>
       <c r="W644" s="3"/>
     </row>
-    <row r="645" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:23">
       <c r="A645">
         <v>648</v>
       </c>
@@ -29085,7 +29103,7 @@
       </c>
       <c r="W645" s="3"/>
     </row>
-    <row r="646" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:23">
       <c r="A646">
         <v>649</v>
       </c>
@@ -29126,7 +29144,7 @@
       </c>
       <c r="W646" s="3"/>
     </row>
-    <row r="647" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:23">
       <c r="A647">
         <v>651</v>
       </c>
@@ -29167,7 +29185,7 @@
       </c>
       <c r="W647" s="3"/>
     </row>
-    <row r="648" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:23">
       <c r="A648">
         <v>652</v>
       </c>
@@ -29208,7 +29226,7 @@
       </c>
       <c r="W648" s="3"/>
     </row>
-    <row r="649" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:23">
       <c r="A649">
         <v>653</v>
       </c>
@@ -29249,7 +29267,7 @@
       </c>
       <c r="W649" s="3"/>
     </row>
-    <row r="650" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:23">
       <c r="A650">
         <v>654</v>
       </c>
@@ -29290,7 +29308,7 @@
       </c>
       <c r="W650" s="3"/>
     </row>
-    <row r="651" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:23">
       <c r="A651">
         <v>655</v>
       </c>
@@ -29331,7 +29349,7 @@
       </c>
       <c r="W651" s="3"/>
     </row>
-    <row r="652" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:23">
       <c r="A652">
         <v>656</v>
       </c>
@@ -29372,7 +29390,7 @@
       </c>
       <c r="W652" s="3"/>
     </row>
-    <row r="653" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:23">
       <c r="A653">
         <v>657</v>
       </c>
@@ -29413,7 +29431,7 @@
       </c>
       <c r="W653" s="3"/>
     </row>
-    <row r="654" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:23">
       <c r="A654">
         <v>658</v>
       </c>
@@ -29454,7 +29472,7 @@
       </c>
       <c r="W654" s="3"/>
     </row>
-    <row r="655" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:23">
       <c r="A655">
         <v>659</v>
       </c>
@@ -29491,7 +29509,7 @@
       </c>
       <c r="W655" s="3"/>
     </row>
-    <row r="656" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:23">
       <c r="A656">
         <v>660</v>
       </c>
@@ -29532,7 +29550,7 @@
       </c>
       <c r="W656" s="3"/>
     </row>
-    <row r="657" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:23">
       <c r="A657">
         <v>661</v>
       </c>
@@ -29572,7 +29590,7 @@
       </c>
       <c r="W657" s="3"/>
     </row>
-    <row r="658" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:23">
       <c r="A658">
         <v>662</v>
       </c>
@@ -29613,7 +29631,7 @@
       </c>
       <c r="W658" s="3"/>
     </row>
-    <row r="659" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:23">
       <c r="A659">
         <v>663</v>
       </c>
@@ -29654,7 +29672,7 @@
       </c>
       <c r="W659" s="3"/>
     </row>
-    <row r="660" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:23">
       <c r="A660">
         <v>664</v>
       </c>
@@ -29691,7 +29709,7 @@
       </c>
       <c r="W660" s="3"/>
     </row>
-    <row r="661" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:23">
       <c r="A661">
         <v>665</v>
       </c>
@@ -29732,7 +29750,7 @@
       </c>
       <c r="W661" s="3"/>
     </row>
-    <row r="662" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:23">
       <c r="A662">
         <v>666</v>
       </c>
@@ -29773,7 +29791,7 @@
       </c>
       <c r="W662" s="3"/>
     </row>
-    <row r="663" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:23">
       <c r="A663">
         <v>668</v>
       </c>
@@ -29811,7 +29829,7 @@
       </c>
       <c r="W663" s="3"/>
     </row>
-    <row r="664" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:23">
       <c r="A664">
         <v>667</v>
       </c>
@@ -29852,7 +29870,7 @@
       </c>
       <c r="W664" s="3"/>
     </row>
-    <row r="665" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:23">
       <c r="A665">
         <v>669</v>
       </c>
@@ -29893,7 +29911,7 @@
       </c>
       <c r="W665" s="3"/>
     </row>
-    <row r="666" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:23">
       <c r="A666">
         <v>670</v>
       </c>
@@ -29933,7 +29951,7 @@
       </c>
       <c r="W666" s="3"/>
     </row>
-    <row r="667" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:23">
       <c r="A667">
         <v>671</v>
       </c>
@@ -29974,7 +29992,7 @@
       </c>
       <c r="W667" s="3"/>
     </row>
-    <row r="668" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:23">
       <c r="A668">
         <v>672</v>
       </c>
@@ -30015,7 +30033,7 @@
       </c>
       <c r="W668" s="3"/>
     </row>
-    <row r="669" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:23">
       <c r="A669">
         <v>674</v>
       </c>
@@ -30056,7 +30074,7 @@
       </c>
       <c r="W669" s="3"/>
     </row>
-    <row r="670" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:23">
       <c r="A670">
         <v>675</v>
       </c>
@@ -30097,7 +30115,7 @@
       </c>
       <c r="W670" s="3"/>
     </row>
-    <row r="671" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:23">
       <c r="A671">
         <v>676</v>
       </c>
@@ -30137,7 +30155,7 @@
       </c>
       <c r="W671" s="3"/>
     </row>
-    <row r="672" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:23">
       <c r="A672">
         <v>677</v>
       </c>
@@ -30177,7 +30195,7 @@
       </c>
       <c r="W672" s="3"/>
     </row>
-    <row r="673" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:23">
       <c r="A673">
         <v>678</v>
       </c>
@@ -30217,7 +30235,7 @@
       </c>
       <c r="W673" s="3"/>
     </row>
-    <row r="674" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:23">
       <c r="A674">
         <v>679</v>
       </c>
@@ -30258,7 +30276,7 @@
       </c>
       <c r="W674" s="3"/>
     </row>
-    <row r="675" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:23">
       <c r="A675">
         <v>680</v>
       </c>
@@ -30299,7 +30317,7 @@
       </c>
       <c r="W675" s="3"/>
     </row>
-    <row r="676" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:23">
       <c r="A676">
         <v>681</v>
       </c>
@@ -30340,7 +30358,7 @@
       </c>
       <c r="W676" s="3"/>
     </row>
-    <row r="677" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:23">
       <c r="A677">
         <v>682</v>
       </c>
@@ -30381,7 +30399,7 @@
       </c>
       <c r="W677" s="3"/>
     </row>
-    <row r="678" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:23">
       <c r="A678">
         <v>683</v>
       </c>
@@ -30422,7 +30440,7 @@
       </c>
       <c r="W678" s="3"/>
     </row>
-    <row r="679" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:23">
       <c r="A679">
         <v>684</v>
       </c>
@@ -30463,7 +30481,7 @@
       </c>
       <c r="W679" s="3"/>
     </row>
-    <row r="680" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:23">
       <c r="A680">
         <v>685</v>
       </c>
@@ -30504,7 +30522,7 @@
       </c>
       <c r="W680" s="3"/>
     </row>
-    <row r="681" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:23">
       <c r="A681">
         <v>686</v>
       </c>
@@ -30545,7 +30563,7 @@
       </c>
       <c r="W681" s="3"/>
     </row>
-    <row r="682" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:23">
       <c r="A682">
         <v>687</v>
       </c>
@@ -30586,7 +30604,7 @@
       </c>
       <c r="W682" s="3"/>
     </row>
-    <row r="683" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:23">
       <c r="A683">
         <v>688</v>
       </c>
@@ -30627,7 +30645,7 @@
       </c>
       <c r="W683" s="3"/>
     </row>
-    <row r="684" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:23">
       <c r="A684">
         <v>689</v>
       </c>
@@ -30665,7 +30683,7 @@
       </c>
       <c r="W684" s="3"/>
     </row>
-    <row r="685" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:23">
       <c r="A685">
         <v>690</v>
       </c>
@@ -30706,7 +30724,7 @@
       </c>
       <c r="W685" s="3"/>
     </row>
-    <row r="686" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:23">
       <c r="A686">
         <v>691</v>
       </c>
@@ -30747,7 +30765,7 @@
       </c>
       <c r="W686" s="3"/>
     </row>
-    <row r="687" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:23">
       <c r="A687">
         <v>692</v>
       </c>
@@ -30788,7 +30806,7 @@
       </c>
       <c r="W687" s="3"/>
     </row>
-    <row r="688" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:23">
       <c r="A688">
         <v>693</v>
       </c>
@@ -30829,7 +30847,7 @@
       </c>
       <c r="W688" s="3"/>
     </row>
-    <row r="689" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:23">
       <c r="A689">
         <v>694</v>
       </c>
@@ -30870,7 +30888,7 @@
       </c>
       <c r="W689" s="3"/>
     </row>
-    <row r="690" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:23">
       <c r="A690">
         <v>695</v>
       </c>
@@ -30911,7 +30929,7 @@
       </c>
       <c r="W690" s="3"/>
     </row>
-    <row r="691" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:23">
       <c r="A691">
         <v>696</v>
       </c>
@@ -30952,7 +30970,7 @@
       </c>
       <c r="W691" s="3"/>
     </row>
-    <row r="692" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:23">
       <c r="A692">
         <v>697</v>
       </c>
@@ -30989,7 +31007,7 @@
       </c>
       <c r="W692" s="3"/>
     </row>
-    <row r="693" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:23">
       <c r="A693">
         <v>698</v>
       </c>
@@ -31029,7 +31047,7 @@
       </c>
       <c r="W693" s="3"/>
     </row>
-    <row r="694" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:23">
       <c r="A694">
         <v>699</v>
       </c>
@@ -31070,7 +31088,7 @@
       </c>
       <c r="W694" s="3"/>
     </row>
-    <row r="695" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:23">
       <c r="A695">
         <v>700</v>
       </c>
@@ -31107,7 +31125,7 @@
       </c>
       <c r="W695" s="3"/>
     </row>
-    <row r="696" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:23">
       <c r="A696">
         <v>701</v>
       </c>
@@ -31148,7 +31166,7 @@
       </c>
       <c r="W696" s="3"/>
     </row>
-    <row r="697" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:23">
       <c r="A697">
         <v>702</v>
       </c>
@@ -31189,7 +31207,7 @@
       </c>
       <c r="W697" s="3"/>
     </row>
-    <row r="698" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:23">
       <c r="A698">
         <v>703</v>
       </c>
@@ -31230,7 +31248,7 @@
       </c>
       <c r="W698" s="3"/>
     </row>
-    <row r="699" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:23">
       <c r="A699">
         <v>704</v>
       </c>
@@ -31271,7 +31289,7 @@
       </c>
       <c r="W699" s="3"/>
     </row>
-    <row r="700" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:23">
       <c r="A700">
         <v>705</v>
       </c>
@@ -31312,7 +31330,7 @@
       </c>
       <c r="W700" s="3"/>
     </row>
-    <row r="701" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:23">
       <c r="A701">
         <v>706</v>
       </c>
@@ -31353,7 +31371,7 @@
       </c>
       <c r="W701" s="3"/>
     </row>
-    <row r="702" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:23">
       <c r="A702">
         <v>707</v>
       </c>
@@ -31394,7 +31412,7 @@
       </c>
       <c r="W702" s="3"/>
     </row>
-    <row r="703" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:23">
       <c r="A703">
         <v>708</v>
       </c>
@@ -31435,7 +31453,7 @@
       </c>
       <c r="W703" s="3"/>
     </row>
-    <row r="704" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:23">
       <c r="A704">
         <v>709</v>
       </c>
@@ -31476,7 +31494,7 @@
       </c>
       <c r="W704" s="3"/>
     </row>
-    <row r="705" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:23">
       <c r="A705">
         <v>710</v>
       </c>
@@ -31517,7 +31535,7 @@
       </c>
       <c r="W705" s="3"/>
     </row>
-    <row r="706" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:23">
       <c r="A706">
         <v>711</v>
       </c>
@@ -31558,7 +31576,7 @@
       </c>
       <c r="W706" s="3"/>
     </row>
-    <row r="707" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:23">
       <c r="A707">
         <v>712</v>
       </c>
@@ -31599,7 +31617,7 @@
       </c>
       <c r="W707" s="3"/>
     </row>
-    <row r="708" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:23">
       <c r="A708">
         <v>713</v>
       </c>
@@ -31637,7 +31655,7 @@
       </c>
       <c r="W708" s="3"/>
     </row>
-    <row r="709" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:23">
       <c r="A709">
         <v>714</v>
       </c>
@@ -31675,7 +31693,7 @@
       </c>
       <c r="W709" s="3"/>
     </row>
-    <row r="710" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:23">
       <c r="A710">
         <v>715</v>
       </c>
@@ -31713,7 +31731,7 @@
       </c>
       <c r="W710" s="3"/>
     </row>
-    <row r="711" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:23">
       <c r="A711">
         <v>716</v>
       </c>
@@ -31761,7 +31779,7 @@
       </c>
       <c r="W711" s="3"/>
     </row>
-    <row r="712" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:23">
       <c r="A712">
         <v>717</v>
       </c>
@@ -31802,7 +31820,7 @@
       </c>
       <c r="W712" s="3"/>
     </row>
-    <row r="713" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:23">
       <c r="A713">
         <v>718</v>
       </c>
@@ -31843,7 +31861,7 @@
       </c>
       <c r="W713" s="3"/>
     </row>
-    <row r="714" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:23">
       <c r="A714">
         <v>719</v>
       </c>
@@ -31884,7 +31902,7 @@
       </c>
       <c r="W714" s="3"/>
     </row>
-    <row r="715" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:23">
       <c r="A715">
         <v>720</v>
       </c>
@@ -31925,7 +31943,7 @@
       </c>
       <c r="W715" s="3"/>
     </row>
-    <row r="716" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:23">
       <c r="A716">
         <v>721</v>
       </c>
@@ -31966,7 +31984,7 @@
       </c>
       <c r="W716" s="3"/>
     </row>
-    <row r="717" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:23">
       <c r="A717">
         <v>722</v>
       </c>
@@ -32007,7 +32025,7 @@
       </c>
       <c r="W717" s="3"/>
     </row>
-    <row r="718" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:23">
       <c r="A718">
         <v>723</v>
       </c>
@@ -32057,7 +32075,7 @@
       </c>
       <c r="W718" s="3"/>
     </row>
-    <row r="719" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:23">
       <c r="A719">
         <v>724</v>
       </c>
@@ -32095,7 +32113,7 @@
       </c>
       <c r="W719" s="3"/>
     </row>
-    <row r="720" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:23">
       <c r="A720">
         <v>725</v>
       </c>
@@ -32133,7 +32151,7 @@
       </c>
       <c r="W720" s="3"/>
     </row>
-    <row r="721" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:23">
       <c r="A721">
         <v>726</v>
       </c>
@@ -32171,7 +32189,7 @@
       </c>
       <c r="W721" s="3"/>
     </row>
-    <row r="722" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:23">
       <c r="A722">
         <v>727</v>
       </c>
@@ -32212,7 +32230,7 @@
       </c>
       <c r="W722" s="3"/>
     </row>
-    <row r="723" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:23">
       <c r="A723">
         <v>728</v>
       </c>
@@ -32253,7 +32271,7 @@
       </c>
       <c r="W723" s="3"/>
     </row>
-    <row r="724" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:23">
       <c r="A724">
         <v>729</v>
       </c>
@@ -32294,7 +32312,7 @@
       </c>
       <c r="W724" s="3"/>
     </row>
-    <row r="725" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:23">
       <c r="A725">
         <v>730</v>
       </c>
@@ -32335,7 +32353,7 @@
       </c>
       <c r="W725" s="3"/>
     </row>
-    <row r="726" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:23">
       <c r="A726">
         <v>731</v>
       </c>
@@ -32376,7 +32394,7 @@
       </c>
       <c r="W726" s="3"/>
     </row>
-    <row r="727" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:23">
       <c r="A727">
         <v>732</v>
       </c>
@@ -32417,7 +32435,7 @@
       </c>
       <c r="W727" s="3"/>
     </row>
-    <row r="728" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:23">
       <c r="A728">
         <v>733</v>
       </c>
@@ -32458,7 +32476,7 @@
       </c>
       <c r="W728" s="3"/>
     </row>
-    <row r="729" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:23">
       <c r="A729">
         <v>734</v>
       </c>
@@ -32499,7 +32517,7 @@
       </c>
       <c r="W729" s="3"/>
     </row>
-    <row r="730" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:23">
       <c r="A730">
         <v>735</v>
       </c>
@@ -32549,7 +32567,7 @@
       </c>
       <c r="W730" s="3"/>
     </row>
-    <row r="731" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:23">
       <c r="A731">
         <v>736</v>
       </c>
@@ -32590,7 +32608,7 @@
       </c>
       <c r="W731" s="3"/>
     </row>
-    <row r="732" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:23">
       <c r="A732">
         <v>737</v>
       </c>
@@ -32630,7 +32648,7 @@
       </c>
       <c r="W732" s="3"/>
     </row>
-    <row r="733" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:23">
       <c r="A733">
         <v>738</v>
       </c>
@@ -32671,7 +32689,7 @@
       </c>
       <c r="W733" s="3"/>
     </row>
-    <row r="734" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:23">
       <c r="A734">
         <v>739</v>
       </c>
@@ -32708,7 +32726,7 @@
       </c>
       <c r="W734" s="3"/>
     </row>
-    <row r="735" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:23">
       <c r="A735">
         <v>740</v>
       </c>
@@ -32746,7 +32764,7 @@
       </c>
       <c r="W735" s="3"/>
     </row>
-    <row r="736" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:23">
       <c r="A736">
         <v>741</v>
       </c>
@@ -32787,7 +32805,7 @@
       </c>
       <c r="W736" s="3"/>
     </row>
-    <row r="737" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:23">
       <c r="A737">
         <v>742</v>
       </c>
@@ -32828,7 +32846,7 @@
       </c>
       <c r="W737" s="3"/>
     </row>
-    <row r="738" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:23">
       <c r="A738">
         <v>743</v>
       </c>
@@ -32878,7 +32896,7 @@
       </c>
       <c r="W738" s="3"/>
     </row>
-    <row r="739" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:23">
       <c r="A739">
         <v>744</v>
       </c>
@@ -32915,7 +32933,7 @@
       </c>
       <c r="W739" s="3"/>
     </row>
-    <row r="740" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:23">
       <c r="A740">
         <v>745</v>
       </c>
@@ -32965,7 +32983,7 @@
       </c>
       <c r="W740" s="3"/>
     </row>
-    <row r="741" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:23">
       <c r="A741">
         <v>746</v>
       </c>
@@ -33015,7 +33033,7 @@
       </c>
       <c r="W741" s="3"/>
     </row>
-    <row r="742" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:23">
       <c r="A742">
         <v>747</v>
       </c>
@@ -33056,7 +33074,7 @@
       </c>
       <c r="W742" s="3"/>
     </row>
-    <row r="743" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:23">
       <c r="A743">
         <v>748</v>
       </c>
@@ -33097,7 +33115,7 @@
       </c>
       <c r="W743" s="3"/>
     </row>
-    <row r="744" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:23">
       <c r="A744">
         <v>749</v>
       </c>
@@ -33137,7 +33155,7 @@
       </c>
       <c r="W744" s="3"/>
     </row>
-    <row r="745" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:23">
       <c r="A745">
         <v>750</v>
       </c>
@@ -33178,7 +33196,7 @@
       </c>
       <c r="W745" s="3"/>
     </row>
-    <row r="746" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:23">
       <c r="A746">
         <v>751</v>
       </c>
@@ -33219,7 +33237,7 @@
       </c>
       <c r="W746" s="3"/>
     </row>
-    <row r="747" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:23">
       <c r="A747">
         <v>752</v>
       </c>
@@ -33259,7 +33277,7 @@
       </c>
       <c r="W747" s="3"/>
     </row>
-    <row r="748" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:23">
       <c r="A748">
         <v>753</v>
       </c>
@@ -33300,7 +33318,7 @@
       </c>
       <c r="W748" s="3"/>
     </row>
-    <row r="749" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:23">
       <c r="A749">
         <v>754</v>
       </c>
@@ -33350,7 +33368,7 @@
       </c>
       <c r="W749" s="3"/>
     </row>
-    <row r="750" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:23">
       <c r="A750">
         <v>755</v>
       </c>
@@ -33390,7 +33408,7 @@
       </c>
       <c r="W750" s="3"/>
     </row>
-    <row r="751" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:23">
       <c r="A751">
         <v>756</v>
       </c>
@@ -33431,7 +33449,7 @@
       </c>
       <c r="W751" s="3"/>
     </row>
-    <row r="752" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:23">
       <c r="A752">
         <v>757</v>
       </c>
@@ -33481,7 +33499,7 @@
       </c>
       <c r="W752" s="3"/>
     </row>
-    <row r="753" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:23">
       <c r="A753">
         <v>758</v>
       </c>
@@ -33521,7 +33539,7 @@
       </c>
       <c r="W753" s="3"/>
     </row>
-    <row r="754" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:23">
       <c r="A754">
         <v>759</v>
       </c>
@@ -33562,7 +33580,7 @@
       </c>
       <c r="W754" s="3"/>
     </row>
-    <row r="755" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:23">
       <c r="A755">
         <v>760</v>
       </c>
@@ -33603,7 +33621,7 @@
       </c>
       <c r="W755" s="3"/>
     </row>
-    <row r="756" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:23">
       <c r="A756">
         <v>762</v>
       </c>
@@ -33653,7 +33671,7 @@
       </c>
       <c r="W756" s="3"/>
     </row>
-    <row r="757" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:23">
       <c r="A757">
         <v>763</v>
       </c>
@@ -33703,7 +33721,7 @@
       </c>
       <c r="W757" s="3"/>
     </row>
-    <row r="758" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:23">
       <c r="A758">
         <v>764</v>
       </c>
@@ -33753,7 +33771,7 @@
       </c>
       <c r="W758" s="3"/>
     </row>
-    <row r="759" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:23">
       <c r="A759">
         <v>765</v>
       </c>
@@ -33794,7 +33812,7 @@
       </c>
       <c r="W759" s="3"/>
     </row>
-    <row r="760" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:23">
       <c r="A760">
         <v>766</v>
       </c>
@@ -33835,7 +33853,7 @@
       </c>
       <c r="W760" s="3"/>
     </row>
-    <row r="761" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:23">
       <c r="A761">
         <v>767</v>
       </c>
@@ -33876,7 +33894,7 @@
       </c>
       <c r="W761" s="3"/>
     </row>
-    <row r="762" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:23">
       <c r="A762">
         <v>768</v>
       </c>
@@ -33926,7 +33944,7 @@
       </c>
       <c r="W762" s="3"/>
     </row>
-    <row r="763" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:23">
       <c r="A763">
         <v>769</v>
       </c>
@@ -33967,7 +33985,7 @@
       </c>
       <c r="W763" s="3"/>
     </row>
-    <row r="764" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:23">
       <c r="A764">
         <v>770</v>
       </c>
@@ -34008,7 +34026,7 @@
       </c>
       <c r="W764" s="3"/>
     </row>
-    <row r="765" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:23">
       <c r="A765">
         <v>771</v>
       </c>
@@ -34058,7 +34076,7 @@
       </c>
       <c r="W765" s="3"/>
     </row>
-    <row r="766" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:23">
       <c r="A766">
         <v>772</v>
       </c>
@@ -34108,7 +34126,7 @@
       </c>
       <c r="W766" s="3"/>
     </row>
-    <row r="767" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:23">
       <c r="A767">
         <v>773</v>
       </c>
@@ -34147,7 +34165,7 @@
       </c>
       <c r="W767" s="3"/>
     </row>
-    <row r="768" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:23">
       <c r="A768">
         <v>774</v>
       </c>
@@ -34188,7 +34206,7 @@
       </c>
       <c r="W768" s="3"/>
     </row>
-    <row r="769" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:23">
       <c r="A769">
         <v>775</v>
       </c>
@@ -34229,7 +34247,7 @@
       </c>
       <c r="W769" s="3"/>
     </row>
-    <row r="770" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:23">
       <c r="A770">
         <v>776</v>
       </c>
@@ -34269,7 +34287,7 @@
       </c>
       <c r="W770" s="3"/>
     </row>
-    <row r="771" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:23">
       <c r="A771">
         <v>777</v>
       </c>
@@ -34319,7 +34337,7 @@
       </c>
       <c r="W771" s="3"/>
     </row>
-    <row r="772" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:23">
       <c r="A772">
         <v>778</v>
       </c>
@@ -34360,7 +34378,7 @@
       </c>
       <c r="W772" s="3"/>
     </row>
-    <row r="773" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:23">
       <c r="A773">
         <v>779</v>
       </c>
@@ -34398,7 +34416,7 @@
       </c>
       <c r="W773" s="3"/>
     </row>
-    <row r="774" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:23">
       <c r="A774">
         <v>780</v>
       </c>
@@ -34439,7 +34457,7 @@
       </c>
       <c r="W774" s="3"/>
     </row>
-    <row r="775" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:23">
       <c r="A775">
         <v>781</v>
       </c>
@@ -34480,7 +34498,7 @@
       </c>
       <c r="W775" s="3"/>
     </row>
-    <row r="776" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:23">
       <c r="A776">
         <v>782</v>
       </c>
@@ -34521,7 +34539,7 @@
       </c>
       <c r="W776" s="3"/>
     </row>
-    <row r="777" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:23">
       <c r="A777">
         <v>783</v>
       </c>
@@ -34562,7 +34580,7 @@
       </c>
       <c r="W777" s="3"/>
     </row>
-    <row r="778" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:23">
       <c r="A778">
         <v>784</v>
       </c>
@@ -34603,7 +34621,7 @@
       </c>
       <c r="W778" s="3"/>
     </row>
-    <row r="779" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:23">
       <c r="A779">
         <v>785</v>
       </c>
@@ -34644,7 +34662,7 @@
       </c>
       <c r="W779" s="3"/>
     </row>
-    <row r="780" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:23">
       <c r="A780">
         <v>786</v>
       </c>
@@ -34685,7 +34703,7 @@
       </c>
       <c r="W780" s="3"/>
     </row>
-    <row r="781" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:23">
       <c r="A781">
         <v>787</v>
       </c>
@@ -34723,7 +34741,7 @@
       </c>
       <c r="W781" s="3"/>
     </row>
-    <row r="782" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:23">
       <c r="A782">
         <v>788</v>
       </c>
@@ -34761,7 +34779,7 @@
       </c>
       <c r="W782" s="3"/>
     </row>
-    <row r="783" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:23">
       <c r="A783">
         <v>789</v>
       </c>
@@ -34802,7 +34820,7 @@
       </c>
       <c r="W783" s="3"/>
     </row>
-    <row r="784" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:23">
       <c r="A784">
         <v>790</v>
       </c>
@@ -34843,7 +34861,7 @@
       </c>
       <c r="W784" s="3"/>
     </row>
-    <row r="785" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:23">
       <c r="A785">
         <v>791</v>
       </c>
@@ -34884,7 +34902,7 @@
       </c>
       <c r="W785" s="3"/>
     </row>
-    <row r="786" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:23">
       <c r="A786">
         <v>792</v>
       </c>
@@ -34925,7 +34943,7 @@
       </c>
       <c r="W786" s="3"/>
     </row>
-    <row r="787" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:23">
       <c r="A787">
         <v>793</v>
       </c>
@@ -34966,7 +34984,7 @@
       </c>
       <c r="W787" s="3"/>
     </row>
-    <row r="788" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:23">
       <c r="A788">
         <v>794</v>
       </c>
@@ -35016,7 +35034,7 @@
       </c>
       <c r="W788" s="3"/>
     </row>
-    <row r="789" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:23">
       <c r="A789">
         <v>795</v>
       </c>
@@ -35056,7 +35074,7 @@
       </c>
       <c r="W789" s="3"/>
     </row>
-    <row r="790" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:23">
       <c r="A790">
         <v>796</v>
       </c>
@@ -35106,7 +35124,7 @@
       </c>
       <c r="W790" s="3"/>
     </row>
-    <row r="791" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:23">
       <c r="A791">
         <v>797</v>
       </c>
@@ -35147,7 +35165,7 @@
       </c>
       <c r="W791" s="3"/>
     </row>
-    <row r="792" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:23">
       <c r="A792">
         <v>798</v>
       </c>
@@ -35186,7 +35204,7 @@
       </c>
       <c r="W792" s="3"/>
     </row>
-    <row r="793" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:23">
       <c r="A793">
         <v>799</v>
       </c>
@@ -35227,8 +35245,8 @@
       </c>
       <c r="W793" s="3"/>
     </row>
-    <row r="794" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A794" s="6">
+    <row r="794" spans="1:23">
+      <c r="A794">
         <v>800</v>
       </c>
       <c r="B794" s="4">
@@ -35252,30 +35270,20 @@
       <c r="H794" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="I794" s="6"/>
-      <c r="J794" s="6"/>
-      <c r="K794" s="6"/>
       <c r="L794" s="3" t="s">
         <v>1158</v>
       </c>
       <c r="M794" s="3" t="s">
         <v>1159</v>
       </c>
-      <c r="N794" s="6"/>
-      <c r="O794" s="6"/>
-      <c r="P794" s="6"/>
-      <c r="Q794" s="6"/>
-      <c r="R794" s="6"/>
-      <c r="S794" s="6"/>
-      <c r="T794" s="6"/>
       <c r="U794" s="3"/>
       <c r="V794" s="3" t="s">
         <v>280</v>
       </c>
       <c r="W794" s="3"/>
     </row>
-    <row r="795" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A795" s="6">
+    <row r="795" spans="1:23">
+      <c r="A795">
         <v>801</v>
       </c>
       <c r="B795" s="4">
@@ -35299,22 +35307,13 @@
       <c r="H795" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="I795" s="6" t="s">
+      <c r="I795" t="s">
         <v>944</v>
       </c>
-      <c r="J795" s="6"/>
-      <c r="K795" s="6"/>
       <c r="L795" s="3"/>
       <c r="M795" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="N795" s="6"/>
-      <c r="O795" s="6"/>
-      <c r="P795" s="6"/>
-      <c r="Q795" s="6"/>
-      <c r="R795" s="6"/>
-      <c r="S795" s="6"/>
-      <c r="T795" s="6"/>
       <c r="U795" s="3" t="s">
         <v>1161</v>
       </c>
@@ -35322,6 +35321,239 @@
         <v>280</v>
       </c>
       <c r="W795" s="3"/>
+    </row>
+    <row r="796" spans="1:23">
+      <c r="A796">
+        <v>802</v>
+      </c>
+      <c r="B796" s="4">
+        <v>46226.622453703698</v>
+      </c>
+      <c r="C796" s="4">
+        <v>46226.623194444401</v>
+      </c>
+      <c r="D796" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E796" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G796" s="1">
+        <v>46225</v>
+      </c>
+      <c r="H796" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J796" t="s">
+        <v>918</v>
+      </c>
+      <c r="L796" s="3"/>
+      <c r="M796" s="3"/>
+      <c r="T796">
+        <v>15</v>
+      </c>
+      <c r="U796" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="V796" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W796" s="3"/>
+    </row>
+    <row r="797" spans="1:23">
+      <c r="A797">
+        <v>803</v>
+      </c>
+      <c r="B797" s="4">
+        <v>46226.623252314799</v>
+      </c>
+      <c r="C797" s="4">
+        <v>46226.623819444401</v>
+      </c>
+      <c r="D797" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E797" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G797" s="1">
+        <v>46225</v>
+      </c>
+      <c r="H797" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J797" t="s">
+        <v>918</v>
+      </c>
+      <c r="L797" s="3"/>
+      <c r="M797" s="3"/>
+      <c r="T797">
+        <v>6</v>
+      </c>
+      <c r="U797" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="V797" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W797" s="3"/>
+    </row>
+    <row r="798" spans="1:23">
+      <c r="A798" s="6">
+        <v>804</v>
+      </c>
+      <c r="B798" s="4">
+        <v>46227.6012962963</v>
+      </c>
+      <c r="C798" s="4">
+        <v>46227.605231481502</v>
+      </c>
+      <c r="D798" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E798" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G798" s="1">
+        <v>46216</v>
+      </c>
+      <c r="H798" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="I798" s="6"/>
+      <c r="J798" s="6"/>
+      <c r="K798" s="6"/>
+      <c r="L798" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M798" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="N798" s="6"/>
+      <c r="O798" s="6"/>
+      <c r="P798" s="6"/>
+      <c r="Q798" s="6"/>
+      <c r="R798" s="6"/>
+      <c r="S798" s="6"/>
+      <c r="T798" s="6"/>
+      <c r="U798" s="3"/>
+      <c r="V798" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="W798" s="3"/>
+    </row>
+    <row r="799" spans="1:23">
+      <c r="A799" s="6">
+        <v>805</v>
+      </c>
+      <c r="B799" s="4">
+        <v>46227.605266203696</v>
+      </c>
+      <c r="C799" s="4">
+        <v>46227.606273148202</v>
+      </c>
+      <c r="D799" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E799" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G799" s="1">
+        <v>46216</v>
+      </c>
+      <c r="H799" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I799" s="6"/>
+      <c r="J799" s="6"/>
+      <c r="K799" s="6"/>
+      <c r="L799" s="3"/>
+      <c r="M799" s="3"/>
+      <c r="N799" s="6"/>
+      <c r="O799" s="6">
+        <v>1</v>
+      </c>
+      <c r="P799" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q799" s="6">
+        <v>0</v>
+      </c>
+      <c r="R799" s="6">
+        <v>0</v>
+      </c>
+      <c r="S799" s="6"/>
+      <c r="T799" s="6">
+        <v>3</v>
+      </c>
+      <c r="U799" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="V799" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="W799" s="3"/>
+    </row>
+    <row r="800" spans="1:23">
+      <c r="A800" s="6">
+        <v>806</v>
+      </c>
+      <c r="B800" s="4">
+        <v>46227.606296296297</v>
+      </c>
+      <c r="C800" s="4">
+        <v>46227.607349537</v>
+      </c>
+      <c r="D800" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E800" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G800" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H800" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I800" s="6"/>
+      <c r="J800" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="K800" s="6"/>
+      <c r="L800" s="3"/>
+      <c r="M800" s="3"/>
+      <c r="N800" s="6"/>
+      <c r="O800" s="6"/>
+      <c r="P800" s="6"/>
+      <c r="Q800" s="6"/>
+      <c r="R800" s="6"/>
+      <c r="S800" s="6"/>
+      <c r="T800" s="6">
+        <v>20</v>
+      </c>
+      <c r="U800" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="V800" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="W800" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="593" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEDFFF89-2C16-464A-9512-D8854BC6F4E1}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5492BC-4F52-4766-A350-FD1161ECEC58}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5633" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5667" uniqueCount="1174">
   <si>
     <t>Id</t>
   </si>
@@ -3540,6 +3540,24 @@
   </si>
   <si>
     <t>Presentation on Central American freshwater mussels (title: Facilitating freshwater mussel conservation through partnership and collaboration).</t>
+  </si>
+  <si>
+    <t>Matamoros, W. A., Soto-Venegas, K. A., Valle-Hernández, M. M., &amp; Quintana, Y. (2026). Eight decades later: Dajaus monticola (Actinopterygii: Mugilidae) resurfaces in the lower Choluteca River, Honduras. Zootaxa, 5853(3), 447–450. https://doi.org/10.11646/zootaxa.5853.3.12</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.11646/zootaxa.5853.3.12</t>
+  </si>
+  <si>
+    <t>https://www.npr.org/2026/07/29/nx-s1-5884979/50-years-after-landmark-laws-some-u-s-rivers-are-recovering-but-threats-remain</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VeH3tAfsfG0</t>
+  </si>
+  <si>
+    <t>field days to collect larval fish and hester dendies data in July</t>
+  </si>
+  <si>
+    <t>talk with the ASM summer students</t>
   </si>
 </sst>
 </file>
@@ -3662,8 +3680,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W800" totalsRowShown="0">
-  <autoFilter ref="A1:W800" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W805" totalsRowShown="0">
+  <autoFilter ref="A1:W805" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W744">
     <sortCondition ref="B1:B744"/>
   </sortState>
@@ -3833,7 +3851,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="806" latestEventMarker="844">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="811" latestEventMarker="849">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4160,7 +4178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W800"/>
+  <dimension ref="A1:W805"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -35405,7 +35423,7 @@
       <c r="W797" s="3"/>
     </row>
     <row r="798" spans="1:23">
-      <c r="A798" s="6">
+      <c r="A798">
         <v>804</v>
       </c>
       <c r="B798" s="4">
@@ -35429,22 +35447,12 @@
       <c r="H798" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="I798" s="6"/>
-      <c r="J798" s="6"/>
-      <c r="K798" s="6"/>
       <c r="L798" s="3" t="s">
         <v>1164</v>
       </c>
       <c r="M798" s="3" t="s">
         <v>1165</v>
       </c>
-      <c r="N798" s="6"/>
-      <c r="O798" s="6"/>
-      <c r="P798" s="6"/>
-      <c r="Q798" s="6"/>
-      <c r="R798" s="6"/>
-      <c r="S798" s="6"/>
-      <c r="T798" s="6"/>
       <c r="U798" s="3"/>
       <c r="V798" s="3" t="s">
         <v>227</v>
@@ -35452,7 +35460,7 @@
       <c r="W798" s="3"/>
     </row>
     <row r="799" spans="1:23">
-      <c r="A799" s="6">
+      <c r="A799">
         <v>805</v>
       </c>
       <c r="B799" s="4">
@@ -35476,26 +35484,21 @@
       <c r="H799" s="3" t="s">
         <v>1056</v>
       </c>
-      <c r="I799" s="6"/>
-      <c r="J799" s="6"/>
-      <c r="K799" s="6"/>
       <c r="L799" s="3"/>
       <c r="M799" s="3"/>
-      <c r="N799" s="6"/>
-      <c r="O799" s="6">
+      <c r="O799">
         <v>1</v>
       </c>
-      <c r="P799" s="6">
+      <c r="P799">
         <v>0</v>
       </c>
-      <c r="Q799" s="6">
+      <c r="Q799">
         <v>0</v>
       </c>
-      <c r="R799" s="6">
+      <c r="R799">
         <v>0</v>
       </c>
-      <c r="S799" s="6"/>
-      <c r="T799" s="6">
+      <c r="T799">
         <v>3</v>
       </c>
       <c r="U799" s="3" t="s">
@@ -35507,7 +35510,7 @@
       <c r="W799" s="3"/>
     </row>
     <row r="800" spans="1:23">
-      <c r="A800" s="6">
+      <c r="A800">
         <v>806</v>
       </c>
       <c r="B800" s="4">
@@ -35531,20 +35534,12 @@
       <c r="H800" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I800" s="6"/>
-      <c r="J800" s="6" t="s">
+      <c r="J800" t="s">
         <v>910</v>
       </c>
-      <c r="K800" s="6"/>
       <c r="L800" s="3"/>
       <c r="M800" s="3"/>
-      <c r="N800" s="6"/>
-      <c r="O800" s="6"/>
-      <c r="P800" s="6"/>
-      <c r="Q800" s="6"/>
-      <c r="R800" s="6"/>
-      <c r="S800" s="6"/>
-      <c r="T800" s="6">
+      <c r="T800">
         <v>20</v>
       </c>
       <c r="U800" s="3" t="s">
@@ -35554,6 +35549,251 @@
         <v>227</v>
       </c>
       <c r="W800" s="3"/>
+    </row>
+    <row r="801" spans="1:23">
+      <c r="A801" s="6">
+        <v>807</v>
+      </c>
+      <c r="B801" s="4">
+        <v>46230.611342592601</v>
+      </c>
+      <c r="C801" s="4">
+        <v>46230.612951388903</v>
+      </c>
+      <c r="D801" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E801" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G801" s="1">
+        <v>46225</v>
+      </c>
+      <c r="H801" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="I801" s="6"/>
+      <c r="J801" s="6"/>
+      <c r="K801" s="6"/>
+      <c r="L801" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="M801" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="N801" s="6"/>
+      <c r="O801" s="6"/>
+      <c r="P801" s="6"/>
+      <c r="Q801" s="6"/>
+      <c r="R801" s="6"/>
+      <c r="S801" s="6"/>
+      <c r="T801" s="6"/>
+      <c r="U801" s="3"/>
+      <c r="V801" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="W801" s="3"/>
+    </row>
+    <row r="802" spans="1:23">
+      <c r="A802" s="6">
+        <v>808</v>
+      </c>
+      <c r="B802" s="4">
+        <v>46233.4</v>
+      </c>
+      <c r="C802" s="4">
+        <v>46233.400277777801</v>
+      </c>
+      <c r="D802" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E802" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G802" s="1">
+        <v>46232</v>
+      </c>
+      <c r="H802" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I802" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="J802" s="6"/>
+      <c r="K802" s="6"/>
+      <c r="L802" s="3"/>
+      <c r="M802" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="N802" s="6"/>
+      <c r="O802" s="6"/>
+      <c r="P802" s="6"/>
+      <c r="Q802" s="6"/>
+      <c r="R802" s="6"/>
+      <c r="S802" s="6"/>
+      <c r="T802" s="6"/>
+      <c r="U802" s="3"/>
+      <c r="V802" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W802" s="3"/>
+    </row>
+    <row r="803" spans="1:23">
+      <c r="A803" s="6">
+        <v>809</v>
+      </c>
+      <c r="B803" s="4">
+        <v>46233.4003703704</v>
+      </c>
+      <c r="C803" s="4">
+        <v>46233.400601851899</v>
+      </c>
+      <c r="D803" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E803" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G803" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H803" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I803" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="J803" s="6"/>
+      <c r="K803" s="6"/>
+      <c r="L803" s="3"/>
+      <c r="M803" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="N803" s="6"/>
+      <c r="O803" s="6"/>
+      <c r="P803" s="6"/>
+      <c r="Q803" s="6"/>
+      <c r="R803" s="6"/>
+      <c r="S803" s="6"/>
+      <c r="T803" s="6"/>
+      <c r="U803" s="3"/>
+      <c r="V803" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W803" s="3"/>
+    </row>
+    <row r="804" spans="1:23">
+      <c r="A804" s="6">
+        <v>810</v>
+      </c>
+      <c r="B804" s="4">
+        <v>46233.400983796302</v>
+      </c>
+      <c r="C804" s="4">
+        <v>46233.401608796303</v>
+      </c>
+      <c r="D804" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E804" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G804" s="1">
+        <v>46225</v>
+      </c>
+      <c r="H804" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I804" s="6"/>
+      <c r="J804" s="6"/>
+      <c r="K804" s="6"/>
+      <c r="L804" s="3"/>
+      <c r="M804" s="3"/>
+      <c r="N804" s="6"/>
+      <c r="O804" s="6">
+        <v>2</v>
+      </c>
+      <c r="P804" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q804" s="6">
+        <v>0</v>
+      </c>
+      <c r="R804" s="6">
+        <v>0</v>
+      </c>
+      <c r="S804" s="6"/>
+      <c r="T804" s="6">
+        <v>5</v>
+      </c>
+      <c r="U804" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="V804" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W804" s="3"/>
+    </row>
+    <row r="805" spans="1:23">
+      <c r="A805" s="6">
+        <v>811</v>
+      </c>
+      <c r="B805" s="4">
+        <v>46233.401643518497</v>
+      </c>
+      <c r="C805" s="4">
+        <v>46233.409097222197</v>
+      </c>
+      <c r="D805" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E805" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G805" s="1">
+        <v>46224</v>
+      </c>
+      <c r="H805" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I805" s="6"/>
+      <c r="J805" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="K805" s="6"/>
+      <c r="L805" s="3"/>
+      <c r="M805" s="3"/>
+      <c r="N805" s="6"/>
+      <c r="O805" s="6"/>
+      <c r="P805" s="6"/>
+      <c r="Q805" s="6"/>
+      <c r="R805" s="6"/>
+      <c r="S805" s="6"/>
+      <c r="T805" s="6">
+        <v>12</v>
+      </c>
+      <c r="U805" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="V805" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W805" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="634" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7A9723-E1C7-4929-9275-35567E31B96A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE5171FE-E214-4C34-8488-954BED889724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5730" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5814" uniqueCount="1202">
   <si>
     <t>Id</t>
   </si>
@@ -3600,6 +3600,48 @@
   </si>
   <si>
     <t>Social media post about wetlands/Marian Byrnes Park</t>
+  </si>
+  <si>
+    <t>Congressman Casten discussion and tour</t>
+  </si>
+  <si>
+    <t>conservation research</t>
+  </si>
+  <si>
+    <t>Morning talk with Guest Relations</t>
+  </si>
+  <si>
+    <t>World Lake Day: Many Lakes One Mission webinar with global presenters and global audience</t>
+  </si>
+  <si>
+    <t>Interview with Inside Climate News about the StAR project</t>
+  </si>
+  <si>
+    <t>https://www.chicagotribune.com/2026/08/31/zebra-shark-eggs-shedd-aquarium-indonesia/</t>
+  </si>
+  <si>
+    <t>Interview with the Chicago Tribune about the StAR project</t>
+  </si>
+  <si>
+    <t>Dry Tortugas trip to monitor bleaching of outplanted corals</t>
+  </si>
+  <si>
+    <t>Interview about StAR for WBEZ</t>
+  </si>
+  <si>
+    <t>DePaul student group with Kathryn Greene</t>
+  </si>
+  <si>
+    <t>Door Co Land Trust hosted webinar about the sucker research they supported through Fund For Lake Michigan (buying 60 acoustic tags for longnose suckers)</t>
+  </si>
+  <si>
+    <t>https://news.wttw.com/2026/09/15/research-has-turned-fish-swimming-ultra-marathons-every-day-chicago-river-take-humans</t>
+  </si>
+  <si>
+    <t>Water Sampling Days following the CSOs</t>
+  </si>
+  <si>
+    <t>Coral DRM survey trip in the Lower Keys</t>
   </si>
 </sst>
 </file>
@@ -3644,7 +3686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3653,7 +3695,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3734,8 +3775,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W814" totalsRowShown="0">
-  <autoFilter ref="A1:W814" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W826" totalsRowShown="0">
+  <autoFilter ref="A1:W826" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="19">
       <extLst>
@@ -3902,7 +3943,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="821" latestEventMarker="859">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="833" latestEventMarker="871">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4229,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W814"/>
+  <dimension ref="A1:W826"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -4240,7 +4281,7 @@
     <col min="16" max="16" width="48.42578125" customWidth="1"/>
     <col min="17" max="17" width="46.85546875" customWidth="1"/>
     <col min="18" max="18" width="50.28515625" customWidth="1"/>
-    <col min="21" max="21" width="62" customWidth="1"/>
+    <col min="21" max="21" width="108.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -36004,7 +36045,7 @@
       <c r="W810" s="3"/>
     </row>
     <row r="811" spans="1:23">
-      <c r="A811" s="8">
+      <c r="A811">
         <v>818</v>
       </c>
       <c r="B811" s="4">
@@ -36028,26 +36069,21 @@
       <c r="H811" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="I811" s="8"/>
-      <c r="J811" s="8"/>
-      <c r="K811" s="8"/>
       <c r="L811" s="3"/>
       <c r="M811" s="3"/>
-      <c r="N811" s="8"/>
-      <c r="O811" s="8">
+      <c r="O811">
         <v>2</v>
       </c>
-      <c r="P811" s="8">
+      <c r="P811">
         <v>0</v>
       </c>
-      <c r="Q811" s="8">
+      <c r="Q811">
         <v>0</v>
       </c>
-      <c r="R811" s="8">
+      <c r="R811">
         <v>0</v>
       </c>
-      <c r="S811" s="8"/>
-      <c r="T811" s="8">
+      <c r="T811">
         <v>14</v>
       </c>
       <c r="U811" s="3" t="s">
@@ -36059,7 +36095,7 @@
       <c r="W811" s="3"/>
     </row>
     <row r="812" spans="1:23">
-      <c r="A812" s="8">
+      <c r="A812">
         <v>819</v>
       </c>
       <c r="B812" s="4">
@@ -36083,20 +36119,12 @@
       <c r="H812" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="I812" s="8"/>
-      <c r="J812" s="8"/>
-      <c r="K812" s="8" t="s">
+      <c r="K812" t="s">
         <v>1184</v>
       </c>
       <c r="L812" s="3"/>
       <c r="M812" s="3"/>
-      <c r="N812" s="8"/>
-      <c r="O812" s="8"/>
-      <c r="P812" s="8"/>
-      <c r="Q812" s="8"/>
-      <c r="R812" s="8"/>
-      <c r="S812" s="8"/>
-      <c r="T812" s="8">
+      <c r="T812">
         <v>7</v>
       </c>
       <c r="U812" s="3" t="s">
@@ -36108,7 +36136,7 @@
       <c r="W812" s="3"/>
     </row>
     <row r="813" spans="1:23">
-      <c r="A813" s="8">
+      <c r="A813">
         <v>820</v>
       </c>
       <c r="B813" s="4">
@@ -36132,20 +36160,12 @@
       <c r="H813" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I813" s="8"/>
-      <c r="J813" s="8" t="s">
+      <c r="J813" t="s">
         <v>965</v>
       </c>
-      <c r="K813" s="8"/>
       <c r="L813" s="3"/>
       <c r="M813" s="3"/>
-      <c r="N813" s="8"/>
-      <c r="O813" s="8"/>
-      <c r="P813" s="8"/>
-      <c r="Q813" s="8"/>
-      <c r="R813" s="8"/>
-      <c r="S813" s="8"/>
-      <c r="T813" s="8">
+      <c r="T813">
         <v>50</v>
       </c>
       <c r="U813" s="3"/>
@@ -36155,7 +36175,7 @@
       <c r="W813" s="3"/>
     </row>
     <row r="814" spans="1:23">
-      <c r="A814" s="8">
+      <c r="A814">
         <v>821</v>
       </c>
       <c r="B814" s="4">
@@ -36179,22 +36199,13 @@
       <c r="H814" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="I814" s="8" t="s">
+      <c r="I814" t="s">
         <v>897</v>
       </c>
-      <c r="J814" s="8"/>
-      <c r="K814" s="8"/>
       <c r="L814" s="3"/>
       <c r="M814" s="3" t="s">
         <v>1186</v>
       </c>
-      <c r="N814" s="8"/>
-      <c r="O814" s="8"/>
-      <c r="P814" s="8"/>
-      <c r="Q814" s="8"/>
-      <c r="R814" s="8"/>
-      <c r="S814" s="8"/>
-      <c r="T814" s="8"/>
       <c r="U814" s="3" t="s">
         <v>1187</v>
       </c>
@@ -36202,6 +36213,519 @@
         <v>894</v>
       </c>
       <c r="W814" s="3"/>
+    </row>
+    <row r="815" spans="1:23">
+      <c r="A815">
+        <v>822</v>
+      </c>
+      <c r="B815" s="4">
+        <v>46260.589027777802</v>
+      </c>
+      <c r="C815" s="4">
+        <v>46260.589618055601</v>
+      </c>
+      <c r="D815" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G815" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H815" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J815" t="s">
+        <v>912</v>
+      </c>
+      <c r="L815" s="3"/>
+      <c r="M815" s="3"/>
+      <c r="T815">
+        <v>5</v>
+      </c>
+      <c r="U815" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="V815" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="W815" s="3"/>
+    </row>
+    <row r="816" spans="1:23">
+      <c r="A816">
+        <v>823</v>
+      </c>
+      <c r="B816" s="4">
+        <v>46260.589641203696</v>
+      </c>
+      <c r="C816" s="4">
+        <v>46260.590104166702</v>
+      </c>
+      <c r="D816" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G816" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H816" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J816" t="s">
+        <v>965</v>
+      </c>
+      <c r="L816" s="3"/>
+      <c r="M816" s="3"/>
+      <c r="T816">
+        <v>25</v>
+      </c>
+      <c r="U816" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="V816" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="W816" s="3"/>
+    </row>
+    <row r="817" spans="1:23">
+      <c r="A817">
+        <v>824</v>
+      </c>
+      <c r="B817" s="4">
+        <v>46261.625775462999</v>
+      </c>
+      <c r="C817" s="4">
+        <v>46261.626990740697</v>
+      </c>
+      <c r="D817" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G817" s="1">
+        <v>46261</v>
+      </c>
+      <c r="H817" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J817" t="s">
+        <v>981</v>
+      </c>
+      <c r="L817" s="3"/>
+      <c r="M817" s="3"/>
+      <c r="T817">
+        <v>82</v>
+      </c>
+      <c r="U817" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="V817" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W817" s="3"/>
+    </row>
+    <row r="818" spans="1:23">
+      <c r="A818">
+        <v>825</v>
+      </c>
+      <c r="B818" s="4">
+        <v>46265.382245370398</v>
+      </c>
+      <c r="C818" s="4">
+        <v>46265.383032407401</v>
+      </c>
+      <c r="D818" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G818" s="1">
+        <v>46246</v>
+      </c>
+      <c r="H818" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="I818" t="s">
+        <v>942</v>
+      </c>
+      <c r="L818" s="3"/>
+      <c r="M818" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="U818" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="V818" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W818" s="3"/>
+    </row>
+    <row r="819" spans="1:23">
+      <c r="A819">
+        <v>826</v>
+      </c>
+      <c r="B819" s="4">
+        <v>46265.383784722202</v>
+      </c>
+      <c r="C819" s="4">
+        <v>46265.384166666699</v>
+      </c>
+      <c r="D819" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G819" s="1">
+        <v>46265</v>
+      </c>
+      <c r="H819" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="I819" t="s">
+        <v>942</v>
+      </c>
+      <c r="L819" s="3"/>
+      <c r="M819" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="U819" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="V819" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W819" s="3"/>
+    </row>
+    <row r="820" spans="1:23">
+      <c r="A820">
+        <v>827</v>
+      </c>
+      <c r="B820" s="4">
+        <v>46266.470115740703</v>
+      </c>
+      <c r="C820" s="4">
+        <v>46266.470601851797</v>
+      </c>
+      <c r="D820" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E820" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G820" s="1">
+        <v>46261</v>
+      </c>
+      <c r="H820" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L820" s="3"/>
+      <c r="M820" s="3"/>
+      <c r="O820">
+        <v>1</v>
+      </c>
+      <c r="P820">
+        <v>0</v>
+      </c>
+      <c r="Q820">
+        <v>0</v>
+      </c>
+      <c r="R820">
+        <v>0</v>
+      </c>
+      <c r="T820">
+        <v>4</v>
+      </c>
+      <c r="U820" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="V820" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W820" s="3"/>
+    </row>
+    <row r="821" spans="1:23">
+      <c r="A821">
+        <v>828</v>
+      </c>
+      <c r="B821" s="4">
+        <v>46266.628344907404</v>
+      </c>
+      <c r="C821" s="4">
+        <v>46266.628877314797</v>
+      </c>
+      <c r="D821" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E821" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G821" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H821" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="I821" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L821" s="3"/>
+      <c r="M821" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="U821" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="V821" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W821" s="3"/>
+    </row>
+    <row r="822" spans="1:23">
+      <c r="A822">
+        <v>829</v>
+      </c>
+      <c r="B822" s="4">
+        <v>46269.585381944402</v>
+      </c>
+      <c r="C822" s="4">
+        <v>46269.585868055598</v>
+      </c>
+      <c r="D822" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E822" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G822" s="1">
+        <v>46268</v>
+      </c>
+      <c r="H822" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J822" t="s">
+        <v>916</v>
+      </c>
+      <c r="L822" s="3"/>
+      <c r="M822" s="3"/>
+      <c r="T822">
+        <v>22</v>
+      </c>
+      <c r="U822" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="V822" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W822" s="3"/>
+    </row>
+    <row r="823" spans="1:23">
+      <c r="A823">
+        <v>830</v>
+      </c>
+      <c r="B823" s="4">
+        <v>46274.607766203699</v>
+      </c>
+      <c r="C823" s="4">
+        <v>46274.608680555597</v>
+      </c>
+      <c r="D823" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E823" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G823" s="1">
+        <v>46274</v>
+      </c>
+      <c r="H823" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J823" t="s">
+        <v>981</v>
+      </c>
+      <c r="L823" s="3"/>
+      <c r="M823" s="3"/>
+      <c r="T823">
+        <v>16</v>
+      </c>
+      <c r="U823" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="V823" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W823" s="3"/>
+    </row>
+    <row r="824" spans="1:23">
+      <c r="A824">
+        <v>831</v>
+      </c>
+      <c r="B824" s="4">
+        <v>46282.640046296299</v>
+      </c>
+      <c r="C824" s="4">
+        <v>46282.640300925901</v>
+      </c>
+      <c r="D824" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E824" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G824" s="1">
+        <v>46280</v>
+      </c>
+      <c r="H824" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="I824" t="s">
+        <v>942</v>
+      </c>
+      <c r="L824" s="3"/>
+      <c r="M824" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="U824" s="3"/>
+      <c r="V824" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W824" s="3"/>
+    </row>
+    <row r="825" spans="1:23">
+      <c r="A825">
+        <v>832</v>
+      </c>
+      <c r="B825" s="4">
+        <v>46282.6403125</v>
+      </c>
+      <c r="C825" s="4">
+        <v>46282.641053240703</v>
+      </c>
+      <c r="D825" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E825" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G825" s="1">
+        <v>46239</v>
+      </c>
+      <c r="H825" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L825" s="3"/>
+      <c r="M825" s="3"/>
+      <c r="O825">
+        <v>1</v>
+      </c>
+      <c r="P825">
+        <v>0</v>
+      </c>
+      <c r="Q825">
+        <v>0</v>
+      </c>
+      <c r="R825">
+        <v>0</v>
+      </c>
+      <c r="T825">
+        <v>22</v>
+      </c>
+      <c r="U825" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="V825" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W825" s="3"/>
+    </row>
+    <row r="826" spans="1:23">
+      <c r="A826">
+        <v>833</v>
+      </c>
+      <c r="B826" s="4">
+        <v>46284.617523148103</v>
+      </c>
+      <c r="C826" s="4">
+        <v>46284.618020833303</v>
+      </c>
+      <c r="D826" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E826" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G826" s="1">
+        <v>46276</v>
+      </c>
+      <c r="H826" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L826" s="3"/>
+      <c r="M826" s="3"/>
+      <c r="O826">
+        <v>2</v>
+      </c>
+      <c r="P826">
+        <v>0</v>
+      </c>
+      <c r="Q826">
+        <v>2</v>
+      </c>
+      <c r="R826">
+        <v>1</v>
+      </c>
+      <c r="T826">
+        <v>7</v>
+      </c>
+      <c r="U826" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="V826" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W826" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE5171FE-E214-4C34-8488-954BED889724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="674" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32437D74-02B3-45E0-A5C4-2CEF65034C45}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5814" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="1216">
   <si>
     <t>Id</t>
   </si>
@@ -3642,6 +3642,48 @@
   </si>
   <si>
     <t>Coral DRM survey trip in the Lower Keys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muller E M., Petrik C., Conn T., Obsorne C C., Villoch M., Clark A S., Koch H., O’Neil K., Engelsma C., Baums I B. (2026) Assisted gene flow yields physiologically robust Acropora palmata with novel allelic and transcriptomic profiles. doi:10.1111/eva.70321 Evolutionary Applications </t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/doi/10.1111/eva.70321</t>
+  </si>
+  <si>
+    <t>Inoue, K., Douglass, S. A., Faiman, J. S., Fisher, B. E., Harris, J. L., McCrea, P., Sietman, B. E., Stodola, A. P., &amp; Zanatta, D. T. (2026). Post-glacial colonization and isolation shape fine-scale population structure in Venustaconcha ellipsiformis: implications for population-level conservation. Heredity. https://doi.org/10.1038/s41437-026-00875-0</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41437-026-00875-0</t>
+  </si>
+  <si>
+    <t>Phillips, G. L., Prow, E. M., Ackiss, A. S., Alvarez, A. C., Bonilla-Gomez, J. L., Chorba, L. H., . . . Doubek, J. P. (2026). Documentation of giant floater (Pyganodon grandis) glochidia attached to larval lake whitefish (Coregonus clupeaformis) in the Laurentian Great Lakes. Journal of Great Lakes Research. https://doi.org/10.1016/j.jglr.2026.102932</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jglr.2026.102932</t>
+  </si>
+  <si>
+    <t>Kentaro and Claire co-authored</t>
+  </si>
+  <si>
+    <t>Inoue, K., Harris, J. L., &amp; Johnson, N. A. (2026). Description of multiple cryptic species of Obovaria Rafinesque, 1819 (Bivalvia: Unionida) from the Mississippi Embayment and Gulf coastal rivers of North America. Zootaxa, 5881(4), 451–488. https://doi.org/10.11646/zootaxa.5881.4.1</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.11646/zootaxa.5881.4.1</t>
+  </si>
+  <si>
+    <t>First Training Workshop on Morphology, Anatomy, and Taxonomy of Freshwater Gastropods of Central America brings people from 4 countries</t>
+  </si>
+  <si>
+    <t>Online and in-person CPSG training: Planning for the conservation of threatened tree and freshwater species</t>
+  </si>
+  <si>
+    <t>Panelist at the Parker/Gentry Award Ceremony at the Field Museum</t>
+  </si>
+  <si>
+    <t>Students and community members</t>
+  </si>
+  <si>
+    <t>Workshop "Participatory Aquatic Monitoring with a Focus on Water Governance" and "Morphological Diagnosis and Taxonomy of Common Families of Aquatic Macroinvertebrates"</t>
   </si>
 </sst>
 </file>
@@ -3686,7 +3728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3695,6 +3737,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3775,8 +3818,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W826" totalsRowShown="0">
-  <autoFilter ref="A1:W826" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W834" totalsRowShown="0">
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:W834" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="yquintana@sheddaquarium.org"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <dateGroupItem year="2026" dateTimeGrouping="year"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val="Capacity Sharing &amp; Training: Number of people benefiting from training or experiences provided by team members including field assistants, ACCA students on the boat or locally who gain hands-on field experience, interns, volunteers, participants in conservation action planning, etc. If two team members are involved, only one team member should enter the number of people so not to overinflate counts."/>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="19">
       <extLst>
@@ -3943,7 +4006,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="833" latestEventMarker="871">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="841" latestEventMarker="879">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4270,8 +4333,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W826"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:W834"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
@@ -4355,7 +4418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" hidden="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4393,7 +4456,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" hidden="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4428,7 +4491,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" hidden="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4463,7 +4526,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" hidden="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4498,7 +4561,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" hidden="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4533,7 +4596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4568,7 +4631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4603,7 +4666,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4638,7 +4701,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4673,7 +4736,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4708,7 +4771,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4746,7 +4809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4784,7 +4847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4822,7 +4885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4860,7 +4923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4898,7 +4961,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4936,7 +4999,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" hidden="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4971,7 +5034,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" hidden="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5006,7 +5069,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5044,7 +5107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5079,7 +5142,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5117,7 +5180,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" hidden="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5152,7 +5215,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" hidden="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5193,7 +5256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" hidden="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5228,7 +5291,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" hidden="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5263,7 +5326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" hidden="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5295,7 +5358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" hidden="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5330,7 +5393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" hidden="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5362,7 +5425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" hidden="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5400,7 +5463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" hidden="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5441,7 +5504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" hidden="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5479,7 +5542,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" hidden="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5520,7 +5583,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" hidden="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5561,7 +5624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" hidden="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5602,7 +5665,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" hidden="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5643,7 +5706,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" hidden="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5684,7 +5747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" hidden="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5725,7 +5788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" hidden="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5760,7 +5823,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" hidden="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5795,7 +5858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" hidden="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5830,7 +5893,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" hidden="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5865,7 +5928,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" hidden="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5903,7 +5966,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" hidden="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5941,7 +6004,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" hidden="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5976,7 +6039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" hidden="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6011,7 +6074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" hidden="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6046,7 +6109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" hidden="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6084,7 +6147,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:23" hidden="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6116,7 +6179,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" hidden="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6154,7 +6217,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" hidden="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6189,7 +6252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" hidden="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6221,7 +6284,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:23" hidden="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6259,7 +6322,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" hidden="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6294,7 +6357,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" hidden="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6329,7 +6392,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:23" hidden="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6367,7 +6430,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:23" hidden="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6405,7 +6468,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:23" hidden="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6443,7 +6506,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" hidden="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6481,7 +6544,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:23" hidden="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6519,7 +6582,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:23" hidden="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6557,7 +6620,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:23" hidden="1">
       <c r="A62">
         <v>67</v>
       </c>
@@ -6589,7 +6652,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:23" hidden="1">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6624,7 +6687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:23" hidden="1">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6662,7 +6725,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:23" hidden="1">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6700,7 +6763,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:23" hidden="1">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6735,7 +6798,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:23" hidden="1">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6770,7 +6833,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:23" hidden="1">
       <c r="A68">
         <v>66</v>
       </c>
@@ -6811,7 +6874,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:23" hidden="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6843,7 +6906,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:23" hidden="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6878,7 +6941,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:23" hidden="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6913,7 +6976,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:23" hidden="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6951,7 +7014,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:23" hidden="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6989,7 +7052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:23" hidden="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7030,7 +7093,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:23" hidden="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7071,7 +7134,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:23" hidden="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7106,7 +7169,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:23" hidden="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7144,7 +7207,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:23" hidden="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7185,7 +7248,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
+    <row r="79" spans="1:23" hidden="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7220,7 +7283,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
+    <row r="80" spans="1:23" hidden="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7261,7 +7324,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:23" hidden="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7299,7 +7362,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:23" hidden="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7337,7 +7400,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:23" hidden="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7375,7 +7438,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:23" hidden="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7416,7 +7479,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:23" hidden="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7454,7 +7517,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:23" hidden="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7495,7 +7558,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
+    <row r="87" spans="1:23" hidden="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7527,7 +7590,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
+    <row r="88" spans="1:23" hidden="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7559,7 +7622,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
+    <row r="89" spans="1:23" hidden="1">
       <c r="A89">
         <v>95</v>
       </c>
@@ -7597,7 +7660,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" hidden="1">
       <c r="A90">
         <v>88</v>
       </c>
@@ -7638,7 +7701,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" hidden="1">
       <c r="A91">
         <v>89</v>
       </c>
@@ -7673,7 +7736,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" hidden="1">
       <c r="A92">
         <v>90</v>
       </c>
@@ -7708,7 +7771,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" hidden="1">
       <c r="A93">
         <v>91</v>
       </c>
@@ -7743,7 +7806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:23">
+    <row r="94" spans="1:23" hidden="1">
       <c r="A94">
         <v>92</v>
       </c>
@@ -7784,7 +7847,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:23" hidden="1">
       <c r="A95">
         <v>93</v>
       </c>
@@ -7822,7 +7885,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:23" hidden="1">
       <c r="A96">
         <v>94</v>
       </c>
@@ -7857,7 +7920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" hidden="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7895,7 +7958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" hidden="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7930,7 +7993,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" hidden="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7968,7 +8031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" hidden="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8003,7 +8066,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" hidden="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8038,7 +8101,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" hidden="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8078,7 +8141,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" hidden="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8118,7 +8181,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" hidden="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8158,7 +8221,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" hidden="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8195,7 +8258,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" hidden="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8232,7 +8295,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" hidden="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8269,7 +8332,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" hidden="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8306,7 +8369,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" hidden="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8343,7 +8406,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" hidden="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8378,7 +8441,7 @@
       </c>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" hidden="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8421,7 +8484,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" hidden="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8464,7 +8527,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" hidden="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8501,7 +8564,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:23">
+    <row r="114" spans="1:23" hidden="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8544,7 +8607,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" hidden="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8583,7 +8646,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:23" hidden="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8620,7 +8683,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" hidden="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8657,7 +8720,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" hidden="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8696,7 +8759,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" hidden="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8731,7 +8794,7 @@
       </c>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23">
+    <row r="120" spans="1:23" hidden="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8769,7 +8832,7 @@
       </c>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23">
+    <row r="121" spans="1:23" hidden="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8809,7 +8872,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" hidden="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8849,7 +8912,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:23" hidden="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8889,7 +8952,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" hidden="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8929,7 +8992,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:23">
+    <row r="125" spans="1:23" hidden="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8969,7 +9032,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" hidden="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9012,7 +9075,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" hidden="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9055,7 +9118,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="128" spans="1:23">
+    <row r="128" spans="1:23" hidden="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -9096,7 +9159,7 @@
       </c>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:23" hidden="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -9137,7 +9200,7 @@
       </c>
       <c r="W129" s="3"/>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" hidden="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -9180,7 +9243,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:23" hidden="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -9217,7 +9280,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" hidden="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -9254,7 +9317,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" hidden="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9291,7 +9354,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" hidden="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9334,7 +9397,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:23" hidden="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9374,7 +9437,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:23">
+    <row r="136" spans="1:23" hidden="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9414,7 +9477,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:23" hidden="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9453,7 +9516,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:23" hidden="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9492,7 +9555,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:23" hidden="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9535,7 +9598,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:23">
+    <row r="140" spans="1:23" hidden="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9575,7 +9638,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="141" spans="1:23">
+    <row r="141" spans="1:23" hidden="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9614,7 +9677,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" hidden="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9653,7 +9716,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="143" spans="1:23">
+    <row r="143" spans="1:23" hidden="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9692,7 +9755,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="144" spans="1:23">
+    <row r="144" spans="1:23" hidden="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9732,7 +9795,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="145" spans="1:23">
+    <row r="145" spans="1:23" hidden="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9775,7 +9838,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="146" spans="1:23">
+    <row r="146" spans="1:23" hidden="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9814,7 +9877,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:23" hidden="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9851,7 +9914,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="148" spans="1:23">
+    <row r="148" spans="1:23" hidden="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9888,7 +9951,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" hidden="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9925,7 +9988,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="150" spans="1:23">
+    <row r="150" spans="1:23" hidden="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9968,7 +10031,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="151" spans="1:23">
+    <row r="151" spans="1:23" hidden="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -10011,7 +10074,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="152" spans="1:23">
+    <row r="152" spans="1:23" hidden="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -10050,7 +10113,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="153" spans="1:23">
+    <row r="153" spans="1:23" hidden="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -10089,7 +10152,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -10126,7 +10189,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="155" spans="1:23">
+    <row r="155" spans="1:23" hidden="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -10165,7 +10228,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:23">
+    <row r="156" spans="1:23" hidden="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -10205,7 +10268,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="157" spans="1:23">
+    <row r="157" spans="1:23" hidden="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -10245,7 +10308,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:23">
+    <row r="158" spans="1:23" hidden="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -10285,7 +10348,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="159" spans="1:23">
+    <row r="159" spans="1:23" hidden="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -10325,7 +10388,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:23">
+    <row r="160" spans="1:23" hidden="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -10368,7 +10431,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" hidden="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -10411,7 +10474,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="162" spans="1:23">
+    <row r="162" spans="1:23" hidden="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -10448,7 +10511,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:23">
+    <row r="163" spans="1:23" hidden="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -10487,7 +10550,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:23">
+    <row r="164" spans="1:23" hidden="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -10524,7 +10587,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:23">
+    <row r="165" spans="1:23" hidden="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -10561,7 +10624,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:23">
+    <row r="166" spans="1:23" hidden="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -10596,7 +10659,7 @@
       </c>
       <c r="W166" s="3"/>
     </row>
-    <row r="167" spans="1:23">
+    <row r="167" spans="1:23" hidden="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -10635,7 +10698,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168" spans="1:23">
+    <row r="168" spans="1:23" hidden="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -10674,7 +10737,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="169" spans="1:23">
+    <row r="169" spans="1:23" hidden="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -10714,7 +10777,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:23">
+    <row r="170" spans="1:23" hidden="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10757,7 +10820,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="171" spans="1:23">
+    <row r="171" spans="1:23" hidden="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10800,7 +10863,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="172" spans="1:23">
+    <row r="172" spans="1:23" hidden="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10837,7 +10900,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="173" spans="1:23">
+    <row r="173" spans="1:23" hidden="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10874,7 +10937,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:23">
+    <row r="174" spans="1:23" hidden="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10913,7 +10976,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="175" spans="1:23">
+    <row r="175" spans="1:23" hidden="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10953,7 +11016,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="176" spans="1:23">
+    <row r="176" spans="1:23" hidden="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10993,7 +11056,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="177" spans="1:23">
+    <row r="177" spans="1:23" hidden="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11033,7 +11096,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="178" spans="1:23">
+    <row r="178" spans="1:23" hidden="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11076,7 +11139,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="179" spans="1:23">
+    <row r="179" spans="1:23" hidden="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11119,7 +11182,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="180" spans="1:23">
+    <row r="180" spans="1:23" hidden="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11162,7 +11225,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="181" spans="1:23">
+    <row r="181" spans="1:23" hidden="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11201,7 +11264,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="182" spans="1:23">
+    <row r="182" spans="1:23" hidden="1">
       <c r="A182">
         <v>182</v>
       </c>
@@ -11240,7 +11303,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="183" spans="1:23">
+    <row r="183" spans="1:23" hidden="1">
       <c r="A183">
         <v>183</v>
       </c>
@@ -11283,7 +11346,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="184" spans="1:23">
+    <row r="184" spans="1:23" hidden="1">
       <c r="A184">
         <v>184</v>
       </c>
@@ -11320,7 +11383,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="185" spans="1:23">
+    <row r="185" spans="1:23" hidden="1">
       <c r="A185">
         <v>185</v>
       </c>
@@ -11363,7 +11426,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="186" spans="1:23">
+    <row r="186" spans="1:23" hidden="1">
       <c r="A186">
         <v>186</v>
       </c>
@@ -11406,7 +11469,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" hidden="1">
       <c r="A187">
         <v>187</v>
       </c>
@@ -11443,7 +11506,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" hidden="1">
       <c r="A188">
         <v>188</v>
       </c>
@@ -11486,7 +11549,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" hidden="1">
       <c r="A189">
         <v>189</v>
       </c>
@@ -11529,7 +11592,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="190" spans="1:23">
+    <row r="190" spans="1:23" hidden="1">
       <c r="A190">
         <v>190</v>
       </c>
@@ -11566,7 +11629,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" hidden="1">
       <c r="A191">
         <v>191</v>
       </c>
@@ -11609,7 +11672,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="192" spans="1:23">
+    <row r="192" spans="1:23" hidden="1">
       <c r="A192">
         <v>192</v>
       </c>
@@ -11646,7 +11709,7 @@
       </c>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" hidden="1">
       <c r="A193">
         <v>193</v>
       </c>
@@ -11685,7 +11748,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" hidden="1">
       <c r="A194">
         <v>194</v>
       </c>
@@ -11724,7 +11787,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" hidden="1">
       <c r="A195">
         <v>195</v>
       </c>
@@ -11765,7 +11828,7 @@
       </c>
       <c r="W195" s="3"/>
     </row>
-    <row r="196" spans="1:23">
+    <row r="196" spans="1:23" hidden="1">
       <c r="A196">
         <v>196</v>
       </c>
@@ -11804,7 +11867,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:23">
+    <row r="197" spans="1:23" hidden="1">
       <c r="A197">
         <v>197</v>
       </c>
@@ -11845,7 +11908,7 @@
       </c>
       <c r="W197" s="3"/>
     </row>
-    <row r="198" spans="1:23">
+    <row r="198" spans="1:23" hidden="1">
       <c r="A198">
         <v>198</v>
       </c>
@@ -11886,7 +11949,7 @@
       </c>
       <c r="W198" s="3"/>
     </row>
-    <row r="199" spans="1:23">
+    <row r="199" spans="1:23" hidden="1">
       <c r="A199">
         <v>199</v>
       </c>
@@ -11926,7 +11989,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" hidden="1">
       <c r="A200">
         <v>200</v>
       </c>
@@ -11963,7 +12026,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" hidden="1">
       <c r="A201">
         <v>201</v>
       </c>
@@ -12000,7 +12063,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" hidden="1">
       <c r="A202">
         <v>202</v>
       </c>
@@ -12037,7 +12100,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="203" spans="1:23">
+    <row r="203" spans="1:23" hidden="1">
       <c r="A203">
         <v>223</v>
       </c>
@@ -12074,7 +12137,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="204" spans="1:23">
+    <row r="204" spans="1:23" hidden="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12111,7 +12174,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" hidden="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12151,7 +12214,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="1:23">
+    <row r="206" spans="1:23" hidden="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12186,7 +12249,7 @@
       </c>
       <c r="W206" s="3"/>
     </row>
-    <row r="207" spans="1:23">
+    <row r="207" spans="1:23" hidden="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12225,7 +12288,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="208" spans="1:23">
+    <row r="208" spans="1:23" hidden="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12264,7 +12327,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="209" spans="1:23">
+    <row r="209" spans="1:23" hidden="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12304,7 +12367,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="210" spans="1:23">
+    <row r="210" spans="1:23" hidden="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12339,7 +12402,7 @@
       </c>
       <c r="W210" s="3"/>
     </row>
-    <row r="211" spans="1:23">
+    <row r="211" spans="1:23" hidden="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12377,7 +12440,7 @@
       </c>
       <c r="W211" s="3"/>
     </row>
-    <row r="212" spans="1:23">
+    <row r="212" spans="1:23" hidden="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12415,7 +12478,7 @@
       </c>
       <c r="W212" s="3"/>
     </row>
-    <row r="213" spans="1:23">
+    <row r="213" spans="1:23" hidden="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12453,7 +12516,7 @@
       </c>
       <c r="W213" s="3"/>
     </row>
-    <row r="214" spans="1:23">
+    <row r="214" spans="1:23" hidden="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12490,7 +12553,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="215" spans="1:23">
+    <row r="215" spans="1:23" hidden="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12525,7 +12588,7 @@
       </c>
       <c r="W215" s="3"/>
     </row>
-    <row r="216" spans="1:23">
+    <row r="216" spans="1:23" hidden="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12560,7 +12623,7 @@
       </c>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23">
+    <row r="217" spans="1:23" hidden="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12597,7 +12660,7 @@
       </c>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23">
+    <row r="218" spans="1:23" hidden="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12634,7 +12697,7 @@
       </c>
       <c r="W218" s="3"/>
     </row>
-    <row r="219" spans="1:23">
+    <row r="219" spans="1:23" hidden="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12673,7 +12736,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="220" spans="1:23">
+    <row r="220" spans="1:23" hidden="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12710,7 +12773,7 @@
       </c>
       <c r="W220" s="3"/>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" hidden="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12749,7 +12812,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:23">
+    <row r="222" spans="1:23" hidden="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12790,7 +12853,7 @@
       </c>
       <c r="W222" s="3"/>
     </row>
-    <row r="223" spans="1:23">
+    <row r="223" spans="1:23" hidden="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12830,7 +12893,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="224" spans="1:23">
+    <row r="224" spans="1:23" hidden="1">
       <c r="A224">
         <v>224</v>
       </c>
@@ -12870,7 +12933,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="225" spans="1:23">
+    <row r="225" spans="1:23" hidden="1">
       <c r="A225">
         <v>225</v>
       </c>
@@ -12913,7 +12976,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:23">
+    <row r="226" spans="1:23" hidden="1">
       <c r="A226">
         <v>226</v>
       </c>
@@ -12953,7 +13016,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="227" spans="1:23">
+    <row r="227" spans="1:23" hidden="1">
       <c r="A227">
         <v>227</v>
       </c>
@@ -12993,7 +13056,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="228" spans="1:23">
+    <row r="228" spans="1:23" hidden="1">
       <c r="A228">
         <v>228</v>
       </c>
@@ -13030,7 +13093,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="229" spans="1:23">
+    <row r="229" spans="1:23" hidden="1">
       <c r="A229">
         <v>229</v>
       </c>
@@ -13073,7 +13136,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="230" spans="1:23">
+    <row r="230" spans="1:23" hidden="1">
       <c r="A230">
         <v>230</v>
       </c>
@@ -13113,7 +13176,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="231" spans="1:23">
+    <row r="231" spans="1:23" hidden="1">
       <c r="A231">
         <v>231</v>
       </c>
@@ -13153,7 +13216,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="232" spans="1:23">
+    <row r="232" spans="1:23" hidden="1">
       <c r="A232">
         <v>232</v>
       </c>
@@ -13190,7 +13253,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" hidden="1">
       <c r="A233">
         <v>233</v>
       </c>
@@ -13233,7 +13296,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" hidden="1">
       <c r="A234">
         <v>234</v>
       </c>
@@ -13272,7 +13335,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="235" spans="1:23">
+    <row r="235" spans="1:23" hidden="1">
       <c r="A235">
         <v>235</v>
       </c>
@@ -13311,7 +13374,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" hidden="1">
       <c r="A236">
         <v>236</v>
       </c>
@@ -13352,7 +13415,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="237" spans="1:23">
+    <row r="237" spans="1:23" hidden="1">
       <c r="A237">
         <v>237</v>
       </c>
@@ -13389,7 +13452,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:23">
+    <row r="238" spans="1:23" hidden="1">
       <c r="A238">
         <v>238</v>
       </c>
@@ -13429,7 +13492,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" hidden="1">
       <c r="A239">
         <v>239</v>
       </c>
@@ -13469,7 +13532,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" hidden="1">
       <c r="A240">
         <v>240</v>
       </c>
@@ -13504,7 +13567,7 @@
       </c>
       <c r="W240" s="3"/>
     </row>
-    <row r="241" spans="1:23">
+    <row r="241" spans="1:23" hidden="1">
       <c r="A241">
         <v>241</v>
       </c>
@@ -13539,7 +13602,7 @@
       </c>
       <c r="W241" s="3"/>
     </row>
-    <row r="242" spans="1:23">
+    <row r="242" spans="1:23" hidden="1">
       <c r="A242">
         <v>242</v>
       </c>
@@ -13579,7 +13642,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="243" spans="1:23">
+    <row r="243" spans="1:23" hidden="1">
       <c r="A243">
         <v>243</v>
       </c>
@@ -13614,7 +13677,7 @@
       </c>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23">
+    <row r="244" spans="1:23" hidden="1">
       <c r="A244">
         <v>244</v>
       </c>
@@ -13653,7 +13716,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="245" spans="1:23">
+    <row r="245" spans="1:23" hidden="1">
       <c r="A245">
         <v>246</v>
       </c>
@@ -13690,7 +13753,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:23">
+    <row r="246" spans="1:23" hidden="1">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13730,7 +13793,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="247" spans="1:23">
+    <row r="247" spans="1:23" hidden="1">
       <c r="A247">
         <v>247</v>
       </c>
@@ -13770,7 +13833,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="248" spans="1:23">
+    <row r="248" spans="1:23" hidden="1">
       <c r="A248">
         <v>248</v>
       </c>
@@ -13807,7 +13870,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="249" spans="1:23">
+    <row r="249" spans="1:23" hidden="1">
       <c r="A249">
         <v>249</v>
       </c>
@@ -13846,7 +13909,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" hidden="1">
       <c r="A250">
         <v>251</v>
       </c>
@@ -13889,7 +13952,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="251" spans="1:23">
+    <row r="251" spans="1:23" hidden="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13924,7 +13987,7 @@
       </c>
       <c r="W251" s="3"/>
     </row>
-    <row r="252" spans="1:23">
+    <row r="252" spans="1:23" hidden="1">
       <c r="A252">
         <v>252</v>
       </c>
@@ -13965,7 +14028,7 @@
       </c>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23">
+    <row r="253" spans="1:23" hidden="1">
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="3"/>
@@ -13979,7 +14042,7 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
     </row>
-    <row r="254" spans="1:23">
+    <row r="254" spans="1:23" hidden="1">
       <c r="A254">
         <v>256</v>
       </c>
@@ -14019,7 +14082,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" hidden="1">
       <c r="A255">
         <v>253</v>
       </c>
@@ -14056,7 +14119,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="256" spans="1:23">
+    <row r="256" spans="1:23" hidden="1">
       <c r="A256">
         <v>255</v>
       </c>
@@ -14093,7 +14156,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="257" spans="1:23">
+    <row r="257" spans="1:23" hidden="1">
       <c r="A257">
         <v>254</v>
       </c>
@@ -14130,7 +14193,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" hidden="1">
       <c r="A258">
         <v>257</v>
       </c>
@@ -14173,7 +14236,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" hidden="1">
       <c r="A259">
         <v>258</v>
       </c>
@@ -14210,7 +14273,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" hidden="1">
       <c r="A260">
         <v>259</v>
       </c>
@@ -14250,7 +14313,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" hidden="1">
       <c r="A261">
         <v>260</v>
       </c>
@@ -14290,7 +14353,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" hidden="1">
       <c r="A262">
         <v>261</v>
       </c>
@@ -14327,7 +14390,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="263" spans="1:23">
+    <row r="263" spans="1:23" hidden="1">
       <c r="A263">
         <v>262</v>
       </c>
@@ -14367,7 +14430,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" hidden="1">
       <c r="A264">
         <v>263</v>
       </c>
@@ -14407,7 +14470,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="265" spans="1:23">
+    <row r="265" spans="1:23" hidden="1">
       <c r="A265">
         <v>264</v>
       </c>
@@ -14447,7 +14510,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266">
         <v>265</v>
       </c>
@@ -14484,7 +14547,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" hidden="1">
       <c r="A267">
         <v>266</v>
       </c>
@@ -14524,7 +14587,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268">
         <v>267</v>
       </c>
@@ -14561,7 +14624,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269">
         <v>268</v>
       </c>
@@ -14598,7 +14661,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" hidden="1">
       <c r="A270">
         <v>269</v>
       </c>
@@ -14641,7 +14704,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="271" spans="1:23">
+    <row r="271" spans="1:23" hidden="1">
       <c r="A271">
         <v>270</v>
       </c>
@@ -14680,7 +14743,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" hidden="1">
       <c r="A272">
         <v>271</v>
       </c>
@@ -14721,7 +14784,7 @@
       </c>
       <c r="W272" s="3"/>
     </row>
-    <row r="273" spans="1:23">
+    <row r="273" spans="1:23" hidden="1">
       <c r="A273">
         <v>272</v>
       </c>
@@ -14764,7 +14827,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274">
         <v>276</v>
       </c>
@@ -14805,7 +14868,7 @@
       </c>
       <c r="W274" s="3"/>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275">
         <v>273</v>
       </c>
@@ -14848,7 +14911,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276">
         <v>274</v>
       </c>
@@ -14888,7 +14951,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="277" spans="1:23">
+    <row r="277" spans="1:23" hidden="1">
       <c r="A277">
         <v>275</v>
       </c>
@@ -14928,7 +14991,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="278" spans="1:23">
+    <row r="278" spans="1:23" hidden="1">
       <c r="A278">
         <v>277</v>
       </c>
@@ -14969,7 +15032,7 @@
       </c>
       <c r="W278" s="3"/>
     </row>
-    <row r="279" spans="1:23">
+    <row r="279" spans="1:23" hidden="1">
       <c r="A279">
         <v>278</v>
       </c>
@@ -15004,7 +15067,7 @@
       </c>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23">
+    <row r="280" spans="1:23" hidden="1">
       <c r="A280">
         <v>279</v>
       </c>
@@ -15042,7 +15105,7 @@
       </c>
       <c r="W280" s="3"/>
     </row>
-    <row r="281" spans="1:23">
+    <row r="281" spans="1:23" hidden="1">
       <c r="A281">
         <v>280</v>
       </c>
@@ -15085,7 +15148,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="282" spans="1:23">
+    <row r="282" spans="1:23" hidden="1">
       <c r="A282">
         <v>281</v>
       </c>
@@ -15125,7 +15188,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="283" spans="1:23">
+    <row r="283" spans="1:23" hidden="1">
       <c r="A283">
         <v>282</v>
       </c>
@@ -15165,7 +15228,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="284" spans="1:23">
+    <row r="284" spans="1:23" hidden="1">
       <c r="A284">
         <v>283</v>
       </c>
@@ -15205,7 +15268,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="285" spans="1:23">
+    <row r="285" spans="1:23" hidden="1">
       <c r="A285">
         <v>284</v>
       </c>
@@ -15245,7 +15308,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="286" spans="1:23">
+    <row r="286" spans="1:23" hidden="1">
       <c r="A286">
         <v>285</v>
       </c>
@@ -15282,7 +15345,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="287" spans="1:23">
+    <row r="287" spans="1:23" hidden="1">
       <c r="A287">
         <v>286</v>
       </c>
@@ -15325,7 +15388,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="288" spans="1:23">
+    <row r="288" spans="1:23" hidden="1">
       <c r="A288">
         <v>287</v>
       </c>
@@ -15362,7 +15425,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="289" spans="1:23">
+    <row r="289" spans="1:23" hidden="1">
       <c r="A289">
         <v>288</v>
       </c>
@@ -15405,7 +15468,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="290" spans="1:23">
+    <row r="290" spans="1:23" hidden="1">
       <c r="A290">
         <v>289</v>
       </c>
@@ -15445,7 +15508,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="291" spans="1:23">
+    <row r="291" spans="1:23" hidden="1">
       <c r="A291">
         <v>290</v>
       </c>
@@ -15482,7 +15545,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="292" spans="1:23">
+    <row r="292" spans="1:23" hidden="1">
       <c r="A292">
         <v>291</v>
       </c>
@@ -15525,7 +15588,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="293" spans="1:23">
+    <row r="293" spans="1:23" hidden="1">
       <c r="A293">
         <v>292</v>
       </c>
@@ -15568,7 +15631,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="294" spans="1:23">
+    <row r="294" spans="1:23" hidden="1">
       <c r="A294">
         <v>294</v>
       </c>
@@ -15607,7 +15670,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" hidden="1">
       <c r="A295">
         <v>293</v>
       </c>
@@ -15650,7 +15713,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296">
         <v>295</v>
       </c>
@@ -15687,7 +15750,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="297" spans="1:23">
+    <row r="297" spans="1:23" hidden="1">
       <c r="A297">
         <v>296</v>
       </c>
@@ -15726,7 +15789,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" hidden="1">
       <c r="A298">
         <v>297</v>
       </c>
@@ -15765,7 +15828,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="299" spans="1:23">
+    <row r="299" spans="1:23" hidden="1">
       <c r="A299">
         <v>298</v>
       </c>
@@ -15804,7 +15867,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="300" spans="1:23">
+    <row r="300" spans="1:23" hidden="1">
       <c r="A300">
         <v>299</v>
       </c>
@@ -15843,7 +15906,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="301" spans="1:23">
+    <row r="301" spans="1:23" hidden="1">
       <c r="A301">
         <v>300</v>
       </c>
@@ -15882,7 +15945,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:23">
+    <row r="302" spans="1:23" hidden="1">
       <c r="A302">
         <v>301</v>
       </c>
@@ -15921,7 +15984,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="303" spans="1:23">
+    <row r="303" spans="1:23" hidden="1">
       <c r="A303">
         <v>302</v>
       </c>
@@ -15960,7 +16023,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="304" spans="1:23">
+    <row r="304" spans="1:23" hidden="1">
       <c r="A304">
         <v>303</v>
       </c>
@@ -15999,7 +16062,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="305" spans="1:23">
+    <row r="305" spans="1:23" hidden="1">
       <c r="A305">
         <v>304</v>
       </c>
@@ -16038,7 +16101,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="306" spans="1:23">
+    <row r="306" spans="1:23" hidden="1">
       <c r="A306">
         <v>305</v>
       </c>
@@ -16077,7 +16140,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="307" spans="1:23">
+    <row r="307" spans="1:23" hidden="1">
       <c r="A307">
         <v>306</v>
       </c>
@@ -16115,7 +16178,7 @@
       </c>
       <c r="W307" s="3"/>
     </row>
-    <row r="308" spans="1:23">
+    <row r="308" spans="1:23" hidden="1">
       <c r="A308">
         <v>307</v>
       </c>
@@ -16154,7 +16217,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="309" spans="1:23">
+    <row r="309" spans="1:23" hidden="1">
       <c r="A309">
         <v>308</v>
       </c>
@@ -16193,7 +16256,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="310" spans="1:23">
+    <row r="310" spans="1:23" hidden="1">
       <c r="A310">
         <v>309</v>
       </c>
@@ -16230,7 +16293,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="311" spans="1:23">
+    <row r="311" spans="1:23" hidden="1">
       <c r="A311">
         <v>310</v>
       </c>
@@ -16267,7 +16330,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="312" spans="1:23">
+    <row r="312" spans="1:23" hidden="1">
       <c r="A312">
         <v>311</v>
       </c>
@@ -16304,7 +16367,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="313" spans="1:23">
+    <row r="313" spans="1:23" hidden="1">
       <c r="A313">
         <v>312</v>
       </c>
@@ -16344,7 +16407,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="314" spans="1:23">
+    <row r="314" spans="1:23" hidden="1">
       <c r="A314">
         <v>313</v>
       </c>
@@ -16381,7 +16444,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="315" spans="1:23">
+    <row r="315" spans="1:23" hidden="1">
       <c r="A315">
         <v>314</v>
       </c>
@@ -16416,7 +16479,7 @@
       </c>
       <c r="W315" s="3"/>
     </row>
-    <row r="316" spans="1:23">
+    <row r="316" spans="1:23" hidden="1">
       <c r="A316">
         <v>315</v>
       </c>
@@ -16453,7 +16516,7 @@
       </c>
       <c r="W316" s="3"/>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" hidden="1">
       <c r="A317">
         <v>316</v>
       </c>
@@ -16488,7 +16551,7 @@
       </c>
       <c r="W317" s="3"/>
     </row>
-    <row r="318" spans="1:23">
+    <row r="318" spans="1:23" hidden="1">
       <c r="A318">
         <v>317</v>
       </c>
@@ -16525,7 +16588,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" hidden="1">
       <c r="A319">
         <v>318</v>
       </c>
@@ -16560,7 +16623,7 @@
       </c>
       <c r="W319" s="3"/>
     </row>
-    <row r="320" spans="1:23">
+    <row r="320" spans="1:23" hidden="1">
       <c r="A320">
         <v>319</v>
       </c>
@@ -16599,7 +16662,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:23" hidden="1">
       <c r="A321">
         <v>320</v>
       </c>
@@ -16634,7 +16697,7 @@
       </c>
       <c r="W321" s="3"/>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" hidden="1">
       <c r="A322">
         <v>321</v>
       </c>
@@ -16671,7 +16734,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:23" hidden="1">
       <c r="A323">
         <v>322</v>
       </c>
@@ -16708,7 +16771,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" hidden="1">
       <c r="A324">
         <v>323</v>
       </c>
@@ -16745,7 +16808,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="325" spans="1:23">
+    <row r="325" spans="1:23" hidden="1">
       <c r="A325">
         <v>324</v>
       </c>
@@ -16784,7 +16847,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="326" spans="1:23">
+    <row r="326" spans="1:23" hidden="1">
       <c r="A326">
         <v>325</v>
       </c>
@@ -16821,7 +16884,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="327" spans="1:23">
+    <row r="327" spans="1:23" hidden="1">
       <c r="A327">
         <v>326</v>
       </c>
@@ -16860,7 +16923,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="328" spans="1:23">
+    <row r="328" spans="1:23" hidden="1">
       <c r="A328">
         <v>327</v>
       </c>
@@ -16895,7 +16958,7 @@
       </c>
       <c r="W328" s="3"/>
     </row>
-    <row r="329" spans="1:23">
+    <row r="329" spans="1:23" hidden="1">
       <c r="A329">
         <v>328</v>
       </c>
@@ -16930,7 +16993,7 @@
       </c>
       <c r="W329" s="3"/>
     </row>
-    <row r="330" spans="1:23">
+    <row r="330" spans="1:23" hidden="1">
       <c r="A330">
         <v>329</v>
       </c>
@@ -16965,7 +17028,7 @@
       </c>
       <c r="W330" s="3"/>
     </row>
-    <row r="331" spans="1:23">
+    <row r="331" spans="1:23" hidden="1">
       <c r="A331">
         <v>330</v>
       </c>
@@ -17000,7 +17063,7 @@
       </c>
       <c r="W331" s="3"/>
     </row>
-    <row r="332" spans="1:23">
+    <row r="332" spans="1:23" hidden="1">
       <c r="A332">
         <v>331</v>
       </c>
@@ -17035,7 +17098,7 @@
       </c>
       <c r="W332" s="3"/>
     </row>
-    <row r="333" spans="1:23">
+    <row r="333" spans="1:23" hidden="1">
       <c r="A333">
         <v>332</v>
       </c>
@@ -17074,7 +17137,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="334" spans="1:23">
+    <row r="334" spans="1:23" hidden="1">
       <c r="A334">
         <v>333</v>
       </c>
@@ -17111,7 +17174,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="335" spans="1:23">
+    <row r="335" spans="1:23" hidden="1">
       <c r="A335">
         <v>334</v>
       </c>
@@ -17151,7 +17214,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="336" spans="1:23">
+    <row r="336" spans="1:23" hidden="1">
       <c r="A336">
         <v>335</v>
       </c>
@@ -17190,7 +17253,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="337" spans="1:23">
+    <row r="337" spans="1:23" hidden="1">
       <c r="A337">
         <v>336</v>
       </c>
@@ -17227,7 +17290,7 @@
       </c>
       <c r="W337" s="3"/>
     </row>
-    <row r="338" spans="1:23">
+    <row r="338" spans="1:23" hidden="1">
       <c r="A338">
         <v>337</v>
       </c>
@@ -17264,7 +17327,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" hidden="1">
       <c r="A339">
         <v>338</v>
       </c>
@@ -17301,7 +17364,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="340" spans="1:23">
+    <row r="340" spans="1:23" hidden="1">
       <c r="A340">
         <v>339</v>
       </c>
@@ -17338,7 +17401,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="341" spans="1:23">
+    <row r="341" spans="1:23" hidden="1">
       <c r="A341">
         <v>340</v>
       </c>
@@ -17375,7 +17438,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="342" spans="1:23">
+    <row r="342" spans="1:23" hidden="1">
       <c r="A342">
         <v>341</v>
       </c>
@@ -17418,7 +17481,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="343" spans="1:23">
+    <row r="343" spans="1:23" hidden="1">
       <c r="A343">
         <v>342</v>
       </c>
@@ -17455,7 +17518,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="344" spans="1:23">
+    <row r="344" spans="1:23" hidden="1">
       <c r="A344">
         <v>343</v>
       </c>
@@ -17490,7 +17553,7 @@
       </c>
       <c r="W344" s="3"/>
     </row>
-    <row r="345" spans="1:23">
+    <row r="345" spans="1:23" hidden="1">
       <c r="A345">
         <v>344</v>
       </c>
@@ -17531,7 +17594,7 @@
       </c>
       <c r="W345" s="3"/>
     </row>
-    <row r="346" spans="1:23">
+    <row r="346" spans="1:23" hidden="1">
       <c r="A346">
         <v>345</v>
       </c>
@@ -17574,7 +17637,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="347" spans="1:23">
+    <row r="347" spans="1:23" hidden="1">
       <c r="A347">
         <v>346</v>
       </c>
@@ -17617,7 +17680,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="348" spans="1:23">
+    <row r="348" spans="1:23" hidden="1">
       <c r="A348">
         <v>347</v>
       </c>
@@ -17656,7 +17719,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="349" spans="1:23">
+    <row r="349" spans="1:23" hidden="1">
       <c r="A349">
         <v>348</v>
       </c>
@@ -17699,7 +17762,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="350" spans="1:23">
+    <row r="350" spans="1:23" hidden="1">
       <c r="A350">
         <v>349</v>
       </c>
@@ -17736,7 +17799,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="351" spans="1:23">
+    <row r="351" spans="1:23" hidden="1">
       <c r="A351">
         <v>350</v>
       </c>
@@ -17776,7 +17839,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="352" spans="1:23">
+    <row r="352" spans="1:23" hidden="1">
       <c r="A352">
         <v>351</v>
       </c>
@@ -17811,7 +17874,7 @@
       </c>
       <c r="W352" s="3"/>
     </row>
-    <row r="353" spans="1:23">
+    <row r="353" spans="1:23" hidden="1">
       <c r="A353">
         <v>352</v>
       </c>
@@ -17854,7 +17917,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="354" spans="1:23">
+    <row r="354" spans="1:23" hidden="1">
       <c r="A354">
         <v>353</v>
       </c>
@@ -17891,7 +17954,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:23">
+    <row r="355" spans="1:23" hidden="1">
       <c r="A355">
         <v>354</v>
       </c>
@@ -17930,7 +17993,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="356" spans="1:23">
+    <row r="356" spans="1:23" hidden="1">
       <c r="A356">
         <v>355</v>
       </c>
@@ -17967,7 +18030,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="357" spans="1:23">
+    <row r="357" spans="1:23" hidden="1">
       <c r="A357">
         <v>356</v>
       </c>
@@ -18004,7 +18067,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="358" spans="1:23">
+    <row r="358" spans="1:23" hidden="1">
       <c r="A358">
         <v>357</v>
       </c>
@@ -18043,7 +18106,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="359" spans="1:23">
+    <row r="359" spans="1:23" hidden="1">
       <c r="A359">
         <v>358</v>
       </c>
@@ -18082,7 +18145,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="360" spans="1:23">
+    <row r="360" spans="1:23" hidden="1">
       <c r="A360">
         <v>359</v>
       </c>
@@ -18122,7 +18185,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="361" spans="1:23">
+    <row r="361" spans="1:23" hidden="1">
       <c r="A361">
         <v>360</v>
       </c>
@@ -18165,7 +18228,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="362" spans="1:23">
+    <row r="362" spans="1:23" hidden="1">
       <c r="A362">
         <v>361</v>
       </c>
@@ -18202,7 +18265,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="363" spans="1:23">
+    <row r="363" spans="1:23" hidden="1">
       <c r="A363">
         <v>362</v>
       </c>
@@ -18241,7 +18304,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="364" spans="1:23">
+    <row r="364" spans="1:23" hidden="1">
       <c r="A364">
         <v>363</v>
       </c>
@@ -18280,7 +18343,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="365" spans="1:23">
+    <row r="365" spans="1:23" hidden="1">
       <c r="A365">
         <v>364</v>
       </c>
@@ -18317,7 +18380,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="366" spans="1:23">
+    <row r="366" spans="1:23" hidden="1">
       <c r="A366">
         <v>365</v>
       </c>
@@ -18356,7 +18419,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="367" spans="1:23">
+    <row r="367" spans="1:23" hidden="1">
       <c r="A367">
         <v>366</v>
       </c>
@@ -18395,7 +18458,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="368" spans="1:23">
+    <row r="368" spans="1:23" hidden="1">
       <c r="A368">
         <v>367</v>
       </c>
@@ -18432,7 +18495,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="369" spans="1:23">
+    <row r="369" spans="1:23" hidden="1">
       <c r="A369">
         <v>368</v>
       </c>
@@ -18469,7 +18532,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="370" spans="1:23">
+    <row r="370" spans="1:23" hidden="1">
       <c r="A370">
         <v>369</v>
       </c>
@@ -18506,7 +18569,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="371" spans="1:23">
+    <row r="371" spans="1:23" hidden="1">
       <c r="A371">
         <v>370</v>
       </c>
@@ -18549,7 +18612,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="372" spans="1:23">
+    <row r="372" spans="1:23" hidden="1">
       <c r="A372">
         <v>371</v>
       </c>
@@ -18586,7 +18649,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="373" spans="1:23">
+    <row r="373" spans="1:23" hidden="1">
       <c r="A373">
         <v>372</v>
       </c>
@@ -18623,7 +18686,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="374" spans="1:23">
+    <row r="374" spans="1:23" hidden="1">
       <c r="A374">
         <v>373</v>
       </c>
@@ -18666,7 +18729,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="375" spans="1:23">
+    <row r="375" spans="1:23" hidden="1">
       <c r="A375">
         <v>374</v>
       </c>
@@ -18703,7 +18766,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="376" spans="1:23">
+    <row r="376" spans="1:23" hidden="1">
       <c r="A376">
         <v>375</v>
       </c>
@@ -18746,7 +18809,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="377" spans="1:23">
+    <row r="377" spans="1:23" hidden="1">
       <c r="A377">
         <v>376</v>
       </c>
@@ -18786,7 +18849,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="378" spans="1:23">
+    <row r="378" spans="1:23" hidden="1">
       <c r="A378">
         <v>377</v>
       </c>
@@ -18823,7 +18886,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="379" spans="1:23">
+    <row r="379" spans="1:23" hidden="1">
       <c r="A379">
         <v>378</v>
       </c>
@@ -18860,7 +18923,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="380" spans="1:23">
+    <row r="380" spans="1:23" hidden="1">
       <c r="A380">
         <v>379</v>
       </c>
@@ -18897,7 +18960,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="381" spans="1:23">
+    <row r="381" spans="1:23" hidden="1">
       <c r="A381">
         <v>380</v>
       </c>
@@ -18937,7 +19000,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="382" spans="1:23">
+    <row r="382" spans="1:23" hidden="1">
       <c r="A382">
         <v>381</v>
       </c>
@@ -18977,7 +19040,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="383" spans="1:23">
+    <row r="383" spans="1:23" hidden="1">
       <c r="A383">
         <v>382</v>
       </c>
@@ -19014,7 +19077,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="384" spans="1:23">
+    <row r="384" spans="1:23" hidden="1">
       <c r="A384">
         <v>383</v>
       </c>
@@ -19053,7 +19116,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="385" spans="1:23">
+    <row r="385" spans="1:23" hidden="1">
       <c r="A385">
         <v>384</v>
       </c>
@@ -19092,7 +19155,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="386" spans="1:23">
+    <row r="386" spans="1:23" hidden="1">
       <c r="A386">
         <v>385</v>
       </c>
@@ -19131,7 +19194,7 @@
       </c>
       <c r="W386" s="3"/>
     </row>
-    <row r="387" spans="1:23">
+    <row r="387" spans="1:23" hidden="1">
       <c r="A387">
         <v>386</v>
       </c>
@@ -19170,7 +19233,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="388" spans="1:23">
+    <row r="388" spans="1:23" hidden="1">
       <c r="A388">
         <v>387</v>
       </c>
@@ -19210,7 +19273,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="389" spans="1:23">
+    <row r="389" spans="1:23" hidden="1">
       <c r="A389">
         <v>388</v>
       </c>
@@ -19250,7 +19313,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="390" spans="1:23">
+    <row r="390" spans="1:23" hidden="1">
       <c r="A390">
         <v>389</v>
       </c>
@@ -19291,7 +19354,7 @@
       </c>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23">
+    <row r="391" spans="1:23" hidden="1">
       <c r="A391">
         <v>390</v>
       </c>
@@ -19332,7 +19395,7 @@
       </c>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23">
+    <row r="392" spans="1:23" hidden="1">
       <c r="A392">
         <v>391</v>
       </c>
@@ -19373,7 +19436,7 @@
       </c>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23">
+    <row r="393" spans="1:23" hidden="1">
       <c r="A393">
         <v>392</v>
       </c>
@@ -19414,7 +19477,7 @@
       </c>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23">
+    <row r="394" spans="1:23" hidden="1">
       <c r="A394">
         <v>393</v>
       </c>
@@ -19451,7 +19514,7 @@
       </c>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23">
+    <row r="395" spans="1:23" hidden="1">
       <c r="A395">
         <v>394</v>
       </c>
@@ -19486,7 +19549,7 @@
       </c>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23">
+    <row r="396" spans="1:23" hidden="1">
       <c r="A396">
         <v>395</v>
       </c>
@@ -19523,7 +19586,7 @@
       </c>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23">
+    <row r="397" spans="1:23" hidden="1">
       <c r="A397">
         <v>396</v>
       </c>
@@ -19558,7 +19621,7 @@
       </c>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23">
+    <row r="398" spans="1:23" hidden="1">
       <c r="A398">
         <v>397</v>
       </c>
@@ -19593,7 +19656,7 @@
       </c>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23">
+    <row r="399" spans="1:23" hidden="1">
       <c r="A399">
         <v>398</v>
       </c>
@@ -19628,7 +19691,7 @@
       </c>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23">
+    <row r="400" spans="1:23" hidden="1">
       <c r="A400">
         <v>399</v>
       </c>
@@ -19663,7 +19726,7 @@
       </c>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23">
+    <row r="401" spans="1:23" hidden="1">
       <c r="A401">
         <v>400</v>
       </c>
@@ -19704,7 +19767,7 @@
       </c>
       <c r="W401" s="3"/>
     </row>
-    <row r="402" spans="1:23">
+    <row r="402" spans="1:23" hidden="1">
       <c r="A402">
         <v>402</v>
       </c>
@@ -19743,7 +19806,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="403" spans="1:23">
+    <row r="403" spans="1:23" hidden="1">
       <c r="A403">
         <v>403</v>
       </c>
@@ -19786,7 +19849,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="404" spans="1:23">
+    <row r="404" spans="1:23" hidden="1">
       <c r="A404">
         <v>404</v>
       </c>
@@ -19829,7 +19892,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="405" spans="1:23">
+    <row r="405" spans="1:23" hidden="1">
       <c r="A405">
         <v>405</v>
       </c>
@@ -19872,7 +19935,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="406" spans="1:23">
+    <row r="406" spans="1:23" hidden="1">
       <c r="A406">
         <v>406</v>
       </c>
@@ -19909,7 +19972,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="407" spans="1:23">
+    <row r="407" spans="1:23" hidden="1">
       <c r="A407">
         <v>407</v>
       </c>
@@ -19952,7 +20015,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="408" spans="1:23">
+    <row r="408" spans="1:23" hidden="1">
       <c r="A408">
         <v>408</v>
       </c>
@@ -19995,7 +20058,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="409" spans="1:23">
+    <row r="409" spans="1:23" hidden="1">
       <c r="A409">
         <v>409</v>
       </c>
@@ -20038,7 +20101,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="410" spans="1:23">
+    <row r="410" spans="1:23" hidden="1">
       <c r="A410">
         <v>410</v>
       </c>
@@ -20077,7 +20140,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="411" spans="1:23">
+    <row r="411" spans="1:23" hidden="1">
       <c r="A411">
         <v>411</v>
       </c>
@@ -20116,7 +20179,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="412" spans="1:23">
+    <row r="412" spans="1:23" hidden="1">
       <c r="A412">
         <v>412</v>
       </c>
@@ -20151,7 +20214,7 @@
       </c>
       <c r="W412" s="3"/>
     </row>
-    <row r="413" spans="1:23">
+    <row r="413" spans="1:23" hidden="1">
       <c r="A413">
         <v>413</v>
       </c>
@@ -20190,7 +20253,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="414" spans="1:23">
+    <row r="414" spans="1:23" hidden="1">
       <c r="A414">
         <v>414</v>
       </c>
@@ -20233,7 +20296,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="415" spans="1:23">
+    <row r="415" spans="1:23" hidden="1">
       <c r="A415">
         <v>415</v>
       </c>
@@ -20272,7 +20335,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="416" spans="1:23">
+    <row r="416" spans="1:23" hidden="1">
       <c r="A416">
         <v>416</v>
       </c>
@@ -20315,7 +20378,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="417" spans="1:23">
+    <row r="417" spans="1:23" hidden="1">
       <c r="A417">
         <v>417</v>
       </c>
@@ -20354,7 +20417,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="418" spans="1:23">
+    <row r="418" spans="1:23" hidden="1">
       <c r="A418">
         <v>418</v>
       </c>
@@ -20391,7 +20454,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="419" spans="1:23">
+    <row r="419" spans="1:23" hidden="1">
       <c r="A419">
         <v>419</v>
       </c>
@@ -20434,7 +20497,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="420" spans="1:23">
+    <row r="420" spans="1:23" hidden="1">
       <c r="A420">
         <v>420</v>
       </c>
@@ -20474,7 +20537,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="421" spans="1:23">
+    <row r="421" spans="1:23" hidden="1">
       <c r="A421">
         <v>421</v>
       </c>
@@ -20511,7 +20574,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="422" spans="1:23">
+    <row r="422" spans="1:23" hidden="1">
       <c r="A422">
         <v>422</v>
       </c>
@@ -20554,7 +20617,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="423" spans="1:23">
+    <row r="423" spans="1:23" hidden="1">
       <c r="A423">
         <v>423</v>
       </c>
@@ -20597,7 +20660,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="424" spans="1:23">
+    <row r="424" spans="1:23" hidden="1">
       <c r="A424">
         <v>424</v>
       </c>
@@ -20640,7 +20703,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="425" spans="1:23">
+    <row r="425" spans="1:23" hidden="1">
       <c r="A425">
         <v>425</v>
       </c>
@@ -20681,7 +20744,7 @@
       </c>
       <c r="W425" s="3"/>
     </row>
-    <row r="426" spans="1:23">
+    <row r="426" spans="1:23" hidden="1">
       <c r="A426">
         <v>426</v>
       </c>
@@ -20724,7 +20787,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="427" spans="1:23">
+    <row r="427" spans="1:23" hidden="1">
       <c r="A427">
         <v>427</v>
       </c>
@@ -20767,7 +20830,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="428" spans="1:23">
+    <row r="428" spans="1:23" hidden="1">
       <c r="A428">
         <v>428</v>
       </c>
@@ -20810,7 +20873,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="429" spans="1:23">
+    <row r="429" spans="1:23" hidden="1">
       <c r="A429">
         <v>429</v>
       </c>
@@ -20847,7 +20910,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="430" spans="1:23">
+    <row r="430" spans="1:23" hidden="1">
       <c r="A430">
         <v>430</v>
       </c>
@@ -20886,7 +20949,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="431" spans="1:23">
+    <row r="431" spans="1:23" hidden="1">
       <c r="A431">
         <v>431</v>
       </c>
@@ -20925,7 +20988,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="432" spans="1:23">
+    <row r="432" spans="1:23" hidden="1">
       <c r="A432">
         <v>432</v>
       </c>
@@ -20963,7 +21026,7 @@
       </c>
       <c r="W432" s="3"/>
     </row>
-    <row r="433" spans="1:23">
+    <row r="433" spans="1:23" hidden="1">
       <c r="A433">
         <v>433</v>
       </c>
@@ -21001,7 +21064,7 @@
       </c>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23">
+    <row r="434" spans="1:23" hidden="1">
       <c r="A434">
         <v>434</v>
       </c>
@@ -21039,7 +21102,7 @@
       </c>
       <c r="W434" s="3"/>
     </row>
-    <row r="435" spans="1:23">
+    <row r="435" spans="1:23" hidden="1">
       <c r="A435">
         <v>435</v>
       </c>
@@ -21077,7 +21140,7 @@
       </c>
       <c r="W435" s="3"/>
     </row>
-    <row r="436" spans="1:23">
+    <row r="436" spans="1:23" hidden="1">
       <c r="A436">
         <v>436</v>
       </c>
@@ -21115,7 +21178,7 @@
       </c>
       <c r="W436" s="3"/>
     </row>
-    <row r="437" spans="1:23">
+    <row r="437" spans="1:23" hidden="1">
       <c r="A437">
         <v>437</v>
       </c>
@@ -21150,7 +21213,7 @@
       </c>
       <c r="W437" s="3"/>
     </row>
-    <row r="438" spans="1:23">
+    <row r="438" spans="1:23" hidden="1">
       <c r="A438">
         <v>438</v>
       </c>
@@ -21187,7 +21250,7 @@
       </c>
       <c r="W438" s="3"/>
     </row>
-    <row r="439" spans="1:23">
+    <row r="439" spans="1:23" hidden="1">
       <c r="A439">
         <v>439</v>
       </c>
@@ -21224,7 +21287,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="440" spans="1:23">
+    <row r="440" spans="1:23" hidden="1">
       <c r="A440">
         <v>440</v>
       </c>
@@ -21261,7 +21324,7 @@
       </c>
       <c r="W440" s="3"/>
     </row>
-    <row r="441" spans="1:23">
+    <row r="441" spans="1:23" hidden="1">
       <c r="A441">
         <v>441</v>
       </c>
@@ -21298,7 +21361,7 @@
       </c>
       <c r="W441" s="3"/>
     </row>
-    <row r="442" spans="1:23">
+    <row r="442" spans="1:23" hidden="1">
       <c r="A442">
         <v>442</v>
       </c>
@@ -21339,7 +21402,7 @@
       </c>
       <c r="W442" s="3"/>
     </row>
-    <row r="443" spans="1:23">
+    <row r="443" spans="1:23" hidden="1">
       <c r="A443">
         <v>443</v>
       </c>
@@ -21378,7 +21441,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="444" spans="1:23">
+    <row r="444" spans="1:23" hidden="1">
       <c r="A444">
         <v>444</v>
       </c>
@@ -21419,7 +21482,7 @@
       </c>
       <c r="W444" s="3"/>
     </row>
-    <row r="445" spans="1:23">
+    <row r="445" spans="1:23" hidden="1">
       <c r="A445">
         <v>445</v>
       </c>
@@ -21459,7 +21522,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="446" spans="1:23">
+    <row r="446" spans="1:23" hidden="1">
       <c r="A446">
         <v>446</v>
       </c>
@@ -21499,7 +21562,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="447" spans="1:23">
+    <row r="447" spans="1:23" hidden="1">
       <c r="A447">
         <v>447</v>
       </c>
@@ -21536,7 +21599,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="448" spans="1:23">
+    <row r="448" spans="1:23" hidden="1">
       <c r="A448">
         <v>448</v>
       </c>
@@ -21575,7 +21638,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="449" spans="1:23">
+    <row r="449" spans="1:23" hidden="1">
       <c r="A449">
         <v>449</v>
       </c>
@@ -21614,7 +21677,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="450" spans="1:23">
+    <row r="450" spans="1:23" hidden="1">
       <c r="A450">
         <v>450</v>
       </c>
@@ -21653,7 +21716,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="451" spans="1:23">
+    <row r="451" spans="1:23" hidden="1">
       <c r="A451">
         <v>451</v>
       </c>
@@ -21693,7 +21756,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="452" spans="1:23">
+    <row r="452" spans="1:23" hidden="1">
       <c r="A452">
         <v>452</v>
       </c>
@@ -21730,7 +21793,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="453" spans="1:23">
+    <row r="453" spans="1:23" hidden="1">
       <c r="A453">
         <v>453</v>
       </c>
@@ -21765,7 +21828,7 @@
       </c>
       <c r="W453" s="3"/>
     </row>
-    <row r="454" spans="1:23">
+    <row r="454" spans="1:23" hidden="1">
       <c r="A454">
         <v>454</v>
       </c>
@@ -21804,7 +21867,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="455" spans="1:23">
+    <row r="455" spans="1:23" hidden="1">
       <c r="A455">
         <v>455</v>
       </c>
@@ -21843,7 +21906,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="456" spans="1:23">
+    <row r="456" spans="1:23" hidden="1">
       <c r="A456">
         <v>456</v>
       </c>
@@ -21882,7 +21945,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="457" spans="1:23">
+    <row r="457" spans="1:23" hidden="1">
       <c r="A457">
         <v>457</v>
       </c>
@@ -21921,7 +21984,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="458" spans="1:23">
+    <row r="458" spans="1:23" hidden="1">
       <c r="A458">
         <v>458</v>
       </c>
@@ -21960,7 +22023,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="459" spans="1:23">
+    <row r="459" spans="1:23" hidden="1">
       <c r="A459">
         <v>459</v>
       </c>
@@ -21999,7 +22062,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="460" spans="1:23">
+    <row r="460" spans="1:23" hidden="1">
       <c r="A460">
         <v>460</v>
       </c>
@@ -22038,7 +22101,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="461" spans="1:23">
+    <row r="461" spans="1:23" hidden="1">
       <c r="A461">
         <v>461</v>
       </c>
@@ -22077,7 +22140,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="462" spans="1:23">
+    <row r="462" spans="1:23" hidden="1">
       <c r="A462">
         <v>462</v>
       </c>
@@ -22116,7 +22179,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="463" spans="1:23">
+    <row r="463" spans="1:23" hidden="1">
       <c r="A463">
         <v>463</v>
       </c>
@@ -22155,7 +22218,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="464" spans="1:23">
+    <row r="464" spans="1:23" hidden="1">
       <c r="A464">
         <v>464</v>
       </c>
@@ -22194,7 +22257,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="465" spans="1:23">
+    <row r="465" spans="1:23" hidden="1">
       <c r="A465">
         <v>465</v>
       </c>
@@ -22233,7 +22296,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="466" spans="1:23">
+    <row r="466" spans="1:23" hidden="1">
       <c r="A466">
         <v>466</v>
       </c>
@@ -22272,7 +22335,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="467" spans="1:23">
+    <row r="467" spans="1:23" hidden="1">
       <c r="A467">
         <v>467</v>
       </c>
@@ -22311,7 +22374,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="468" spans="1:23">
+    <row r="468" spans="1:23" hidden="1">
       <c r="A468">
         <v>468</v>
       </c>
@@ -22350,7 +22413,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="469" spans="1:23">
+    <row r="469" spans="1:23" hidden="1">
       <c r="A469">
         <v>469</v>
       </c>
@@ -22389,7 +22452,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="470" spans="1:23">
+    <row r="470" spans="1:23" hidden="1">
       <c r="A470">
         <v>470</v>
       </c>
@@ -22426,7 +22489,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="471" spans="1:23">
+    <row r="471" spans="1:23" hidden="1">
       <c r="A471">
         <v>471</v>
       </c>
@@ -22466,7 +22529,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="472" spans="1:23">
+    <row r="472" spans="1:23" hidden="1">
       <c r="A472">
         <v>472</v>
       </c>
@@ -22503,7 +22566,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="473" spans="1:23">
+    <row r="473" spans="1:23" hidden="1">
       <c r="A473">
         <v>473</v>
       </c>
@@ -22542,7 +22605,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="474" spans="1:23">
+    <row r="474" spans="1:23" hidden="1">
       <c r="A474">
         <v>474</v>
       </c>
@@ -22581,7 +22644,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="475" spans="1:23">
+    <row r="475" spans="1:23" hidden="1">
       <c r="A475">
         <v>475</v>
       </c>
@@ -22618,7 +22681,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="476" spans="1:23">
+    <row r="476" spans="1:23" hidden="1">
       <c r="A476">
         <v>476</v>
       </c>
@@ -22655,7 +22718,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="477" spans="1:23">
+    <row r="477" spans="1:23" hidden="1">
       <c r="A477">
         <v>477</v>
       </c>
@@ -22698,7 +22761,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="478" spans="1:23">
+    <row r="478" spans="1:23" hidden="1">
       <c r="A478">
         <v>478</v>
       </c>
@@ -22737,7 +22800,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="479" spans="1:23">
+    <row r="479" spans="1:23" hidden="1">
       <c r="A479">
         <v>479</v>
       </c>
@@ -22776,7 +22839,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="480" spans="1:23">
+    <row r="480" spans="1:23" hidden="1">
       <c r="A480">
         <v>480</v>
       </c>
@@ -22813,7 +22876,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="481" spans="1:23">
+    <row r="481" spans="1:23" hidden="1">
       <c r="A481">
         <v>481</v>
       </c>
@@ -22850,7 +22913,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="482" spans="1:23">
+    <row r="482" spans="1:23" hidden="1">
       <c r="A482">
         <v>482</v>
       </c>
@@ -22887,7 +22950,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="483" spans="1:23">
+    <row r="483" spans="1:23" hidden="1">
       <c r="A483">
         <v>483</v>
       </c>
@@ -22926,7 +22989,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="484" spans="1:23">
+    <row r="484" spans="1:23" hidden="1">
       <c r="A484">
         <v>484</v>
       </c>
@@ -22965,7 +23028,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="485" spans="1:23">
+    <row r="485" spans="1:23" hidden="1">
       <c r="A485">
         <v>485</v>
       </c>
@@ -23002,7 +23065,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="486" spans="1:23">
+    <row r="486" spans="1:23" hidden="1">
       <c r="A486">
         <v>486</v>
       </c>
@@ -23039,7 +23102,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="487" spans="1:23">
+    <row r="487" spans="1:23" hidden="1">
       <c r="A487">
         <v>487</v>
       </c>
@@ -23076,7 +23139,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="488" spans="1:23">
+    <row r="488" spans="1:23" hidden="1">
       <c r="A488">
         <v>488</v>
       </c>
@@ -23114,7 +23177,7 @@
       </c>
       <c r="W488" s="3"/>
     </row>
-    <row r="489" spans="1:23">
+    <row r="489" spans="1:23" hidden="1">
       <c r="A489">
         <v>489</v>
       </c>
@@ -23153,7 +23216,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="490" spans="1:23">
+    <row r="490" spans="1:23" hidden="1">
       <c r="A490">
         <v>490</v>
       </c>
@@ -23192,7 +23255,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="491" spans="1:23">
+    <row r="491" spans="1:23" hidden="1">
       <c r="A491">
         <v>491</v>
       </c>
@@ -23229,7 +23292,7 @@
       </c>
       <c r="W491" s="3"/>
     </row>
-    <row r="492" spans="1:23">
+    <row r="492" spans="1:23" hidden="1">
       <c r="A492">
         <v>492</v>
       </c>
@@ -23266,7 +23329,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="493" spans="1:23">
+    <row r="493" spans="1:23" hidden="1">
       <c r="A493">
         <v>493</v>
       </c>
@@ -23304,7 +23367,7 @@
       </c>
       <c r="W493" s="3"/>
     </row>
-    <row r="494" spans="1:23">
+    <row r="494" spans="1:23" hidden="1">
       <c r="A494">
         <v>494</v>
       </c>
@@ -23341,7 +23404,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="495" spans="1:23">
+    <row r="495" spans="1:23" hidden="1">
       <c r="A495">
         <v>495</v>
       </c>
@@ -23378,7 +23441,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="496" spans="1:23">
+    <row r="496" spans="1:23" hidden="1">
       <c r="A496">
         <v>496</v>
       </c>
@@ -23421,7 +23484,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="497" spans="1:23">
+    <row r="497" spans="1:23" hidden="1">
       <c r="A497">
         <v>497</v>
       </c>
@@ -23458,7 +23521,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="498" spans="1:23">
+    <row r="498" spans="1:23" hidden="1">
       <c r="A498">
         <v>498</v>
       </c>
@@ -23497,7 +23560,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="499" spans="1:23">
+    <row r="499" spans="1:23" hidden="1">
       <c r="A499">
         <v>499</v>
       </c>
@@ -23540,7 +23603,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="500" spans="1:23">
+    <row r="500" spans="1:23" hidden="1">
       <c r="A500">
         <v>500</v>
       </c>
@@ -23583,7 +23646,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="501" spans="1:23">
+    <row r="501" spans="1:23" hidden="1">
       <c r="A501">
         <v>501</v>
       </c>
@@ -23620,7 +23683,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="502" spans="1:23">
+    <row r="502" spans="1:23" hidden="1">
       <c r="A502">
         <v>502</v>
       </c>
@@ -23659,7 +23722,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="503" spans="1:23">
+    <row r="503" spans="1:23" hidden="1">
       <c r="A503">
         <v>503</v>
       </c>
@@ -23696,7 +23759,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="504" spans="1:23">
+    <row r="504" spans="1:23" hidden="1">
       <c r="A504">
         <v>504</v>
       </c>
@@ -23739,7 +23802,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="505" spans="1:23">
+    <row r="505" spans="1:23" hidden="1">
       <c r="A505">
         <v>505</v>
       </c>
@@ -23778,7 +23841,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="506" spans="1:23">
+    <row r="506" spans="1:23" hidden="1">
       <c r="A506">
         <v>506</v>
       </c>
@@ -23817,7 +23880,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="507" spans="1:23">
+    <row r="507" spans="1:23" hidden="1">
       <c r="A507">
         <v>507</v>
       </c>
@@ -23856,7 +23919,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="508" spans="1:23">
+    <row r="508" spans="1:23" hidden="1">
       <c r="A508">
         <v>508</v>
       </c>
@@ -23899,7 +23962,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="509" spans="1:23">
+    <row r="509" spans="1:23" hidden="1">
       <c r="A509">
         <v>509</v>
       </c>
@@ -23936,7 +23999,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="510" spans="1:23">
+    <row r="510" spans="1:23" hidden="1">
       <c r="A510">
         <v>510</v>
       </c>
@@ -23975,7 +24038,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="511" spans="1:23">
+    <row r="511" spans="1:23" hidden="1">
       <c r="A511">
         <v>511</v>
       </c>
@@ -24014,7 +24077,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="512" spans="1:23">
+    <row r="512" spans="1:23" hidden="1">
       <c r="A512">
         <v>512</v>
       </c>
@@ -24053,7 +24116,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="513" spans="1:23">
+    <row r="513" spans="1:23" hidden="1">
       <c r="A513">
         <v>513</v>
       </c>
@@ -24092,7 +24155,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="514" spans="1:23">
+    <row r="514" spans="1:23" hidden="1">
       <c r="A514">
         <v>514</v>
       </c>
@@ -24131,7 +24194,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="515" spans="1:23">
+    <row r="515" spans="1:23" hidden="1">
       <c r="A515">
         <v>515</v>
       </c>
@@ -24174,7 +24237,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="516" spans="1:23">
+    <row r="516" spans="1:23" hidden="1">
       <c r="A516">
         <v>516</v>
       </c>
@@ -24213,7 +24276,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="517" spans="1:23">
+    <row r="517" spans="1:23" hidden="1">
       <c r="A517">
         <v>517</v>
       </c>
@@ -24252,7 +24315,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="518" spans="1:23">
+    <row r="518" spans="1:23" hidden="1">
       <c r="A518">
         <v>518</v>
       </c>
@@ -24289,7 +24352,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="519" spans="1:23">
+    <row r="519" spans="1:23" hidden="1">
       <c r="A519">
         <v>519</v>
       </c>
@@ -24329,7 +24392,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="520" spans="1:23">
+    <row r="520" spans="1:23" hidden="1">
       <c r="A520">
         <v>520</v>
       </c>
@@ -24366,7 +24429,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="521" spans="1:23">
+    <row r="521" spans="1:23" hidden="1">
       <c r="A521">
         <v>521</v>
       </c>
@@ -24409,7 +24472,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="522" spans="1:23">
+    <row r="522" spans="1:23" hidden="1">
       <c r="A522">
         <v>522</v>
       </c>
@@ -24448,7 +24511,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="523" spans="1:23">
+    <row r="523" spans="1:23" hidden="1">
       <c r="A523">
         <v>523</v>
       </c>
@@ -24487,7 +24550,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="524" spans="1:23">
+    <row r="524" spans="1:23" hidden="1">
       <c r="A524">
         <v>524</v>
       </c>
@@ -24524,7 +24587,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="525" spans="1:23">
+    <row r="525" spans="1:23" hidden="1">
       <c r="A525">
         <v>525</v>
       </c>
@@ -24561,7 +24624,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="526" spans="1:23">
+    <row r="526" spans="1:23" hidden="1">
       <c r="A526">
         <v>526</v>
       </c>
@@ -24604,7 +24667,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="527" spans="1:23">
+    <row r="527" spans="1:23" hidden="1">
       <c r="A527">
         <v>527</v>
       </c>
@@ -24647,7 +24710,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="528" spans="1:23">
+    <row r="528" spans="1:23" hidden="1">
       <c r="A528">
         <v>528</v>
       </c>
@@ -24690,7 +24753,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="529" spans="1:23">
+    <row r="529" spans="1:23" hidden="1">
       <c r="A529">
         <v>529</v>
       </c>
@@ -24731,7 +24794,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="530" spans="1:23">
+    <row r="530" spans="1:23" hidden="1">
       <c r="A530">
         <v>530</v>
       </c>
@@ -24770,7 +24833,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="531" spans="1:23">
+    <row r="531" spans="1:23" hidden="1">
       <c r="A531">
         <v>531</v>
       </c>
@@ -24809,7 +24872,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="532" spans="1:23">
+    <row r="532" spans="1:23" hidden="1">
       <c r="A532">
         <v>532</v>
       </c>
@@ -24844,7 +24907,7 @@
       </c>
       <c r="W532" s="3"/>
     </row>
-    <row r="533" spans="1:23">
+    <row r="533" spans="1:23" hidden="1">
       <c r="A533">
         <v>533</v>
       </c>
@@ -24885,7 +24948,7 @@
       </c>
       <c r="W533" s="3"/>
     </row>
-    <row r="534" spans="1:23">
+    <row r="534" spans="1:23" hidden="1">
       <c r="A534">
         <v>534</v>
       </c>
@@ -24923,7 +24986,7 @@
       </c>
       <c r="W534" s="3"/>
     </row>
-    <row r="535" spans="1:23">
+    <row r="535" spans="1:23" hidden="1">
       <c r="A535">
         <v>535</v>
       </c>
@@ -24961,7 +25024,7 @@
       </c>
       <c r="W535" s="3"/>
     </row>
-    <row r="536" spans="1:23">
+    <row r="536" spans="1:23" hidden="1">
       <c r="A536">
         <v>536</v>
       </c>
@@ -24999,7 +25062,7 @@
       </c>
       <c r="W536" s="3"/>
     </row>
-    <row r="537" spans="1:23">
+    <row r="537" spans="1:23" hidden="1">
       <c r="A537">
         <v>537</v>
       </c>
@@ -25037,7 +25100,7 @@
       </c>
       <c r="W537" s="3"/>
     </row>
-    <row r="538" spans="1:23">
+    <row r="538" spans="1:23" hidden="1">
       <c r="A538">
         <v>538</v>
       </c>
@@ -25075,7 +25138,7 @@
       </c>
       <c r="W538" s="3"/>
     </row>
-    <row r="539" spans="1:23">
+    <row r="539" spans="1:23" hidden="1">
       <c r="A539">
         <v>539</v>
       </c>
@@ -25113,7 +25176,7 @@
       </c>
       <c r="W539" s="3"/>
     </row>
-    <row r="540" spans="1:23">
+    <row r="540" spans="1:23" hidden="1">
       <c r="A540">
         <v>540</v>
       </c>
@@ -25154,7 +25217,7 @@
       </c>
       <c r="W540" s="3"/>
     </row>
-    <row r="541" spans="1:23">
+    <row r="541" spans="1:23" hidden="1">
       <c r="A541">
         <v>541</v>
       </c>
@@ -25195,7 +25258,7 @@
       </c>
       <c r="W541" s="3"/>
     </row>
-    <row r="542" spans="1:23">
+    <row r="542" spans="1:23" hidden="1">
       <c r="A542">
         <v>542</v>
       </c>
@@ -25232,7 +25295,7 @@
       </c>
       <c r="W542" s="3"/>
     </row>
-    <row r="543" spans="1:23">
+    <row r="543" spans="1:23" hidden="1">
       <c r="A543">
         <v>543</v>
       </c>
@@ -25271,7 +25334,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="544" spans="1:23">
+    <row r="544" spans="1:23" hidden="1">
       <c r="A544">
         <v>544</v>
       </c>
@@ -25308,7 +25371,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="545" spans="1:23">
+    <row r="545" spans="1:23" hidden="1">
       <c r="A545">
         <v>545</v>
       </c>
@@ -25345,7 +25408,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="546" spans="1:23">
+    <row r="546" spans="1:23" hidden="1">
       <c r="A546">
         <v>546</v>
       </c>
@@ -25385,7 +25448,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="547" spans="1:23">
+    <row r="547" spans="1:23" hidden="1">
       <c r="A547">
         <v>547</v>
       </c>
@@ -25422,7 +25485,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="548" spans="1:23">
+    <row r="548" spans="1:23" hidden="1">
       <c r="A548">
         <v>548</v>
       </c>
@@ -25459,7 +25522,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="549" spans="1:23">
+    <row r="549" spans="1:23" hidden="1">
       <c r="A549">
         <v>549</v>
       </c>
@@ -25496,7 +25559,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="550" spans="1:23">
+    <row r="550" spans="1:23" hidden="1">
       <c r="A550">
         <v>550</v>
       </c>
@@ -25533,7 +25596,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="551" spans="1:23">
+    <row r="551" spans="1:23" hidden="1">
       <c r="A551">
         <v>551</v>
       </c>
@@ -25570,7 +25633,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="552" spans="1:23">
+    <row r="552" spans="1:23" hidden="1">
       <c r="A552">
         <v>552</v>
       </c>
@@ -25607,7 +25670,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="553" spans="1:23">
+    <row r="553" spans="1:23" hidden="1">
       <c r="A553">
         <v>553</v>
       </c>
@@ -25644,7 +25707,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="554" spans="1:23">
+    <row r="554" spans="1:23" hidden="1">
       <c r="A554">
         <v>554</v>
       </c>
@@ -25681,7 +25744,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="555" spans="1:23">
+    <row r="555" spans="1:23" hidden="1">
       <c r="A555">
         <v>555</v>
       </c>
@@ -25718,7 +25781,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="556" spans="1:23">
+    <row r="556" spans="1:23" hidden="1">
       <c r="A556">
         <v>556</v>
       </c>
@@ -25755,7 +25818,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="557" spans="1:23">
+    <row r="557" spans="1:23" hidden="1">
       <c r="A557">
         <v>557</v>
       </c>
@@ -25792,7 +25855,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="558" spans="1:23">
+    <row r="558" spans="1:23" hidden="1">
       <c r="A558">
         <v>558</v>
       </c>
@@ -25829,7 +25892,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="559" spans="1:23">
+    <row r="559" spans="1:23" hidden="1">
       <c r="A559">
         <v>559</v>
       </c>
@@ -25868,7 +25931,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="560" spans="1:23">
+    <row r="560" spans="1:23" hidden="1">
       <c r="A560">
         <v>560</v>
       </c>
@@ -25905,7 +25968,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="561" spans="1:23">
+    <row r="561" spans="1:23" hidden="1">
       <c r="A561">
         <v>561</v>
       </c>
@@ -25940,7 +26003,7 @@
       </c>
       <c r="W561" s="3"/>
     </row>
-    <row r="562" spans="1:23">
+    <row r="562" spans="1:23" hidden="1">
       <c r="A562">
         <v>562</v>
       </c>
@@ -25975,7 +26038,7 @@
       </c>
       <c r="W562" s="3"/>
     </row>
-    <row r="563" spans="1:23">
+    <row r="563" spans="1:23" hidden="1">
       <c r="A563">
         <v>563</v>
       </c>
@@ -26010,7 +26073,7 @@
       </c>
       <c r="W563" s="3"/>
     </row>
-    <row r="564" spans="1:23">
+    <row r="564" spans="1:23" hidden="1">
       <c r="A564">
         <v>564</v>
       </c>
@@ -26045,7 +26108,7 @@
       </c>
       <c r="W564" s="3"/>
     </row>
-    <row r="565" spans="1:23">
+    <row r="565" spans="1:23" hidden="1">
       <c r="A565">
         <v>565</v>
       </c>
@@ -26080,7 +26143,7 @@
       </c>
       <c r="W565" s="3"/>
     </row>
-    <row r="566" spans="1:23">
+    <row r="566" spans="1:23" hidden="1">
       <c r="A566">
         <v>566</v>
       </c>
@@ -26119,7 +26182,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="567" spans="1:23">
+    <row r="567" spans="1:23" hidden="1">
       <c r="A567">
         <v>567</v>
       </c>
@@ -26158,7 +26221,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="568" spans="1:23">
+    <row r="568" spans="1:23" hidden="1">
       <c r="A568">
         <v>568</v>
       </c>
@@ -26197,7 +26260,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="569" spans="1:23">
+    <row r="569" spans="1:23" hidden="1">
       <c r="A569">
         <v>569</v>
       </c>
@@ -26232,7 +26295,7 @@
       </c>
       <c r="W569" s="3"/>
     </row>
-    <row r="570" spans="1:23">
+    <row r="570" spans="1:23" hidden="1">
       <c r="A570">
         <v>570</v>
       </c>
@@ -26271,7 +26334,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="571" spans="1:23">
+    <row r="571" spans="1:23" hidden="1">
       <c r="A571">
         <v>571</v>
       </c>
@@ -26312,7 +26375,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="572" spans="1:23">
+    <row r="572" spans="1:23" hidden="1">
       <c r="A572">
         <v>572</v>
       </c>
@@ -26351,7 +26414,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="573" spans="1:23">
+    <row r="573" spans="1:23" hidden="1">
       <c r="A573">
         <v>573</v>
       </c>
@@ -26388,7 +26451,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="574" spans="1:23">
+    <row r="574" spans="1:23" hidden="1">
       <c r="A574">
         <v>574</v>
       </c>
@@ -26427,7 +26490,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="575" spans="1:23">
+    <row r="575" spans="1:23" hidden="1">
       <c r="A575">
         <v>575</v>
       </c>
@@ -26466,7 +26529,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="576" spans="1:23">
+    <row r="576" spans="1:23" hidden="1">
       <c r="A576">
         <v>576</v>
       </c>
@@ -26503,7 +26566,7 @@
       </c>
       <c r="W576" s="3"/>
     </row>
-    <row r="577" spans="1:23">
+    <row r="577" spans="1:23" hidden="1">
       <c r="A577">
         <v>577</v>
       </c>
@@ -26540,7 +26603,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="578" spans="1:23">
+    <row r="578" spans="1:23" hidden="1">
       <c r="A578">
         <v>578</v>
       </c>
@@ -26579,7 +26642,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="579" spans="1:23">
+    <row r="579" spans="1:23" hidden="1">
       <c r="A579">
         <v>579</v>
       </c>
@@ -26616,7 +26679,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="580" spans="1:23">
+    <row r="580" spans="1:23" hidden="1">
       <c r="A580">
         <v>580</v>
       </c>
@@ -26651,7 +26714,7 @@
       </c>
       <c r="W580" s="3"/>
     </row>
-    <row r="581" spans="1:23">
+    <row r="581" spans="1:23" hidden="1">
       <c r="A581">
         <v>581</v>
       </c>
@@ -26690,7 +26753,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="582" spans="1:23">
+    <row r="582" spans="1:23" hidden="1">
       <c r="A582">
         <v>582</v>
       </c>
@@ -26728,7 +26791,7 @@
       </c>
       <c r="W582" s="3"/>
     </row>
-    <row r="583" spans="1:23">
+    <row r="583" spans="1:23" hidden="1">
       <c r="A583">
         <v>583</v>
       </c>
@@ -26766,7 +26829,7 @@
       </c>
       <c r="W583" s="3"/>
     </row>
-    <row r="584" spans="1:23">
+    <row r="584" spans="1:23" hidden="1">
       <c r="A584">
         <v>584</v>
       </c>
@@ -26801,7 +26864,7 @@
       </c>
       <c r="W584" s="3"/>
     </row>
-    <row r="585" spans="1:23">
+    <row r="585" spans="1:23" hidden="1">
       <c r="A585">
         <v>585</v>
       </c>
@@ -26836,7 +26899,7 @@
       </c>
       <c r="W585" s="3"/>
     </row>
-    <row r="586" spans="1:23">
+    <row r="586" spans="1:23" hidden="1">
       <c r="A586">
         <v>586</v>
       </c>
@@ -26871,7 +26934,7 @@
       </c>
       <c r="W586" s="3"/>
     </row>
-    <row r="587" spans="1:23">
+    <row r="587" spans="1:23" hidden="1">
       <c r="A587">
         <v>587</v>
       </c>
@@ -26906,7 +26969,7 @@
       </c>
       <c r="W587" s="3"/>
     </row>
-    <row r="588" spans="1:23">
+    <row r="588" spans="1:23" hidden="1">
       <c r="A588">
         <v>588</v>
       </c>
@@ -26941,7 +27004,7 @@
       </c>
       <c r="W588" s="3"/>
     </row>
-    <row r="589" spans="1:23">
+    <row r="589" spans="1:23" hidden="1">
       <c r="A589">
         <v>589</v>
       </c>
@@ -26976,7 +27039,7 @@
       </c>
       <c r="W589" s="3"/>
     </row>
-    <row r="590" spans="1:23">
+    <row r="590" spans="1:23" hidden="1">
       <c r="A590">
         <v>590</v>
       </c>
@@ -27011,7 +27074,7 @@
       </c>
       <c r="W590" s="3"/>
     </row>
-    <row r="591" spans="1:23">
+    <row r="591" spans="1:23" hidden="1">
       <c r="A591">
         <v>591</v>
       </c>
@@ -27046,7 +27109,7 @@
       </c>
       <c r="W591" s="3"/>
     </row>
-    <row r="592" spans="1:23">
+    <row r="592" spans="1:23" hidden="1">
       <c r="A592">
         <v>592</v>
       </c>
@@ -27083,7 +27146,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="593" spans="1:23">
+    <row r="593" spans="1:23" hidden="1">
       <c r="A593">
         <v>593</v>
       </c>
@@ -27120,7 +27183,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="594" spans="1:23">
+    <row r="594" spans="1:23" hidden="1">
       <c r="A594">
         <v>594</v>
       </c>
@@ -27163,7 +27226,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="595" spans="1:23">
+    <row r="595" spans="1:23" hidden="1">
       <c r="A595">
         <v>595</v>
       </c>
@@ -27206,7 +27269,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="596" spans="1:23">
+    <row r="596" spans="1:23" hidden="1">
       <c r="A596">
         <v>596</v>
       </c>
@@ -27249,7 +27312,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="597" spans="1:23">
+    <row r="597" spans="1:23" hidden="1">
       <c r="A597">
         <v>597</v>
       </c>
@@ -27292,7 +27355,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="598" spans="1:23">
+    <row r="598" spans="1:23" hidden="1">
       <c r="A598">
         <v>598</v>
       </c>
@@ -27335,7 +27398,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="599" spans="1:23">
+    <row r="599" spans="1:23" hidden="1">
       <c r="A599">
         <v>599</v>
       </c>
@@ -27378,7 +27441,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="600" spans="1:23">
+    <row r="600" spans="1:23" hidden="1">
       <c r="A600">
         <v>600</v>
       </c>
@@ -27418,7 +27481,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="601" spans="1:23">
+    <row r="601" spans="1:23" hidden="1">
       <c r="A601">
         <v>601</v>
       </c>
@@ -27461,7 +27524,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="602" spans="1:23">
+    <row r="602" spans="1:23" hidden="1">
       <c r="A602">
         <v>602</v>
       </c>
@@ -27504,7 +27567,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="603" spans="1:23">
+    <row r="603" spans="1:23" hidden="1">
       <c r="A603">
         <v>605</v>
       </c>
@@ -27542,7 +27605,7 @@
       </c>
       <c r="W603" s="3"/>
     </row>
-    <row r="604" spans="1:23">
+    <row r="604" spans="1:23" hidden="1">
       <c r="A604">
         <v>607</v>
       </c>
@@ -27583,7 +27646,7 @@
       </c>
       <c r="W604" s="3"/>
     </row>
-    <row r="605" spans="1:23">
+    <row r="605" spans="1:23" hidden="1">
       <c r="A605">
         <v>608</v>
       </c>
@@ -27624,7 +27687,7 @@
       </c>
       <c r="W605" s="3"/>
     </row>
-    <row r="606" spans="1:23">
+    <row r="606" spans="1:23" hidden="1">
       <c r="A606">
         <v>611</v>
       </c>
@@ -27662,7 +27725,7 @@
       </c>
       <c r="W606" s="3"/>
     </row>
-    <row r="607" spans="1:23">
+    <row r="607" spans="1:23" hidden="1">
       <c r="A607">
         <v>612</v>
       </c>
@@ -27700,7 +27763,7 @@
       </c>
       <c r="W607" s="3"/>
     </row>
-    <row r="608" spans="1:23">
+    <row r="608" spans="1:23" hidden="1">
       <c r="A608">
         <v>613</v>
       </c>
@@ -27738,7 +27801,7 @@
       </c>
       <c r="W608" s="3"/>
     </row>
-    <row r="609" spans="1:23">
+    <row r="609" spans="1:23" hidden="1">
       <c r="A609">
         <v>614</v>
       </c>
@@ -27776,7 +27839,7 @@
       </c>
       <c r="W609" s="3"/>
     </row>
-    <row r="610" spans="1:23">
+    <row r="610" spans="1:23" hidden="1">
       <c r="A610">
         <v>615</v>
       </c>
@@ -27814,7 +27877,7 @@
       </c>
       <c r="W610" s="3"/>
     </row>
-    <row r="611" spans="1:23">
+    <row r="611" spans="1:23" hidden="1">
       <c r="A611">
         <v>616</v>
       </c>
@@ -27852,7 +27915,7 @@
       </c>
       <c r="W611" s="3"/>
     </row>
-    <row r="612" spans="1:23">
+    <row r="612" spans="1:23" hidden="1">
       <c r="A612">
         <v>617</v>
       </c>
@@ -27893,7 +27956,7 @@
       </c>
       <c r="W612" s="3"/>
     </row>
-    <row r="613" spans="1:23">
+    <row r="613" spans="1:23" hidden="1">
       <c r="A613">
         <v>618</v>
       </c>
@@ -27934,7 +27997,7 @@
       </c>
       <c r="W613" s="3"/>
     </row>
-    <row r="614" spans="1:23">
+    <row r="614" spans="1:23" hidden="1">
       <c r="A614">
         <v>619</v>
       </c>
@@ -27975,7 +28038,7 @@
       </c>
       <c r="W614" s="3"/>
     </row>
-    <row r="615" spans="1:23">
+    <row r="615" spans="1:23" hidden="1">
       <c r="A615">
         <v>620</v>
       </c>
@@ -28016,7 +28079,7 @@
       </c>
       <c r="W615" s="3"/>
     </row>
-    <row r="616" spans="1:23">
+    <row r="616" spans="1:23" hidden="1">
       <c r="A616">
         <v>621</v>
       </c>
@@ -28057,7 +28120,7 @@
       </c>
       <c r="W616" s="3"/>
     </row>
-    <row r="617" spans="1:23">
+    <row r="617" spans="1:23" hidden="1">
       <c r="A617">
         <v>622</v>
       </c>
@@ -28098,7 +28161,7 @@
       </c>
       <c r="W617" s="3"/>
     </row>
-    <row r="618" spans="1:23">
+    <row r="618" spans="1:23" hidden="1">
       <c r="A618">
         <v>623</v>
       </c>
@@ -28139,7 +28202,7 @@
       </c>
       <c r="W618" s="3"/>
     </row>
-    <row r="619" spans="1:23">
+    <row r="619" spans="1:23" hidden="1">
       <c r="A619">
         <v>624</v>
       </c>
@@ -28180,7 +28243,7 @@
       </c>
       <c r="W619" s="3"/>
     </row>
-    <row r="620" spans="1:23">
+    <row r="620" spans="1:23" hidden="1">
       <c r="A620">
         <v>625</v>
       </c>
@@ -28221,7 +28284,7 @@
       </c>
       <c r="W620" s="3"/>
     </row>
-    <row r="621" spans="1:23">
+    <row r="621" spans="1:23" hidden="1">
       <c r="A621">
         <v>626</v>
       </c>
@@ -28262,7 +28325,7 @@
       </c>
       <c r="W621" s="3"/>
     </row>
-    <row r="622" spans="1:23">
+    <row r="622" spans="1:23" hidden="1">
       <c r="A622">
         <v>627</v>
       </c>
@@ -28303,7 +28366,7 @@
       </c>
       <c r="W622" s="3"/>
     </row>
-    <row r="623" spans="1:23">
+    <row r="623" spans="1:23" hidden="1">
       <c r="A623">
         <v>628</v>
       </c>
@@ -28341,7 +28404,7 @@
       </c>
       <c r="W623" s="3"/>
     </row>
-    <row r="624" spans="1:23">
+    <row r="624" spans="1:23" hidden="1">
       <c r="A624">
         <v>629</v>
       </c>
@@ -28379,7 +28442,7 @@
       </c>
       <c r="W624" s="3"/>
     </row>
-    <row r="625" spans="1:23">
+    <row r="625" spans="1:23" hidden="1">
       <c r="A625">
         <v>630</v>
       </c>
@@ -28420,7 +28483,7 @@
       </c>
       <c r="W625" s="3"/>
     </row>
-    <row r="626" spans="1:23">
+    <row r="626" spans="1:23" hidden="1">
       <c r="A626">
         <v>631</v>
       </c>
@@ -28458,7 +28521,7 @@
       </c>
       <c r="W626" s="3"/>
     </row>
-    <row r="627" spans="1:23">
+    <row r="627" spans="1:23" hidden="1">
       <c r="A627">
         <v>632</v>
       </c>
@@ -28496,7 +28559,7 @@
       </c>
       <c r="W627" s="3"/>
     </row>
-    <row r="628" spans="1:23">
+    <row r="628" spans="1:23" hidden="1">
       <c r="A628">
         <v>633</v>
       </c>
@@ -28537,7 +28600,7 @@
       </c>
       <c r="W628" s="3"/>
     </row>
-    <row r="629" spans="1:23">
+    <row r="629" spans="1:23" hidden="1">
       <c r="A629">
         <v>634</v>
       </c>
@@ -28578,7 +28641,7 @@
       </c>
       <c r="W629" s="3"/>
     </row>
-    <row r="630" spans="1:23">
+    <row r="630" spans="1:23" hidden="1">
       <c r="A630">
         <v>635</v>
       </c>
@@ -28617,7 +28680,7 @@
       </c>
       <c r="W630" s="3"/>
     </row>
-    <row r="631" spans="1:23">
+    <row r="631" spans="1:23" hidden="1">
       <c r="A631">
         <v>636</v>
       </c>
@@ -28654,7 +28717,7 @@
       </c>
       <c r="W631" s="3"/>
     </row>
-    <row r="632" spans="1:23">
+    <row r="632" spans="1:23" hidden="1">
       <c r="A632">
         <v>637</v>
       </c>
@@ -28695,7 +28758,7 @@
       </c>
       <c r="W632" s="3"/>
     </row>
-    <row r="633" spans="1:23">
+    <row r="633" spans="1:23" hidden="1">
       <c r="A633">
         <v>638</v>
       </c>
@@ -28736,7 +28799,7 @@
       </c>
       <c r="W633" s="3"/>
     </row>
-    <row r="634" spans="1:23">
+    <row r="634" spans="1:23" hidden="1">
       <c r="A634">
         <v>639</v>
       </c>
@@ -28777,7 +28840,7 @@
       </c>
       <c r="W634" s="3"/>
     </row>
-    <row r="635" spans="1:23">
+    <row r="635" spans="1:23" hidden="1">
       <c r="A635">
         <v>640</v>
       </c>
@@ -28817,7 +28880,7 @@
       </c>
       <c r="W635" s="3"/>
     </row>
-    <row r="636" spans="1:23">
+    <row r="636" spans="1:23" hidden="1">
       <c r="A636">
         <v>641</v>
       </c>
@@ -28858,7 +28921,7 @@
       </c>
       <c r="W636" s="3"/>
     </row>
-    <row r="637" spans="1:23">
+    <row r="637" spans="1:23" hidden="1">
       <c r="A637">
         <v>642</v>
       </c>
@@ -28899,7 +28962,7 @@
       </c>
       <c r="W637" s="3"/>
     </row>
-    <row r="638" spans="1:23">
+    <row r="638" spans="1:23" hidden="1">
       <c r="A638">
         <v>643</v>
       </c>
@@ -28940,7 +29003,7 @@
       </c>
       <c r="W638" s="3"/>
     </row>
-    <row r="639" spans="1:23">
+    <row r="639" spans="1:23" hidden="1">
       <c r="A639">
         <v>644</v>
       </c>
@@ -28977,7 +29040,7 @@
       </c>
       <c r="W639" s="3"/>
     </row>
-    <row r="640" spans="1:23">
+    <row r="640" spans="1:23" hidden="1">
       <c r="A640">
         <v>650</v>
       </c>
@@ -29018,7 +29081,7 @@
       </c>
       <c r="W640" s="3"/>
     </row>
-    <row r="641" spans="1:23">
+    <row r="641" spans="1:23" hidden="1">
       <c r="A641">
         <v>645</v>
       </c>
@@ -29059,7 +29122,7 @@
       </c>
       <c r="W641" s="3"/>
     </row>
-    <row r="642" spans="1:23">
+    <row r="642" spans="1:23" hidden="1">
       <c r="A642">
         <v>646</v>
       </c>
@@ -29095,7 +29158,7 @@
       </c>
       <c r="W642" s="3"/>
     </row>
-    <row r="643" spans="1:23">
+    <row r="643" spans="1:23" hidden="1">
       <c r="A643">
         <v>647</v>
       </c>
@@ -29136,7 +29199,7 @@
       </c>
       <c r="W643" s="3"/>
     </row>
-    <row r="644" spans="1:23">
+    <row r="644" spans="1:23" hidden="1">
       <c r="A644">
         <v>648</v>
       </c>
@@ -29174,7 +29237,7 @@
       </c>
       <c r="W644" s="3"/>
     </row>
-    <row r="645" spans="1:23">
+    <row r="645" spans="1:23" hidden="1">
       <c r="A645">
         <v>649</v>
       </c>
@@ -29215,7 +29278,7 @@
       </c>
       <c r="W645" s="3"/>
     </row>
-    <row r="646" spans="1:23">
+    <row r="646" spans="1:23" hidden="1">
       <c r="A646">
         <v>651</v>
       </c>
@@ -29256,7 +29319,7 @@
       </c>
       <c r="W646" s="3"/>
     </row>
-    <row r="647" spans="1:23">
+    <row r="647" spans="1:23" hidden="1">
       <c r="A647">
         <v>652</v>
       </c>
@@ -29297,7 +29360,7 @@
       </c>
       <c r="W647" s="3"/>
     </row>
-    <row r="648" spans="1:23">
+    <row r="648" spans="1:23" hidden="1">
       <c r="A648">
         <v>653</v>
       </c>
@@ -29338,7 +29401,7 @@
       </c>
       <c r="W648" s="3"/>
     </row>
-    <row r="649" spans="1:23">
+    <row r="649" spans="1:23" hidden="1">
       <c r="A649">
         <v>654</v>
       </c>
@@ -29379,7 +29442,7 @@
       </c>
       <c r="W649" s="3"/>
     </row>
-    <row r="650" spans="1:23">
+    <row r="650" spans="1:23" hidden="1">
       <c r="A650">
         <v>655</v>
       </c>
@@ -29420,7 +29483,7 @@
       </c>
       <c r="W650" s="3"/>
     </row>
-    <row r="651" spans="1:23">
+    <row r="651" spans="1:23" hidden="1">
       <c r="A651">
         <v>656</v>
       </c>
@@ -29461,7 +29524,7 @@
       </c>
       <c r="W651" s="3"/>
     </row>
-    <row r="652" spans="1:23">
+    <row r="652" spans="1:23" hidden="1">
       <c r="A652">
         <v>657</v>
       </c>
@@ -29502,7 +29565,7 @@
       </c>
       <c r="W652" s="3"/>
     </row>
-    <row r="653" spans="1:23">
+    <row r="653" spans="1:23" hidden="1">
       <c r="A653">
         <v>658</v>
       </c>
@@ -29543,7 +29606,7 @@
       </c>
       <c r="W653" s="3"/>
     </row>
-    <row r="654" spans="1:23">
+    <row r="654" spans="1:23" hidden="1">
       <c r="A654">
         <v>659</v>
       </c>
@@ -29580,7 +29643,7 @@
       </c>
       <c r="W654" s="3"/>
     </row>
-    <row r="655" spans="1:23">
+    <row r="655" spans="1:23" hidden="1">
       <c r="A655">
         <v>660</v>
       </c>
@@ -29621,7 +29684,7 @@
       </c>
       <c r="W655" s="3"/>
     </row>
-    <row r="656" spans="1:23">
+    <row r="656" spans="1:23" hidden="1">
       <c r="A656">
         <v>661</v>
       </c>
@@ -29661,7 +29724,7 @@
       </c>
       <c r="W656" s="3"/>
     </row>
-    <row r="657" spans="1:23">
+    <row r="657" spans="1:23" hidden="1">
       <c r="A657">
         <v>662</v>
       </c>
@@ -29702,7 +29765,7 @@
       </c>
       <c r="W657" s="3"/>
     </row>
-    <row r="658" spans="1:23">
+    <row r="658" spans="1:23" hidden="1">
       <c r="A658">
         <v>663</v>
       </c>
@@ -29743,7 +29806,7 @@
       </c>
       <c r="W658" s="3"/>
     </row>
-    <row r="659" spans="1:23">
+    <row r="659" spans="1:23" hidden="1">
       <c r="A659">
         <v>664</v>
       </c>
@@ -29780,7 +29843,7 @@
       </c>
       <c r="W659" s="3"/>
     </row>
-    <row r="660" spans="1:23">
+    <row r="660" spans="1:23" hidden="1">
       <c r="A660">
         <v>665</v>
       </c>
@@ -29821,7 +29884,7 @@
       </c>
       <c r="W660" s="3"/>
     </row>
-    <row r="661" spans="1:23">
+    <row r="661" spans="1:23" hidden="1">
       <c r="A661">
         <v>666</v>
       </c>
@@ -29862,7 +29925,7 @@
       </c>
       <c r="W661" s="3"/>
     </row>
-    <row r="662" spans="1:23">
+    <row r="662" spans="1:23" hidden="1">
       <c r="A662">
         <v>668</v>
       </c>
@@ -29900,7 +29963,7 @@
       </c>
       <c r="W662" s="3"/>
     </row>
-    <row r="663" spans="1:23">
+    <row r="663" spans="1:23" hidden="1">
       <c r="A663">
         <v>667</v>
       </c>
@@ -29941,7 +30004,7 @@
       </c>
       <c r="W663" s="3"/>
     </row>
-    <row r="664" spans="1:23">
+    <row r="664" spans="1:23" hidden="1">
       <c r="A664">
         <v>669</v>
       </c>
@@ -29982,7 +30045,7 @@
       </c>
       <c r="W664" s="3"/>
     </row>
-    <row r="665" spans="1:23">
+    <row r="665" spans="1:23" hidden="1">
       <c r="A665">
         <v>670</v>
       </c>
@@ -30022,7 +30085,7 @@
       </c>
       <c r="W665" s="3"/>
     </row>
-    <row r="666" spans="1:23">
+    <row r="666" spans="1:23" hidden="1">
       <c r="A666">
         <v>671</v>
       </c>
@@ -30063,7 +30126,7 @@
       </c>
       <c r="W666" s="3"/>
     </row>
-    <row r="667" spans="1:23">
+    <row r="667" spans="1:23" hidden="1">
       <c r="A667">
         <v>672</v>
       </c>
@@ -30104,7 +30167,7 @@
       </c>
       <c r="W667" s="3"/>
     </row>
-    <row r="668" spans="1:23">
+    <row r="668" spans="1:23" hidden="1">
       <c r="A668">
         <v>674</v>
       </c>
@@ -30145,7 +30208,7 @@
       </c>
       <c r="W668" s="3"/>
     </row>
-    <row r="669" spans="1:23">
+    <row r="669" spans="1:23" hidden="1">
       <c r="A669">
         <v>675</v>
       </c>
@@ -30186,7 +30249,7 @@
       </c>
       <c r="W669" s="3"/>
     </row>
-    <row r="670" spans="1:23">
+    <row r="670" spans="1:23" hidden="1">
       <c r="A670">
         <v>676</v>
       </c>
@@ -30226,7 +30289,7 @@
       </c>
       <c r="W670" s="3"/>
     </row>
-    <row r="671" spans="1:23">
+    <row r="671" spans="1:23" hidden="1">
       <c r="A671">
         <v>677</v>
       </c>
@@ -30266,7 +30329,7 @@
       </c>
       <c r="W671" s="3"/>
     </row>
-    <row r="672" spans="1:23">
+    <row r="672" spans="1:23" hidden="1">
       <c r="A672">
         <v>678</v>
       </c>
@@ -30306,7 +30369,7 @@
       </c>
       <c r="W672" s="3"/>
     </row>
-    <row r="673" spans="1:23">
+    <row r="673" spans="1:23" hidden="1">
       <c r="A673">
         <v>679</v>
       </c>
@@ -30347,7 +30410,7 @@
       </c>
       <c r="W673" s="3"/>
     </row>
-    <row r="674" spans="1:23">
+    <row r="674" spans="1:23" hidden="1">
       <c r="A674">
         <v>680</v>
       </c>
@@ -30388,7 +30451,7 @@
       </c>
       <c r="W674" s="3"/>
     </row>
-    <row r="675" spans="1:23">
+    <row r="675" spans="1:23" hidden="1">
       <c r="A675">
         <v>681</v>
       </c>
@@ -30429,7 +30492,7 @@
       </c>
       <c r="W675" s="3"/>
     </row>
-    <row r="676" spans="1:23">
+    <row r="676" spans="1:23" hidden="1">
       <c r="A676">
         <v>682</v>
       </c>
@@ -30470,7 +30533,7 @@
       </c>
       <c r="W676" s="3"/>
     </row>
-    <row r="677" spans="1:23">
+    <row r="677" spans="1:23" hidden="1">
       <c r="A677">
         <v>683</v>
       </c>
@@ -30511,7 +30574,7 @@
       </c>
       <c r="W677" s="3"/>
     </row>
-    <row r="678" spans="1:23">
+    <row r="678" spans="1:23" hidden="1">
       <c r="A678">
         <v>684</v>
       </c>
@@ -30552,7 +30615,7 @@
       </c>
       <c r="W678" s="3"/>
     </row>
-    <row r="679" spans="1:23">
+    <row r="679" spans="1:23" hidden="1">
       <c r="A679">
         <v>685</v>
       </c>
@@ -30593,7 +30656,7 @@
       </c>
       <c r="W679" s="3"/>
     </row>
-    <row r="680" spans="1:23">
+    <row r="680" spans="1:23" hidden="1">
       <c r="A680">
         <v>686</v>
       </c>
@@ -30634,7 +30697,7 @@
       </c>
       <c r="W680" s="3"/>
     </row>
-    <row r="681" spans="1:23">
+    <row r="681" spans="1:23" hidden="1">
       <c r="A681">
         <v>687</v>
       </c>
@@ -30675,7 +30738,7 @@
       </c>
       <c r="W681" s="3"/>
     </row>
-    <row r="682" spans="1:23">
+    <row r="682" spans="1:23" hidden="1">
       <c r="A682">
         <v>688</v>
       </c>
@@ -30716,7 +30779,7 @@
       </c>
       <c r="W682" s="3"/>
     </row>
-    <row r="683" spans="1:23">
+    <row r="683" spans="1:23" hidden="1">
       <c r="A683">
         <v>689</v>
       </c>
@@ -30754,7 +30817,7 @@
       </c>
       <c r="W683" s="3"/>
     </row>
-    <row r="684" spans="1:23">
+    <row r="684" spans="1:23" hidden="1">
       <c r="A684">
         <v>690</v>
       </c>
@@ -30795,7 +30858,7 @@
       </c>
       <c r="W684" s="3"/>
     </row>
-    <row r="685" spans="1:23">
+    <row r="685" spans="1:23" hidden="1">
       <c r="A685">
         <v>691</v>
       </c>
@@ -30836,7 +30899,7 @@
       </c>
       <c r="W685" s="3"/>
     </row>
-    <row r="686" spans="1:23">
+    <row r="686" spans="1:23" hidden="1">
       <c r="A686">
         <v>692</v>
       </c>
@@ -30877,7 +30940,7 @@
       </c>
       <c r="W686" s="3"/>
     </row>
-    <row r="687" spans="1:23">
+    <row r="687" spans="1:23" hidden="1">
       <c r="A687">
         <v>693</v>
       </c>
@@ -30918,7 +30981,7 @@
       </c>
       <c r="W687" s="3"/>
     </row>
-    <row r="688" spans="1:23">
+    <row r="688" spans="1:23" hidden="1">
       <c r="A688">
         <v>694</v>
       </c>
@@ -30959,7 +31022,7 @@
       </c>
       <c r="W688" s="3"/>
     </row>
-    <row r="689" spans="1:23">
+    <row r="689" spans="1:23" hidden="1">
       <c r="A689">
         <v>695</v>
       </c>
@@ -31000,7 +31063,7 @@
       </c>
       <c r="W689" s="3"/>
     </row>
-    <row r="690" spans="1:23">
+    <row r="690" spans="1:23" hidden="1">
       <c r="A690">
         <v>696</v>
       </c>
@@ -31041,7 +31104,7 @@
       </c>
       <c r="W690" s="3"/>
     </row>
-    <row r="691" spans="1:23">
+    <row r="691" spans="1:23" hidden="1">
       <c r="A691">
         <v>697</v>
       </c>
@@ -31078,7 +31141,7 @@
       </c>
       <c r="W691" s="3"/>
     </row>
-    <row r="692" spans="1:23">
+    <row r="692" spans="1:23" hidden="1">
       <c r="A692">
         <v>698</v>
       </c>
@@ -31118,7 +31181,7 @@
       </c>
       <c r="W692" s="3"/>
     </row>
-    <row r="693" spans="1:23">
+    <row r="693" spans="1:23" hidden="1">
       <c r="A693">
         <v>699</v>
       </c>
@@ -31159,7 +31222,7 @@
       </c>
       <c r="W693" s="3"/>
     </row>
-    <row r="694" spans="1:23">
+    <row r="694" spans="1:23" hidden="1">
       <c r="A694">
         <v>700</v>
       </c>
@@ -31196,7 +31259,7 @@
       </c>
       <c r="W694" s="3"/>
     </row>
-    <row r="695" spans="1:23">
+    <row r="695" spans="1:23" hidden="1">
       <c r="A695">
         <v>701</v>
       </c>
@@ -31237,7 +31300,7 @@
       </c>
       <c r="W695" s="3"/>
     </row>
-    <row r="696" spans="1:23">
+    <row r="696" spans="1:23" hidden="1">
       <c r="A696">
         <v>702</v>
       </c>
@@ -31278,7 +31341,7 @@
       </c>
       <c r="W696" s="3"/>
     </row>
-    <row r="697" spans="1:23">
+    <row r="697" spans="1:23" hidden="1">
       <c r="A697">
         <v>703</v>
       </c>
@@ -31319,7 +31382,7 @@
       </c>
       <c r="W697" s="3"/>
     </row>
-    <row r="698" spans="1:23">
+    <row r="698" spans="1:23" hidden="1">
       <c r="A698">
         <v>704</v>
       </c>
@@ -31360,7 +31423,7 @@
       </c>
       <c r="W698" s="3"/>
     </row>
-    <row r="699" spans="1:23">
+    <row r="699" spans="1:23" hidden="1">
       <c r="A699">
         <v>705</v>
       </c>
@@ -31401,7 +31464,7 @@
       </c>
       <c r="W699" s="3"/>
     </row>
-    <row r="700" spans="1:23">
+    <row r="700" spans="1:23" hidden="1">
       <c r="A700">
         <v>706</v>
       </c>
@@ -31442,7 +31505,7 @@
       </c>
       <c r="W700" s="3"/>
     </row>
-    <row r="701" spans="1:23">
+    <row r="701" spans="1:23" hidden="1">
       <c r="A701">
         <v>707</v>
       </c>
@@ -31483,7 +31546,7 @@
       </c>
       <c r="W701" s="3"/>
     </row>
-    <row r="702" spans="1:23">
+    <row r="702" spans="1:23" hidden="1">
       <c r="A702">
         <v>708</v>
       </c>
@@ -31524,7 +31587,7 @@
       </c>
       <c r="W702" s="3"/>
     </row>
-    <row r="703" spans="1:23">
+    <row r="703" spans="1:23" hidden="1">
       <c r="A703">
         <v>709</v>
       </c>
@@ -31565,7 +31628,7 @@
       </c>
       <c r="W703" s="3"/>
     </row>
-    <row r="704" spans="1:23">
+    <row r="704" spans="1:23" hidden="1">
       <c r="A704">
         <v>710</v>
       </c>
@@ -31606,7 +31669,7 @@
       </c>
       <c r="W704" s="3"/>
     </row>
-    <row r="705" spans="1:23">
+    <row r="705" spans="1:23" hidden="1">
       <c r="A705">
         <v>711</v>
       </c>
@@ -31647,7 +31710,7 @@
       </c>
       <c r="W705" s="3"/>
     </row>
-    <row r="706" spans="1:23">
+    <row r="706" spans="1:23" hidden="1">
       <c r="A706">
         <v>712</v>
       </c>
@@ -31688,7 +31751,7 @@
       </c>
       <c r="W706" s="3"/>
     </row>
-    <row r="707" spans="1:23">
+    <row r="707" spans="1:23" hidden="1">
       <c r="A707">
         <v>713</v>
       </c>
@@ -31726,7 +31789,7 @@
       </c>
       <c r="W707" s="3"/>
     </row>
-    <row r="708" spans="1:23">
+    <row r="708" spans="1:23" hidden="1">
       <c r="A708">
         <v>714</v>
       </c>
@@ -31764,7 +31827,7 @@
       </c>
       <c r="W708" s="3"/>
     </row>
-    <row r="709" spans="1:23">
+    <row r="709" spans="1:23" hidden="1">
       <c r="A709">
         <v>715</v>
       </c>
@@ -31802,7 +31865,7 @@
       </c>
       <c r="W709" s="3"/>
     </row>
-    <row r="710" spans="1:23">
+    <row r="710" spans="1:23" hidden="1">
       <c r="A710">
         <v>716</v>
       </c>
@@ -31850,7 +31913,7 @@
       </c>
       <c r="W710" s="3"/>
     </row>
-    <row r="711" spans="1:23">
+    <row r="711" spans="1:23" hidden="1">
       <c r="A711">
         <v>717</v>
       </c>
@@ -31891,7 +31954,7 @@
       </c>
       <c r="W711" s="3"/>
     </row>
-    <row r="712" spans="1:23">
+    <row r="712" spans="1:23" hidden="1">
       <c r="A712">
         <v>718</v>
       </c>
@@ -31932,7 +31995,7 @@
       </c>
       <c r="W712" s="3"/>
     </row>
-    <row r="713" spans="1:23">
+    <row r="713" spans="1:23" hidden="1">
       <c r="A713">
         <v>719</v>
       </c>
@@ -31973,7 +32036,7 @@
       </c>
       <c r="W713" s="3"/>
     </row>
-    <row r="714" spans="1:23">
+    <row r="714" spans="1:23" hidden="1">
       <c r="A714">
         <v>720</v>
       </c>
@@ -32014,7 +32077,7 @@
       </c>
       <c r="W714" s="3"/>
     </row>
-    <row r="715" spans="1:23">
+    <row r="715" spans="1:23" hidden="1">
       <c r="A715">
         <v>721</v>
       </c>
@@ -32055,7 +32118,7 @@
       </c>
       <c r="W715" s="3"/>
     </row>
-    <row r="716" spans="1:23">
+    <row r="716" spans="1:23" hidden="1">
       <c r="A716">
         <v>722</v>
       </c>
@@ -32096,7 +32159,7 @@
       </c>
       <c r="W716" s="3"/>
     </row>
-    <row r="717" spans="1:23">
+    <row r="717" spans="1:23" hidden="1">
       <c r="A717">
         <v>723</v>
       </c>
@@ -32146,7 +32209,7 @@
       </c>
       <c r="W717" s="3"/>
     </row>
-    <row r="718" spans="1:23">
+    <row r="718" spans="1:23" hidden="1">
       <c r="A718">
         <v>724</v>
       </c>
@@ -32184,7 +32247,7 @@
       </c>
       <c r="W718" s="3"/>
     </row>
-    <row r="719" spans="1:23">
+    <row r="719" spans="1:23" hidden="1">
       <c r="A719">
         <v>725</v>
       </c>
@@ -32222,7 +32285,7 @@
       </c>
       <c r="W719" s="3"/>
     </row>
-    <row r="720" spans="1:23">
+    <row r="720" spans="1:23" hidden="1">
       <c r="A720">
         <v>726</v>
       </c>
@@ -32260,7 +32323,7 @@
       </c>
       <c r="W720" s="3"/>
     </row>
-    <row r="721" spans="1:23">
+    <row r="721" spans="1:23" hidden="1">
       <c r="A721">
         <v>727</v>
       </c>
@@ -32301,7 +32364,7 @@
       </c>
       <c r="W721" s="3"/>
     </row>
-    <row r="722" spans="1:23">
+    <row r="722" spans="1:23" hidden="1">
       <c r="A722">
         <v>728</v>
       </c>
@@ -32342,7 +32405,7 @@
       </c>
       <c r="W722" s="3"/>
     </row>
-    <row r="723" spans="1:23">
+    <row r="723" spans="1:23" hidden="1">
       <c r="A723">
         <v>729</v>
       </c>
@@ -32383,7 +32446,7 @@
       </c>
       <c r="W723" s="3"/>
     </row>
-    <row r="724" spans="1:23">
+    <row r="724" spans="1:23" hidden="1">
       <c r="A724">
         <v>730</v>
       </c>
@@ -32424,7 +32487,7 @@
       </c>
       <c r="W724" s="3"/>
     </row>
-    <row r="725" spans="1:23">
+    <row r="725" spans="1:23" hidden="1">
       <c r="A725">
         <v>731</v>
       </c>
@@ -32465,7 +32528,7 @@
       </c>
       <c r="W725" s="3"/>
     </row>
-    <row r="726" spans="1:23">
+    <row r="726" spans="1:23" hidden="1">
       <c r="A726">
         <v>732</v>
       </c>
@@ -32506,7 +32569,7 @@
       </c>
       <c r="W726" s="3"/>
     </row>
-    <row r="727" spans="1:23">
+    <row r="727" spans="1:23" hidden="1">
       <c r="A727">
         <v>733</v>
       </c>
@@ -32547,7 +32610,7 @@
       </c>
       <c r="W727" s="3"/>
     </row>
-    <row r="728" spans="1:23">
+    <row r="728" spans="1:23" hidden="1">
       <c r="A728">
         <v>734</v>
       </c>
@@ -32588,7 +32651,7 @@
       </c>
       <c r="W728" s="3"/>
     </row>
-    <row r="729" spans="1:23">
+    <row r="729" spans="1:23" hidden="1">
       <c r="A729">
         <v>735</v>
       </c>
@@ -32638,7 +32701,7 @@
       </c>
       <c r="W729" s="3"/>
     </row>
-    <row r="730" spans="1:23">
+    <row r="730" spans="1:23" hidden="1">
       <c r="A730">
         <v>736</v>
       </c>
@@ -32679,7 +32742,7 @@
       </c>
       <c r="W730" s="3"/>
     </row>
-    <row r="731" spans="1:23">
+    <row r="731" spans="1:23" hidden="1">
       <c r="A731">
         <v>737</v>
       </c>
@@ -32719,7 +32782,7 @@
       </c>
       <c r="W731" s="3"/>
     </row>
-    <row r="732" spans="1:23">
+    <row r="732" spans="1:23" hidden="1">
       <c r="A732">
         <v>738</v>
       </c>
@@ -32760,7 +32823,7 @@
       </c>
       <c r="W732" s="3"/>
     </row>
-    <row r="733" spans="1:23">
+    <row r="733" spans="1:23" hidden="1">
       <c r="A733">
         <v>739</v>
       </c>
@@ -32797,7 +32860,7 @@
       </c>
       <c r="W733" s="3"/>
     </row>
-    <row r="734" spans="1:23">
+    <row r="734" spans="1:23" hidden="1">
       <c r="A734">
         <v>740</v>
       </c>
@@ -32835,7 +32898,7 @@
       </c>
       <c r="W734" s="3"/>
     </row>
-    <row r="735" spans="1:23">
+    <row r="735" spans="1:23" hidden="1">
       <c r="A735">
         <v>741</v>
       </c>
@@ -32876,7 +32939,7 @@
       </c>
       <c r="W735" s="3"/>
     </row>
-    <row r="736" spans="1:23">
+    <row r="736" spans="1:23" hidden="1">
       <c r="A736">
         <v>742</v>
       </c>
@@ -32917,7 +32980,7 @@
       </c>
       <c r="W736" s="3"/>
     </row>
-    <row r="737" spans="1:23">
+    <row r="737" spans="1:23" hidden="1">
       <c r="A737">
         <v>743</v>
       </c>
@@ -32967,7 +33030,7 @@
       </c>
       <c r="W737" s="3"/>
     </row>
-    <row r="738" spans="1:23">
+    <row r="738" spans="1:23" hidden="1">
       <c r="A738">
         <v>744</v>
       </c>
@@ -33004,7 +33067,7 @@
       </c>
       <c r="W738" s="3"/>
     </row>
-    <row r="739" spans="1:23">
+    <row r="739" spans="1:23" hidden="1">
       <c r="A739">
         <v>745</v>
       </c>
@@ -33054,7 +33117,7 @@
       </c>
       <c r="W739" s="3"/>
     </row>
-    <row r="740" spans="1:23">
+    <row r="740" spans="1:23" hidden="1">
       <c r="A740">
         <v>746</v>
       </c>
@@ -33104,7 +33167,7 @@
       </c>
       <c r="W740" s="3"/>
     </row>
-    <row r="741" spans="1:23">
+    <row r="741" spans="1:23" hidden="1">
       <c r="A741">
         <v>747</v>
       </c>
@@ -33186,7 +33249,7 @@
       </c>
       <c r="W742" s="3"/>
     </row>
-    <row r="743" spans="1:23">
+    <row r="743" spans="1:23" hidden="1">
       <c r="A743">
         <v>749</v>
       </c>
@@ -33226,7 +33289,7 @@
       </c>
       <c r="W743" s="3"/>
     </row>
-    <row r="744" spans="1:23">
+    <row r="744" spans="1:23" hidden="1">
       <c r="A744">
         <v>750</v>
       </c>
@@ -33267,7 +33330,7 @@
       </c>
       <c r="W744" s="3"/>
     </row>
-    <row r="745" spans="1:23">
+    <row r="745" spans="1:23" hidden="1">
       <c r="A745">
         <v>751</v>
       </c>
@@ -33308,7 +33371,7 @@
       </c>
       <c r="W745" s="3"/>
     </row>
-    <row r="746" spans="1:23">
+    <row r="746" spans="1:23" hidden="1">
       <c r="A746">
         <v>752</v>
       </c>
@@ -33348,7 +33411,7 @@
       </c>
       <c r="W746" s="3"/>
     </row>
-    <row r="747" spans="1:23">
+    <row r="747" spans="1:23" hidden="1">
       <c r="A747">
         <v>753</v>
       </c>
@@ -33389,7 +33452,7 @@
       </c>
       <c r="W747" s="3"/>
     </row>
-    <row r="748" spans="1:23">
+    <row r="748" spans="1:23" hidden="1">
       <c r="A748">
         <v>754</v>
       </c>
@@ -33439,7 +33502,7 @@
       </c>
       <c r="W748" s="3"/>
     </row>
-    <row r="749" spans="1:23">
+    <row r="749" spans="1:23" hidden="1">
       <c r="A749">
         <v>755</v>
       </c>
@@ -33479,7 +33542,7 @@
       </c>
       <c r="W749" s="3"/>
     </row>
-    <row r="750" spans="1:23">
+    <row r="750" spans="1:23" hidden="1">
       <c r="A750">
         <v>756</v>
       </c>
@@ -33520,7 +33583,7 @@
       </c>
       <c r="W750" s="3"/>
     </row>
-    <row r="751" spans="1:23">
+    <row r="751" spans="1:23" hidden="1">
       <c r="A751">
         <v>757</v>
       </c>
@@ -33570,7 +33633,7 @@
       </c>
       <c r="W751" s="3"/>
     </row>
-    <row r="752" spans="1:23">
+    <row r="752" spans="1:23" hidden="1">
       <c r="A752">
         <v>758</v>
       </c>
@@ -33610,7 +33673,7 @@
       </c>
       <c r="W752" s="3"/>
     </row>
-    <row r="753" spans="1:23">
+    <row r="753" spans="1:23" hidden="1">
       <c r="A753">
         <v>759</v>
       </c>
@@ -33651,7 +33714,7 @@
       </c>
       <c r="W753" s="3"/>
     </row>
-    <row r="754" spans="1:23">
+    <row r="754" spans="1:23" hidden="1">
       <c r="A754">
         <v>760</v>
       </c>
@@ -33692,7 +33755,7 @@
       </c>
       <c r="W754" s="3"/>
     </row>
-    <row r="755" spans="1:23">
+    <row r="755" spans="1:23" hidden="1">
       <c r="A755">
         <v>762</v>
       </c>
@@ -33742,7 +33805,7 @@
       </c>
       <c r="W755" s="3"/>
     </row>
-    <row r="756" spans="1:23">
+    <row r="756" spans="1:23" hidden="1">
       <c r="A756">
         <v>763</v>
       </c>
@@ -33792,7 +33855,7 @@
       </c>
       <c r="W756" s="3"/>
     </row>
-    <row r="757" spans="1:23">
+    <row r="757" spans="1:23" hidden="1">
       <c r="A757">
         <v>764</v>
       </c>
@@ -33842,7 +33905,7 @@
       </c>
       <c r="W757" s="3"/>
     </row>
-    <row r="758" spans="1:23">
+    <row r="758" spans="1:23" hidden="1">
       <c r="A758">
         <v>765</v>
       </c>
@@ -33883,7 +33946,7 @@
       </c>
       <c r="W758" s="3"/>
     </row>
-    <row r="759" spans="1:23">
+    <row r="759" spans="1:23" hidden="1">
       <c r="A759">
         <v>766</v>
       </c>
@@ -33924,7 +33987,7 @@
       </c>
       <c r="W759" s="3"/>
     </row>
-    <row r="760" spans="1:23">
+    <row r="760" spans="1:23" hidden="1">
       <c r="A760">
         <v>767</v>
       </c>
@@ -33965,7 +34028,7 @@
       </c>
       <c r="W760" s="3"/>
     </row>
-    <row r="761" spans="1:23">
+    <row r="761" spans="1:23" hidden="1">
       <c r="A761">
         <v>768</v>
       </c>
@@ -34015,7 +34078,7 @@
       </c>
       <c r="W761" s="3"/>
     </row>
-    <row r="762" spans="1:23">
+    <row r="762" spans="1:23" hidden="1">
       <c r="A762">
         <v>769</v>
       </c>
@@ -34056,7 +34119,7 @@
       </c>
       <c r="W762" s="3"/>
     </row>
-    <row r="763" spans="1:23">
+    <row r="763" spans="1:23" hidden="1">
       <c r="A763">
         <v>770</v>
       </c>
@@ -34097,7 +34160,7 @@
       </c>
       <c r="W763" s="3"/>
     </row>
-    <row r="764" spans="1:23">
+    <row r="764" spans="1:23" hidden="1">
       <c r="A764">
         <v>771</v>
       </c>
@@ -34147,7 +34210,7 @@
       </c>
       <c r="W764" s="3"/>
     </row>
-    <row r="765" spans="1:23">
+    <row r="765" spans="1:23" hidden="1">
       <c r="A765">
         <v>772</v>
       </c>
@@ -34197,7 +34260,7 @@
       </c>
       <c r="W765" s="3"/>
     </row>
-    <row r="766" spans="1:23">
+    <row r="766" spans="1:23" hidden="1">
       <c r="A766">
         <v>773</v>
       </c>
@@ -34236,7 +34299,7 @@
       </c>
       <c r="W766" s="3"/>
     </row>
-    <row r="767" spans="1:23">
+    <row r="767" spans="1:23" hidden="1">
       <c r="A767">
         <v>774</v>
       </c>
@@ -34277,7 +34340,7 @@
       </c>
       <c r="W767" s="3"/>
     </row>
-    <row r="768" spans="1:23">
+    <row r="768" spans="1:23" hidden="1">
       <c r="A768">
         <v>775</v>
       </c>
@@ -34318,7 +34381,7 @@
       </c>
       <c r="W768" s="3"/>
     </row>
-    <row r="769" spans="1:23">
+    <row r="769" spans="1:23" hidden="1">
       <c r="A769">
         <v>776</v>
       </c>
@@ -34358,7 +34421,7 @@
       </c>
       <c r="W769" s="3"/>
     </row>
-    <row r="770" spans="1:23">
+    <row r="770" spans="1:23" hidden="1">
       <c r="A770">
         <v>777</v>
       </c>
@@ -34408,7 +34471,7 @@
       </c>
       <c r="W770" s="3"/>
     </row>
-    <row r="771" spans="1:23">
+    <row r="771" spans="1:23" hidden="1">
       <c r="A771">
         <v>778</v>
       </c>
@@ -34449,7 +34512,7 @@
       </c>
       <c r="W771" s="3"/>
     </row>
-    <row r="772" spans="1:23">
+    <row r="772" spans="1:23" hidden="1">
       <c r="A772">
         <v>779</v>
       </c>
@@ -34487,7 +34550,7 @@
       </c>
       <c r="W772" s="3"/>
     </row>
-    <row r="773" spans="1:23">
+    <row r="773" spans="1:23" hidden="1">
       <c r="A773">
         <v>780</v>
       </c>
@@ -34528,7 +34591,7 @@
       </c>
       <c r="W773" s="3"/>
     </row>
-    <row r="774" spans="1:23">
+    <row r="774" spans="1:23" hidden="1">
       <c r="A774">
         <v>781</v>
       </c>
@@ -34569,7 +34632,7 @@
       </c>
       <c r="W774" s="3"/>
     </row>
-    <row r="775" spans="1:23">
+    <row r="775" spans="1:23" hidden="1">
       <c r="A775">
         <v>782</v>
       </c>
@@ -34692,7 +34755,7 @@
       </c>
       <c r="W777" s="3"/>
     </row>
-    <row r="778" spans="1:23">
+    <row r="778" spans="1:23" hidden="1">
       <c r="A778">
         <v>785</v>
       </c>
@@ -34774,7 +34837,7 @@
       </c>
       <c r="W779" s="3"/>
     </row>
-    <row r="780" spans="1:23">
+    <row r="780" spans="1:23" hidden="1">
       <c r="A780">
         <v>787</v>
       </c>
@@ -34812,7 +34875,7 @@
       </c>
       <c r="W780" s="3"/>
     </row>
-    <row r="781" spans="1:23">
+    <row r="781" spans="1:23" hidden="1">
       <c r="A781">
         <v>788</v>
       </c>
@@ -34850,7 +34913,7 @@
       </c>
       <c r="W781" s="3"/>
     </row>
-    <row r="782" spans="1:23">
+    <row r="782" spans="1:23" hidden="1">
       <c r="A782">
         <v>789</v>
       </c>
@@ -34891,7 +34954,7 @@
       </c>
       <c r="W782" s="3"/>
     </row>
-    <row r="783" spans="1:23">
+    <row r="783" spans="1:23" hidden="1">
       <c r="A783">
         <v>790</v>
       </c>
@@ -34932,7 +34995,7 @@
       </c>
       <c r="W783" s="3"/>
     </row>
-    <row r="784" spans="1:23">
+    <row r="784" spans="1:23" hidden="1">
       <c r="A784">
         <v>791</v>
       </c>
@@ -34973,7 +35036,7 @@
       </c>
       <c r="W784" s="3"/>
     </row>
-    <row r="785" spans="1:23">
+    <row r="785" spans="1:23" hidden="1">
       <c r="A785">
         <v>792</v>
       </c>
@@ -35014,7 +35077,7 @@
       </c>
       <c r="W785" s="3"/>
     </row>
-    <row r="786" spans="1:23">
+    <row r="786" spans="1:23" hidden="1">
       <c r="A786">
         <v>793</v>
       </c>
@@ -35055,7 +35118,7 @@
       </c>
       <c r="W786" s="3"/>
     </row>
-    <row r="787" spans="1:23">
+    <row r="787" spans="1:23" hidden="1">
       <c r="A787">
         <v>794</v>
       </c>
@@ -35105,7 +35168,7 @@
       </c>
       <c r="W787" s="3"/>
     </row>
-    <row r="788" spans="1:23">
+    <row r="788" spans="1:23" hidden="1">
       <c r="A788">
         <v>795</v>
       </c>
@@ -35145,7 +35208,7 @@
       </c>
       <c r="W788" s="3"/>
     </row>
-    <row r="789" spans="1:23">
+    <row r="789" spans="1:23" hidden="1">
       <c r="A789">
         <v>796</v>
       </c>
@@ -35195,7 +35258,7 @@
       </c>
       <c r="W789" s="3"/>
     </row>
-    <row r="790" spans="1:23">
+    <row r="790" spans="1:23" hidden="1">
       <c r="A790">
         <v>797</v>
       </c>
@@ -35236,7 +35299,7 @@
       </c>
       <c r="W790" s="3"/>
     </row>
-    <row r="791" spans="1:23">
+    <row r="791" spans="1:23" hidden="1">
       <c r="A791">
         <v>798</v>
       </c>
@@ -35275,7 +35338,7 @@
       </c>
       <c r="W791" s="3"/>
     </row>
-    <row r="792" spans="1:23">
+    <row r="792" spans="1:23" hidden="1">
       <c r="A792">
         <v>799</v>
       </c>
@@ -35316,7 +35379,7 @@
       </c>
       <c r="W792" s="3"/>
     </row>
-    <row r="793" spans="1:23">
+    <row r="793" spans="1:23" hidden="1">
       <c r="A793">
         <v>800</v>
       </c>
@@ -35353,7 +35416,7 @@
       </c>
       <c r="W793" s="3"/>
     </row>
-    <row r="794" spans="1:23">
+    <row r="794" spans="1:23" hidden="1">
       <c r="A794">
         <v>801</v>
       </c>
@@ -35393,7 +35456,7 @@
       </c>
       <c r="W794" s="3"/>
     </row>
-    <row r="795" spans="1:23">
+    <row r="795" spans="1:23" hidden="1">
       <c r="A795">
         <v>802</v>
       </c>
@@ -35434,7 +35497,7 @@
       </c>
       <c r="W795" s="3"/>
     </row>
-    <row r="796" spans="1:23">
+    <row r="796" spans="1:23" hidden="1">
       <c r="A796">
         <v>803</v>
       </c>
@@ -35475,7 +35538,7 @@
       </c>
       <c r="W796" s="3"/>
     </row>
-    <row r="797" spans="1:23">
+    <row r="797" spans="1:23" hidden="1">
       <c r="A797">
         <v>804</v>
       </c>
@@ -35512,7 +35575,7 @@
       </c>
       <c r="W797" s="3"/>
     </row>
-    <row r="798" spans="1:23">
+    <row r="798" spans="1:23" hidden="1">
       <c r="A798">
         <v>805</v>
       </c>
@@ -35562,7 +35625,7 @@
       </c>
       <c r="W798" s="3"/>
     </row>
-    <row r="799" spans="1:23">
+    <row r="799" spans="1:23" hidden="1">
       <c r="A799">
         <v>806</v>
       </c>
@@ -35603,7 +35666,7 @@
       </c>
       <c r="W799" s="3"/>
     </row>
-    <row r="800" spans="1:23">
+    <row r="800" spans="1:23" hidden="1">
       <c r="A800">
         <v>807</v>
       </c>
@@ -35640,7 +35703,7 @@
       </c>
       <c r="W800" s="3"/>
     </row>
-    <row r="801" spans="1:23">
+    <row r="801" spans="1:23" hidden="1">
       <c r="A801">
         <v>808</v>
       </c>
@@ -35678,7 +35741,7 @@
       </c>
       <c r="W801" s="3"/>
     </row>
-    <row r="802" spans="1:23">
+    <row r="802" spans="1:23" hidden="1">
       <c r="A802">
         <v>809</v>
       </c>
@@ -35716,7 +35779,7 @@
       </c>
       <c r="W802" s="3"/>
     </row>
-    <row r="803" spans="1:23">
+    <row r="803" spans="1:23" hidden="1">
       <c r="A803">
         <v>810</v>
       </c>
@@ -35766,7 +35829,7 @@
       </c>
       <c r="W803" s="3"/>
     </row>
-    <row r="804" spans="1:23">
+    <row r="804" spans="1:23" hidden="1">
       <c r="A804">
         <v>811</v>
       </c>
@@ -35807,7 +35870,7 @@
       </c>
       <c r="W804" s="3"/>
     </row>
-    <row r="805" spans="1:23">
+    <row r="805" spans="1:23" hidden="1">
       <c r="A805">
         <v>812</v>
       </c>
@@ -35847,7 +35910,7 @@
       </c>
       <c r="W805" s="3"/>
     </row>
-    <row r="806" spans="1:23">
+    <row r="806" spans="1:23" hidden="1">
       <c r="A806">
         <v>813</v>
       </c>
@@ -35887,7 +35950,7 @@
       </c>
       <c r="W806" s="3"/>
     </row>
-    <row r="807" spans="1:23">
+    <row r="807" spans="1:23" hidden="1">
       <c r="A807">
         <v>814</v>
       </c>
@@ -35925,7 +35988,7 @@
       </c>
       <c r="W807" s="3"/>
     </row>
-    <row r="808" spans="1:23">
+    <row r="808" spans="1:23" hidden="1">
       <c r="A808">
         <v>815</v>
       </c>
@@ -35966,7 +36029,7 @@
       </c>
       <c r="W808" s="3"/>
     </row>
-    <row r="809" spans="1:23">
+    <row r="809" spans="1:23" hidden="1">
       <c r="A809">
         <v>816</v>
       </c>
@@ -36003,7 +36066,7 @@
       </c>
       <c r="W809" s="3"/>
     </row>
-    <row r="810" spans="1:23">
+    <row r="810" spans="1:23" hidden="1">
       <c r="A810">
         <v>817</v>
       </c>
@@ -36044,7 +36107,7 @@
       </c>
       <c r="W810" s="3"/>
     </row>
-    <row r="811" spans="1:23">
+    <row r="811" spans="1:23" hidden="1">
       <c r="A811">
         <v>818</v>
       </c>
@@ -36094,7 +36157,7 @@
       </c>
       <c r="W811" s="3"/>
     </row>
-    <row r="812" spans="1:23">
+    <row r="812" spans="1:23" hidden="1">
       <c r="A812">
         <v>819</v>
       </c>
@@ -36135,7 +36198,7 @@
       </c>
       <c r="W812" s="3"/>
     </row>
-    <row r="813" spans="1:23">
+    <row r="813" spans="1:23" hidden="1">
       <c r="A813">
         <v>820</v>
       </c>
@@ -36174,7 +36237,7 @@
       </c>
       <c r="W813" s="3"/>
     </row>
-    <row r="814" spans="1:23">
+    <row r="814" spans="1:23" hidden="1">
       <c r="A814">
         <v>821</v>
       </c>
@@ -36214,7 +36277,7 @@
       </c>
       <c r="W814" s="3"/>
     </row>
-    <row r="815" spans="1:23">
+    <row r="815" spans="1:23" hidden="1">
       <c r="A815">
         <v>822</v>
       </c>
@@ -36255,7 +36318,7 @@
       </c>
       <c r="W815" s="3"/>
     </row>
-    <row r="816" spans="1:23">
+    <row r="816" spans="1:23" hidden="1">
       <c r="A816">
         <v>823</v>
       </c>
@@ -36296,7 +36359,7 @@
       </c>
       <c r="W816" s="3"/>
     </row>
-    <row r="817" spans="1:23">
+    <row r="817" spans="1:23" hidden="1">
       <c r="A817">
         <v>824</v>
       </c>
@@ -36337,7 +36400,7 @@
       </c>
       <c r="W817" s="3"/>
     </row>
-    <row r="818" spans="1:23">
+    <row r="818" spans="1:23" hidden="1">
       <c r="A818">
         <v>825</v>
       </c>
@@ -36377,7 +36440,7 @@
       </c>
       <c r="W818" s="3"/>
     </row>
-    <row r="819" spans="1:23">
+    <row r="819" spans="1:23" hidden="1">
       <c r="A819">
         <v>826</v>
       </c>
@@ -36417,7 +36480,7 @@
       </c>
       <c r="W819" s="3"/>
     </row>
-    <row r="820" spans="1:23">
+    <row r="820" spans="1:23" hidden="1">
       <c r="A820">
         <v>827</v>
       </c>
@@ -36467,7 +36530,7 @@
       </c>
       <c r="W820" s="3"/>
     </row>
-    <row r="821" spans="1:23">
+    <row r="821" spans="1:23" hidden="1">
       <c r="A821">
         <v>828</v>
       </c>
@@ -36507,7 +36570,7 @@
       </c>
       <c r="W821" s="3"/>
     </row>
-    <row r="822" spans="1:23">
+    <row r="822" spans="1:23" hidden="1">
       <c r="A822">
         <v>829</v>
       </c>
@@ -36548,7 +36611,7 @@
       </c>
       <c r="W822" s="3"/>
     </row>
-    <row r="823" spans="1:23">
+    <row r="823" spans="1:23" hidden="1">
       <c r="A823">
         <v>830</v>
       </c>
@@ -36589,7 +36652,7 @@
       </c>
       <c r="W823" s="3"/>
     </row>
-    <row r="824" spans="1:23">
+    <row r="824" spans="1:23" hidden="1">
       <c r="A824">
         <v>831</v>
       </c>
@@ -36627,7 +36690,7 @@
       </c>
       <c r="W824" s="3"/>
     </row>
-    <row r="825" spans="1:23">
+    <row r="825" spans="1:23" hidden="1">
       <c r="A825">
         <v>832</v>
       </c>
@@ -36677,7 +36740,7 @@
       </c>
       <c r="W825" s="3"/>
     </row>
-    <row r="826" spans="1:23">
+    <row r="826" spans="1:23" hidden="1">
       <c r="A826">
         <v>833</v>
       </c>
@@ -36726,6 +36789,328 @@
         <v>280</v>
       </c>
       <c r="W826" s="3"/>
+    </row>
+    <row r="827" spans="1:23" hidden="1">
+      <c r="A827">
+        <v>834</v>
+      </c>
+      <c r="B827" s="4">
+        <v>46288.418148148201</v>
+      </c>
+      <c r="C827" s="4">
+        <v>46288.4195833333</v>
+      </c>
+      <c r="D827" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E827" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G827" s="1">
+        <v>46288</v>
+      </c>
+      <c r="H827" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M827" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="U827" s="3"/>
+      <c r="V827" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W827" s="3"/>
+    </row>
+    <row r="828" spans="1:23" hidden="1">
+      <c r="A828">
+        <v>835</v>
+      </c>
+      <c r="B828" s="4">
+        <v>46288.442442129599</v>
+      </c>
+      <c r="C828" s="4">
+        <v>46288.446053240703</v>
+      </c>
+      <c r="D828" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E828" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G828" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H828" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="L828" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M828" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="U828" s="3"/>
+      <c r="V828" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="W828" s="3"/>
+    </row>
+    <row r="829" spans="1:23" hidden="1">
+      <c r="A829">
+        <v>836</v>
+      </c>
+      <c r="B829" s="4">
+        <v>46288.446099537003</v>
+      </c>
+      <c r="C829" s="4">
+        <v>46288.450555555602</v>
+      </c>
+      <c r="D829" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E829" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G829" s="1">
+        <v>46264</v>
+      </c>
+      <c r="H829" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="L829" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M829" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="U829" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="V829" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="W829" s="3"/>
+    </row>
+    <row r="830" spans="1:23" hidden="1">
+      <c r="A830">
+        <v>837</v>
+      </c>
+      <c r="B830" s="4">
+        <v>46288.450590277796</v>
+      </c>
+      <c r="C830" s="4">
+        <v>46288.451365740701</v>
+      </c>
+      <c r="D830" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E830" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G830" s="1">
+        <v>46288</v>
+      </c>
+      <c r="H830" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="L830" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="M830" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="U830" s="3"/>
+      <c r="V830" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="W830" s="3"/>
+    </row>
+    <row r="831" spans="1:23">
+      <c r="A831">
+        <v>838</v>
+      </c>
+      <c r="B831" s="4">
+        <v>46288.471956018497</v>
+      </c>
+      <c r="C831" s="4">
+        <v>46288.479560185202</v>
+      </c>
+      <c r="D831" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E831" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G831" s="1">
+        <v>46282</v>
+      </c>
+      <c r="H831" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="K831" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L831" s="3"/>
+      <c r="M831" s="3"/>
+      <c r="T831">
+        <v>13</v>
+      </c>
+      <c r="U831" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="V831" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="W831" s="3"/>
+    </row>
+    <row r="832" spans="1:23">
+      <c r="A832">
+        <v>839</v>
+      </c>
+      <c r="B832" s="4">
+        <v>46288.479814814797</v>
+      </c>
+      <c r="C832" s="4">
+        <v>46288.481527777803</v>
+      </c>
+      <c r="D832" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E832" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G832" s="1">
+        <v>46280</v>
+      </c>
+      <c r="H832" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="K832" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L832" s="3"/>
+      <c r="M832" s="3"/>
+      <c r="T832">
+        <v>21</v>
+      </c>
+      <c r="U832" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="V832" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="W832" s="3"/>
+    </row>
+    <row r="833" spans="1:23" hidden="1">
+      <c r="A833">
+        <v>840</v>
+      </c>
+      <c r="B833" s="4">
+        <v>46288.481597222199</v>
+      </c>
+      <c r="C833" s="4">
+        <v>46288.4835185185</v>
+      </c>
+      <c r="D833" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E833" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G833" s="1">
+        <v>46267</v>
+      </c>
+      <c r="H833" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J833" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L833" s="3"/>
+      <c r="M833" s="3"/>
+      <c r="T833">
+        <v>50</v>
+      </c>
+      <c r="U833" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="V833" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="W833" s="3"/>
+    </row>
+    <row r="834" spans="1:23">
+      <c r="A834" s="8">
+        <v>841</v>
+      </c>
+      <c r="B834" s="4">
+        <v>46288.486631944397</v>
+      </c>
+      <c r="C834" s="4">
+        <v>46288.492384259298</v>
+      </c>
+      <c r="D834" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E834" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G834" s="1">
+        <v>46234</v>
+      </c>
+      <c r="H834" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="I834" s="8"/>
+      <c r="J834" s="8"/>
+      <c r="K834" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L834" s="3"/>
+      <c r="M834" s="3"/>
+      <c r="N834" s="8"/>
+      <c r="O834" s="8"/>
+      <c r="P834" s="8"/>
+      <c r="Q834" s="8"/>
+      <c r="R834" s="8"/>
+      <c r="S834" s="8"/>
+      <c r="T834" s="8">
+        <v>158</v>
+      </c>
+      <c r="U834" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="V834" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="W834" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="706" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18BB2EA2-4858-4C0B-8AB8-8DD5DCE5D135}"/>
+  <xr:revisionPtr revIDLastSave="713" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC643704-EE88-485B-AEF0-332BBE42D76E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5964" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5970" uniqueCount="1231">
   <si>
     <t>Id</t>
   </si>
@@ -3726,6 +3726,9 @@
   </si>
   <si>
     <t>Workshop "Participatory Aquatic Monitoring with a Focus on Water Governance" and "Morphological Diagnosis and Taxonomy of Common Families of Aquatic Macroinvertebrates"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtime receiver maintenance and meeting new property owners in Sturgeon Bay </t>
   </si>
 </sst>
 </file>
@@ -3770,7 +3773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3779,6 +3782,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3859,8 +3863,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W848" totalsRowShown="0">
-  <autoFilter ref="A1:W848" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W849" totalsRowShown="0">
+  <autoFilter ref="A1:W849" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="myoungquist@sheddaquarium.org"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W848">
     <sortCondition ref="E1:E848"/>
   </sortState>
@@ -4030,7 +4040,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="854" latestEventMarker="892">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="855" latestEventMarker="893">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4357,7 +4367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W848"/>
+  <dimension ref="A1:W849"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -4442,7 +4452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15">
+    <row r="2" spans="1:23" ht="15" hidden="1">
       <c r="A2">
         <v>129</v>
       </c>
@@ -4485,7 +4495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15">
+    <row r="3" spans="1:23" ht="15" hidden="1">
       <c r="A3">
         <v>130</v>
       </c>
@@ -4522,7 +4532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15">
+    <row r="4" spans="1:23" ht="15" hidden="1">
       <c r="A4">
         <v>131</v>
       </c>
@@ -4559,7 +4569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15">
+    <row r="5" spans="1:23" ht="15" hidden="1">
       <c r="A5">
         <v>132</v>
       </c>
@@ -4596,7 +4606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15">
+    <row r="6" spans="1:23" ht="15" hidden="1">
       <c r="A6">
         <v>133</v>
       </c>
@@ -4639,7 +4649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15">
+    <row r="7" spans="1:23" ht="15" hidden="1">
       <c r="A7">
         <v>134</v>
       </c>
@@ -4679,7 +4689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15">
+    <row r="8" spans="1:23" ht="15" hidden="1">
       <c r="A8">
         <v>135</v>
       </c>
@@ -4719,7 +4729,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15">
+    <row r="9" spans="1:23" ht="15" hidden="1">
       <c r="A9">
         <v>136</v>
       </c>
@@ -4758,7 +4768,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15">
+    <row r="10" spans="1:23" ht="15" hidden="1">
       <c r="A10">
         <v>137</v>
       </c>
@@ -4797,7 +4807,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15">
+    <row r="11" spans="1:23" ht="15" hidden="1">
       <c r="A11">
         <v>138</v>
       </c>
@@ -4840,7 +4850,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15">
+    <row r="12" spans="1:23" ht="15" hidden="1">
       <c r="A12">
         <v>139</v>
       </c>
@@ -4880,7 +4890,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15">
+    <row r="13" spans="1:23" ht="15" hidden="1">
       <c r="A13">
         <v>140</v>
       </c>
@@ -4919,7 +4929,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15">
+    <row r="14" spans="1:23" ht="15" hidden="1">
       <c r="A14">
         <v>141</v>
       </c>
@@ -4958,7 +4968,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15">
+    <row r="15" spans="1:23" ht="15" hidden="1">
       <c r="A15">
         <v>142</v>
       </c>
@@ -4997,7 +5007,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15">
+    <row r="16" spans="1:23" ht="15" hidden="1">
       <c r="A16">
         <v>143</v>
       </c>
@@ -5037,7 +5047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15">
+    <row r="17" spans="1:23" ht="15" hidden="1">
       <c r="A17">
         <v>144</v>
       </c>
@@ -5080,7 +5090,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15">
+    <row r="18" spans="1:23" ht="15" hidden="1">
       <c r="A18">
         <v>145</v>
       </c>
@@ -5119,7 +5129,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15">
+    <row r="19" spans="1:23" ht="15" hidden="1">
       <c r="A19">
         <v>146</v>
       </c>
@@ -5156,7 +5166,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15">
+    <row r="20" spans="1:23" ht="15" hidden="1">
       <c r="A20">
         <v>147</v>
       </c>
@@ -5193,7 +5203,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15">
+    <row r="21" spans="1:23" ht="15" hidden="1">
       <c r="A21">
         <v>148</v>
       </c>
@@ -5230,7 +5240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="15">
+    <row r="22" spans="1:23" ht="15" hidden="1">
       <c r="A22">
         <v>149</v>
       </c>
@@ -5273,7 +5283,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15">
+    <row r="23" spans="1:23" ht="15" hidden="1">
       <c r="A23">
         <v>150</v>
       </c>
@@ -5316,7 +5326,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="15">
+    <row r="24" spans="1:23" ht="15" hidden="1">
       <c r="A24">
         <v>151</v>
       </c>
@@ -5355,7 +5365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="15">
+    <row r="25" spans="1:23" ht="15" hidden="1">
       <c r="A25">
         <v>152</v>
       </c>
@@ -5394,7 +5404,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="15">
+    <row r="26" spans="1:23" ht="15" hidden="1">
       <c r="A26">
         <v>270</v>
       </c>
@@ -5433,7 +5443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="15">
+    <row r="27" spans="1:23" ht="15" hidden="1">
       <c r="A27">
         <v>272</v>
       </c>
@@ -5476,7 +5486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="15">
+    <row r="28" spans="1:23" ht="15" hidden="1">
       <c r="A28">
         <v>273</v>
       </c>
@@ -5519,7 +5529,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="15">
+    <row r="29" spans="1:23" ht="15" hidden="1">
       <c r="A29">
         <v>274</v>
       </c>
@@ -5559,7 +5569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="15">
+    <row r="30" spans="1:23" ht="15" hidden="1">
       <c r="A30">
         <v>275</v>
       </c>
@@ -5599,7 +5609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="15">
+    <row r="31" spans="1:23" ht="15" hidden="1">
       <c r="A31">
         <v>294</v>
       </c>
@@ -5638,7 +5648,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="15">
+    <row r="32" spans="1:23" ht="15" hidden="1">
       <c r="A32">
         <v>518</v>
       </c>
@@ -5675,7 +5685,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="15">
+    <row r="33" spans="1:23" ht="15" hidden="1">
       <c r="A33">
         <v>519</v>
       </c>
@@ -5715,7 +5725,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="15">
+    <row r="34" spans="1:23" ht="15" hidden="1">
       <c r="A34">
         <v>520</v>
       </c>
@@ -5752,7 +5762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="15">
+    <row r="35" spans="1:23" ht="15" hidden="1">
       <c r="A35">
         <v>521</v>
       </c>
@@ -5795,7 +5805,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="15">
+    <row r="36" spans="1:23" ht="15" hidden="1">
       <c r="A36">
         <v>522</v>
       </c>
@@ -5834,7 +5844,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="15">
+    <row r="37" spans="1:23" ht="15" hidden="1">
       <c r="A37">
         <v>523</v>
       </c>
@@ -5873,7 +5883,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15">
+    <row r="38" spans="1:23" ht="15" hidden="1">
       <c r="A38">
         <v>524</v>
       </c>
@@ -5910,7 +5920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="15">
+    <row r="39" spans="1:23" ht="15" hidden="1">
       <c r="A39">
         <v>525</v>
       </c>
@@ -5947,7 +5957,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="15">
+    <row r="40" spans="1:23" ht="15" hidden="1">
       <c r="A40">
         <v>526</v>
       </c>
@@ -5990,7 +6000,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="15">
+    <row r="41" spans="1:23" ht="15" hidden="1">
       <c r="A41">
         <v>527</v>
       </c>
@@ -6033,7 +6043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="15">
+    <row r="42" spans="1:23" ht="15" hidden="1">
       <c r="A42">
         <v>528</v>
       </c>
@@ -6076,7 +6086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="15">
+    <row r="43" spans="1:23" ht="15" hidden="1">
       <c r="A43">
         <v>529</v>
       </c>
@@ -6117,7 +6127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="15">
+    <row r="44" spans="1:23" ht="15" hidden="1">
       <c r="A44">
         <v>530</v>
       </c>
@@ -6156,7 +6166,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="15">
+    <row r="45" spans="1:23" ht="15" hidden="1">
       <c r="A45">
         <v>531</v>
       </c>
@@ -6195,7 +6205,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="15">
+    <row r="46" spans="1:23" ht="15" hidden="1">
       <c r="A46">
         <v>544</v>
       </c>
@@ -6232,7 +6242,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="15">
+    <row r="47" spans="1:23" ht="15" hidden="1">
       <c r="A47">
         <v>580</v>
       </c>
@@ -6267,7 +6277,7 @@
       </c>
       <c r="W47" s="3"/>
     </row>
-    <row r="48" spans="1:23" ht="15">
+    <row r="48" spans="1:23" ht="15" hidden="1">
       <c r="A48">
         <v>686</v>
       </c>
@@ -6308,7 +6318,7 @@
       </c>
       <c r="W48" s="3"/>
     </row>
-    <row r="49" spans="1:23" ht="15">
+    <row r="49" spans="1:23" ht="15" hidden="1">
       <c r="A49">
         <v>687</v>
       </c>
@@ -6349,7 +6359,7 @@
       </c>
       <c r="W49" s="3"/>
     </row>
-    <row r="50" spans="1:23" ht="15">
+    <row r="50" spans="1:23" ht="15" hidden="1">
       <c r="A50">
         <v>688</v>
       </c>
@@ -6390,7 +6400,7 @@
       </c>
       <c r="W50" s="3"/>
     </row>
-    <row r="51" spans="1:23" ht="15">
+    <row r="51" spans="1:23" ht="15" hidden="1">
       <c r="A51">
         <v>689</v>
       </c>
@@ -6428,7 +6438,7 @@
       </c>
       <c r="W51" s="3"/>
     </row>
-    <row r="52" spans="1:23" ht="15">
+    <row r="52" spans="1:23" ht="15" hidden="1">
       <c r="A52">
         <v>690</v>
       </c>
@@ -6469,7 +6479,7 @@
       </c>
       <c r="W52" s="3"/>
     </row>
-    <row r="53" spans="1:23" ht="15">
+    <row r="53" spans="1:23" ht="15" hidden="1">
       <c r="A53">
         <v>691</v>
       </c>
@@ -6510,7 +6520,7 @@
       </c>
       <c r="W53" s="3"/>
     </row>
-    <row r="54" spans="1:23" ht="15">
+    <row r="54" spans="1:23" ht="15" hidden="1">
       <c r="A54">
         <v>692</v>
       </c>
@@ -6551,7 +6561,7 @@
       </c>
       <c r="W54" s="3"/>
     </row>
-    <row r="55" spans="1:23" ht="15">
+    <row r="55" spans="1:23" ht="15" hidden="1">
       <c r="A55">
         <v>693</v>
       </c>
@@ -6592,7 +6602,7 @@
       </c>
       <c r="W55" s="3"/>
     </row>
-    <row r="56" spans="1:23" ht="15">
+    <row r="56" spans="1:23" ht="15" hidden="1">
       <c r="A56">
         <v>694</v>
       </c>
@@ -6633,7 +6643,7 @@
       </c>
       <c r="W56" s="3"/>
     </row>
-    <row r="57" spans="1:23" ht="15">
+    <row r="57" spans="1:23" ht="15" hidden="1">
       <c r="A57">
         <v>695</v>
       </c>
@@ -6674,7 +6684,7 @@
       </c>
       <c r="W57" s="3"/>
     </row>
-    <row r="58" spans="1:23" ht="15">
+    <row r="58" spans="1:23" ht="15" hidden="1">
       <c r="A58">
         <v>696</v>
       </c>
@@ -6715,7 +6725,7 @@
       </c>
       <c r="W58" s="3"/>
     </row>
-    <row r="59" spans="1:23" ht="15">
+    <row r="59" spans="1:23" ht="15" hidden="1">
       <c r="A59">
         <v>697</v>
       </c>
@@ -6752,7 +6762,7 @@
       </c>
       <c r="W59" s="3"/>
     </row>
-    <row r="60" spans="1:23" ht="15">
+    <row r="60" spans="1:23" ht="15" hidden="1">
       <c r="A60">
         <v>698</v>
       </c>
@@ -6792,7 +6802,7 @@
       </c>
       <c r="W60" s="3"/>
     </row>
-    <row r="61" spans="1:23" ht="15">
+    <row r="61" spans="1:23" ht="15" hidden="1">
       <c r="A61">
         <v>765</v>
       </c>
@@ -6833,7 +6843,7 @@
       </c>
       <c r="W61" s="3"/>
     </row>
-    <row r="62" spans="1:23" ht="15">
+    <row r="62" spans="1:23" ht="15" hidden="1">
       <c r="A62">
         <v>766</v>
       </c>
@@ -6874,7 +6884,7 @@
       </c>
       <c r="W62" s="3"/>
     </row>
-    <row r="63" spans="1:23" ht="15">
+    <row r="63" spans="1:23" ht="15" hidden="1">
       <c r="A63">
         <v>767</v>
       </c>
@@ -6915,7 +6925,7 @@
       </c>
       <c r="W63" s="3"/>
     </row>
-    <row r="64" spans="1:23" ht="15">
+    <row r="64" spans="1:23" ht="15" hidden="1">
       <c r="A64">
         <v>768</v>
       </c>
@@ -6965,7 +6975,7 @@
       </c>
       <c r="W64" s="3"/>
     </row>
-    <row r="65" spans="1:23" ht="15">
+    <row r="65" spans="1:23" ht="15" hidden="1">
       <c r="A65">
         <v>769</v>
       </c>
@@ -7006,7 +7016,7 @@
       </c>
       <c r="W65" s="3"/>
     </row>
-    <row r="66" spans="1:23" ht="15">
+    <row r="66" spans="1:23" ht="15" hidden="1">
       <c r="A66">
         <v>770</v>
       </c>
@@ -7047,7 +7057,7 @@
       </c>
       <c r="W66" s="3"/>
     </row>
-    <row r="67" spans="1:23" ht="15">
+    <row r="67" spans="1:23" ht="15" hidden="1">
       <c r="A67">
         <v>771</v>
       </c>
@@ -7097,7 +7107,7 @@
       </c>
       <c r="W67" s="3"/>
     </row>
-    <row r="68" spans="1:23" ht="15">
+    <row r="68" spans="1:23" ht="15" hidden="1">
       <c r="A68">
         <v>772</v>
       </c>
@@ -7147,7 +7157,7 @@
       </c>
       <c r="W68" s="3"/>
     </row>
-    <row r="69" spans="1:23" ht="15">
+    <row r="69" spans="1:23" ht="15" hidden="1">
       <c r="A69">
         <v>15</v>
       </c>
@@ -7185,7 +7195,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="15">
+    <row r="70" spans="1:23" ht="15" hidden="1">
       <c r="A70">
         <v>16</v>
       </c>
@@ -7223,7 +7233,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="15">
+    <row r="71" spans="1:23" ht="15" hidden="1">
       <c r="A71">
         <v>17</v>
       </c>
@@ -7258,7 +7268,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="15">
+    <row r="72" spans="1:23" ht="15" hidden="1">
       <c r="A72">
         <v>18</v>
       </c>
@@ -7293,7 +7303,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="15">
+    <row r="73" spans="1:23" ht="15" hidden="1">
       <c r="A73">
         <v>19</v>
       </c>
@@ -7331,7 +7341,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="15">
+    <row r="74" spans="1:23" ht="15" hidden="1">
       <c r="A74">
         <v>20</v>
       </c>
@@ -7366,7 +7376,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="15">
+    <row r="75" spans="1:23" ht="15" hidden="1">
       <c r="A75">
         <v>26</v>
       </c>
@@ -7398,7 +7408,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="15">
+    <row r="76" spans="1:23" ht="15" hidden="1">
       <c r="A76">
         <v>48</v>
       </c>
@@ -7430,7 +7440,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="15">
+    <row r="77" spans="1:23" ht="15" hidden="1">
       <c r="A77">
         <v>59</v>
       </c>
@@ -7468,7 +7478,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="15">
+    <row r="78" spans="1:23" ht="15" hidden="1">
       <c r="A78">
         <v>63</v>
       </c>
@@ -7506,7 +7516,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="15">
+    <row r="79" spans="1:23" ht="15" hidden="1">
       <c r="A79">
         <v>64</v>
       </c>
@@ -7541,7 +7551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="15">
+    <row r="80" spans="1:23" ht="15" hidden="1">
       <c r="A80">
         <v>65</v>
       </c>
@@ -7576,7 +7586,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="15">
+    <row r="81" spans="1:23" ht="15" hidden="1">
       <c r="A81">
         <v>66</v>
       </c>
@@ -7617,7 +7627,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="15">
+    <row r="82" spans="1:23" ht="15" hidden="1">
       <c r="A82">
         <v>68</v>
       </c>
@@ -7649,7 +7659,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="15">
+    <row r="83" spans="1:23" ht="15" hidden="1">
       <c r="A83">
         <v>117</v>
       </c>
@@ -7688,7 +7698,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="15">
+    <row r="84" spans="1:23" ht="15" hidden="1">
       <c r="A84">
         <v>118</v>
       </c>
@@ -7723,7 +7733,7 @@
       </c>
       <c r="W84" s="3"/>
     </row>
-    <row r="85" spans="1:23" ht="15">
+    <row r="85" spans="1:23" ht="15" hidden="1">
       <c r="A85">
         <v>119</v>
       </c>
@@ -7761,7 +7771,7 @@
       </c>
       <c r="W85" s="3"/>
     </row>
-    <row r="86" spans="1:23" ht="15">
+    <row r="86" spans="1:23" ht="15" hidden="1">
       <c r="A86">
         <v>204</v>
       </c>
@@ -7801,7 +7811,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="15">
+    <row r="87" spans="1:23" ht="15" hidden="1">
       <c r="A87">
         <v>205</v>
       </c>
@@ -7836,7 +7846,7 @@
       </c>
       <c r="W87" s="3"/>
     </row>
-    <row r="88" spans="1:23" ht="15">
+    <row r="88" spans="1:23" ht="15" hidden="1">
       <c r="A88">
         <v>206</v>
       </c>
@@ -7875,7 +7885,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="15">
+    <row r="89" spans="1:23" ht="15" hidden="1">
       <c r="A89">
         <v>207</v>
       </c>
@@ -7914,7 +7924,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="15">
+    <row r="90" spans="1:23" ht="15" hidden="1">
       <c r="A90">
         <v>208</v>
       </c>
@@ -7954,7 +7964,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="15">
+    <row r="91" spans="1:23" ht="15" hidden="1">
       <c r="A91">
         <v>209</v>
       </c>
@@ -7989,7 +7999,7 @@
       </c>
       <c r="W91" s="3"/>
     </row>
-    <row r="92" spans="1:23" ht="15">
+    <row r="92" spans="1:23" ht="15" hidden="1">
       <c r="A92">
         <v>210</v>
       </c>
@@ -8027,7 +8037,7 @@
       </c>
       <c r="W92" s="3"/>
     </row>
-    <row r="93" spans="1:23" ht="15">
+    <row r="93" spans="1:23" ht="15" hidden="1">
       <c r="A93">
         <v>211</v>
       </c>
@@ -8065,7 +8075,7 @@
       </c>
       <c r="W93" s="3"/>
     </row>
-    <row r="94" spans="1:23" ht="15">
+    <row r="94" spans="1:23" ht="15" hidden="1">
       <c r="A94">
         <v>212</v>
       </c>
@@ -8103,7 +8113,7 @@
       </c>
       <c r="W94" s="3"/>
     </row>
-    <row r="95" spans="1:23" ht="15">
+    <row r="95" spans="1:23" ht="15" hidden="1">
       <c r="A95">
         <v>213</v>
       </c>
@@ -8140,7 +8150,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="15">
+    <row r="96" spans="1:23" ht="15" hidden="1">
       <c r="A96">
         <v>214</v>
       </c>
@@ -8175,7 +8185,7 @@
       </c>
       <c r="W96" s="3"/>
     </row>
-    <row r="97" spans="1:23" ht="15">
+    <row r="97" spans="1:23" ht="15" hidden="1">
       <c r="A97">
         <v>215</v>
       </c>
@@ -8210,7 +8220,7 @@
       </c>
       <c r="W97" s="3"/>
     </row>
-    <row r="98" spans="1:23" ht="15">
+    <row r="98" spans="1:23" ht="15" hidden="1">
       <c r="A98">
         <v>216</v>
       </c>
@@ -8247,7 +8257,7 @@
       </c>
       <c r="W98" s="3"/>
     </row>
-    <row r="99" spans="1:23" ht="15">
+    <row r="99" spans="1:23" ht="15" hidden="1">
       <c r="A99">
         <v>217</v>
       </c>
@@ -8284,7 +8294,7 @@
       </c>
       <c r="W99" s="3"/>
     </row>
-    <row r="100" spans="1:23" ht="15">
+    <row r="100" spans="1:23" ht="15" hidden="1">
       <c r="A100">
         <v>218</v>
       </c>
@@ -8323,7 +8333,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="15">
+    <row r="101" spans="1:23" ht="15" hidden="1">
       <c r="A101">
         <v>219</v>
       </c>
@@ -8360,7 +8370,7 @@
       </c>
       <c r="W101" s="3"/>
     </row>
-    <row r="102" spans="1:23" ht="15">
+    <row r="102" spans="1:23" ht="15" hidden="1">
       <c r="A102">
         <v>220</v>
       </c>
@@ -8399,7 +8409,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="15">
+    <row r="103" spans="1:23" ht="15" hidden="1">
       <c r="A103">
         <v>314</v>
       </c>
@@ -8434,7 +8444,7 @@
       </c>
       <c r="W103" s="3"/>
     </row>
-    <row r="104" spans="1:23" ht="15">
+    <row r="104" spans="1:23" ht="15" hidden="1">
       <c r="A104">
         <v>315</v>
       </c>
@@ -8471,7 +8481,7 @@
       </c>
       <c r="W104" s="3"/>
     </row>
-    <row r="105" spans="1:23" ht="15">
+    <row r="105" spans="1:23" ht="15" hidden="1">
       <c r="A105">
         <v>316</v>
       </c>
@@ -8506,7 +8516,7 @@
       </c>
       <c r="W105" s="3"/>
     </row>
-    <row r="106" spans="1:23" ht="15">
+    <row r="106" spans="1:23" ht="15" hidden="1">
       <c r="A106">
         <v>320</v>
       </c>
@@ -8541,7 +8551,7 @@
       </c>
       <c r="W106" s="3"/>
     </row>
-    <row r="107" spans="1:23" ht="15">
+    <row r="107" spans="1:23" ht="15" hidden="1">
       <c r="A107">
         <v>328</v>
       </c>
@@ -8576,7 +8586,7 @@
       </c>
       <c r="W107" s="3"/>
     </row>
-    <row r="108" spans="1:23" ht="15">
+    <row r="108" spans="1:23" ht="15" hidden="1">
       <c r="A108">
         <v>329</v>
       </c>
@@ -8611,7 +8621,7 @@
       </c>
       <c r="W108" s="3"/>
     </row>
-    <row r="109" spans="1:23" ht="15">
+    <row r="109" spans="1:23" ht="15" hidden="1">
       <c r="A109">
         <v>330</v>
       </c>
@@ -8646,7 +8656,7 @@
       </c>
       <c r="W109" s="3"/>
     </row>
-    <row r="110" spans="1:23" ht="15">
+    <row r="110" spans="1:23" ht="15" hidden="1">
       <c r="A110">
         <v>331</v>
       </c>
@@ -8681,7 +8691,7 @@
       </c>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23" ht="15">
+    <row r="111" spans="1:23" ht="15" hidden="1">
       <c r="A111">
         <v>335</v>
       </c>
@@ -8720,7 +8730,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="15">
+    <row r="112" spans="1:23" ht="15" hidden="1">
       <c r="A112">
         <v>336</v>
       </c>
@@ -8757,7 +8767,7 @@
       </c>
       <c r="W112" s="3"/>
     </row>
-    <row r="113" spans="1:23" ht="15">
+    <row r="113" spans="1:23" ht="15" hidden="1">
       <c r="A113">
         <v>347</v>
       </c>
@@ -8796,7 +8806,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="15">
+    <row r="114" spans="1:23" ht="15" hidden="1">
       <c r="A114">
         <v>356</v>
       </c>
@@ -8833,7 +8843,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="15">
+    <row r="115" spans="1:23" ht="15" hidden="1">
       <c r="A115">
         <v>368</v>
       </c>
@@ -8870,7 +8880,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="15">
+    <row r="116" spans="1:23" ht="15" hidden="1">
       <c r="A116">
         <v>370</v>
       </c>
@@ -8913,7 +8923,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="15">
+    <row r="117" spans="1:23" ht="15" hidden="1">
       <c r="A117">
         <v>412</v>
       </c>
@@ -8948,7 +8958,7 @@
       </c>
       <c r="W117" s="3"/>
     </row>
-    <row r="118" spans="1:23" ht="15">
+    <row r="118" spans="1:23" ht="15" hidden="1">
       <c r="A118">
         <v>432</v>
       </c>
@@ -8986,7 +8996,7 @@
       </c>
       <c r="W118" s="3"/>
     </row>
-    <row r="119" spans="1:23" ht="15">
+    <row r="119" spans="1:23" ht="15" hidden="1">
       <c r="A119">
         <v>433</v>
       </c>
@@ -9024,7 +9034,7 @@
       </c>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23" ht="15">
+    <row r="120" spans="1:23" ht="15" hidden="1">
       <c r="A120">
         <v>434</v>
       </c>
@@ -9062,7 +9072,7 @@
       </c>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23" ht="15">
+    <row r="121" spans="1:23" ht="15" hidden="1">
       <c r="A121">
         <v>435</v>
       </c>
@@ -9100,7 +9110,7 @@
       </c>
       <c r="W121" s="3"/>
     </row>
-    <row r="122" spans="1:23" ht="15">
+    <row r="122" spans="1:23" ht="15" hidden="1">
       <c r="A122">
         <v>436</v>
       </c>
@@ -9138,7 +9148,7 @@
       </c>
       <c r="W122" s="3"/>
     </row>
-    <row r="123" spans="1:23" ht="15">
+    <row r="123" spans="1:23" ht="15" hidden="1">
       <c r="A123">
         <v>437</v>
       </c>
@@ -9173,7 +9183,7 @@
       </c>
       <c r="W123" s="3"/>
     </row>
-    <row r="124" spans="1:23" ht="15">
+    <row r="124" spans="1:23" ht="15" hidden="1">
       <c r="A124">
         <v>438</v>
       </c>
@@ -9210,7 +9220,7 @@
       </c>
       <c r="W124" s="3"/>
     </row>
-    <row r="125" spans="1:23" ht="15">
+    <row r="125" spans="1:23" ht="15" hidden="1">
       <c r="A125">
         <v>485</v>
       </c>
@@ -9247,7 +9257,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="126" spans="1:23" ht="15">
+    <row r="126" spans="1:23" ht="15" hidden="1">
       <c r="A126">
         <v>486</v>
       </c>
@@ -9284,7 +9294,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="127" spans="1:23" ht="15">
+    <row r="127" spans="1:23" ht="15" hidden="1">
       <c r="A127">
         <v>487</v>
       </c>
@@ -9321,7 +9331,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="15">
+    <row r="128" spans="1:23" ht="15" hidden="1">
       <c r="A128">
         <v>488</v>
       </c>
@@ -9359,7 +9369,7 @@
       </c>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23" ht="15">
+    <row r="129" spans="1:23" ht="15" hidden="1">
       <c r="A129">
         <v>516</v>
       </c>
@@ -9398,7 +9408,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="15">
+    <row r="130" spans="1:23" ht="15" hidden="1">
       <c r="A130">
         <v>517</v>
       </c>
@@ -9437,7 +9447,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="15">
+    <row r="131" spans="1:23" ht="15" hidden="1">
       <c r="A131">
         <v>645</v>
       </c>
@@ -9478,7 +9488,7 @@
       </c>
       <c r="W131" s="3"/>
     </row>
-    <row r="132" spans="1:23" ht="15">
+    <row r="132" spans="1:23" ht="15" hidden="1">
       <c r="A132">
         <v>646</v>
       </c>
@@ -9514,7 +9524,7 @@
       </c>
       <c r="W132" s="3"/>
     </row>
-    <row r="133" spans="1:23" ht="15">
+    <row r="133" spans="1:23" ht="15" hidden="1">
       <c r="A133">
         <v>699</v>
       </c>
@@ -9555,7 +9565,7 @@
       </c>
       <c r="W133" s="3"/>
     </row>
-    <row r="134" spans="1:23" ht="15">
+    <row r="134" spans="1:23" ht="15" hidden="1">
       <c r="A134">
         <v>700</v>
       </c>
@@ -9592,7 +9602,7 @@
       </c>
       <c r="W134" s="3"/>
     </row>
-    <row r="135" spans="1:23" ht="15">
+    <row r="135" spans="1:23" ht="15" hidden="1">
       <c r="A135">
         <v>701</v>
       </c>
@@ -9633,7 +9643,7 @@
       </c>
       <c r="W135" s="3"/>
     </row>
-    <row r="136" spans="1:23" ht="15">
+    <row r="136" spans="1:23" ht="15" hidden="1">
       <c r="A136">
         <v>702</v>
       </c>
@@ -9674,7 +9684,7 @@
       </c>
       <c r="W136" s="3"/>
     </row>
-    <row r="137" spans="1:23" ht="15">
+    <row r="137" spans="1:23" ht="15" hidden="1">
       <c r="A137">
         <v>703</v>
       </c>
@@ -9715,7 +9725,7 @@
       </c>
       <c r="W137" s="3"/>
     </row>
-    <row r="138" spans="1:23" ht="15">
+    <row r="138" spans="1:23" ht="15" hidden="1">
       <c r="A138">
         <v>704</v>
       </c>
@@ -9756,7 +9766,7 @@
       </c>
       <c r="W138" s="3"/>
     </row>
-    <row r="139" spans="1:23" ht="15">
+    <row r="139" spans="1:23" ht="15" hidden="1">
       <c r="A139">
         <v>705</v>
       </c>
@@ -9797,7 +9807,7 @@
       </c>
       <c r="W139" s="3"/>
     </row>
-    <row r="140" spans="1:23" ht="15">
+    <row r="140" spans="1:23" ht="15" hidden="1">
       <c r="A140">
         <v>706</v>
       </c>
@@ -9838,7 +9848,7 @@
       </c>
       <c r="W140" s="3"/>
     </row>
-    <row r="141" spans="1:23" ht="15">
+    <row r="141" spans="1:23" ht="15" hidden="1">
       <c r="A141">
         <v>707</v>
       </c>
@@ -9879,7 +9889,7 @@
       </c>
       <c r="W141" s="3"/>
     </row>
-    <row r="142" spans="1:23" ht="15">
+    <row r="142" spans="1:23" ht="15" hidden="1">
       <c r="A142">
         <v>720</v>
       </c>
@@ -9920,7 +9930,7 @@
       </c>
       <c r="W142" s="3"/>
     </row>
-    <row r="143" spans="1:23" ht="15">
+    <row r="143" spans="1:23" ht="15" hidden="1">
       <c r="A143">
         <v>737</v>
       </c>
@@ -9960,7 +9970,7 @@
       </c>
       <c r="W143" s="3"/>
     </row>
-    <row r="144" spans="1:23" ht="15">
+    <row r="144" spans="1:23" ht="15" hidden="1">
       <c r="A144">
         <v>740</v>
       </c>
@@ -9998,7 +10008,7 @@
       </c>
       <c r="W144" s="3"/>
     </row>
-    <row r="145" spans="1:23" ht="15">
+    <row r="145" spans="1:23" ht="15" hidden="1">
       <c r="A145">
         <v>741</v>
       </c>
@@ -10039,7 +10049,7 @@
       </c>
       <c r="W145" s="3"/>
     </row>
-    <row r="146" spans="1:23" ht="15">
+    <row r="146" spans="1:23" ht="15" hidden="1">
       <c r="A146">
         <v>742</v>
       </c>
@@ -10080,7 +10090,7 @@
       </c>
       <c r="W146" s="3"/>
     </row>
-    <row r="147" spans="1:23" ht="15">
+    <row r="147" spans="1:23" ht="15" hidden="1">
       <c r="A147">
         <v>743</v>
       </c>
@@ -10130,7 +10140,7 @@
       </c>
       <c r="W147" s="3"/>
     </row>
-    <row r="148" spans="1:23" ht="15">
+    <row r="148" spans="1:23" ht="15" hidden="1">
       <c r="A148">
         <v>750</v>
       </c>
@@ -10171,7 +10181,7 @@
       </c>
       <c r="W148" s="3"/>
     </row>
-    <row r="149" spans="1:23" ht="15">
+    <row r="149" spans="1:23" ht="15" hidden="1">
       <c r="A149">
         <v>751</v>
       </c>
@@ -10212,7 +10222,7 @@
       </c>
       <c r="W149" s="3"/>
     </row>
-    <row r="150" spans="1:23" ht="15">
+    <row r="150" spans="1:23" ht="15" hidden="1">
       <c r="A150">
         <v>787</v>
       </c>
@@ -10250,7 +10260,7 @@
       </c>
       <c r="W150" s="3"/>
     </row>
-    <row r="151" spans="1:23" ht="15">
+    <row r="151" spans="1:23" ht="15" hidden="1">
       <c r="A151">
         <v>788</v>
       </c>
@@ -10288,7 +10298,7 @@
       </c>
       <c r="W151" s="3"/>
     </row>
-    <row r="152" spans="1:23" ht="15">
+    <row r="152" spans="1:23" ht="15" hidden="1">
       <c r="A152">
         <v>808</v>
       </c>
@@ -10326,7 +10336,7 @@
       </c>
       <c r="W152" s="3"/>
     </row>
-    <row r="153" spans="1:23" ht="15">
+    <row r="153" spans="1:23" ht="15" hidden="1">
       <c r="A153">
         <v>809</v>
       </c>
@@ -10364,7 +10374,7 @@
       </c>
       <c r="W153" s="3"/>
     </row>
-    <row r="154" spans="1:23" ht="15">
+    <row r="154" spans="1:23" ht="15" hidden="1">
       <c r="A154">
         <v>810</v>
       </c>
@@ -10414,7 +10424,7 @@
       </c>
       <c r="W154" s="3"/>
     </row>
-    <row r="155" spans="1:23" ht="15">
+    <row r="155" spans="1:23" ht="15" hidden="1">
       <c r="A155">
         <v>811</v>
       </c>
@@ -10455,7 +10465,7 @@
       </c>
       <c r="W155" s="3"/>
     </row>
-    <row r="156" spans="1:23" ht="15">
+    <row r="156" spans="1:23" ht="15" hidden="1">
       <c r="A156">
         <v>829</v>
       </c>
@@ -10496,7 +10506,7 @@
       </c>
       <c r="W156" s="3"/>
     </row>
-    <row r="157" spans="1:23" ht="15">
+    <row r="157" spans="1:23" ht="15" hidden="1">
       <c r="A157">
         <v>831</v>
       </c>
@@ -10534,7 +10544,7 @@
       </c>
       <c r="W157" s="3"/>
     </row>
-    <row r="158" spans="1:23" ht="15">
+    <row r="158" spans="1:23" ht="15" hidden="1">
       <c r="A158">
         <v>832</v>
       </c>
@@ -10584,7 +10594,7 @@
       </c>
       <c r="W158" s="3"/>
     </row>
-    <row r="159" spans="1:23" ht="15">
+    <row r="159" spans="1:23" ht="15" hidden="1">
       <c r="A159">
         <v>14</v>
       </c>
@@ -10622,7 +10632,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="15">
+    <row r="160" spans="1:23" ht="15" hidden="1">
       <c r="A160">
         <v>31</v>
       </c>
@@ -10660,7 +10670,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="161" spans="1:23" ht="15">
+    <row r="161" spans="1:23" ht="15" hidden="1">
       <c r="A161">
         <v>32</v>
       </c>
@@ -10701,7 +10711,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="15">
+    <row r="162" spans="1:23" ht="15" hidden="1">
       <c r="A162">
         <v>33</v>
       </c>
@@ -10742,7 +10752,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="15">
+    <row r="163" spans="1:23" ht="15" hidden="1">
       <c r="A163">
         <v>34</v>
       </c>
@@ -10783,7 +10793,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="15">
+    <row r="164" spans="1:23" ht="15" hidden="1">
       <c r="A164">
         <v>35</v>
       </c>
@@ -10824,7 +10834,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="15">
+    <row r="165" spans="1:23" ht="15" hidden="1">
       <c r="A165">
         <v>36</v>
       </c>
@@ -10865,7 +10875,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="15">
+    <row r="166" spans="1:23" ht="15" hidden="1">
       <c r="A166">
         <v>37</v>
       </c>
@@ -10906,7 +10916,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="15">
+    <row r="167" spans="1:23" ht="15" hidden="1">
       <c r="A167">
         <v>84</v>
       </c>
@@ -10944,7 +10954,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="15">
+    <row r="168" spans="1:23" ht="15" hidden="1">
       <c r="A168">
         <v>85</v>
       </c>
@@ -10985,7 +10995,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="15">
+    <row r="169" spans="1:23" ht="15" hidden="1">
       <c r="A169">
         <v>114</v>
       </c>
@@ -11024,7 +11034,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="15">
+    <row r="170" spans="1:23" ht="15" hidden="1">
       <c r="A170">
         <v>171</v>
       </c>
@@ -11061,7 +11071,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="15">
+    <row r="171" spans="1:23" ht="15" hidden="1">
       <c r="A171">
         <v>172</v>
       </c>
@@ -11098,7 +11108,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="15">
+    <row r="172" spans="1:23" ht="15" hidden="1">
       <c r="A172">
         <v>321</v>
       </c>
@@ -11135,7 +11145,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="15">
+    <row r="173" spans="1:23" ht="15" hidden="1">
       <c r="A173">
         <v>337</v>
       </c>
@@ -11172,7 +11182,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="15">
+    <row r="174" spans="1:23" ht="15" hidden="1">
       <c r="A174">
         <v>339</v>
       </c>
@@ -11209,7 +11219,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="15">
+    <row r="175" spans="1:23" ht="15" hidden="1">
       <c r="A175">
         <v>379</v>
       </c>
@@ -11246,7 +11256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="15">
+    <row r="176" spans="1:23" ht="15" hidden="1">
       <c r="A176">
         <v>385</v>
       </c>
@@ -11285,7 +11295,7 @@
       </c>
       <c r="W176" s="3"/>
     </row>
-    <row r="177" spans="1:23" ht="15">
+    <row r="177" spans="1:23" ht="15" hidden="1">
       <c r="A177">
         <v>495</v>
       </c>
@@ -11322,7 +11332,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="15">
+    <row r="178" spans="1:23" ht="15" hidden="1">
       <c r="A178">
         <v>572</v>
       </c>
@@ -11361,7 +11371,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="15">
+    <row r="179" spans="1:23" ht="15" hidden="1">
       <c r="A179">
         <v>573</v>
       </c>
@@ -11398,7 +11408,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="15">
+    <row r="180" spans="1:23" ht="15" hidden="1">
       <c r="A180">
         <v>632</v>
       </c>
@@ -11436,7 +11446,7 @@
       </c>
       <c r="W180" s="3"/>
     </row>
-    <row r="181" spans="1:23" ht="15">
+    <row r="181" spans="1:23" ht="15" hidden="1">
       <c r="A181">
         <v>633</v>
       </c>
@@ -11477,7 +11487,7 @@
       </c>
       <c r="W181" s="3"/>
     </row>
-    <row r="182" spans="1:23" ht="15">
+    <row r="182" spans="1:23" ht="15" hidden="1">
       <c r="A182">
         <v>634</v>
       </c>
@@ -11518,7 +11528,7 @@
       </c>
       <c r="W182" s="3"/>
     </row>
-    <row r="183" spans="1:23" ht="15">
+    <row r="183" spans="1:23" ht="15" hidden="1">
       <c r="A183">
         <v>635</v>
       </c>
@@ -11557,7 +11567,7 @@
       </c>
       <c r="W183" s="3"/>
     </row>
-    <row r="184" spans="1:23" ht="15">
+    <row r="184" spans="1:23" ht="15" hidden="1">
       <c r="A184">
         <v>650</v>
       </c>
@@ -11598,7 +11608,7 @@
       </c>
       <c r="W184" s="3"/>
     </row>
-    <row r="185" spans="1:23" ht="15">
+    <row r="185" spans="1:23" ht="15" hidden="1">
       <c r="A185">
         <v>653</v>
       </c>
@@ -11639,7 +11649,7 @@
       </c>
       <c r="W185" s="3"/>
     </row>
-    <row r="186" spans="1:23" ht="15">
+    <row r="186" spans="1:23" ht="15" hidden="1">
       <c r="A186">
         <v>721</v>
       </c>
@@ -11680,7 +11690,7 @@
       </c>
       <c r="W186" s="3"/>
     </row>
-    <row r="187" spans="1:23" ht="15">
+    <row r="187" spans="1:23" ht="15" hidden="1">
       <c r="A187">
         <v>722</v>
       </c>
@@ -11721,7 +11731,7 @@
       </c>
       <c r="W187" s="3"/>
     </row>
-    <row r="188" spans="1:23" ht="15">
+    <row r="188" spans="1:23" ht="15" hidden="1">
       <c r="A188">
         <v>752</v>
       </c>
@@ -11761,7 +11771,7 @@
       </c>
       <c r="W188" s="3"/>
     </row>
-    <row r="189" spans="1:23" ht="15">
+    <row r="189" spans="1:23" ht="15" hidden="1">
       <c r="A189">
         <v>753</v>
       </c>
@@ -11802,7 +11812,7 @@
       </c>
       <c r="W189" s="3"/>
     </row>
-    <row r="190" spans="1:23" ht="15">
+    <row r="190" spans="1:23" ht="15" hidden="1">
       <c r="A190">
         <v>754</v>
       </c>
@@ -11852,7 +11862,7 @@
       </c>
       <c r="W190" s="3"/>
     </row>
-    <row r="191" spans="1:23" ht="15">
+    <row r="191" spans="1:23" ht="15" hidden="1">
       <c r="A191">
         <v>799</v>
       </c>
@@ -11893,7 +11903,7 @@
       </c>
       <c r="W191" s="3"/>
     </row>
-    <row r="192" spans="1:23" ht="15">
+    <row r="192" spans="1:23" ht="15" hidden="1">
       <c r="A192">
         <v>822</v>
       </c>
@@ -11934,7 +11944,7 @@
       </c>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23" ht="15">
+    <row r="193" spans="1:23" ht="15" hidden="1">
       <c r="A193">
         <v>823</v>
       </c>
@@ -11975,7 +11985,7 @@
       </c>
       <c r="W193" s="3"/>
     </row>
-    <row r="194" spans="1:23" ht="15">
+    <row r="194" spans="1:23" ht="15" hidden="1">
       <c r="A194">
         <v>38</v>
       </c>
@@ -12010,7 +12020,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="195" spans="1:23" ht="15">
+    <row r="195" spans="1:23" ht="15" hidden="1">
       <c r="A195">
         <v>39</v>
       </c>
@@ -12045,7 +12055,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="196" spans="1:23" ht="15">
+    <row r="196" spans="1:23" ht="15" hidden="1">
       <c r="A196">
         <v>40</v>
       </c>
@@ -12080,7 +12090,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="197" spans="1:23" ht="15">
+    <row r="197" spans="1:23" ht="15" hidden="1">
       <c r="A197">
         <v>41</v>
       </c>
@@ -12115,7 +12125,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="15">
+    <row r="198" spans="1:23" ht="15" hidden="1">
       <c r="A198">
         <v>42</v>
       </c>
@@ -12153,7 +12163,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="15">
+    <row r="199" spans="1:23" ht="15" hidden="1">
       <c r="A199">
         <v>43</v>
       </c>
@@ -12191,7 +12201,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="200" spans="1:23" ht="15">
+    <row r="200" spans="1:23" ht="15" hidden="1">
       <c r="A200">
         <v>56</v>
       </c>
@@ -12229,7 +12239,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="15">
+    <row r="201" spans="1:23" ht="15" hidden="1">
       <c r="A201">
         <v>58</v>
       </c>
@@ -12267,7 +12277,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="202" spans="1:23" ht="15">
+    <row r="202" spans="1:23" ht="15" hidden="1">
       <c r="A202">
         <v>60</v>
       </c>
@@ -12305,7 +12315,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="203" spans="1:23" ht="15">
+    <row r="203" spans="1:23" ht="15" hidden="1">
       <c r="A203">
         <v>250</v>
       </c>
@@ -12340,7 +12350,7 @@
       </c>
       <c r="W203" s="3"/>
     </row>
-    <row r="204" spans="1:23" ht="15">
+    <row r="204" spans="1:23" ht="15" hidden="1">
       <c r="A204">
         <v>256</v>
       </c>
@@ -12380,7 +12390,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="205" spans="1:23" ht="15">
+    <row r="205" spans="1:23" ht="15" hidden="1">
       <c r="A205">
         <v>260</v>
       </c>
@@ -12420,7 +12430,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="15">
+    <row r="206" spans="1:23" ht="15" hidden="1">
       <c r="A206">
         <v>262</v>
       </c>
@@ -12460,7 +12470,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="15">
+    <row r="207" spans="1:23" ht="15" hidden="1">
       <c r="A207">
         <v>263</v>
       </c>
@@ -12500,7 +12510,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="15">
+    <row r="208" spans="1:23" ht="15" hidden="1">
       <c r="A208">
         <v>264</v>
       </c>
@@ -12540,7 +12550,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="15">
+    <row r="209" spans="1:23" ht="15" hidden="1">
       <c r="A209">
         <v>265</v>
       </c>
@@ -12577,7 +12587,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="210" spans="1:23" ht="15">
+    <row r="210" spans="1:23" ht="15" hidden="1">
       <c r="A210">
         <v>266</v>
       </c>
@@ -12617,7 +12627,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="211" spans="1:23" ht="15">
+    <row r="211" spans="1:23" ht="15" hidden="1">
       <c r="A211">
         <v>372</v>
       </c>
@@ -12654,7 +12664,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="15">
+    <row r="212" spans="1:23" ht="15" hidden="1">
       <c r="A212">
         <v>373</v>
       </c>
@@ -12697,7 +12707,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="213" spans="1:23" ht="15">
+    <row r="213" spans="1:23" ht="15" hidden="1">
       <c r="A213">
         <v>374</v>
       </c>
@@ -12734,7 +12744,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="15">
+    <row r="214" spans="1:23" ht="15" hidden="1">
       <c r="A214">
         <v>375</v>
       </c>
@@ -12777,7 +12787,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="15">
+    <row r="215" spans="1:23" ht="15" hidden="1">
       <c r="A215">
         <v>376</v>
       </c>
@@ -12817,7 +12827,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="15">
+    <row r="216" spans="1:23" ht="15" hidden="1">
       <c r="A216">
         <v>708</v>
       </c>
@@ -12858,7 +12868,7 @@
       </c>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23" ht="15">
+    <row r="217" spans="1:23" ht="15" hidden="1">
       <c r="A217">
         <v>709</v>
       </c>
@@ -12899,7 +12909,7 @@
       </c>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23" ht="15">
+    <row r="218" spans="1:23" ht="15" hidden="1">
       <c r="A218">
         <v>49</v>
       </c>
@@ -12937,7 +12947,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="15">
+    <row r="219" spans="1:23" ht="15" hidden="1">
       <c r="A219">
         <v>50</v>
       </c>
@@ -12972,7 +12982,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="15">
+    <row r="220" spans="1:23" ht="15" hidden="1">
       <c r="A220">
         <v>51</v>
       </c>
@@ -13004,7 +13014,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="221" spans="1:23" ht="15">
+    <row r="221" spans="1:23" ht="15" hidden="1">
       <c r="A221">
         <v>52</v>
       </c>
@@ -13042,7 +13052,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="15">
+    <row r="222" spans="1:23" ht="15" hidden="1">
       <c r="A222">
         <v>53</v>
       </c>
@@ -13077,7 +13087,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="15">
+    <row r="223" spans="1:23" ht="15" hidden="1">
       <c r="A223">
         <v>98</v>
       </c>
@@ -13115,7 +13125,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="15">
+    <row r="224" spans="1:23" ht="15" hidden="1">
       <c r="A224">
         <v>99</v>
       </c>
@@ -13150,7 +13160,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="15">
+    <row r="225" spans="1:23" ht="15" hidden="1">
       <c r="A225">
         <v>100</v>
       </c>
@@ -13185,7 +13195,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="15">
+    <row r="226" spans="1:23" ht="15" hidden="1">
       <c r="A226">
         <v>101</v>
       </c>
@@ -13225,7 +13235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="15">
+    <row r="227" spans="1:23" ht="15" hidden="1">
       <c r="A227">
         <v>195</v>
       </c>
@@ -13266,7 +13276,7 @@
       </c>
       <c r="W227" s="3"/>
     </row>
-    <row r="228" spans="1:23" ht="15">
+    <row r="228" spans="1:23" ht="15" hidden="1">
       <c r="A228">
         <v>196</v>
       </c>
@@ -13305,7 +13315,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="15">
+    <row r="229" spans="1:23" ht="15" hidden="1">
       <c r="A229">
         <v>197</v>
       </c>
@@ -13346,7 +13356,7 @@
       </c>
       <c r="W229" s="3"/>
     </row>
-    <row r="230" spans="1:23" ht="15">
+    <row r="230" spans="1:23" ht="15" hidden="1">
       <c r="A230">
         <v>198</v>
       </c>
@@ -13387,7 +13397,7 @@
       </c>
       <c r="W230" s="3"/>
     </row>
-    <row r="231" spans="1:23" ht="15">
+    <row r="231" spans="1:23" ht="15" hidden="1">
       <c r="A231">
         <v>350</v>
       </c>
@@ -13427,7 +13437,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="15">
+    <row r="232" spans="1:23" ht="15" hidden="1">
       <c r="A232">
         <v>351</v>
       </c>
@@ -13462,7 +13472,7 @@
       </c>
       <c r="W232" s="3"/>
     </row>
-    <row r="233" spans="1:23" ht="15">
+    <row r="233" spans="1:23" ht="15" hidden="1">
       <c r="A233">
         <v>440</v>
       </c>
@@ -13499,7 +13509,7 @@
       </c>
       <c r="W233" s="3"/>
     </row>
-    <row r="234" spans="1:23" ht="15">
+    <row r="234" spans="1:23" ht="15" hidden="1">
       <c r="A234">
         <v>441</v>
       </c>
@@ -13536,7 +13546,7 @@
       </c>
       <c r="W234" s="3"/>
     </row>
-    <row r="235" spans="1:23" ht="15">
+    <row r="235" spans="1:23" ht="15" hidden="1">
       <c r="A235">
         <v>442</v>
       </c>
@@ -13577,7 +13587,7 @@
       </c>
       <c r="W235" s="3"/>
     </row>
-    <row r="236" spans="1:23" ht="15">
+    <row r="236" spans="1:23" ht="15" hidden="1">
       <c r="A236">
         <v>443</v>
       </c>
@@ -13616,7 +13626,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="15">
+    <row r="237" spans="1:23" ht="15" hidden="1">
       <c r="A237">
         <v>444</v>
       </c>
@@ -13657,7 +13667,7 @@
       </c>
       <c r="W237" s="3"/>
     </row>
-    <row r="238" spans="1:23" ht="15">
+    <row r="238" spans="1:23" ht="15" hidden="1">
       <c r="A238">
         <v>445</v>
       </c>
@@ -13697,7 +13707,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="239" spans="1:23" ht="15">
+    <row r="239" spans="1:23" ht="15" hidden="1">
       <c r="A239">
         <v>446</v>
       </c>
@@ -13737,7 +13747,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="240" spans="1:23" ht="15">
+    <row r="240" spans="1:23" ht="15" hidden="1">
       <c r="A240">
         <v>447</v>
       </c>
@@ -13774,7 +13784,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="15">
+    <row r="241" spans="1:23" ht="15" hidden="1">
       <c r="A241">
         <v>561</v>
       </c>
@@ -13809,7 +13819,7 @@
       </c>
       <c r="W241" s="3"/>
     </row>
-    <row r="242" spans="1:23" ht="15">
+    <row r="242" spans="1:23" ht="15" hidden="1">
       <c r="A242">
         <v>562</v>
       </c>
@@ -13844,7 +13854,7 @@
       </c>
       <c r="W242" s="3"/>
     </row>
-    <row r="243" spans="1:23" ht="15">
+    <row r="243" spans="1:23" ht="15" hidden="1">
       <c r="A243">
         <v>563</v>
       </c>
@@ -13879,7 +13889,7 @@
       </c>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23" ht="15">
+    <row r="244" spans="1:23" ht="15" hidden="1">
       <c r="A244">
         <v>564</v>
       </c>
@@ -13914,7 +13924,7 @@
       </c>
       <c r="W244" s="3"/>
     </row>
-    <row r="245" spans="1:23" ht="15">
+    <row r="245" spans="1:23" ht="15" hidden="1">
       <c r="A245">
         <v>565</v>
       </c>
@@ -13949,7 +13959,7 @@
       </c>
       <c r="W245" s="3"/>
     </row>
-    <row r="246" spans="1:23" ht="15">
+    <row r="246" spans="1:23" ht="15" hidden="1">
       <c r="A246">
         <v>569</v>
       </c>
@@ -13984,7 +13994,7 @@
       </c>
       <c r="W246" s="3"/>
     </row>
-    <row r="247" spans="1:23" ht="15">
+    <row r="247" spans="1:23" ht="15" hidden="1">
       <c r="A247">
         <v>682</v>
       </c>
@@ -14025,7 +14035,7 @@
       </c>
       <c r="W247" s="3"/>
     </row>
-    <row r="248" spans="1:23" ht="15">
+    <row r="248" spans="1:23" ht="15" hidden="1">
       <c r="A248">
         <v>683</v>
       </c>
@@ -14066,7 +14076,7 @@
       </c>
       <c r="W248" s="3"/>
     </row>
-    <row r="249" spans="1:23" ht="15">
+    <row r="249" spans="1:23" ht="15" hidden="1">
       <c r="A249">
         <v>684</v>
       </c>
@@ -14107,7 +14117,7 @@
       </c>
       <c r="W249" s="3"/>
     </row>
-    <row r="250" spans="1:23" ht="15">
+    <row r="250" spans="1:23" ht="15" hidden="1">
       <c r="A250">
         <v>685</v>
       </c>
@@ -14148,7 +14158,7 @@
       </c>
       <c r="W250" s="3"/>
     </row>
-    <row r="251" spans="1:23" ht="15">
+    <row r="251" spans="1:23" ht="15" hidden="1">
       <c r="A251">
         <v>780</v>
       </c>
@@ -14189,7 +14199,7 @@
       </c>
       <c r="W251" s="3"/>
     </row>
-    <row r="252" spans="1:23" ht="15">
+    <row r="252" spans="1:23" ht="15" hidden="1">
       <c r="A252">
         <v>789</v>
       </c>
@@ -14230,7 +14240,7 @@
       </c>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23" ht="15">
+    <row r="253" spans="1:23" ht="15" hidden="1">
       <c r="A253">
         <v>790</v>
       </c>
@@ -14271,7 +14281,7 @@
       </c>
       <c r="W253" s="3"/>
     </row>
-    <row r="254" spans="1:23" ht="15">
+    <row r="254" spans="1:23" ht="15" hidden="1">
       <c r="A254">
         <v>791</v>
       </c>
@@ -14312,7 +14322,7 @@
       </c>
       <c r="W254" s="3"/>
     </row>
-    <row r="255" spans="1:23" ht="15">
+    <row r="255" spans="1:23" ht="15" hidden="1">
       <c r="A255">
         <v>792</v>
       </c>
@@ -14353,7 +14363,7 @@
       </c>
       <c r="W255" s="3"/>
     </row>
-    <row r="256" spans="1:23" ht="15">
+    <row r="256" spans="1:23" ht="15" hidden="1">
       <c r="A256">
         <v>793</v>
       </c>
@@ -14394,7 +14404,7 @@
       </c>
       <c r="W256" s="3"/>
     </row>
-    <row r="257" spans="1:23" ht="15">
+    <row r="257" spans="1:23" ht="15" hidden="1">
       <c r="A257">
         <v>794</v>
       </c>
@@ -14444,7 +14454,7 @@
       </c>
       <c r="W257" s="3"/>
     </row>
-    <row r="258" spans="1:23" ht="15">
+    <row r="258" spans="1:23" ht="15" hidden="1">
       <c r="A258">
         <v>853</v>
       </c>
@@ -14485,7 +14495,7 @@
       </c>
       <c r="W258" s="3"/>
     </row>
-    <row r="259" spans="1:23" ht="15">
+    <row r="259" spans="1:23" ht="15" hidden="1">
       <c r="A259">
         <v>854</v>
       </c>
@@ -14526,7 +14536,7 @@
       </c>
       <c r="W259" s="3"/>
     </row>
-    <row r="260" spans="1:23" ht="15">
+    <row r="260" spans="1:23" ht="15" hidden="1">
       <c r="A260">
         <v>854</v>
       </c>
@@ -14567,7 +14577,7 @@
       </c>
       <c r="W260" s="3"/>
     </row>
-    <row r="261" spans="1:23" ht="15">
+    <row r="261" spans="1:23" ht="15" hidden="1">
       <c r="A261">
         <v>86</v>
       </c>
@@ -14599,7 +14609,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="15">
+    <row r="262" spans="1:23" ht="15" hidden="1">
       <c r="A262">
         <v>87</v>
       </c>
@@ -14631,7 +14641,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="15">
+    <row r="263" spans="1:23" ht="15" hidden="1">
       <c r="A263">
         <v>95</v>
       </c>
@@ -14669,7 +14679,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="15">
+    <row r="264" spans="1:23" ht="15" hidden="1">
       <c r="A264">
         <v>240</v>
       </c>
@@ -14704,7 +14714,7 @@
       </c>
       <c r="W264" s="3"/>
     </row>
-    <row r="265" spans="1:23" ht="15">
+    <row r="265" spans="1:23" ht="15" hidden="1">
       <c r="A265">
         <v>241</v>
       </c>
@@ -14739,7 +14749,7 @@
       </c>
       <c r="W265" s="3"/>
     </row>
-    <row r="266" spans="1:23" ht="15">
+    <row r="266" spans="1:23" ht="15" hidden="1">
       <c r="A266">
         <v>242</v>
       </c>
@@ -14779,7 +14789,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="15">
+    <row r="267" spans="1:23" ht="15" hidden="1">
       <c r="A267">
         <v>243</v>
       </c>
@@ -14814,7 +14824,7 @@
       </c>
       <c r="W267" s="3"/>
     </row>
-    <row r="268" spans="1:23" ht="15">
+    <row r="268" spans="1:23" ht="15" hidden="1">
       <c r="A268">
         <v>245</v>
       </c>
@@ -14854,7 +14864,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="15">
+    <row r="269" spans="1:23" ht="15" hidden="1">
       <c r="A269">
         <v>247</v>
       </c>
@@ -14894,7 +14904,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="15">
+    <row r="270" spans="1:23" ht="15" hidden="1">
       <c r="A270">
         <v>252</v>
       </c>
@@ -14935,7 +14945,7 @@
       </c>
       <c r="W270" s="3"/>
     </row>
-    <row r="271" spans="1:23" ht="15">
+    <row r="271" spans="1:23" ht="15" hidden="1">
       <c r="A271">
         <v>271</v>
       </c>
@@ -14976,7 +14986,7 @@
       </c>
       <c r="W271" s="3"/>
     </row>
-    <row r="272" spans="1:23" ht="15">
+    <row r="272" spans="1:23" ht="15" hidden="1">
       <c r="A272">
         <v>276</v>
       </c>
@@ -15017,7 +15027,7 @@
       </c>
       <c r="W272" s="3"/>
     </row>
-    <row r="273" spans="1:23" ht="15">
+    <row r="273" spans="1:23" ht="15" hidden="1">
       <c r="A273">
         <v>277</v>
       </c>
@@ -15058,7 +15068,7 @@
       </c>
       <c r="W273" s="3"/>
     </row>
-    <row r="274" spans="1:23" ht="15">
+    <row r="274" spans="1:23" ht="15" hidden="1">
       <c r="A274">
         <v>278</v>
       </c>
@@ -15093,7 +15103,7 @@
       </c>
       <c r="W274" s="3"/>
     </row>
-    <row r="275" spans="1:23" ht="15">
+    <row r="275" spans="1:23" ht="15" hidden="1">
       <c r="A275">
         <v>279</v>
       </c>
@@ -15131,7 +15141,7 @@
       </c>
       <c r="W275" s="3"/>
     </row>
-    <row r="276" spans="1:23" ht="15">
+    <row r="276" spans="1:23" ht="15" hidden="1">
       <c r="A276">
         <v>327</v>
       </c>
@@ -15166,7 +15176,7 @@
       </c>
       <c r="W276" s="3"/>
     </row>
-    <row r="277" spans="1:23" ht="15">
+    <row r="277" spans="1:23" ht="15" hidden="1">
       <c r="A277">
         <v>532</v>
       </c>
@@ -15201,7 +15211,7 @@
       </c>
       <c r="W277" s="3"/>
     </row>
-    <row r="278" spans="1:23" ht="15">
+    <row r="278" spans="1:23" ht="15" hidden="1">
       <c r="A278">
         <v>533</v>
       </c>
@@ -15242,7 +15252,7 @@
       </c>
       <c r="W278" s="3"/>
     </row>
-    <row r="279" spans="1:23" ht="15">
+    <row r="279" spans="1:23" ht="15" hidden="1">
       <c r="A279">
         <v>534</v>
       </c>
@@ -15280,7 +15290,7 @@
       </c>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23" ht="15">
+    <row r="280" spans="1:23" ht="15" hidden="1">
       <c r="A280">
         <v>535</v>
       </c>
@@ -15318,7 +15328,7 @@
       </c>
       <c r="W280" s="3"/>
     </row>
-    <row r="281" spans="1:23" ht="15">
+    <row r="281" spans="1:23" ht="15" hidden="1">
       <c r="A281">
         <v>536</v>
       </c>
@@ -15356,7 +15366,7 @@
       </c>
       <c r="W281" s="3"/>
     </row>
-    <row r="282" spans="1:23" ht="15">
+    <row r="282" spans="1:23" ht="15" hidden="1">
       <c r="A282">
         <v>537</v>
       </c>
@@ -15394,7 +15404,7 @@
       </c>
       <c r="W282" s="3"/>
     </row>
-    <row r="283" spans="1:23" ht="15">
+    <row r="283" spans="1:23" ht="15" hidden="1">
       <c r="A283">
         <v>538</v>
       </c>
@@ -15432,7 +15442,7 @@
       </c>
       <c r="W283" s="3"/>
     </row>
-    <row r="284" spans="1:23" ht="15">
+    <row r="284" spans="1:23" ht="15" hidden="1">
       <c r="A284">
         <v>539</v>
       </c>
@@ -15470,7 +15480,7 @@
       </c>
       <c r="W284" s="3"/>
     </row>
-    <row r="285" spans="1:23" ht="15">
+    <row r="285" spans="1:23" ht="15" hidden="1">
       <c r="A285">
         <v>540</v>
       </c>
@@ -15511,7 +15521,7 @@
       </c>
       <c r="W285" s="3"/>
     </row>
-    <row r="286" spans="1:23" ht="15">
+    <row r="286" spans="1:23" ht="15" hidden="1">
       <c r="A286">
         <v>541</v>
       </c>
@@ -15552,7 +15562,7 @@
       </c>
       <c r="W286" s="3"/>
     </row>
-    <row r="287" spans="1:23" ht="15">
+    <row r="287" spans="1:23" ht="15" hidden="1">
       <c r="A287">
         <v>666</v>
       </c>
@@ -15593,7 +15603,7 @@
       </c>
       <c r="W287" s="3"/>
     </row>
-    <row r="288" spans="1:23" ht="15">
+    <row r="288" spans="1:23" ht="15" hidden="1">
       <c r="A288">
         <v>681</v>
       </c>
@@ -15634,7 +15644,7 @@
       </c>
       <c r="W288" s="3"/>
     </row>
-    <row r="289" spans="1:23" ht="15">
+    <row r="289" spans="1:23" ht="15" hidden="1">
       <c r="A289">
         <v>760</v>
       </c>
@@ -15675,7 +15685,7 @@
       </c>
       <c r="W289" s="3"/>
     </row>
-    <row r="290" spans="1:23" ht="15">
+    <row r="290" spans="1:23" ht="15" hidden="1">
       <c r="A290">
         <v>762</v>
       </c>
@@ -15725,7 +15735,7 @@
       </c>
       <c r="W290" s="3"/>
     </row>
-    <row r="291" spans="1:23" ht="15">
+    <row r="291" spans="1:23" ht="15" hidden="1">
       <c r="A291">
         <v>763</v>
       </c>
@@ -15775,7 +15785,7 @@
       </c>
       <c r="W291" s="3"/>
     </row>
-    <row r="292" spans="1:23" ht="15">
+    <row r="292" spans="1:23" ht="15" hidden="1">
       <c r="A292">
         <v>764</v>
       </c>
@@ -15825,7 +15835,7 @@
       </c>
       <c r="W292" s="3"/>
     </row>
-    <row r="293" spans="1:23" ht="15">
+    <row r="293" spans="1:23" ht="15" hidden="1">
       <c r="A293">
         <v>847</v>
       </c>
@@ -15866,7 +15876,7 @@
       </c>
       <c r="W293" s="3"/>
     </row>
-    <row r="294" spans="1:23" ht="15">
+    <row r="294" spans="1:23" ht="15" hidden="1">
       <c r="A294">
         <v>852</v>
       </c>
@@ -15907,7 +15917,7 @@
       </c>
       <c r="W294" s="3"/>
     </row>
-    <row r="295" spans="1:23" ht="15">
+    <row r="295" spans="1:23" ht="15" hidden="1">
       <c r="A295">
         <v>5</v>
       </c>
@@ -15942,7 +15952,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="296" spans="1:23" ht="15">
+    <row r="296" spans="1:23" ht="15" hidden="1">
       <c r="A296">
         <v>6</v>
       </c>
@@ -15977,7 +15987,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="15">
+    <row r="297" spans="1:23" ht="15" hidden="1">
       <c r="A297">
         <v>7</v>
       </c>
@@ -16012,7 +16022,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="298" spans="1:23" ht="15">
+    <row r="298" spans="1:23" ht="15" hidden="1">
       <c r="A298">
         <v>8</v>
       </c>
@@ -16047,7 +16057,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="15">
+    <row r="299" spans="1:23" ht="15" hidden="1">
       <c r="A299">
         <v>9</v>
       </c>
@@ -16082,7 +16092,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="15">
+    <row r="300" spans="1:23" ht="15" hidden="1">
       <c r="A300">
         <v>10</v>
       </c>
@@ -16117,7 +16127,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="15">
+    <row r="301" spans="1:23" ht="15" hidden="1">
       <c r="A301">
         <v>11</v>
       </c>
@@ -16155,7 +16165,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="15">
+    <row r="302" spans="1:23" ht="15" hidden="1">
       <c r="A302">
         <v>12</v>
       </c>
@@ -16193,7 +16203,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="15">
+    <row r="303" spans="1:23" ht="15" hidden="1">
       <c r="A303">
         <v>13</v>
       </c>
@@ -16231,7 +16241,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="15">
+    <row r="304" spans="1:23" ht="15" hidden="1">
       <c r="A304">
         <v>27</v>
       </c>
@@ -16266,7 +16276,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="15">
+    <row r="305" spans="1:23" ht="15" hidden="1">
       <c r="A305">
         <v>28</v>
       </c>
@@ -16298,7 +16308,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="15">
+    <row r="306" spans="1:23" ht="15" hidden="1">
       <c r="A306">
         <v>29</v>
       </c>
@@ -16336,7 +16346,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="15">
+    <row r="307" spans="1:23" ht="15" hidden="1">
       <c r="A307">
         <v>30</v>
       </c>
@@ -16377,7 +16387,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="15">
+    <row r="308" spans="1:23" ht="15" hidden="1">
       <c r="A308">
         <v>67</v>
       </c>
@@ -16409,7 +16419,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="15">
+    <row r="309" spans="1:23" ht="15" hidden="1">
       <c r="A309">
         <v>69</v>
       </c>
@@ -16444,7 +16454,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="15">
+    <row r="310" spans="1:23" ht="15" hidden="1">
       <c r="A310">
         <v>70</v>
       </c>
@@ -16479,7 +16489,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="15">
+    <row r="311" spans="1:23" ht="15" hidden="1">
       <c r="A311">
         <v>71</v>
       </c>
@@ -16517,7 +16527,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="15">
+    <row r="312" spans="1:23" ht="15" hidden="1">
       <c r="A312">
         <v>72</v>
       </c>
@@ -16555,7 +16565,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="15">
+    <row r="313" spans="1:23" ht="15" hidden="1">
       <c r="A313">
         <v>115</v>
       </c>
@@ -16592,7 +16602,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="15">
+    <row r="314" spans="1:23" ht="15" hidden="1">
       <c r="A314">
         <v>160</v>
       </c>
@@ -16635,7 +16645,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="15">
+    <row r="315" spans="1:23" ht="15" hidden="1">
       <c r="A315">
         <v>161</v>
       </c>
@@ -16672,7 +16682,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="15">
+    <row r="316" spans="1:23" ht="15" hidden="1">
       <c r="A316">
         <v>162</v>
       </c>
@@ -16711,7 +16721,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="317" spans="1:23" ht="15">
+    <row r="317" spans="1:23" ht="15" hidden="1">
       <c r="A317">
         <v>163</v>
       </c>
@@ -16748,7 +16758,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="15">
+    <row r="318" spans="1:23" ht="15" hidden="1">
       <c r="A318">
         <v>164</v>
       </c>
@@ -16785,7 +16795,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="15">
+    <row r="319" spans="1:23" ht="15" hidden="1">
       <c r="A319">
         <v>165</v>
       </c>
@@ -16820,7 +16830,7 @@
       </c>
       <c r="W319" s="3"/>
     </row>
-    <row r="320" spans="1:23" ht="15">
+    <row r="320" spans="1:23" ht="15" hidden="1">
       <c r="A320">
         <v>173</v>
       </c>
@@ -16859,7 +16869,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="15">
+    <row r="321" spans="1:23" ht="15" hidden="1">
       <c r="A321">
         <v>174</v>
       </c>
@@ -16899,7 +16909,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="15">
+    <row r="322" spans="1:23" ht="15" hidden="1">
       <c r="A322">
         <v>193</v>
       </c>
@@ -16938,7 +16948,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="15">
+    <row r="323" spans="1:23" ht="15" hidden="1">
       <c r="A323">
         <v>194</v>
       </c>
@@ -16977,7 +16987,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="15">
+    <row r="324" spans="1:23" ht="15" hidden="1">
       <c r="A324">
         <v>202</v>
       </c>
@@ -17014,7 +17024,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="15">
+    <row r="325" spans="1:23" ht="15" hidden="1">
       <c r="A325">
         <v>295</v>
       </c>
@@ -17051,7 +17061,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="15">
+    <row r="326" spans="1:23" ht="15" hidden="1">
       <c r="A326">
         <v>296</v>
       </c>
@@ -17090,7 +17100,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="15">
+    <row r="327" spans="1:23" ht="15" hidden="1">
       <c r="A327">
         <v>306</v>
       </c>
@@ -17128,7 +17138,7 @@
       </c>
       <c r="W327" s="3"/>
     </row>
-    <row r="328" spans="1:23" ht="15">
+    <row r="328" spans="1:23" ht="15" hidden="1">
       <c r="A328">
         <v>307</v>
       </c>
@@ -17167,7 +17177,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="15">
+    <row r="329" spans="1:23" ht="15" hidden="1">
       <c r="A329">
         <v>310</v>
       </c>
@@ -17204,7 +17214,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="15">
+    <row r="330" spans="1:23" ht="15" hidden="1">
       <c r="A330">
         <v>312</v>
       </c>
@@ -17244,7 +17254,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="15">
+    <row r="331" spans="1:23" ht="15" hidden="1">
       <c r="A331">
         <v>313</v>
       </c>
@@ -17281,7 +17291,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="15">
+    <row r="332" spans="1:23" ht="15" hidden="1">
       <c r="A332">
         <v>318</v>
       </c>
@@ -17316,7 +17326,7 @@
       </c>
       <c r="W332" s="3"/>
     </row>
-    <row r="333" spans="1:23" ht="15">
+    <row r="333" spans="1:23" ht="15" hidden="1">
       <c r="A333">
         <v>322</v>
       </c>
@@ -17353,7 +17363,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="15">
+    <row r="334" spans="1:23" ht="15" hidden="1">
       <c r="A334">
         <v>326</v>
       </c>
@@ -17392,7 +17402,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="15">
+    <row r="335" spans="1:23" ht="15" hidden="1">
       <c r="A335">
         <v>332</v>
       </c>
@@ -17431,7 +17441,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="15">
+    <row r="336" spans="1:23" ht="15" hidden="1">
       <c r="A336">
         <v>333</v>
       </c>
@@ -17468,7 +17478,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="15">
+    <row r="337" spans="1:23" ht="15" hidden="1">
       <c r="A337">
         <v>334</v>
       </c>
@@ -17508,7 +17518,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="15">
+    <row r="338" spans="1:23" ht="15" hidden="1">
       <c r="A338">
         <v>343</v>
       </c>
@@ -17543,7 +17553,7 @@
       </c>
       <c r="W338" s="3"/>
     </row>
-    <row r="339" spans="1:23" ht="15">
+    <row r="339" spans="1:23" ht="15" hidden="1">
       <c r="A339">
         <v>344</v>
       </c>
@@ -17584,7 +17594,7 @@
       </c>
       <c r="W339" s="3"/>
     </row>
-    <row r="340" spans="1:23" ht="15">
+    <row r="340" spans="1:23" ht="15" hidden="1">
       <c r="A340">
         <v>357</v>
       </c>
@@ -17623,7 +17633,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="15">
+    <row r="341" spans="1:23" ht="15" hidden="1">
       <c r="A341">
         <v>358</v>
       </c>
@@ -17662,7 +17672,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="15">
+    <row r="342" spans="1:23" ht="15" hidden="1">
       <c r="A342">
         <v>359</v>
       </c>
@@ -17702,7 +17712,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="15">
+    <row r="343" spans="1:23" ht="15" hidden="1">
       <c r="A343">
         <v>360</v>
       </c>
@@ -17745,7 +17755,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="15">
+    <row r="344" spans="1:23" ht="15" hidden="1">
       <c r="A344">
         <v>362</v>
       </c>
@@ -17784,7 +17794,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="15">
+    <row r="345" spans="1:23" ht="15" hidden="1">
       <c r="A345">
         <v>364</v>
       </c>
@@ -17821,7 +17831,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="15">
+    <row r="346" spans="1:23" ht="15" hidden="1">
       <c r="A346">
         <v>365</v>
       </c>
@@ -17860,7 +17870,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="15">
+    <row r="347" spans="1:23" ht="15" hidden="1">
       <c r="A347">
         <v>380</v>
       </c>
@@ -17900,7 +17910,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="15">
+    <row r="348" spans="1:23" ht="15" hidden="1">
       <c r="A348">
         <v>381</v>
       </c>
@@ -17940,7 +17950,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="15">
+    <row r="349" spans="1:23" ht="15" hidden="1">
       <c r="A349">
         <v>382</v>
       </c>
@@ -17977,7 +17987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="15">
+    <row r="350" spans="1:23" ht="15" hidden="1">
       <c r="A350">
         <v>383</v>
       </c>
@@ -18016,7 +18026,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="15">
+    <row r="351" spans="1:23" ht="15" hidden="1">
       <c r="A351">
         <v>384</v>
       </c>
@@ -18055,7 +18065,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="15">
+    <row r="352" spans="1:23" ht="15" hidden="1">
       <c r="A352">
         <v>386</v>
       </c>
@@ -18094,7 +18104,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="15">
+    <row r="353" spans="1:23" ht="15" hidden="1">
       <c r="A353">
         <v>410</v>
       </c>
@@ -18133,7 +18143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="15">
+    <row r="354" spans="1:23" ht="15" hidden="1">
       <c r="A354">
         <v>411</v>
       </c>
@@ -18172,7 +18182,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="15">
+    <row r="355" spans="1:23" ht="15" hidden="1">
       <c r="A355">
         <v>417</v>
       </c>
@@ -18211,7 +18221,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="15">
+    <row r="356" spans="1:23" ht="15" hidden="1">
       <c r="A356">
         <v>418</v>
       </c>
@@ -18248,7 +18258,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="15">
+    <row r="357" spans="1:23" ht="15" hidden="1">
       <c r="A357">
         <v>419</v>
       </c>
@@ -18291,7 +18301,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="15">
+    <row r="358" spans="1:23" ht="15" hidden="1">
       <c r="A358">
         <v>420</v>
       </c>
@@ -18331,7 +18341,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="15">
+    <row r="359" spans="1:23" ht="15" hidden="1">
       <c r="A359">
         <v>451</v>
       </c>
@@ -18371,7 +18381,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="15">
+    <row r="360" spans="1:23" ht="15" hidden="1">
       <c r="A360">
         <v>452</v>
       </c>
@@ -18408,7 +18418,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="15">
+    <row r="361" spans="1:23" ht="15" hidden="1">
       <c r="A361">
         <v>453</v>
       </c>
@@ -18443,7 +18453,7 @@
       </c>
       <c r="W361" s="3"/>
     </row>
-    <row r="362" spans="1:23" ht="15">
+    <row r="362" spans="1:23" ht="15" hidden="1">
       <c r="A362">
         <v>454</v>
       </c>
@@ -18482,7 +18492,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="15">
+    <row r="363" spans="1:23" ht="15" hidden="1">
       <c r="A363">
         <v>455</v>
       </c>
@@ -18521,7 +18531,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="15">
+    <row r="364" spans="1:23" ht="15" hidden="1">
       <c r="A364">
         <v>481</v>
       </c>
@@ -18558,7 +18568,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="15">
+    <row r="365" spans="1:23" ht="15" hidden="1">
       <c r="A365">
         <v>482</v>
       </c>
@@ -18595,7 +18605,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="15">
+    <row r="366" spans="1:23" ht="15" hidden="1">
       <c r="A366">
         <v>566</v>
       </c>
@@ -18634,7 +18644,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="15">
+    <row r="367" spans="1:23" ht="15" hidden="1">
       <c r="A367">
         <v>567</v>
       </c>
@@ -18673,7 +18683,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="15">
+    <row r="368" spans="1:23" ht="15" hidden="1">
       <c r="A368">
         <v>615</v>
       </c>
@@ -18711,7 +18721,7 @@
       </c>
       <c r="W368" s="3"/>
     </row>
-    <row r="369" spans="1:23" ht="15">
+    <row r="369" spans="1:23" ht="15" hidden="1">
       <c r="A369">
         <v>616</v>
       </c>
@@ -18749,7 +18759,7 @@
       </c>
       <c r="W369" s="3"/>
     </row>
-    <row r="370" spans="1:23" ht="15">
+    <row r="370" spans="1:23" ht="15" hidden="1">
       <c r="A370">
         <v>617</v>
       </c>
@@ -18790,7 +18800,7 @@
       </c>
       <c r="W370" s="3"/>
     </row>
-    <row r="371" spans="1:23" ht="15">
+    <row r="371" spans="1:23" ht="15" hidden="1">
       <c r="A371">
         <v>618</v>
       </c>
@@ -18831,7 +18841,7 @@
       </c>
       <c r="W371" s="3"/>
     </row>
-    <row r="372" spans="1:23" ht="15">
+    <row r="372" spans="1:23" ht="15" hidden="1">
       <c r="A372">
         <v>619</v>
       </c>
@@ -18872,7 +18882,7 @@
       </c>
       <c r="W372" s="3"/>
     </row>
-    <row r="373" spans="1:23" ht="15">
+    <row r="373" spans="1:23" ht="15" hidden="1">
       <c r="A373">
         <v>620</v>
       </c>
@@ -18913,7 +18923,7 @@
       </c>
       <c r="W373" s="3"/>
     </row>
-    <row r="374" spans="1:23" ht="15">
+    <row r="374" spans="1:23" ht="15" hidden="1">
       <c r="A374">
         <v>621</v>
       </c>
@@ -18954,7 +18964,7 @@
       </c>
       <c r="W374" s="3"/>
     </row>
-    <row r="375" spans="1:23" ht="15">
+    <row r="375" spans="1:23" ht="15" hidden="1">
       <c r="A375">
         <v>622</v>
       </c>
@@ -18995,7 +19005,7 @@
       </c>
       <c r="W375" s="3"/>
     </row>
-    <row r="376" spans="1:23" ht="15">
+    <row r="376" spans="1:23" ht="15" hidden="1">
       <c r="A376">
         <v>636</v>
       </c>
@@ -19032,7 +19042,7 @@
       </c>
       <c r="W376" s="3"/>
     </row>
-    <row r="377" spans="1:23" ht="15">
+    <row r="377" spans="1:23" ht="15" hidden="1">
       <c r="A377">
         <v>639</v>
       </c>
@@ -19073,7 +19083,7 @@
       </c>
       <c r="W377" s="3"/>
     </row>
-    <row r="378" spans="1:23" ht="15">
+    <row r="378" spans="1:23" ht="15" hidden="1">
       <c r="A378">
         <v>648</v>
       </c>
@@ -19111,7 +19121,7 @@
       </c>
       <c r="W378" s="3"/>
     </row>
-    <row r="379" spans="1:23" ht="15">
+    <row r="379" spans="1:23" ht="15" hidden="1">
       <c r="A379">
         <v>649</v>
       </c>
@@ -19152,7 +19162,7 @@
       </c>
       <c r="W379" s="3"/>
     </row>
-    <row r="380" spans="1:23" ht="15">
+    <row r="380" spans="1:23" ht="15" hidden="1">
       <c r="A380">
         <v>660</v>
       </c>
@@ -19193,7 +19203,7 @@
       </c>
       <c r="W380" s="3"/>
     </row>
-    <row r="381" spans="1:23" ht="15">
+    <row r="381" spans="1:23" ht="15" hidden="1">
       <c r="A381">
         <v>661</v>
       </c>
@@ -19233,7 +19243,7 @@
       </c>
       <c r="W381" s="3"/>
     </row>
-    <row r="382" spans="1:23" ht="15">
+    <row r="382" spans="1:23" ht="15" hidden="1">
       <c r="A382">
         <v>730</v>
       </c>
@@ -19274,7 +19284,7 @@
       </c>
       <c r="W382" s="3"/>
     </row>
-    <row r="383" spans="1:23" ht="15">
+    <row r="383" spans="1:23" ht="15" hidden="1">
       <c r="A383">
         <v>731</v>
       </c>
@@ -19315,7 +19325,7 @@
       </c>
       <c r="W383" s="3"/>
     </row>
-    <row r="384" spans="1:23" ht="15">
+    <row r="384" spans="1:23" ht="15" hidden="1">
       <c r="A384">
         <v>732</v>
       </c>
@@ -19356,7 +19366,7 @@
       </c>
       <c r="W384" s="3"/>
     </row>
-    <row r="385" spans="1:23" ht="15">
+    <row r="385" spans="1:23" ht="15" hidden="1">
       <c r="A385">
         <v>733</v>
       </c>
@@ -19397,7 +19407,7 @@
       </c>
       <c r="W385" s="3"/>
     </row>
-    <row r="386" spans="1:23" ht="15">
+    <row r="386" spans="1:23" ht="15" hidden="1">
       <c r="A386">
         <v>734</v>
       </c>
@@ -19438,7 +19448,7 @@
       </c>
       <c r="W386" s="3"/>
     </row>
-    <row r="387" spans="1:23" ht="15">
+    <row r="387" spans="1:23" ht="15" hidden="1">
       <c r="A387">
         <v>735</v>
       </c>
@@ -19488,7 +19498,7 @@
       </c>
       <c r="W387" s="3"/>
     </row>
-    <row r="388" spans="1:23" ht="15">
+    <row r="388" spans="1:23" ht="15" hidden="1">
       <c r="A388">
         <v>736</v>
       </c>
@@ -19529,7 +19539,7 @@
       </c>
       <c r="W388" s="3"/>
     </row>
-    <row r="389" spans="1:23" ht="15">
+    <row r="389" spans="1:23" ht="15" hidden="1">
       <c r="A389">
         <v>755</v>
       </c>
@@ -19569,7 +19579,7 @@
       </c>
       <c r="W389" s="3"/>
     </row>
-    <row r="390" spans="1:23" ht="15">
+    <row r="390" spans="1:23" ht="15" hidden="1">
       <c r="A390">
         <v>756</v>
       </c>
@@ -19610,7 +19620,7 @@
       </c>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23" ht="15">
+    <row r="391" spans="1:23" ht="15" hidden="1">
       <c r="A391">
         <v>757</v>
       </c>
@@ -19660,7 +19670,7 @@
       </c>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23" ht="15">
+    <row r="392" spans="1:23" ht="15" hidden="1">
       <c r="A392">
         <v>758</v>
       </c>
@@ -19700,7 +19710,7 @@
       </c>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23" ht="15">
+    <row r="393" spans="1:23" ht="15" hidden="1">
       <c r="A393">
         <v>773</v>
       </c>
@@ -19739,7 +19749,7 @@
       </c>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23" ht="15">
+    <row r="394" spans="1:23" ht="15" hidden="1">
       <c r="A394">
         <v>795</v>
       </c>
@@ -19779,7 +19789,7 @@
       </c>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23" ht="15">
+    <row r="395" spans="1:23" ht="15" hidden="1">
       <c r="A395">
         <v>802</v>
       </c>
@@ -19820,7 +19830,7 @@
       </c>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23" ht="15">
+    <row r="396" spans="1:23" ht="15" hidden="1">
       <c r="A396">
         <v>803</v>
       </c>
@@ -19861,7 +19871,7 @@
       </c>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23" ht="15">
+    <row r="397" spans="1:23" ht="15" hidden="1">
       <c r="A397">
         <v>812</v>
       </c>
@@ -19901,7 +19911,7 @@
       </c>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23" ht="15">
+    <row r="398" spans="1:23" ht="15" hidden="1">
       <c r="A398">
         <v>814</v>
       </c>
@@ -19939,7 +19949,7 @@
       </c>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23" ht="15">
+    <row r="399" spans="1:23" ht="15" hidden="1">
       <c r="A399">
         <v>824</v>
       </c>
@@ -19980,7 +19990,7 @@
       </c>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23" ht="15">
+    <row r="400" spans="1:23" ht="15" hidden="1">
       <c r="A400">
         <v>830</v>
       </c>
@@ -20021,7 +20031,7 @@
       </c>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23" ht="15">
+    <row r="401" spans="1:23" ht="15" hidden="1">
       <c r="A401">
         <v>120</v>
       </c>
@@ -20061,7 +20071,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="402" spans="1:23" ht="15">
+    <row r="402" spans="1:23" ht="15" hidden="1">
       <c r="A402">
         <v>121</v>
       </c>
@@ -20101,7 +20111,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="403" spans="1:23" ht="15">
+    <row r="403" spans="1:23" ht="15" hidden="1">
       <c r="A403">
         <v>122</v>
       </c>
@@ -20141,7 +20151,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="404" spans="1:23" ht="15">
+    <row r="404" spans="1:23" ht="15" hidden="1">
       <c r="A404">
         <v>123</v>
       </c>
@@ -20181,7 +20191,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="405" spans="1:23" ht="15">
+    <row r="405" spans="1:23" ht="15" hidden="1">
       <c r="A405">
         <v>124</v>
       </c>
@@ -20221,7 +20231,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="406" spans="1:23" ht="15">
+    <row r="406" spans="1:23" ht="15" hidden="1">
       <c r="A406">
         <v>125</v>
       </c>
@@ -20264,7 +20274,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="15">
+    <row r="407" spans="1:23" ht="15" hidden="1">
       <c r="A407">
         <v>127</v>
       </c>
@@ -20305,7 +20315,7 @@
       </c>
       <c r="W407" s="3"/>
     </row>
-    <row r="408" spans="1:23" ht="15">
+    <row r="408" spans="1:23" ht="15" hidden="1">
       <c r="A408">
         <v>128</v>
       </c>
@@ -20346,7 +20356,7 @@
       </c>
       <c r="W408" s="3"/>
     </row>
-    <row r="409" spans="1:23" ht="15">
+    <row r="409" spans="1:23" ht="15" hidden="1">
       <c r="A409">
         <v>280</v>
       </c>
@@ -20389,7 +20399,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="15">
+    <row r="410" spans="1:23" ht="15" hidden="1">
       <c r="A410">
         <v>281</v>
       </c>
@@ -20429,7 +20439,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="411" spans="1:23" ht="15">
+    <row r="411" spans="1:23" ht="15" hidden="1">
       <c r="A411">
         <v>282</v>
       </c>
@@ -20469,7 +20479,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="412" spans="1:23" ht="15">
+    <row r="412" spans="1:23" ht="15" hidden="1">
       <c r="A412">
         <v>283</v>
       </c>
@@ -20509,7 +20519,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="413" spans="1:23" ht="15">
+    <row r="413" spans="1:23" ht="15" hidden="1">
       <c r="A413">
         <v>284</v>
       </c>
@@ -20549,7 +20559,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="414" spans="1:23" ht="15">
+    <row r="414" spans="1:23" ht="15" hidden="1">
       <c r="A414">
         <v>285</v>
       </c>
@@ -20586,7 +20596,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="415" spans="1:23" ht="15">
+    <row r="415" spans="1:23" ht="15" hidden="1">
       <c r="A415">
         <v>286</v>
       </c>
@@ -20629,7 +20639,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="416" spans="1:23" ht="15">
+    <row r="416" spans="1:23" ht="15" hidden="1">
       <c r="A416">
         <v>287</v>
       </c>
@@ -20666,7 +20676,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="417" spans="1:23" ht="15">
+    <row r="417" spans="1:23" ht="15" hidden="1">
       <c r="A417">
         <v>288</v>
       </c>
@@ -20709,7 +20719,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="418" spans="1:23" ht="15">
+    <row r="418" spans="1:23" ht="15" hidden="1">
       <c r="A418">
         <v>289</v>
       </c>
@@ -20749,7 +20759,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="419" spans="1:23" ht="15">
+    <row r="419" spans="1:23" ht="15" hidden="1">
       <c r="A419">
         <v>290</v>
       </c>
@@ -20786,7 +20796,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="420" spans="1:23" ht="15">
+    <row r="420" spans="1:23" ht="15" hidden="1">
       <c r="A420">
         <v>291</v>
       </c>
@@ -20829,7 +20839,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="421" spans="1:23" ht="15">
+    <row r="421" spans="1:23" ht="15" hidden="1">
       <c r="A421">
         <v>292</v>
       </c>
@@ -20872,7 +20882,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="422" spans="1:23" ht="15">
+    <row r="422" spans="1:23" ht="15" hidden="1">
       <c r="A422">
         <v>293</v>
       </c>
@@ -20915,7 +20925,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="423" spans="1:23" ht="15">
+    <row r="423" spans="1:23" ht="15" hidden="1">
       <c r="A423">
         <v>542</v>
       </c>
@@ -20952,7 +20962,7 @@
       </c>
       <c r="W423" s="3"/>
     </row>
-    <row r="424" spans="1:23" ht="15">
+    <row r="424" spans="1:23" ht="15" hidden="1">
       <c r="A424">
         <v>611</v>
       </c>
@@ -20990,7 +21000,7 @@
       </c>
       <c r="W424" s="3"/>
     </row>
-    <row r="425" spans="1:23" ht="15">
+    <row r="425" spans="1:23" ht="15" hidden="1">
       <c r="A425">
         <v>612</v>
       </c>
@@ -21028,7 +21038,7 @@
       </c>
       <c r="W425" s="3"/>
     </row>
-    <row r="426" spans="1:23" ht="15">
+    <row r="426" spans="1:23" ht="15" hidden="1">
       <c r="A426">
         <v>613</v>
       </c>
@@ -21066,7 +21076,7 @@
       </c>
       <c r="W426" s="3"/>
     </row>
-    <row r="427" spans="1:23" ht="15">
+    <row r="427" spans="1:23" ht="15" hidden="1">
       <c r="A427">
         <v>614</v>
       </c>
@@ -21104,7 +21114,7 @@
       </c>
       <c r="W427" s="3"/>
     </row>
-    <row r="428" spans="1:23" ht="15">
+    <row r="428" spans="1:23" ht="15" hidden="1">
       <c r="A428">
         <v>663</v>
       </c>
@@ -21145,7 +21155,7 @@
       </c>
       <c r="W428" s="3"/>
     </row>
-    <row r="429" spans="1:23" ht="15">
+    <row r="429" spans="1:23" ht="15" hidden="1">
       <c r="A429">
         <v>664</v>
       </c>
@@ -21182,7 +21192,7 @@
       </c>
       <c r="W429" s="3"/>
     </row>
-    <row r="430" spans="1:23" ht="15">
+    <row r="430" spans="1:23" ht="15" hidden="1">
       <c r="A430">
         <v>804</v>
       </c>
@@ -21219,7 +21229,7 @@
       </c>
       <c r="W430" s="3"/>
     </row>
-    <row r="431" spans="1:23" ht="15">
+    <row r="431" spans="1:23" ht="15" hidden="1">
       <c r="A431">
         <v>805</v>
       </c>
@@ -21269,7 +21279,7 @@
       </c>
       <c r="W431" s="3"/>
     </row>
-    <row r="432" spans="1:23" ht="15">
+    <row r="432" spans="1:23" ht="15" hidden="1">
       <c r="A432">
         <v>806</v>
       </c>
@@ -21310,7 +21320,7 @@
       </c>
       <c r="W432" s="3"/>
     </row>
-    <row r="433" spans="1:23" ht="15">
+    <row r="433" spans="1:23" ht="15" hidden="1">
       <c r="A433">
         <v>835</v>
       </c>
@@ -21347,7 +21357,7 @@
       </c>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23" ht="15">
+    <row r="434" spans="1:23" ht="15" hidden="1">
       <c r="A434">
         <v>836</v>
       </c>
@@ -21386,7 +21396,7 @@
       </c>
       <c r="W434" s="3"/>
     </row>
-    <row r="435" spans="1:23" ht="15">
+    <row r="435" spans="1:23" ht="15" hidden="1">
       <c r="A435">
         <v>837</v>
       </c>
@@ -24304,7 +24314,7 @@
       </c>
       <c r="W508" s="3"/>
     </row>
-    <row r="509" spans="1:23" ht="15">
+    <row r="509" spans="1:23" ht="15" hidden="1">
       <c r="A509">
         <v>1</v>
       </c>
@@ -24342,7 +24352,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="510" spans="1:23" ht="15">
+    <row r="510" spans="1:23" ht="15" hidden="1">
       <c r="A510">
         <v>21</v>
       </c>
@@ -24380,7 +24390,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="511" spans="1:23" ht="15">
+    <row r="511" spans="1:23" ht="15" hidden="1">
       <c r="A511">
         <v>22</v>
       </c>
@@ -24415,7 +24425,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="512" spans="1:23" ht="15">
+    <row r="512" spans="1:23" ht="15" hidden="1">
       <c r="A512">
         <v>23</v>
       </c>
@@ -24456,7 +24466,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="513" spans="1:23" ht="15">
+    <row r="513" spans="1:23" ht="15" hidden="1">
       <c r="A513">
         <v>24</v>
       </c>
@@ -24491,7 +24501,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="514" spans="1:23" ht="15">
+    <row r="514" spans="1:23" ht="15" hidden="1">
       <c r="A514">
         <v>44</v>
       </c>
@@ -24526,7 +24536,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="515" spans="1:23" ht="15">
+    <row r="515" spans="1:23" ht="15" hidden="1">
       <c r="A515">
         <v>45</v>
       </c>
@@ -24561,7 +24571,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="516" spans="1:23" ht="15">
+    <row r="516" spans="1:23" ht="15" hidden="1">
       <c r="A516">
         <v>46</v>
       </c>
@@ -24596,7 +24606,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="517" spans="1:23" ht="15">
+    <row r="517" spans="1:23" ht="15" hidden="1">
       <c r="A517">
         <v>47</v>
       </c>
@@ -24634,7 +24644,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="518" spans="1:23" ht="15">
+    <row r="518" spans="1:23" ht="15" hidden="1">
       <c r="A518">
         <v>57</v>
       </c>
@@ -24672,7 +24682,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="519" spans="1:23" ht="15">
+    <row r="519" spans="1:23" ht="15" hidden="1">
       <c r="A519">
         <v>61</v>
       </c>
@@ -24707,7 +24717,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="520" spans="1:23" ht="15">
+    <row r="520" spans="1:23" ht="15" hidden="1">
       <c r="A520">
         <v>154</v>
       </c>
@@ -24746,7 +24756,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="521" spans="1:23" ht="15">
+    <row r="521" spans="1:23" ht="15" hidden="1">
       <c r="A521">
         <v>155</v>
       </c>
@@ -24786,7 +24796,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="522" spans="1:23" ht="15">
+    <row r="522" spans="1:23" ht="15" hidden="1">
       <c r="A522">
         <v>156</v>
       </c>
@@ -24826,7 +24836,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="523" spans="1:23" ht="15">
+    <row r="523" spans="1:23" ht="15" hidden="1">
       <c r="A523">
         <v>157</v>
       </c>
@@ -24866,7 +24876,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="524" spans="1:23" ht="15">
+    <row r="524" spans="1:23" ht="15" hidden="1">
       <c r="A524">
         <v>158</v>
       </c>
@@ -24906,7 +24916,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="525" spans="1:23" ht="15">
+    <row r="525" spans="1:23" ht="15" hidden="1">
       <c r="A525">
         <v>166</v>
       </c>
@@ -24945,7 +24955,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="526" spans="1:23" ht="15">
+    <row r="526" spans="1:23" ht="15" hidden="1">
       <c r="A526">
         <v>167</v>
       </c>
@@ -24984,7 +24994,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="527" spans="1:23" ht="15">
+    <row r="527" spans="1:23" ht="15" hidden="1">
       <c r="A527">
         <v>168</v>
       </c>
@@ -25024,7 +25034,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="528" spans="1:23" ht="15">
+    <row r="528" spans="1:23" ht="15" hidden="1">
       <c r="A528">
         <v>169</v>
       </c>
@@ -25067,7 +25077,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="529" spans="1:23" ht="15">
+    <row r="529" spans="1:23" ht="15" hidden="1">
       <c r="A529">
         <v>170</v>
       </c>
@@ -25110,7 +25120,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="530" spans="1:23" ht="15">
+    <row r="530" spans="1:23" ht="15" hidden="1">
       <c r="A530">
         <v>203</v>
       </c>
@@ -25147,7 +25157,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="531" spans="1:23" ht="15">
+    <row r="531" spans="1:23" ht="15" hidden="1">
       <c r="A531">
         <v>297</v>
       </c>
@@ -25186,7 +25196,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="532" spans="1:23" ht="15">
+    <row r="532" spans="1:23" ht="15" hidden="1">
       <c r="A532">
         <v>298</v>
       </c>
@@ -25225,7 +25235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="533" spans="1:23" ht="15">
+    <row r="533" spans="1:23" ht="15" hidden="1">
       <c r="A533">
         <v>299</v>
       </c>
@@ -25264,7 +25274,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="534" spans="1:23" ht="15">
+    <row r="534" spans="1:23" ht="15" hidden="1">
       <c r="A534">
         <v>300</v>
       </c>
@@ -25303,7 +25313,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="535" spans="1:23" ht="15">
+    <row r="535" spans="1:23" ht="15" hidden="1">
       <c r="A535">
         <v>301</v>
       </c>
@@ -25342,7 +25352,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="536" spans="1:23" ht="15">
+    <row r="536" spans="1:23" ht="15" hidden="1">
       <c r="A536">
         <v>302</v>
       </c>
@@ -25381,7 +25391,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="537" spans="1:23" ht="15">
+    <row r="537" spans="1:23" ht="15" hidden="1">
       <c r="A537">
         <v>303</v>
       </c>
@@ -25420,7 +25430,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="538" spans="1:23" ht="15">
+    <row r="538" spans="1:23" ht="15" hidden="1">
       <c r="A538">
         <v>304</v>
       </c>
@@ -25459,7 +25469,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="539" spans="1:23" ht="15">
+    <row r="539" spans="1:23" ht="15" hidden="1">
       <c r="A539">
         <v>305</v>
       </c>
@@ -25498,7 +25508,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="540" spans="1:23" ht="15">
+    <row r="540" spans="1:23" ht="15" hidden="1">
       <c r="A540">
         <v>308</v>
       </c>
@@ -25537,7 +25547,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="541" spans="1:23" ht="15">
+    <row r="541" spans="1:23" ht="15" hidden="1">
       <c r="A541">
         <v>309</v>
       </c>
@@ -25574,7 +25584,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="542" spans="1:23" ht="15">
+    <row r="542" spans="1:23" ht="15" hidden="1">
       <c r="A542">
         <v>319</v>
       </c>
@@ -25613,7 +25623,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="543" spans="1:23" ht="15">
+    <row r="543" spans="1:23" ht="15" hidden="1">
       <c r="A543">
         <v>323</v>
       </c>
@@ -25650,7 +25660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="544" spans="1:23" ht="15">
+    <row r="544" spans="1:23" ht="15" hidden="1">
       <c r="A544">
         <v>324</v>
       </c>
@@ -25689,7 +25699,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="545" spans="1:23" ht="15">
+    <row r="545" spans="1:23" ht="15" hidden="1">
       <c r="A545">
         <v>349</v>
       </c>
@@ -25726,7 +25736,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="546" spans="1:23" ht="15">
+    <row r="546" spans="1:23" ht="15" hidden="1">
       <c r="A546">
         <v>353</v>
       </c>
@@ -25763,7 +25773,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="547" spans="1:23" ht="15">
+    <row r="547" spans="1:23" ht="15" hidden="1">
       <c r="A547">
         <v>354</v>
       </c>
@@ -25802,7 +25812,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="548" spans="1:23" ht="15">
+    <row r="548" spans="1:23" ht="15" hidden="1">
       <c r="A548">
         <v>355</v>
       </c>
@@ -25839,7 +25849,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="549" spans="1:23" ht="15">
+    <row r="549" spans="1:23" ht="15" hidden="1">
       <c r="A549">
         <v>361</v>
       </c>
@@ -25876,7 +25886,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="550" spans="1:23" ht="15">
+    <row r="550" spans="1:23" ht="15" hidden="1">
       <c r="A550">
         <v>363</v>
       </c>
@@ -25915,7 +25925,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="551" spans="1:23" ht="15">
+    <row r="551" spans="1:23" ht="15" hidden="1">
       <c r="A551">
         <v>366</v>
       </c>
@@ -25954,7 +25964,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="552" spans="1:23" ht="15">
+    <row r="552" spans="1:23" ht="15" hidden="1">
       <c r="A552">
         <v>367</v>
       </c>
@@ -25991,7 +26001,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="553" spans="1:23" ht="15">
+    <row r="553" spans="1:23" ht="15" hidden="1">
       <c r="A553">
         <v>369</v>
       </c>
@@ -26028,7 +26038,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="554" spans="1:23" ht="15">
+    <row r="554" spans="1:23" ht="15" hidden="1">
       <c r="A554">
         <v>416</v>
       </c>
@@ -26071,7 +26081,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="555" spans="1:23" ht="15">
+    <row r="555" spans="1:23" ht="15" hidden="1">
       <c r="A555">
         <v>456</v>
       </c>
@@ -26110,7 +26120,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="556" spans="1:23" ht="15">
+    <row r="556" spans="1:23" ht="15" hidden="1">
       <c r="A556">
         <v>457</v>
       </c>
@@ -26149,7 +26159,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="557" spans="1:23" ht="15">
+    <row r="557" spans="1:23" ht="15" hidden="1">
       <c r="A557">
         <v>458</v>
       </c>
@@ -26188,7 +26198,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="558" spans="1:23" ht="15">
+    <row r="558" spans="1:23" ht="15" hidden="1">
       <c r="A558">
         <v>459</v>
       </c>
@@ -26227,7 +26237,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="559" spans="1:23" ht="15">
+    <row r="559" spans="1:23" ht="15" hidden="1">
       <c r="A559">
         <v>460</v>
       </c>
@@ -26266,7 +26276,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="560" spans="1:23" ht="15">
+    <row r="560" spans="1:23" ht="15" hidden="1">
       <c r="A560">
         <v>461</v>
       </c>
@@ -26305,7 +26315,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="561" spans="1:23" ht="15">
+    <row r="561" spans="1:23" ht="15" hidden="1">
       <c r="A561">
         <v>462</v>
       </c>
@@ -26344,7 +26354,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="562" spans="1:23" ht="15">
+    <row r="562" spans="1:23" ht="15" hidden="1">
       <c r="A562">
         <v>463</v>
       </c>
@@ -26383,7 +26393,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="563" spans="1:23" ht="15">
+    <row r="563" spans="1:23" ht="15" hidden="1">
       <c r="A563">
         <v>464</v>
       </c>
@@ -26422,7 +26432,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="564" spans="1:23" ht="15">
+    <row r="564" spans="1:23" ht="15" hidden="1">
       <c r="A564">
         <v>465</v>
       </c>
@@ -26461,7 +26471,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="565" spans="1:23" ht="15">
+    <row r="565" spans="1:23" ht="15" hidden="1">
       <c r="A565">
         <v>466</v>
       </c>
@@ -26500,7 +26510,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="566" spans="1:23" ht="15">
+    <row r="566" spans="1:23" ht="15" hidden="1">
       <c r="A566">
         <v>467</v>
       </c>
@@ -26539,7 +26549,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="567" spans="1:23" ht="15">
+    <row r="567" spans="1:23" ht="15" hidden="1">
       <c r="A567">
         <v>468</v>
       </c>
@@ -26578,7 +26588,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="568" spans="1:23" ht="15">
+    <row r="568" spans="1:23" ht="15" hidden="1">
       <c r="A568">
         <v>469</v>
       </c>
@@ -26617,7 +26627,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="569" spans="1:23" ht="15">
+    <row r="569" spans="1:23" ht="15" hidden="1">
       <c r="A569">
         <v>470</v>
       </c>
@@ -26654,7 +26664,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="570" spans="1:23" ht="15">
+    <row r="570" spans="1:23" ht="15" hidden="1">
       <c r="A570">
         <v>471</v>
       </c>
@@ -26694,7 +26704,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="571" spans="1:23" ht="15">
+    <row r="571" spans="1:23" ht="15" hidden="1">
       <c r="A571">
         <v>473</v>
       </c>
@@ -26733,7 +26743,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="572" spans="1:23" ht="15">
+    <row r="572" spans="1:23" ht="15" hidden="1">
       <c r="A572">
         <v>474</v>
       </c>
@@ -26772,7 +26782,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="573" spans="1:23" ht="15">
+    <row r="573" spans="1:23" ht="15" hidden="1">
       <c r="A573">
         <v>475</v>
       </c>
@@ -26809,7 +26819,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="574" spans="1:23" ht="15">
+    <row r="574" spans="1:23" ht="15" hidden="1">
       <c r="A574">
         <v>476</v>
       </c>
@@ -26846,7 +26856,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="575" spans="1:23" ht="15">
+    <row r="575" spans="1:23" ht="15" hidden="1">
       <c r="A575">
         <v>477</v>
       </c>
@@ -26889,7 +26899,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="576" spans="1:23" ht="15">
+    <row r="576" spans="1:23" ht="15" hidden="1">
       <c r="A576">
         <v>478</v>
       </c>
@@ -26928,7 +26938,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="577" spans="1:23" ht="15">
+    <row r="577" spans="1:23" ht="15" hidden="1">
       <c r="A577">
         <v>479</v>
       </c>
@@ -26967,7 +26977,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="578" spans="1:23" ht="15">
+    <row r="578" spans="1:23" ht="15" hidden="1">
       <c r="A578">
         <v>483</v>
       </c>
@@ -27006,7 +27016,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="579" spans="1:23" ht="15">
+    <row r="579" spans="1:23" ht="15" hidden="1">
       <c r="A579">
         <v>484</v>
       </c>
@@ -27045,7 +27055,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="580" spans="1:23" ht="15">
+    <row r="580" spans="1:23" ht="15" hidden="1">
       <c r="A580">
         <v>489</v>
       </c>
@@ -27084,7 +27094,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="581" spans="1:23" ht="15">
+    <row r="581" spans="1:23" ht="15" hidden="1">
       <c r="A581">
         <v>490</v>
       </c>
@@ -27123,7 +27133,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="582" spans="1:23" ht="15">
+    <row r="582" spans="1:23" ht="15" hidden="1">
       <c r="A582">
         <v>491</v>
       </c>
@@ -27160,7 +27170,7 @@
       </c>
       <c r="W582" s="3"/>
     </row>
-    <row r="583" spans="1:23" ht="15">
+    <row r="583" spans="1:23" ht="15" hidden="1">
       <c r="A583">
         <v>492</v>
       </c>
@@ -27197,7 +27207,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="584" spans="1:23" ht="15">
+    <row r="584" spans="1:23" ht="15" hidden="1">
       <c r="A584">
         <v>493</v>
       </c>
@@ -27235,7 +27245,7 @@
       </c>
       <c r="W584" s="3"/>
     </row>
-    <row r="585" spans="1:23" ht="15">
+    <row r="585" spans="1:23" ht="15" hidden="1">
       <c r="A585">
         <v>559</v>
       </c>
@@ -27274,7 +27284,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="586" spans="1:23" ht="15">
+    <row r="586" spans="1:23" ht="15" hidden="1">
       <c r="A586">
         <v>560</v>
       </c>
@@ -27311,7 +27321,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="587" spans="1:23" ht="15">
+    <row r="587" spans="1:23" ht="15" hidden="1">
       <c r="A587">
         <v>568</v>
       </c>
@@ -27350,7 +27360,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="588" spans="1:23" ht="15">
+    <row r="588" spans="1:23" ht="15" hidden="1">
       <c r="A588">
         <v>570</v>
       </c>
@@ -27389,7 +27399,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="589" spans="1:23" ht="15">
+    <row r="589" spans="1:23" ht="15" hidden="1">
       <c r="A589">
         <v>574</v>
       </c>
@@ -27428,7 +27438,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="590" spans="1:23" ht="15">
+    <row r="590" spans="1:23" ht="15" hidden="1">
       <c r="A590">
         <v>576</v>
       </c>
@@ -27465,7 +27475,7 @@
       </c>
       <c r="W590" s="3"/>
     </row>
-    <row r="591" spans="1:23" ht="15">
+    <row r="591" spans="1:23" ht="15" hidden="1">
       <c r="A591">
         <v>600</v>
       </c>
@@ -27505,7 +27515,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="592" spans="1:23" ht="15">
+    <row r="592" spans="1:23" ht="15" hidden="1">
       <c r="A592">
         <v>637</v>
       </c>
@@ -27546,7 +27556,7 @@
       </c>
       <c r="W592" s="3"/>
     </row>
-    <row r="593" spans="1:23" ht="15">
+    <row r="593" spans="1:23" ht="15" hidden="1">
       <c r="A593">
         <v>638</v>
       </c>
@@ -27587,7 +27597,7 @@
       </c>
       <c r="W593" s="3"/>
     </row>
-    <row r="594" spans="1:23" ht="15">
+    <row r="594" spans="1:23" ht="15" hidden="1">
       <c r="A594">
         <v>640</v>
       </c>
@@ -27627,7 +27637,7 @@
       </c>
       <c r="W594" s="3"/>
     </row>
-    <row r="595" spans="1:23" ht="15">
+    <row r="595" spans="1:23" ht="15" hidden="1">
       <c r="A595">
         <v>656</v>
       </c>
@@ -27668,7 +27678,7 @@
       </c>
       <c r="W595" s="3"/>
     </row>
-    <row r="596" spans="1:23" ht="15">
+    <row r="596" spans="1:23" ht="15" hidden="1">
       <c r="A596">
         <v>657</v>
       </c>
@@ -27709,7 +27719,7 @@
       </c>
       <c r="W596" s="3"/>
     </row>
-    <row r="597" spans="1:23" ht="15">
+    <row r="597" spans="1:23" ht="15" hidden="1">
       <c r="A597">
         <v>658</v>
       </c>
@@ -27750,7 +27760,7 @@
       </c>
       <c r="W597" s="3"/>
     </row>
-    <row r="598" spans="1:23" ht="15">
+    <row r="598" spans="1:23" ht="15" hidden="1">
       <c r="A598">
         <v>659</v>
       </c>
@@ -27787,7 +27797,7 @@
       </c>
       <c r="W598" s="3"/>
     </row>
-    <row r="599" spans="1:23" ht="15">
+    <row r="599" spans="1:23" ht="15" hidden="1">
       <c r="A599">
         <v>665</v>
       </c>
@@ -27828,7 +27838,7 @@
       </c>
       <c r="W599" s="3"/>
     </row>
-    <row r="600" spans="1:23" ht="15">
+    <row r="600" spans="1:23" ht="15" hidden="1">
       <c r="A600">
         <v>710</v>
       </c>
@@ -27869,7 +27879,7 @@
       </c>
       <c r="W600" s="3"/>
     </row>
-    <row r="601" spans="1:23" ht="15">
+    <row r="601" spans="1:23" ht="15" hidden="1">
       <c r="A601">
         <v>711</v>
       </c>
@@ -27910,7 +27920,7 @@
       </c>
       <c r="W601" s="3"/>
     </row>
-    <row r="602" spans="1:23" ht="15">
+    <row r="602" spans="1:23" ht="15" hidden="1">
       <c r="A602">
         <v>739</v>
       </c>
@@ -27947,7 +27957,7 @@
       </c>
       <c r="W602" s="3"/>
     </row>
-    <row r="603" spans="1:23" ht="15">
+    <row r="603" spans="1:23" ht="15" hidden="1">
       <c r="A603">
         <v>745</v>
       </c>
@@ -27997,7 +28007,7 @@
       </c>
       <c r="W603" s="3"/>
     </row>
-    <row r="604" spans="1:23" ht="15">
+    <row r="604" spans="1:23" ht="15" hidden="1">
       <c r="A604">
         <v>796</v>
       </c>
@@ -28047,7 +28057,7 @@
       </c>
       <c r="W604" s="3"/>
     </row>
-    <row r="605" spans="1:23" ht="15">
+    <row r="605" spans="1:23" ht="15" hidden="1">
       <c r="A605">
         <v>800</v>
       </c>
@@ -28084,7 +28094,7 @@
       </c>
       <c r="W605" s="3"/>
     </row>
-    <row r="606" spans="1:23" ht="15">
+    <row r="606" spans="1:23" ht="15" hidden="1">
       <c r="A606">
         <v>801</v>
       </c>
@@ -28124,7 +28134,7 @@
       </c>
       <c r="W606" s="3"/>
     </row>
-    <row r="607" spans="1:23" ht="15">
+    <row r="607" spans="1:23" ht="15" hidden="1">
       <c r="A607">
         <v>827</v>
       </c>
@@ -28174,7 +28184,7 @@
       </c>
       <c r="W607" s="3"/>
     </row>
-    <row r="608" spans="1:23" ht="15">
+    <row r="608" spans="1:23" ht="15" hidden="1">
       <c r="A608">
         <v>833</v>
       </c>
@@ -28224,7 +28234,7 @@
       </c>
       <c r="W608" s="3"/>
     </row>
-    <row r="609" spans="1:23" ht="15">
+    <row r="609" spans="1:23" ht="15" hidden="1">
       <c r="A609">
         <v>843</v>
       </c>
@@ -28261,7 +28271,7 @@
       </c>
       <c r="W609" s="3"/>
     </row>
-    <row r="610" spans="1:23" ht="15">
+    <row r="610" spans="1:23" ht="15" hidden="1">
       <c r="A610">
         <v>850</v>
       </c>
@@ -28302,7 +28312,7 @@
       </c>
       <c r="W610" s="3"/>
     </row>
-    <row r="611" spans="1:23" ht="15">
+    <row r="611" spans="1:23" ht="15" hidden="1">
       <c r="A611">
         <v>2</v>
       </c>
@@ -28337,7 +28347,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="612" spans="1:23" ht="15">
+    <row r="612" spans="1:23" ht="15" hidden="1">
       <c r="A612">
         <v>3</v>
       </c>
@@ -28372,7 +28382,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="613" spans="1:23" ht="15">
+    <row r="613" spans="1:23" ht="15" hidden="1">
       <c r="A613">
         <v>4</v>
       </c>
@@ -28407,7 +28417,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="614" spans="1:23" ht="15">
+    <row r="614" spans="1:23" ht="15" hidden="1">
       <c r="A614">
         <v>25</v>
       </c>
@@ -28442,7 +28452,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="615" spans="1:23" ht="15">
+    <row r="615" spans="1:23" ht="15" hidden="1">
       <c r="A615">
         <v>88</v>
       </c>
@@ -28483,7 +28493,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="616" spans="1:23" ht="15">
+    <row r="616" spans="1:23" ht="15" hidden="1">
       <c r="A616">
         <v>89</v>
       </c>
@@ -28518,7 +28528,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="617" spans="1:23" ht="15">
+    <row r="617" spans="1:23" ht="15" hidden="1">
       <c r="A617">
         <v>90</v>
       </c>
@@ -28553,7 +28563,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="618" spans="1:23" ht="15">
+    <row r="618" spans="1:23" ht="15" hidden="1">
       <c r="A618">
         <v>91</v>
       </c>
@@ -28588,7 +28598,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="619" spans="1:23" ht="15">
+    <row r="619" spans="1:23" ht="15" hidden="1">
       <c r="A619">
         <v>92</v>
       </c>
@@ -28629,7 +28639,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="620" spans="1:23" ht="15">
+    <row r="620" spans="1:23" ht="15" hidden="1">
       <c r="A620">
         <v>93</v>
       </c>
@@ -28667,7 +28677,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="621" spans="1:23" ht="15">
+    <row r="621" spans="1:23" ht="15" hidden="1">
       <c r="A621">
         <v>94</v>
       </c>
@@ -28702,7 +28712,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="622" spans="1:23" ht="15">
+    <row r="622" spans="1:23" ht="15" hidden="1">
       <c r="A622">
         <v>96</v>
       </c>
@@ -28740,7 +28750,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="623" spans="1:23" ht="15">
+    <row r="623" spans="1:23" ht="15" hidden="1">
       <c r="A623">
         <v>97</v>
       </c>
@@ -28775,7 +28785,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="624" spans="1:23" ht="15">
+    <row r="624" spans="1:23" ht="15" hidden="1">
       <c r="A624">
         <v>126</v>
       </c>
@@ -28818,7 +28828,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="625" spans="1:23" ht="15">
+    <row r="625" spans="1:23" ht="15" hidden="1">
       <c r="A625">
         <v>223</v>
       </c>
@@ -28855,7 +28865,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="626" spans="1:23" ht="15">
+    <row r="626" spans="1:23" ht="15" hidden="1">
       <c r="A626">
         <v>224</v>
       </c>
@@ -28895,7 +28905,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="627" spans="1:23" ht="15">
+    <row r="627" spans="1:23" ht="15" hidden="1">
       <c r="A627">
         <v>225</v>
       </c>
@@ -28938,7 +28948,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="628" spans="1:23" ht="15">
+    <row r="628" spans="1:23" ht="15" hidden="1">
       <c r="A628">
         <v>226</v>
       </c>
@@ -28978,7 +28988,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="629" spans="1:23" ht="15">
+    <row r="629" spans="1:23" ht="15" hidden="1">
       <c r="A629">
         <v>227</v>
       </c>
@@ -29018,7 +29028,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="630" spans="1:23" ht="15">
+    <row r="630" spans="1:23" ht="15" hidden="1">
       <c r="A630">
         <v>228</v>
       </c>
@@ -29055,7 +29065,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="631" spans="1:23" ht="15">
+    <row r="631" spans="1:23" ht="15" hidden="1">
       <c r="A631">
         <v>229</v>
       </c>
@@ -29098,7 +29108,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="632" spans="1:23" ht="15">
+    <row r="632" spans="1:23" ht="15" hidden="1">
       <c r="A632">
         <v>230</v>
       </c>
@@ -29138,7 +29148,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="633" spans="1:23" ht="15">
+    <row r="633" spans="1:23" ht="15" hidden="1">
       <c r="A633">
         <v>231</v>
       </c>
@@ -29178,7 +29188,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="634" spans="1:23" ht="15">
+    <row r="634" spans="1:23" ht="15" hidden="1">
       <c r="A634">
         <v>232</v>
       </c>
@@ -29215,7 +29225,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="635" spans="1:23" ht="15">
+    <row r="635" spans="1:23" ht="15" hidden="1">
       <c r="A635">
         <v>233</v>
       </c>
@@ -29258,7 +29268,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="636" spans="1:23" ht="15">
+    <row r="636" spans="1:23" ht="15" hidden="1">
       <c r="A636">
         <v>234</v>
       </c>
@@ -29297,7 +29307,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="637" spans="1:23" ht="15">
+    <row r="637" spans="1:23" ht="15" hidden="1">
       <c r="A637">
         <v>235</v>
       </c>
@@ -29336,7 +29346,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="638" spans="1:23" ht="15">
+    <row r="638" spans="1:23" ht="15" hidden="1">
       <c r="A638">
         <v>236</v>
       </c>
@@ -29377,7 +29387,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="639" spans="1:23" ht="15">
+    <row r="639" spans="1:23" ht="15" hidden="1">
       <c r="A639">
         <v>340</v>
       </c>
@@ -29414,7 +29424,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="640" spans="1:23" ht="15">
+    <row r="640" spans="1:23" ht="15" hidden="1">
       <c r="A640">
         <v>341</v>
       </c>
@@ -29457,7 +29467,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="641" spans="1:23" ht="15">
+    <row r="641" spans="1:23" ht="15" hidden="1">
       <c r="A641">
         <v>342</v>
       </c>
@@ -29494,7 +29504,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="642" spans="1:23" ht="15">
+    <row r="642" spans="1:23" ht="15" hidden="1">
       <c r="A642">
         <v>348</v>
       </c>
@@ -29537,7 +29547,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="643" spans="1:23" ht="15">
+    <row r="643" spans="1:23" ht="15" hidden="1">
       <c r="A643">
         <v>377</v>
       </c>
@@ -29574,7 +29584,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="644" spans="1:23" ht="15">
+    <row r="644" spans="1:23" ht="15" hidden="1">
       <c r="A644">
         <v>378</v>
       </c>
@@ -29611,7 +29621,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="645" spans="1:23" ht="15">
+    <row r="645" spans="1:23" ht="15" hidden="1">
       <c r="A645">
         <v>402</v>
       </c>
@@ -29650,7 +29660,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="646" spans="1:23" ht="15">
+    <row r="646" spans="1:23" ht="15" hidden="1">
       <c r="A646">
         <v>403</v>
       </c>
@@ -29693,7 +29703,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="647" spans="1:23" ht="15">
+    <row r="647" spans="1:23" ht="15" hidden="1">
       <c r="A647">
         <v>404</v>
       </c>
@@ -29736,7 +29746,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="648" spans="1:23" ht="15">
+    <row r="648" spans="1:23" ht="15" hidden="1">
       <c r="A648">
         <v>405</v>
       </c>
@@ -29779,7 +29789,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="649" spans="1:23" ht="15">
+    <row r="649" spans="1:23" ht="15" hidden="1">
       <c r="A649">
         <v>406</v>
       </c>
@@ -29816,7 +29826,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="650" spans="1:23" ht="15">
+    <row r="650" spans="1:23" ht="15" hidden="1">
       <c r="A650">
         <v>407</v>
       </c>
@@ -29859,7 +29869,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="651" spans="1:23" ht="15">
+    <row r="651" spans="1:23" ht="15" hidden="1">
       <c r="A651">
         <v>408</v>
       </c>
@@ -29902,7 +29912,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="652" spans="1:23" ht="15">
+    <row r="652" spans="1:23" ht="15" hidden="1">
       <c r="A652">
         <v>409</v>
       </c>
@@ -29945,7 +29955,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="653" spans="1:23" ht="15">
+    <row r="653" spans="1:23" ht="15" hidden="1">
       <c r="A653">
         <v>439</v>
       </c>
@@ -29982,7 +29992,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="654" spans="1:23" ht="15">
+    <row r="654" spans="1:23" ht="15" hidden="1">
       <c r="A654">
         <v>448</v>
       </c>
@@ -30021,7 +30031,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="655" spans="1:23" ht="15">
+    <row r="655" spans="1:23" ht="15" hidden="1">
       <c r="A655">
         <v>449</v>
       </c>
@@ -30060,7 +30070,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="656" spans="1:23" ht="15">
+    <row r="656" spans="1:23" ht="15" hidden="1">
       <c r="A656">
         <v>450</v>
       </c>
@@ -30099,7 +30109,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="657" spans="1:23" ht="15">
+    <row r="657" spans="1:23" ht="15" hidden="1">
       <c r="A657">
         <v>480</v>
       </c>
@@ -30136,7 +30146,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="658" spans="1:23" ht="15">
+    <row r="658" spans="1:23" ht="15" hidden="1">
       <c r="A658">
         <v>546</v>
       </c>
@@ -30176,7 +30186,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="659" spans="1:23" ht="15">
+    <row r="659" spans="1:23" ht="15" hidden="1">
       <c r="A659">
         <v>547</v>
       </c>
@@ -30213,7 +30223,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="660" spans="1:23" ht="15">
+    <row r="660" spans="1:23" ht="15" hidden="1">
       <c r="A660">
         <v>548</v>
       </c>
@@ -30250,7 +30260,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="661" spans="1:23" ht="15">
+    <row r="661" spans="1:23" ht="15" hidden="1">
       <c r="A661">
         <v>549</v>
       </c>
@@ -30287,7 +30297,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="662" spans="1:23" ht="15">
+    <row r="662" spans="1:23" ht="15" hidden="1">
       <c r="A662">
         <v>550</v>
       </c>
@@ -30324,7 +30334,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="663" spans="1:23" ht="15">
+    <row r="663" spans="1:23" ht="15" hidden="1">
       <c r="A663">
         <v>551</v>
       </c>
@@ -30361,7 +30371,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="664" spans="1:23" ht="15">
+    <row r="664" spans="1:23" ht="15" hidden="1">
       <c r="A664">
         <v>552</v>
       </c>
@@ -30398,7 +30408,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="665" spans="1:23" ht="15">
+    <row r="665" spans="1:23" ht="15" hidden="1">
       <c r="A665">
         <v>553</v>
       </c>
@@ -30435,7 +30445,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="666" spans="1:23" ht="15">
+    <row r="666" spans="1:23" ht="15" hidden="1">
       <c r="A666">
         <v>554</v>
       </c>
@@ -30472,7 +30482,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="667" spans="1:23" ht="15">
+    <row r="667" spans="1:23" ht="15" hidden="1">
       <c r="A667">
         <v>555</v>
       </c>
@@ -30509,7 +30519,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="668" spans="1:23" ht="15">
+    <row r="668" spans="1:23" ht="15" hidden="1">
       <c r="A668">
         <v>556</v>
       </c>
@@ -30546,7 +30556,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="669" spans="1:23" ht="15">
+    <row r="669" spans="1:23" ht="15" hidden="1">
       <c r="A669">
         <v>557</v>
       </c>
@@ -30583,7 +30593,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="670" spans="1:23" ht="15">
+    <row r="670" spans="1:23" ht="15" hidden="1">
       <c r="A670">
         <v>558</v>
       </c>
@@ -30620,7 +30630,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="671" spans="1:23" ht="15">
+    <row r="671" spans="1:23" ht="15" hidden="1">
       <c r="A671">
         <v>575</v>
       </c>
@@ -30659,7 +30669,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="672" spans="1:23" ht="15">
+    <row r="672" spans="1:23" ht="15" hidden="1">
       <c r="A672">
         <v>623</v>
       </c>
@@ -30700,7 +30710,7 @@
       </c>
       <c r="W672" s="3"/>
     </row>
-    <row r="673" spans="1:23" ht="15">
+    <row r="673" spans="1:23" ht="15" hidden="1">
       <c r="A673">
         <v>624</v>
       </c>
@@ -30741,7 +30751,7 @@
       </c>
       <c r="W673" s="3"/>
     </row>
-    <row r="674" spans="1:23" ht="15">
+    <row r="674" spans="1:23" ht="15" hidden="1">
       <c r="A674">
         <v>625</v>
       </c>
@@ -30782,7 +30792,7 @@
       </c>
       <c r="W674" s="3"/>
     </row>
-    <row r="675" spans="1:23" ht="15">
+    <row r="675" spans="1:23" ht="15" hidden="1">
       <c r="A675">
         <v>626</v>
       </c>
@@ -30823,7 +30833,7 @@
       </c>
       <c r="W675" s="3"/>
     </row>
-    <row r="676" spans="1:23" ht="15">
+    <row r="676" spans="1:23" ht="15" hidden="1">
       <c r="A676">
         <v>627</v>
       </c>
@@ -30864,7 +30874,7 @@
       </c>
       <c r="W676" s="3"/>
     </row>
-    <row r="677" spans="1:23" ht="15">
+    <row r="677" spans="1:23" ht="15" hidden="1">
       <c r="A677">
         <v>628</v>
       </c>
@@ -30902,7 +30912,7 @@
       </c>
       <c r="W677" s="3"/>
     </row>
-    <row r="678" spans="1:23" ht="15">
+    <row r="678" spans="1:23" ht="15" hidden="1">
       <c r="A678">
         <v>647</v>
       </c>
@@ -30943,7 +30953,7 @@
       </c>
       <c r="W678" s="3"/>
     </row>
-    <row r="679" spans="1:23" ht="15">
+    <row r="679" spans="1:23" ht="15" hidden="1">
       <c r="A679">
         <v>667</v>
       </c>
@@ -30984,7 +30994,7 @@
       </c>
       <c r="W679" s="3"/>
     </row>
-    <row r="680" spans="1:23" ht="15">
+    <row r="680" spans="1:23" ht="15" hidden="1">
       <c r="A680">
         <v>677</v>
       </c>
@@ -31024,7 +31034,7 @@
       </c>
       <c r="W680" s="3"/>
     </row>
-    <row r="681" spans="1:23" ht="15">
+    <row r="681" spans="1:23" ht="15" hidden="1">
       <c r="A681">
         <v>678</v>
       </c>
@@ -31064,7 +31074,7 @@
       </c>
       <c r="W681" s="3"/>
     </row>
-    <row r="682" spans="1:23" ht="15">
+    <row r="682" spans="1:23" ht="15" hidden="1">
       <c r="A682">
         <v>679</v>
       </c>
@@ -31105,7 +31115,7 @@
       </c>
       <c r="W682" s="3"/>
     </row>
-    <row r="683" spans="1:23" ht="15">
+    <row r="683" spans="1:23" ht="15" hidden="1">
       <c r="A683">
         <v>680</v>
       </c>
@@ -31146,7 +31156,7 @@
       </c>
       <c r="W683" s="3"/>
     </row>
-    <row r="684" spans="1:23" ht="15">
+    <row r="684" spans="1:23" ht="15" hidden="1">
       <c r="A684">
         <v>718</v>
       </c>
@@ -31187,7 +31197,7 @@
       </c>
       <c r="W684" s="3"/>
     </row>
-    <row r="685" spans="1:23" ht="15">
+    <row r="685" spans="1:23" ht="15" hidden="1">
       <c r="A685">
         <v>719</v>
       </c>
@@ -31228,7 +31238,7 @@
       </c>
       <c r="W685" s="3"/>
     </row>
-    <row r="686" spans="1:23" ht="15">
+    <row r="686" spans="1:23" ht="15" hidden="1">
       <c r="A686">
         <v>774</v>
       </c>
@@ -31269,7 +31279,7 @@
       </c>
       <c r="W686" s="3"/>
     </row>
-    <row r="687" spans="1:23" ht="15">
+    <row r="687" spans="1:23" ht="15" hidden="1">
       <c r="A687">
         <v>775</v>
       </c>
@@ -31310,7 +31320,7 @@
       </c>
       <c r="W687" s="3"/>
     </row>
-    <row r="688" spans="1:23" ht="15">
+    <row r="688" spans="1:23" ht="15" hidden="1">
       <c r="A688">
         <v>776</v>
       </c>
@@ -31350,7 +31360,7 @@
       </c>
       <c r="W688" s="3"/>
     </row>
-    <row r="689" spans="1:23" ht="15">
+    <row r="689" spans="1:23" ht="15" hidden="1">
       <c r="A689">
         <v>848</v>
       </c>
@@ -31400,7 +31410,7 @@
       </c>
       <c r="W689" s="3"/>
     </row>
-    <row r="690" spans="1:23" ht="15">
+    <row r="690" spans="1:23" ht="15" hidden="1">
       <c r="A690">
         <v>849</v>
       </c>
@@ -31441,7 +31451,7 @@
       </c>
       <c r="W690" s="3"/>
     </row>
-    <row r="691" spans="1:23" ht="15">
+    <row r="691" spans="1:23" ht="15" hidden="1">
       <c r="A691">
         <v>851</v>
       </c>
@@ -31482,7 +31492,7 @@
       </c>
       <c r="W691" s="3"/>
     </row>
-    <row r="692" spans="1:23" ht="15">
+    <row r="692" spans="1:23" ht="15" hidden="1">
       <c r="A692">
         <v>54</v>
       </c>
@@ -31517,7 +31527,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="693" spans="1:23" ht="15">
+    <row r="693" spans="1:23" ht="15" hidden="1">
       <c r="A693">
         <v>55</v>
       </c>
@@ -31555,7 +31565,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="694" spans="1:23" ht="15">
+    <row r="694" spans="1:23" ht="15" hidden="1">
       <c r="A694">
         <v>62</v>
       </c>
@@ -31593,7 +31603,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="695" spans="1:23" ht="15">
+    <row r="695" spans="1:23" ht="15" hidden="1">
       <c r="A695">
         <v>83</v>
       </c>
@@ -31634,7 +31644,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="696" spans="1:23" ht="15">
+    <row r="696" spans="1:23" ht="15" hidden="1">
       <c r="A696">
         <v>116</v>
       </c>
@@ -31671,7 +31681,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="697" spans="1:23" ht="15">
+    <row r="697" spans="1:23" ht="15" hidden="1">
       <c r="A697">
         <v>153</v>
       </c>
@@ -31708,7 +31718,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="698" spans="1:23" ht="15">
+    <row r="698" spans="1:23" ht="15" hidden="1">
       <c r="A698">
         <v>159</v>
       </c>
@@ -31751,7 +31761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="699" spans="1:23" ht="15">
+    <row r="699" spans="1:23" ht="15" hidden="1">
       <c r="A699">
         <v>199</v>
       </c>
@@ -31791,7 +31801,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="700" spans="1:23" ht="15">
+    <row r="700" spans="1:23" ht="15" hidden="1">
       <c r="A700">
         <v>200</v>
       </c>
@@ -31828,7 +31838,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="701" spans="1:23" ht="15">
+    <row r="701" spans="1:23" ht="15" hidden="1">
       <c r="A701">
         <v>201</v>
       </c>
@@ -31865,7 +31875,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="702" spans="1:23" ht="15">
+    <row r="702" spans="1:23" ht="15" hidden="1">
       <c r="A702">
         <v>249</v>
       </c>
@@ -31904,7 +31914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="703" spans="1:23" ht="15">
+    <row r="703" spans="1:23" ht="15" hidden="1">
       <c r="A703">
         <v>253</v>
       </c>
@@ -31941,7 +31951,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="704" spans="1:23" ht="15">
+    <row r="704" spans="1:23" ht="15" hidden="1">
       <c r="A704">
         <v>254</v>
       </c>
@@ -31978,7 +31988,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="705" spans="1:23" ht="15">
+    <row r="705" spans="1:23" ht="15" hidden="1">
       <c r="A705">
         <v>258</v>
       </c>
@@ -32015,7 +32025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="706" spans="1:23" ht="15">
+    <row r="706" spans="1:23" ht="15" hidden="1">
       <c r="A706">
         <v>259</v>
       </c>
@@ -32055,7 +32065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="707" spans="1:23" ht="15">
+    <row r="707" spans="1:23" ht="15" hidden="1">
       <c r="A707">
         <v>261</v>
       </c>
@@ -32092,7 +32102,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="708" spans="1:23" ht="15">
+    <row r="708" spans="1:23" ht="15" hidden="1">
       <c r="A708">
         <v>267</v>
       </c>
@@ -32129,7 +32139,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="709" spans="1:23" ht="15">
+    <row r="709" spans="1:23" ht="15" hidden="1">
       <c r="A709">
         <v>268</v>
       </c>
@@ -32166,7 +32176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="710" spans="1:23" ht="15">
+    <row r="710" spans="1:23" ht="15" hidden="1">
       <c r="A710">
         <v>269</v>
       </c>
@@ -32209,7 +32219,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="711" spans="1:23" ht="15">
+    <row r="711" spans="1:23" ht="15" hidden="1">
       <c r="A711">
         <v>311</v>
       </c>
@@ -32246,7 +32256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="712" spans="1:23" ht="15">
+    <row r="712" spans="1:23" ht="15" hidden="1">
       <c r="A712">
         <v>317</v>
       </c>
@@ -32283,7 +32293,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="713" spans="1:23" ht="15">
+    <row r="713" spans="1:23" ht="15" hidden="1">
       <c r="A713">
         <v>338</v>
       </c>
@@ -32320,7 +32330,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="714" spans="1:23" ht="15">
+    <row r="714" spans="1:23" ht="15" hidden="1">
       <c r="A714">
         <v>371</v>
       </c>
@@ -32357,7 +32367,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="715" spans="1:23" ht="15">
+    <row r="715" spans="1:23" ht="15" hidden="1">
       <c r="A715">
         <v>472</v>
       </c>
@@ -32394,7 +32404,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="716" spans="1:23" ht="15">
+    <row r="716" spans="1:23" ht="15" hidden="1">
       <c r="A716">
         <v>494</v>
       </c>
@@ -32431,7 +32441,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="717" spans="1:23" ht="15">
+    <row r="717" spans="1:23" ht="15" hidden="1">
       <c r="A717">
         <v>496</v>
       </c>
@@ -32474,7 +32484,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="718" spans="1:23" ht="15">
+    <row r="718" spans="1:23" ht="15" hidden="1">
       <c r="A718">
         <v>497</v>
       </c>
@@ -32511,7 +32521,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="719" spans="1:23" ht="15">
+    <row r="719" spans="1:23" ht="15" hidden="1">
       <c r="A719">
         <v>498</v>
       </c>
@@ -32550,7 +32560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="720" spans="1:23" ht="15">
+    <row r="720" spans="1:23" ht="15" hidden="1">
       <c r="A720">
         <v>499</v>
       </c>
@@ -32593,7 +32603,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="721" spans="1:23" ht="15">
+    <row r="721" spans="1:23" ht="15" hidden="1">
       <c r="A721">
         <v>500</v>
       </c>
@@ -32636,7 +32646,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="722" spans="1:23" ht="15">
+    <row r="722" spans="1:23" ht="15" hidden="1">
       <c r="A722">
         <v>501</v>
       </c>
@@ -32673,7 +32683,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="723" spans="1:23" ht="15">
+    <row r="723" spans="1:23" ht="15" hidden="1">
       <c r="A723">
         <v>502</v>
       </c>
@@ -32712,7 +32722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="724" spans="1:23" ht="15">
+    <row r="724" spans="1:23" ht="15" hidden="1">
       <c r="A724">
         <v>503</v>
       </c>
@@ -32749,7 +32759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="725" spans="1:23" ht="15">
+    <row r="725" spans="1:23" ht="15" hidden="1">
       <c r="A725">
         <v>504</v>
       </c>
@@ -32792,7 +32802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="726" spans="1:23" ht="15">
+    <row r="726" spans="1:23" ht="15" hidden="1">
       <c r="A726">
         <v>505</v>
       </c>
@@ -32831,7 +32841,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="727" spans="1:23" ht="15">
+    <row r="727" spans="1:23" ht="15" hidden="1">
       <c r="A727">
         <v>506</v>
       </c>
@@ -32870,7 +32880,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="728" spans="1:23" ht="15">
+    <row r="728" spans="1:23" ht="15" hidden="1">
       <c r="A728">
         <v>507</v>
       </c>
@@ -32909,7 +32919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="729" spans="1:23" ht="15">
+    <row r="729" spans="1:23" ht="15" hidden="1">
       <c r="A729">
         <v>508</v>
       </c>
@@ -32952,7 +32962,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="730" spans="1:23" ht="15">
+    <row r="730" spans="1:23" ht="15" hidden="1">
       <c r="A730">
         <v>509</v>
       </c>
@@ -32989,7 +32999,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="731" spans="1:23" ht="15">
+    <row r="731" spans="1:23" ht="15" hidden="1">
       <c r="A731">
         <v>510</v>
       </c>
@@ -33028,7 +33038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="732" spans="1:23" ht="15">
+    <row r="732" spans="1:23" ht="15" hidden="1">
       <c r="A732">
         <v>511</v>
       </c>
@@ -33067,7 +33077,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="733" spans="1:23" ht="15">
+    <row r="733" spans="1:23" ht="15" hidden="1">
       <c r="A733">
         <v>512</v>
       </c>
@@ -33106,7 +33116,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="734" spans="1:23" ht="15">
+    <row r="734" spans="1:23" ht="15" hidden="1">
       <c r="A734">
         <v>513</v>
       </c>
@@ -33145,7 +33155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="735" spans="1:23" ht="15">
+    <row r="735" spans="1:23" ht="15" hidden="1">
       <c r="A735">
         <v>514</v>
       </c>
@@ -33184,7 +33194,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="736" spans="1:23" ht="15">
+    <row r="736" spans="1:23" ht="15" hidden="1">
       <c r="A736">
         <v>515</v>
       </c>
@@ -33227,7 +33237,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="737" spans="1:23" ht="15">
+    <row r="737" spans="1:23" ht="15" hidden="1">
       <c r="A737">
         <v>571</v>
       </c>
@@ -33268,7 +33278,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="738" spans="1:23" ht="15">
+    <row r="738" spans="1:23" ht="15" hidden="1">
       <c r="A738">
         <v>579</v>
       </c>
@@ -33305,7 +33315,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="739" spans="1:23" ht="15">
+    <row r="739" spans="1:23" ht="15" hidden="1">
       <c r="A739">
         <v>581</v>
       </c>
@@ -33344,7 +33354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="740" spans="1:23" ht="15">
+    <row r="740" spans="1:23" ht="15" hidden="1">
       <c r="A740">
         <v>592</v>
       </c>
@@ -33381,7 +33391,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="741" spans="1:23" ht="15">
+    <row r="741" spans="1:23" ht="15" hidden="1">
       <c r="A741">
         <v>601</v>
       </c>
@@ -33424,7 +33434,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="742" spans="1:23" ht="15">
+    <row r="742" spans="1:23" ht="15" hidden="1">
       <c r="A742">
         <v>602</v>
       </c>
@@ -33467,7 +33477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="743" spans="1:23" ht="15">
+    <row r="743" spans="1:23" ht="15" hidden="1">
       <c r="A743">
         <v>651</v>
       </c>
@@ -33508,7 +33518,7 @@
       </c>
       <c r="W743" s="3"/>
     </row>
-    <row r="744" spans="1:23" ht="15">
+    <row r="744" spans="1:23" ht="15" hidden="1">
       <c r="A744">
         <v>652</v>
       </c>
@@ -33549,7 +33559,7 @@
       </c>
       <c r="W744" s="3"/>
     </row>
-    <row r="745" spans="1:23" ht="15">
+    <row r="745" spans="1:23" ht="15" hidden="1">
       <c r="A745">
         <v>712</v>
       </c>
@@ -33590,7 +33600,7 @@
       </c>
       <c r="W745" s="3"/>
     </row>
-    <row r="746" spans="1:23" ht="15">
+    <row r="746" spans="1:23" ht="15" hidden="1">
       <c r="A746">
         <v>738</v>
       </c>
@@ -33631,7 +33641,7 @@
       </c>
       <c r="W746" s="3"/>
     </row>
-    <row r="747" spans="1:23" ht="15">
+    <row r="747" spans="1:23" ht="15" hidden="1">
       <c r="A747">
         <v>744</v>
       </c>
@@ -33668,7 +33678,7 @@
       </c>
       <c r="W747" s="3"/>
     </row>
-    <row r="748" spans="1:23" ht="15">
+    <row r="748" spans="1:23" ht="15" hidden="1">
       <c r="A748">
         <v>759</v>
       </c>
@@ -33709,7 +33719,7 @@
       </c>
       <c r="W748" s="3"/>
     </row>
-    <row r="749" spans="1:23" ht="15">
+    <row r="749" spans="1:23" ht="15" hidden="1">
       <c r="A749">
         <v>797</v>
       </c>
@@ -33750,7 +33760,7 @@
       </c>
       <c r="W749" s="3"/>
     </row>
-    <row r="750" spans="1:23" ht="15">
+    <row r="750" spans="1:23" ht="15" hidden="1">
       <c r="A750">
         <v>798</v>
       </c>
@@ -33789,7 +33799,7 @@
       </c>
       <c r="W750" s="3"/>
     </row>
-    <row r="751" spans="1:23" ht="15">
+    <row r="751" spans="1:23" ht="15" hidden="1">
       <c r="A751">
         <v>813</v>
       </c>
@@ -33829,7 +33839,7 @@
       </c>
       <c r="W751" s="3"/>
     </row>
-    <row r="752" spans="1:23" ht="15">
+    <row r="752" spans="1:23" ht="15" hidden="1">
       <c r="A752">
         <v>825</v>
       </c>
@@ -33869,7 +33879,7 @@
       </c>
       <c r="W752" s="3"/>
     </row>
-    <row r="753" spans="1:23" ht="15">
+    <row r="753" spans="1:23" ht="15" hidden="1">
       <c r="A753">
         <v>826</v>
       </c>
@@ -33909,7 +33919,7 @@
       </c>
       <c r="W753" s="3"/>
     </row>
-    <row r="754" spans="1:23" ht="15">
+    <row r="754" spans="1:23" ht="15" hidden="1">
       <c r="A754">
         <v>828</v>
       </c>
@@ -33949,7 +33959,7 @@
       </c>
       <c r="W754" s="3"/>
     </row>
-    <row r="755" spans="1:23" ht="15">
+    <row r="755" spans="1:23" ht="15" hidden="1">
       <c r="A755">
         <v>842</v>
       </c>
@@ -33990,7 +34000,7 @@
       </c>
       <c r="W755" s="3"/>
     </row>
-    <row r="756" spans="1:23" ht="15">
+    <row r="756" spans="1:23" ht="15" hidden="1">
       <c r="A756">
         <v>844</v>
       </c>
@@ -34031,7 +34041,7 @@
       </c>
       <c r="W756" s="3"/>
     </row>
-    <row r="757" spans="1:23" ht="15">
+    <row r="757" spans="1:23" ht="15" hidden="1">
       <c r="A757">
         <v>237</v>
       </c>
@@ -34068,7 +34078,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="758" spans="1:23" ht="15">
+    <row r="758" spans="1:23" ht="15" hidden="1">
       <c r="A758">
         <v>238</v>
       </c>
@@ -34108,7 +34118,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="759" spans="1:23" ht="15">
+    <row r="759" spans="1:23" ht="15" hidden="1">
       <c r="A759">
         <v>239</v>
       </c>
@@ -34148,7 +34158,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="760" spans="1:23" ht="15">
+    <row r="760" spans="1:23" ht="15" hidden="1">
       <c r="A760">
         <v>543</v>
       </c>
@@ -34187,7 +34197,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="761" spans="1:23" ht="15">
+    <row r="761" spans="1:23" ht="15" hidden="1">
       <c r="A761">
         <v>545</v>
       </c>
@@ -34224,7 +34234,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="762" spans="1:23" ht="15">
+    <row r="762" spans="1:23" ht="15" hidden="1">
       <c r="A762">
         <v>605</v>
       </c>
@@ -34262,7 +34272,7 @@
       </c>
       <c r="W762" s="3"/>
     </row>
-    <row r="763" spans="1:23" ht="15">
+    <row r="763" spans="1:23" ht="15" hidden="1">
       <c r="A763">
         <v>654</v>
       </c>
@@ -34303,7 +34313,7 @@
       </c>
       <c r="W763" s="3"/>
     </row>
-    <row r="764" spans="1:23" ht="15">
+    <row r="764" spans="1:23" ht="15" hidden="1">
       <c r="A764">
         <v>655</v>
       </c>
@@ -34344,7 +34354,7 @@
       </c>
       <c r="W764" s="3"/>
     </row>
-    <row r="765" spans="1:23" ht="15">
+    <row r="765" spans="1:23" ht="15" hidden="1">
       <c r="A765">
         <v>729</v>
       </c>
@@ -34385,7 +34395,7 @@
       </c>
       <c r="W765" s="3"/>
     </row>
-    <row r="766" spans="1:23" ht="15">
+    <row r="766" spans="1:23" ht="15" hidden="1">
       <c r="A766">
         <v>815</v>
       </c>
@@ -34426,7 +34436,7 @@
       </c>
       <c r="W766" s="3"/>
     </row>
-    <row r="767" spans="1:23" ht="15">
+    <row r="767" spans="1:23" ht="15" hidden="1">
       <c r="A767">
         <v>834</v>
       </c>
@@ -34463,7 +34473,7 @@
       </c>
       <c r="W767" s="3"/>
     </row>
-    <row r="768" spans="1:23" ht="15">
+    <row r="768" spans="1:23" ht="15" hidden="1">
       <c r="A768">
         <v>73</v>
       </c>
@@ -34504,7 +34514,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="769" spans="1:23" ht="15">
+    <row r="769" spans="1:23" ht="15" hidden="1">
       <c r="A769">
         <v>74</v>
       </c>
@@ -34545,7 +34555,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="770" spans="1:23" ht="15">
+    <row r="770" spans="1:23" ht="15" hidden="1">
       <c r="A770">
         <v>75</v>
       </c>
@@ -34580,7 +34590,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="771" spans="1:23" ht="15">
+    <row r="771" spans="1:23" ht="15" hidden="1">
       <c r="A771">
         <v>76</v>
       </c>
@@ -34618,7 +34628,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="772" spans="1:23" ht="15">
+    <row r="772" spans="1:23" ht="15" hidden="1">
       <c r="A772">
         <v>77</v>
       </c>
@@ -34659,7 +34669,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="773" spans="1:23" ht="15">
+    <row r="773" spans="1:23" ht="15" hidden="1">
       <c r="A773">
         <v>78</v>
       </c>
@@ -34694,7 +34704,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="774" spans="1:23" ht="15">
+    <row r="774" spans="1:23" ht="15" hidden="1">
       <c r="A774">
         <v>79</v>
       </c>
@@ -34735,7 +34745,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="775" spans="1:23" ht="15">
+    <row r="775" spans="1:23" ht="15" hidden="1">
       <c r="A775">
         <v>80</v>
       </c>
@@ -34773,7 +34783,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="776" spans="1:23" ht="15">
+    <row r="776" spans="1:23" ht="15" hidden="1">
       <c r="A776">
         <v>81</v>
       </c>
@@ -34811,7 +34821,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="777" spans="1:23" ht="15">
+    <row r="777" spans="1:23" ht="15" hidden="1">
       <c r="A777">
         <v>82</v>
       </c>
@@ -34849,7 +34859,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="778" spans="1:23" ht="15">
+    <row r="778" spans="1:23" ht="15" hidden="1">
       <c r="A778">
         <v>175</v>
       </c>
@@ -34889,7 +34899,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="779" spans="1:23" ht="15">
+    <row r="779" spans="1:23" ht="15" hidden="1">
       <c r="A779">
         <v>176</v>
       </c>
@@ -34929,7 +34939,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="780" spans="1:23" ht="15">
+    <row r="780" spans="1:23" ht="15" hidden="1">
       <c r="A780">
         <v>177</v>
       </c>
@@ -34972,7 +34982,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="781" spans="1:23" ht="15">
+    <row r="781" spans="1:23" ht="15" hidden="1">
       <c r="A781">
         <v>178</v>
       </c>
@@ -35015,7 +35025,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="782" spans="1:23" ht="15">
+    <row r="782" spans="1:23" ht="15" hidden="1">
       <c r="A782">
         <v>179</v>
       </c>
@@ -35058,7 +35068,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="783" spans="1:23" ht="15">
+    <row r="783" spans="1:23" ht="15" hidden="1">
       <c r="A783">
         <v>180</v>
       </c>
@@ -35097,7 +35107,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="784" spans="1:23" ht="15">
+    <row r="784" spans="1:23" ht="15" hidden="1">
       <c r="A784">
         <v>182</v>
       </c>
@@ -35136,7 +35146,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="785" spans="1:23" ht="15">
+    <row r="785" spans="1:23" ht="15" hidden="1">
       <c r="A785">
         <v>183</v>
       </c>
@@ -35179,7 +35189,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="786" spans="1:23" ht="15">
+    <row r="786" spans="1:23" ht="15" hidden="1">
       <c r="A786">
         <v>184</v>
       </c>
@@ -35216,7 +35226,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="787" spans="1:23" ht="15">
+    <row r="787" spans="1:23" ht="15" hidden="1">
       <c r="A787">
         <v>185</v>
       </c>
@@ -35259,7 +35269,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="788" spans="1:23" ht="15">
+    <row r="788" spans="1:23" ht="15" hidden="1">
       <c r="A788">
         <v>186</v>
       </c>
@@ -35302,7 +35312,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="789" spans="1:23" ht="15">
+    <row r="789" spans="1:23" ht="15" hidden="1">
       <c r="A789">
         <v>187</v>
       </c>
@@ -35339,7 +35349,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="790" spans="1:23" ht="15">
+    <row r="790" spans="1:23" ht="15" hidden="1">
       <c r="A790">
         <v>188</v>
       </c>
@@ -35382,7 +35392,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="791" spans="1:23" ht="15">
+    <row r="791" spans="1:23" ht="15" hidden="1">
       <c r="A791">
         <v>189</v>
       </c>
@@ -35425,7 +35435,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="792" spans="1:23" ht="15">
+    <row r="792" spans="1:23" ht="15" hidden="1">
       <c r="A792">
         <v>190</v>
       </c>
@@ -35462,7 +35472,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="793" spans="1:23" ht="15">
+    <row r="793" spans="1:23" ht="15" hidden="1">
       <c r="A793">
         <v>191</v>
       </c>
@@ -35505,7 +35515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="794" spans="1:23" ht="15">
+    <row r="794" spans="1:23" ht="15" hidden="1">
       <c r="A794">
         <v>192</v>
       </c>
@@ -35542,7 +35552,7 @@
       </c>
       <c r="W794" s="3"/>
     </row>
-    <row r="795" spans="1:23" ht="15">
+    <row r="795" spans="1:23" ht="15" hidden="1">
       <c r="A795">
         <v>221</v>
       </c>
@@ -35583,7 +35593,7 @@
       </c>
       <c r="W795" s="3"/>
     </row>
-    <row r="796" spans="1:23" ht="15">
+    <row r="796" spans="1:23" ht="15" hidden="1">
       <c r="A796">
         <v>325</v>
       </c>
@@ -35620,7 +35630,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="797" spans="1:23" ht="15">
+    <row r="797" spans="1:23" ht="15" hidden="1">
       <c r="A797">
         <v>345</v>
       </c>
@@ -35663,7 +35673,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="798" spans="1:23" ht="15">
+    <row r="798" spans="1:23" ht="15" hidden="1">
       <c r="A798">
         <v>346</v>
       </c>
@@ -35706,7 +35716,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="799" spans="1:23" ht="15">
+    <row r="799" spans="1:23" ht="15" hidden="1">
       <c r="A799">
         <v>352</v>
       </c>
@@ -35749,7 +35759,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="800" spans="1:23" ht="15">
+    <row r="800" spans="1:23" ht="15" hidden="1">
       <c r="A800">
         <v>413</v>
       </c>
@@ -35788,7 +35798,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="801" spans="1:23" ht="15">
+    <row r="801" spans="1:23" ht="15" hidden="1">
       <c r="A801">
         <v>414</v>
       </c>
@@ -35831,7 +35841,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="802" spans="1:23" ht="15">
+    <row r="802" spans="1:23" ht="15" hidden="1">
       <c r="A802">
         <v>415</v>
       </c>
@@ -35870,7 +35880,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="803" spans="1:23" ht="15">
+    <row r="803" spans="1:23" ht="15" hidden="1">
       <c r="A803">
         <v>421</v>
       </c>
@@ -35907,7 +35917,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="804" spans="1:23" ht="15">
+    <row r="804" spans="1:23" ht="15" hidden="1">
       <c r="A804">
         <v>422</v>
       </c>
@@ -35950,7 +35960,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="805" spans="1:23" ht="15">
+    <row r="805" spans="1:23" ht="15" hidden="1">
       <c r="A805">
         <v>423</v>
       </c>
@@ -35993,7 +36003,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="806" spans="1:23" ht="15">
+    <row r="806" spans="1:23" ht="15" hidden="1">
       <c r="A806">
         <v>424</v>
       </c>
@@ -36036,7 +36046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="807" spans="1:23" ht="15">
+    <row r="807" spans="1:23" ht="15" hidden="1">
       <c r="A807">
         <v>425</v>
       </c>
@@ -36077,7 +36087,7 @@
       </c>
       <c r="W807" s="3"/>
     </row>
-    <row r="808" spans="1:23" ht="15">
+    <row r="808" spans="1:23" ht="15" hidden="1">
       <c r="A808">
         <v>426</v>
       </c>
@@ -36120,7 +36130,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="809" spans="1:23" ht="15">
+    <row r="809" spans="1:23" ht="15" hidden="1">
       <c r="A809">
         <v>427</v>
       </c>
@@ -36163,7 +36173,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="810" spans="1:23" ht="15">
+    <row r="810" spans="1:23" ht="15" hidden="1">
       <c r="A810">
         <v>428</v>
       </c>
@@ -36206,7 +36216,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="811" spans="1:23" ht="15">
+    <row r="811" spans="1:23" ht="15" hidden="1">
       <c r="A811">
         <v>429</v>
       </c>
@@ -36243,7 +36253,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="812" spans="1:23" ht="15">
+    <row r="812" spans="1:23" ht="15" hidden="1">
       <c r="A812">
         <v>430</v>
       </c>
@@ -36282,7 +36292,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="813" spans="1:23" ht="15">
+    <row r="813" spans="1:23" ht="15" hidden="1">
       <c r="A813">
         <v>431</v>
       </c>
@@ -36321,7 +36331,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="814" spans="1:23" ht="15">
+    <row r="814" spans="1:23" ht="15" hidden="1">
       <c r="A814">
         <v>577</v>
       </c>
@@ -36358,7 +36368,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="815" spans="1:23" ht="15">
+    <row r="815" spans="1:23" ht="15" hidden="1">
       <c r="A815">
         <v>578</v>
       </c>
@@ -36397,7 +36407,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="816" spans="1:23" ht="15">
+    <row r="816" spans="1:23" ht="15" hidden="1">
       <c r="A816">
         <v>593</v>
       </c>
@@ -36434,7 +36444,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="817" spans="1:23" ht="15">
+    <row r="817" spans="1:23" ht="15" hidden="1">
       <c r="A817">
         <v>594</v>
       </c>
@@ -36477,7 +36487,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="818" spans="1:23" ht="15">
+    <row r="818" spans="1:23" ht="15" hidden="1">
       <c r="A818">
         <v>595</v>
       </c>
@@ -36520,7 +36530,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="819" spans="1:23" ht="15">
+    <row r="819" spans="1:23" ht="15" hidden="1">
       <c r="A819">
         <v>596</v>
       </c>
@@ -36563,7 +36573,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="820" spans="1:23" ht="15">
+    <row r="820" spans="1:23" ht="15" hidden="1">
       <c r="A820">
         <v>597</v>
       </c>
@@ -36606,7 +36616,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="821" spans="1:23" ht="15">
+    <row r="821" spans="1:23" ht="15" hidden="1">
       <c r="A821">
         <v>598</v>
       </c>
@@ -36649,7 +36659,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="822" spans="1:23" ht="15">
+    <row r="822" spans="1:23" ht="15" hidden="1">
       <c r="A822">
         <v>599</v>
       </c>
@@ -36692,7 +36702,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="823" spans="1:23" ht="15">
+    <row r="823" spans="1:23" ht="15" hidden="1">
       <c r="A823">
         <v>629</v>
       </c>
@@ -36730,7 +36740,7 @@
       </c>
       <c r="W823" s="3"/>
     </row>
-    <row r="824" spans="1:23" ht="15">
+    <row r="824" spans="1:23" ht="15" hidden="1">
       <c r="A824">
         <v>630</v>
       </c>
@@ -36771,7 +36781,7 @@
       </c>
       <c r="W824" s="3"/>
     </row>
-    <row r="825" spans="1:23" ht="15">
+    <row r="825" spans="1:23" ht="15" hidden="1">
       <c r="A825">
         <v>631</v>
       </c>
@@ -36809,7 +36819,7 @@
       </c>
       <c r="W825" s="3"/>
     </row>
-    <row r="826" spans="1:23" ht="15">
+    <row r="826" spans="1:23" ht="15" hidden="1">
       <c r="A826">
         <v>641</v>
       </c>
@@ -36850,7 +36860,7 @@
       </c>
       <c r="W826" s="3"/>
     </row>
-    <row r="827" spans="1:23" ht="15">
+    <row r="827" spans="1:23" ht="15" hidden="1">
       <c r="A827">
         <v>642</v>
       </c>
@@ -36891,7 +36901,7 @@
       </c>
       <c r="W827" s="3"/>
     </row>
-    <row r="828" spans="1:23" ht="15">
+    <row r="828" spans="1:23" ht="15" hidden="1">
       <c r="A828">
         <v>643</v>
       </c>
@@ -36932,7 +36942,7 @@
       </c>
       <c r="W828" s="3"/>
     </row>
-    <row r="829" spans="1:23" ht="15">
+    <row r="829" spans="1:23" ht="15" hidden="1">
       <c r="A829">
         <v>644</v>
       </c>
@@ -36969,7 +36979,7 @@
       </c>
       <c r="W829" s="3"/>
     </row>
-    <row r="830" spans="1:23" ht="15">
+    <row r="830" spans="1:23" ht="15" hidden="1">
       <c r="A830">
         <v>662</v>
       </c>
@@ -37010,7 +37020,7 @@
       </c>
       <c r="W830" s="3"/>
     </row>
-    <row r="831" spans="1:23" ht="15">
+    <row r="831" spans="1:23" ht="15" hidden="1">
       <c r="A831">
         <v>746</v>
       </c>
@@ -37060,7 +37070,7 @@
       </c>
       <c r="W831" s="3"/>
     </row>
-    <row r="832" spans="1:23" ht="15">
+    <row r="832" spans="1:23" ht="15" hidden="1">
       <c r="A832">
         <v>747</v>
       </c>
@@ -37101,7 +37111,7 @@
       </c>
       <c r="W832" s="3"/>
     </row>
-    <row r="833" spans="1:23" ht="15">
+    <row r="833" spans="1:23" ht="15" hidden="1">
       <c r="A833">
         <v>748</v>
       </c>
@@ -37142,7 +37152,7 @@
       </c>
       <c r="W833" s="3"/>
     </row>
-    <row r="834" spans="1:23" ht="15">
+    <row r="834" spans="1:23" ht="15" hidden="1">
       <c r="A834">
         <v>749</v>
       </c>
@@ -37182,7 +37192,7 @@
       </c>
       <c r="W834" s="3"/>
     </row>
-    <row r="835" spans="1:23" ht="15">
+    <row r="835" spans="1:23" ht="15" hidden="1">
       <c r="A835">
         <v>781</v>
       </c>
@@ -37223,7 +37233,7 @@
       </c>
       <c r="W835" s="3"/>
     </row>
-    <row r="836" spans="1:23" ht="15">
+    <row r="836" spans="1:23" ht="15" hidden="1">
       <c r="A836">
         <v>782</v>
       </c>
@@ -37264,7 +37274,7 @@
       </c>
       <c r="W836" s="3"/>
     </row>
-    <row r="837" spans="1:23" ht="15">
+    <row r="837" spans="1:23" ht="15" hidden="1">
       <c r="A837">
         <v>783</v>
       </c>
@@ -37305,7 +37315,7 @@
       </c>
       <c r="W837" s="3"/>
     </row>
-    <row r="838" spans="1:23" ht="15">
+    <row r="838" spans="1:23" ht="15" hidden="1">
       <c r="A838">
         <v>784</v>
       </c>
@@ -37346,7 +37356,7 @@
       </c>
       <c r="W838" s="3"/>
     </row>
-    <row r="839" spans="1:23" ht="15">
+    <row r="839" spans="1:23" ht="15" hidden="1">
       <c r="A839">
         <v>785</v>
       </c>
@@ -37387,7 +37397,7 @@
       </c>
       <c r="W839" s="3"/>
     </row>
-    <row r="840" spans="1:23" ht="15">
+    <row r="840" spans="1:23" ht="15" hidden="1">
       <c r="A840">
         <v>786</v>
       </c>
@@ -37428,7 +37438,7 @@
       </c>
       <c r="W840" s="3"/>
     </row>
-    <row r="841" spans="1:23" ht="15">
+    <row r="841" spans="1:23" ht="15" hidden="1">
       <c r="A841">
         <v>807</v>
       </c>
@@ -37465,7 +37475,7 @@
       </c>
       <c r="W841" s="3"/>
     </row>
-    <row r="842" spans="1:23" ht="15">
+    <row r="842" spans="1:23" ht="15" hidden="1">
       <c r="A842">
         <v>816</v>
       </c>
@@ -37502,7 +37512,7 @@
       </c>
       <c r="W842" s="3"/>
     </row>
-    <row r="843" spans="1:23" ht="15">
+    <row r="843" spans="1:23" ht="15" hidden="1">
       <c r="A843">
         <v>817</v>
       </c>
@@ -37543,7 +37553,7 @@
       </c>
       <c r="W843" s="3"/>
     </row>
-    <row r="844" spans="1:23" ht="15">
+    <row r="844" spans="1:23" ht="15" hidden="1">
       <c r="A844">
         <v>838</v>
       </c>
@@ -37584,7 +37594,7 @@
       </c>
       <c r="W844" s="3"/>
     </row>
-    <row r="845" spans="1:23" ht="15">
+    <row r="845" spans="1:23" ht="15" hidden="1">
       <c r="A845">
         <v>839</v>
       </c>
@@ -37625,7 +37635,7 @@
       </c>
       <c r="W845" s="3"/>
     </row>
-    <row r="846" spans="1:23" ht="15">
+    <row r="846" spans="1:23" ht="15" hidden="1">
       <c r="A846">
         <v>840</v>
       </c>
@@ -37666,7 +37676,7 @@
       </c>
       <c r="W846" s="3"/>
     </row>
-    <row r="847" spans="1:23" ht="15">
+    <row r="847" spans="1:23" ht="15" hidden="1">
       <c r="A847">
         <v>841</v>
       </c>
@@ -37707,7 +37717,7 @@
       </c>
       <c r="W847" s="3"/>
     </row>
-    <row r="848" spans="1:23" ht="15">
+    <row r="848" spans="1:23" ht="15" hidden="1">
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
       <c r="D848" s="3"/>
@@ -37720,6 +37730,61 @@
       <c r="U848" s="3"/>
       <c r="V848" s="3"/>
       <c r="W848" s="3"/>
+    </row>
+    <row r="849" spans="1:23" hidden="1">
+      <c r="A849" s="8">
+        <v>855</v>
+      </c>
+      <c r="B849" s="4">
+        <v>46296.636863425898</v>
+      </c>
+      <c r="C849" s="4">
+        <v>46296.637638888897</v>
+      </c>
+      <c r="D849" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E849" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F849" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G849" s="1">
+        <v>46277</v>
+      </c>
+      <c r="H849" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I849" s="8"/>
+      <c r="J849" s="8"/>
+      <c r="K849" s="8"/>
+      <c r="L849" s="3"/>
+      <c r="M849" s="3"/>
+      <c r="N849" s="8"/>
+      <c r="O849" s="8">
+        <v>1</v>
+      </c>
+      <c r="P849" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q849" s="8">
+        <v>0</v>
+      </c>
+      <c r="R849" s="8">
+        <v>0</v>
+      </c>
+      <c r="S849" s="8"/>
+      <c r="T849" s="8">
+        <v>1</v>
+      </c>
+      <c r="U849" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="V849" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="W849" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="713" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC643704-EE88-485B-AEF0-332BBE42D76E}"/>
+  <xr:revisionPtr revIDLastSave="716" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B182243-AC77-473D-9A2C-94281F5FF4BB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5970" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6063" uniqueCount="1249">
   <si>
     <t>Id</t>
   </si>
@@ -3729,6 +3729,60 @@
   </si>
   <si>
     <t xml:space="preserve">Realtime receiver maintenance and meeting new property owners in Sturgeon Bay </t>
+  </si>
+  <si>
+    <t>Conn T, Renton J, Chamberland VF, Dellaert Z, Reusch TBH, Werner B, Baums IB (2026) Mosaic Accumulation of Somatic Genetic Variation and Estimates of Age in the Long-Lived Reef-Building Coral Acropora palmata. Molecular Ecology 35, e70580. https://doi.org/10.1111/mec.70580</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/doi/10.1111/mec.70580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEGO student group </t>
+  </si>
+  <si>
+    <t>LEGO student group meeting who are putting together coral ideas, short presentation and longer conversation</t>
+  </si>
+  <si>
+    <t>conch cruise</t>
+  </si>
+  <si>
+    <t>https://news.mongabay.com/2026/08/mobile-queen-conch-hatcheries-strive-to-help-the-species-engage-caribbean-communities/</t>
+  </si>
+  <si>
+    <t>interview</t>
+  </si>
+  <si>
+    <t>https://www.miamiherald.com/news/local/environment/climate-change/article316672970.html</t>
+  </si>
+  <si>
+    <t>First ever conservation L&amp;L @ CACS</t>
+  </si>
+  <si>
+    <t>screw reel project w NWU</t>
+  </si>
+  <si>
+    <t>purdue students</t>
+  </si>
+  <si>
+    <t>Presentation to department of environment leadership in cayman island</t>
+  </si>
+  <si>
+    <t>GaLa</t>
+  </si>
+  <si>
+    <t>GaLa - think this is appropriate place to put this</t>
+  </si>
+  <si>
+    <t>https://insideclimatenews.org/news/11102026/bahamas-development-seagrass-conch-legal-battle/</t>
+  </si>
+  <si>
+    <t>For Hope College's Invertebrate Zoology class</t>
+  </si>
+  <si>
+    <t>MSI Science Works</t>
+  </si>
+  <si>
+    <t>I had direct conversation with at least 103 people but the attendence was 5000 people</t>
   </si>
 </sst>
 </file>
@@ -3863,8 +3917,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W849" totalsRowShown="0">
-  <autoFilter ref="A1:W849" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W862" totalsRowShown="0">
+  <autoFilter ref="A1:W862" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="myoungquist@sheddaquarium.org"/>
@@ -4040,7 +4094,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="855" latestEventMarker="893">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="868" latestEventMarker="906">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4367,7 +4421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W849"/>
+  <dimension ref="A1:W862"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -37732,7 +37786,7 @@
       <c r="W848" s="3"/>
     </row>
     <row r="849" spans="1:23" hidden="1">
-      <c r="A849" s="8">
+      <c r="A849">
         <v>855</v>
       </c>
       <c r="B849" s="4">
@@ -37756,26 +37810,21 @@
       <c r="H849" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I849" s="8"/>
-      <c r="J849" s="8"/>
-      <c r="K849" s="8"/>
       <c r="L849" s="3"/>
       <c r="M849" s="3"/>
-      <c r="N849" s="8"/>
-      <c r="O849" s="8">
+      <c r="O849">
         <v>1</v>
       </c>
-      <c r="P849" s="8">
+      <c r="P849">
         <v>0</v>
       </c>
-      <c r="Q849" s="8">
+      <c r="Q849">
         <v>0</v>
       </c>
-      <c r="R849" s="8">
+      <c r="R849">
         <v>0</v>
       </c>
-      <c r="S849" s="8"/>
-      <c r="T849" s="8">
+      <c r="T849">
         <v>1</v>
       </c>
       <c r="U849" s="3" t="s">
@@ -37785,6 +37834,647 @@
         <v>501</v>
       </c>
       <c r="W849" s="3"/>
+    </row>
+    <row r="850" spans="1:23">
+      <c r="A850" s="8">
+        <v>856</v>
+      </c>
+      <c r="B850" s="4">
+        <v>46300.638784722199</v>
+      </c>
+      <c r="C850" s="4">
+        <v>46300.639247685198</v>
+      </c>
+      <c r="D850" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E850" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F850" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G850" s="1">
+        <v>46297</v>
+      </c>
+      <c r="H850" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I850" s="8"/>
+      <c r="J850" s="8"/>
+      <c r="K850" s="8"/>
+      <c r="L850" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M850" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N850" s="8"/>
+      <c r="O850" s="8"/>
+      <c r="P850" s="8"/>
+      <c r="Q850" s="8"/>
+      <c r="R850" s="8"/>
+      <c r="S850" s="8"/>
+      <c r="T850" s="8"/>
+      <c r="U850" s="3"/>
+      <c r="V850" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="W850" s="3"/>
+    </row>
+    <row r="851" spans="1:23">
+      <c r="A851" s="8">
+        <v>857</v>
+      </c>
+      <c r="B851" s="4">
+        <v>46308.4991435185</v>
+      </c>
+      <c r="C851" s="4">
+        <v>46308.546909722201</v>
+      </c>
+      <c r="D851" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="E851" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="F851" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G851" s="1">
+        <v>46308</v>
+      </c>
+      <c r="H851" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I851" s="8"/>
+      <c r="J851" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="K851" s="8"/>
+      <c r="L851" s="3"/>
+      <c r="M851" s="3"/>
+      <c r="N851" s="8"/>
+      <c r="O851" s="8"/>
+      <c r="P851" s="8"/>
+      <c r="Q851" s="8"/>
+      <c r="R851" s="8"/>
+      <c r="S851" s="8"/>
+      <c r="T851" s="8">
+        <v>11</v>
+      </c>
+      <c r="U851" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="V851" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="W851" s="3"/>
+    </row>
+    <row r="852" spans="1:23">
+      <c r="A852" s="8">
+        <v>858</v>
+      </c>
+      <c r="B852" s="4">
+        <v>46314.4581481481</v>
+      </c>
+      <c r="C852" s="4">
+        <v>46314.460810185199</v>
+      </c>
+      <c r="D852" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E852" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F852" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G852" s="1">
+        <v>46214</v>
+      </c>
+      <c r="H852" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I852" s="8"/>
+      <c r="J852" s="8"/>
+      <c r="K852" s="8"/>
+      <c r="L852" s="3"/>
+      <c r="M852" s="3"/>
+      <c r="N852" s="8"/>
+      <c r="O852" s="8">
+        <v>1</v>
+      </c>
+      <c r="P852" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q852" s="8">
+        <v>3</v>
+      </c>
+      <c r="R852" s="8">
+        <v>0</v>
+      </c>
+      <c r="S852" s="8"/>
+      <c r="T852" s="8">
+        <v>7</v>
+      </c>
+      <c r="U852" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="V852" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W852" s="3"/>
+    </row>
+    <row r="853" spans="1:23">
+      <c r="A853" s="8">
+        <v>859</v>
+      </c>
+      <c r="B853" s="4">
+        <v>46314.460856481499</v>
+      </c>
+      <c r="C853" s="4">
+        <v>46314.461875000001</v>
+      </c>
+      <c r="D853" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E853" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F853" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G853" s="1">
+        <v>46252</v>
+      </c>
+      <c r="H853" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I853" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J853" s="8"/>
+      <c r="K853" s="8"/>
+      <c r="L853" s="3"/>
+      <c r="M853" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N853" s="8"/>
+      <c r="O853" s="8"/>
+      <c r="P853" s="8"/>
+      <c r="Q853" s="8"/>
+      <c r="R853" s="8"/>
+      <c r="S853" s="8"/>
+      <c r="T853" s="8"/>
+      <c r="U853" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="V853" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W853" s="3"/>
+    </row>
+    <row r="854" spans="1:23">
+      <c r="A854" s="8">
+        <v>860</v>
+      </c>
+      <c r="B854" s="4">
+        <v>46314.461898148104</v>
+      </c>
+      <c r="C854" s="4">
+        <v>46314.463136574101</v>
+      </c>
+      <c r="D854" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E854" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F854" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G854" s="1">
+        <v>46225</v>
+      </c>
+      <c r="H854" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I854" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J854" s="8"/>
+      <c r="K854" s="8"/>
+      <c r="L854" s="3"/>
+      <c r="M854" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N854" s="8"/>
+      <c r="O854" s="8"/>
+      <c r="P854" s="8"/>
+      <c r="Q854" s="8"/>
+      <c r="R854" s="8"/>
+      <c r="S854" s="8"/>
+      <c r="T854" s="8"/>
+      <c r="U854" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="V854" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W854" s="3"/>
+    </row>
+    <row r="855" spans="1:23">
+      <c r="A855" s="8">
+        <v>861</v>
+      </c>
+      <c r="B855" s="4">
+        <v>46314.463159722203</v>
+      </c>
+      <c r="C855" s="4">
+        <v>46314.463599536997</v>
+      </c>
+      <c r="D855" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E855" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F855" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G855" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H855" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I855" s="8"/>
+      <c r="J855" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K855" s="8"/>
+      <c r="L855" s="3"/>
+      <c r="M855" s="3"/>
+      <c r="N855" s="8"/>
+      <c r="O855" s="8"/>
+      <c r="P855" s="8"/>
+      <c r="Q855" s="8"/>
+      <c r="R855" s="8"/>
+      <c r="S855" s="8"/>
+      <c r="T855" s="8">
+        <v>15</v>
+      </c>
+      <c r="U855" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="V855" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W855" s="3"/>
+    </row>
+    <row r="856" spans="1:23">
+      <c r="A856" s="8">
+        <v>862</v>
+      </c>
+      <c r="B856" s="4">
+        <v>46314.463622685202</v>
+      </c>
+      <c r="C856" s="4">
+        <v>46314.464351851901</v>
+      </c>
+      <c r="D856" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E856" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F856" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G856" s="1">
+        <v>46234</v>
+      </c>
+      <c r="H856" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I856" s="8"/>
+      <c r="J856" s="8"/>
+      <c r="K856" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="L856" s="3"/>
+      <c r="M856" s="3"/>
+      <c r="N856" s="8"/>
+      <c r="O856" s="8"/>
+      <c r="P856" s="8"/>
+      <c r="Q856" s="8"/>
+      <c r="R856" s="8"/>
+      <c r="S856" s="8"/>
+      <c r="T856" s="8">
+        <v>4</v>
+      </c>
+      <c r="U856" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="V856" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W856" s="3"/>
+    </row>
+    <row r="857" spans="1:23">
+      <c r="A857" s="8">
+        <v>863</v>
+      </c>
+      <c r="B857" s="4">
+        <v>46314.464375000003</v>
+      </c>
+      <c r="C857" s="4">
+        <v>46314.465185185203</v>
+      </c>
+      <c r="D857" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E857" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F857" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G857" s="1">
+        <v>46245</v>
+      </c>
+      <c r="H857" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I857" s="8"/>
+      <c r="J857" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="K857" s="8"/>
+      <c r="L857" s="3"/>
+      <c r="M857" s="3"/>
+      <c r="N857" s="8"/>
+      <c r="O857" s="8"/>
+      <c r="P857" s="8"/>
+      <c r="Q857" s="8"/>
+      <c r="R857" s="8"/>
+      <c r="S857" s="8"/>
+      <c r="T857" s="8">
+        <v>14</v>
+      </c>
+      <c r="U857" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="V857" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W857" s="3"/>
+    </row>
+    <row r="858" spans="1:23">
+      <c r="A858" s="8">
+        <v>864</v>
+      </c>
+      <c r="B858" s="4">
+        <v>46314.465208333299</v>
+      </c>
+      <c r="C858" s="4">
+        <v>46314.467337962997</v>
+      </c>
+      <c r="D858" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E858" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F858" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G858" s="1">
+        <v>46290</v>
+      </c>
+      <c r="H858" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I858" s="8"/>
+      <c r="J858" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K858" s="8"/>
+      <c r="L858" s="3"/>
+      <c r="M858" s="3"/>
+      <c r="N858" s="8"/>
+      <c r="O858" s="8"/>
+      <c r="P858" s="8"/>
+      <c r="Q858" s="8"/>
+      <c r="R858" s="8"/>
+      <c r="S858" s="8"/>
+      <c r="T858" s="8">
+        <v>5</v>
+      </c>
+      <c r="U858" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="V858" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W858" s="3"/>
+    </row>
+    <row r="859" spans="1:23">
+      <c r="A859" s="8">
+        <v>865</v>
+      </c>
+      <c r="B859" s="4">
+        <v>46314.467361111099</v>
+      </c>
+      <c r="C859" s="4">
+        <v>46314.468171296299</v>
+      </c>
+      <c r="D859" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E859" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F859" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G859" s="1">
+        <v>46291</v>
+      </c>
+      <c r="H859" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I859" s="8"/>
+      <c r="J859" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K859" s="8"/>
+      <c r="L859" s="3"/>
+      <c r="M859" s="3"/>
+      <c r="N859" s="8"/>
+      <c r="O859" s="8"/>
+      <c r="P859" s="8"/>
+      <c r="Q859" s="8"/>
+      <c r="R859" s="8"/>
+      <c r="S859" s="8"/>
+      <c r="T859" s="8">
+        <v>650</v>
+      </c>
+      <c r="U859" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="V859" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W859" s="3"/>
+    </row>
+    <row r="860" spans="1:23">
+      <c r="A860" s="8">
+        <v>866</v>
+      </c>
+      <c r="B860" s="4">
+        <v>46314.4683449074</v>
+      </c>
+      <c r="C860" s="4">
+        <v>46314.4692476852</v>
+      </c>
+      <c r="D860" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E860" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F860" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G860" s="1">
+        <v>46306</v>
+      </c>
+      <c r="H860" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I860" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J860" s="8"/>
+      <c r="K860" s="8"/>
+      <c r="L860" s="3"/>
+      <c r="M860" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="N860" s="8"/>
+      <c r="O860" s="8"/>
+      <c r="P860" s="8"/>
+      <c r="Q860" s="8"/>
+      <c r="R860" s="8"/>
+      <c r="S860" s="8"/>
+      <c r="T860" s="8"/>
+      <c r="U860" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="V860" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W860" s="3"/>
+    </row>
+    <row r="861" spans="1:23">
+      <c r="A861" s="8">
+        <v>867</v>
+      </c>
+      <c r="B861" s="4">
+        <v>46314.4692939815</v>
+      </c>
+      <c r="C861" s="4">
+        <v>46314.469710648104</v>
+      </c>
+      <c r="D861" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E861" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F861" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G861" s="1">
+        <v>46315</v>
+      </c>
+      <c r="H861" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I861" s="8"/>
+      <c r="J861" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K861" s="8"/>
+      <c r="L861" s="3"/>
+      <c r="M861" s="3"/>
+      <c r="N861" s="8"/>
+      <c r="O861" s="8"/>
+      <c r="P861" s="8"/>
+      <c r="Q861" s="8"/>
+      <c r="R861" s="8"/>
+      <c r="S861" s="8"/>
+      <c r="T861" s="8">
+        <v>12</v>
+      </c>
+      <c r="U861" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="V861" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W861" s="3"/>
+    </row>
+    <row r="862" spans="1:23">
+      <c r="A862" s="8">
+        <v>868</v>
+      </c>
+      <c r="B862" s="4">
+        <v>46314.470173611102</v>
+      </c>
+      <c r="C862" s="4">
+        <v>46314.471608796302</v>
+      </c>
+      <c r="D862" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E862" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F862" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G862" s="1">
+        <v>46305</v>
+      </c>
+      <c r="H862" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I862" s="8"/>
+      <c r="J862" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="K862" s="8"/>
+      <c r="L862" s="3"/>
+      <c r="M862" s="3"/>
+      <c r="N862" s="8"/>
+      <c r="O862" s="8"/>
+      <c r="P862" s="8"/>
+      <c r="Q862" s="8"/>
+      <c r="R862" s="8"/>
+      <c r="S862" s="8"/>
+      <c r="T862" s="8">
+        <v>103</v>
+      </c>
+      <c r="U862" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="V862" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W862" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
